--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL43"/>
+  <dimension ref="A1:AL51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6591,13 +6591,19 @@
       <c r="D41" t="n">
         <v>7750</v>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>7750</v>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>13-Nov-2025 08:16:51</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>14-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -6658,7 +6664,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6681,15 +6687,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
+      <c r="AA41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
       </c>
-      <c r="AE41" t="inlineStr"/>
+      <c r="AE41" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF41" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -6731,13 +6743,19 @@
       <c r="D42" t="n">
         <v>6750</v>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>6750</v>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>13-Nov-2025 17:32:13</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>14-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -6798,7 +6816,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6821,15 +6839,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+      <c r="AA42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC42" t="n">
         <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
       </c>
-      <c r="AE42" t="inlineStr"/>
+      <c r="AE42" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF42" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -6875,13 +6899,19 @@
       <c r="D43" t="n">
         <v>11250</v>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>11250</v>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>13-Nov-2025 20:24:29</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>14-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -6942,7 +6972,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6965,15 +6995,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
+      <c r="AA43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC43" t="n">
         <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
       </c>
-      <c r="AE43" t="inlineStr"/>
+      <c r="AE43" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr">
@@ -6995,6 +7031,1166 @@
         </is>
       </c>
       <c r="AL43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>16595</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KOLASANI SYAMANTH LAKSHMI VEER</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>9849989564</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8550</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8550</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>14-Nov-2025 20:15:44</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P44" t="n">
+        <v>11000316697401</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1763131313</v>
+      </c>
+      <c r="R44" t="n">
+        <v>108572296490</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI44" t="n">
+        <v>18669</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>262480,264030</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>16036</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DUVVU BHARGAVA SRI SAI</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8850</v>
+      </c>
+      <c r="E45" t="n">
+        <v>8850</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>14-Nov-2025 20:40:21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P45" t="n">
+        <v>11000316700245</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1763132856</v>
+      </c>
+      <c r="R45" t="n">
+        <v>108572419761</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI45" t="n">
+        <v>18964</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>262817,264320</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>16036</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DUVVU BHARGAVA SRI SAI</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E46" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>14-Nov-2025 20:43:12</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P46" t="n">
+        <v>11000316701281</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1763133080</v>
+      </c>
+      <c r="R46" t="n">
+        <v>108572433794</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI46" t="n">
+        <v>18964</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>265970</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>15541</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RASAJNA VOBBILISETTY</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>9849969449</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8850</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 08:00:27</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P47" t="n">
+        <v>11000316726912</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1763173641</v>
+      </c>
+      <c r="R47" t="n">
+        <v>108573859508</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI47" t="n">
+        <v>18766</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>262401,264163</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>16020</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>DUVVU MAHALAKSHMI</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8550</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 10:35:50</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P48" t="n">
+        <v>11000316759740</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1763183095</v>
+      </c>
+      <c r="R48" t="n">
+        <v>108574613225</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI48" t="n">
+        <v>18522</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>262132,263952</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>16795</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MOHAMMAD ALINA SAMDANI</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>8790615241</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 14:02:46</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P49" t="n">
+        <v>11000316792543</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1763195595</v>
+      </c>
+      <c r="R49" t="n">
+        <v>689600444274</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI49" t="n">
+        <v>18523</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>265622</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>17178</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GUNIPE NIHARIKA</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9966262514</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 14:21:46</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P50" t="n">
+        <v>11000316794728</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1763196672</v>
+      </c>
+      <c r="R50" t="n">
+        <v>108575833074</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI50" t="n">
+        <v>19893</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>265185</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>15915</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>KURAKULA JATHIN</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8106938482</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8850</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 19:52:03</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P51" t="n">
+        <v>11000316837646</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1763216495</v>
+      </c>
+      <c r="R51" t="n">
+        <v>108577731862</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI51" t="n">
+        <v>18704</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>262588,264203</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
+  <dimension ref="A1:AL55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7503,13 +7503,19 @@
       <c r="D47" t="n">
         <v>8850</v>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>8850</v>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>15-Nov-2025 08:00:27</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>17-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -7570,7 +7576,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -7593,15 +7599,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
+      <c r="AA47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
       </c>
-      <c r="AE47" t="inlineStr"/>
+      <c r="AE47" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF47" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -7643,13 +7655,19 @@
       <c r="D48" t="n">
         <v>8550</v>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>8550</v>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>15-Nov-2025 10:35:50</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>17-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -7710,7 +7728,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -7733,15 +7751,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
+      <c r="AA48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC48" t="n">
         <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
       </c>
-      <c r="AE48" t="inlineStr"/>
+      <c r="AE48" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF48" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -7783,13 +7807,19 @@
       <c r="D49" t="n">
         <v>8050</v>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>8050</v>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>15-Nov-2025 14:02:46</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>17-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -7850,7 +7880,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -7873,15 +7903,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
+      <c r="AA49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
       </c>
-      <c r="AE49" t="inlineStr"/>
+      <c r="AE49" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF49" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -7927,13 +7963,19 @@
       <c r="D50" t="n">
         <v>7750</v>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>7750</v>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>15-Nov-2025 14:21:46</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>17-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -7994,7 +8036,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -8017,15 +8059,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
+      <c r="AA50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
       </c>
-      <c r="AE50" t="inlineStr"/>
+      <c r="AE50" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF50" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -8067,13 +8115,19 @@
       <c r="D51" t="n">
         <v>8850</v>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>8850</v>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>15-Nov-2025 19:52:03</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>17-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -8134,7 +8188,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -8157,15 +8211,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
+      <c r="AA51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC51" t="n">
         <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
       </c>
-      <c r="AE51" t="inlineStr"/>
+      <c r="AE51" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF51" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -8191,6 +8251,582 @@
         </is>
       </c>
       <c r="AL51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>17069</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GUNTURU VIDYA SRI</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>8885883431</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8850</v>
+      </c>
+      <c r="E52" t="n">
+        <v>8850</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>17-Nov-2025 15:34:07</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>18-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P52" t="n">
+        <v>11000317106839</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1763373817</v>
+      </c>
+      <c r="R52" t="n">
+        <v>253874637302</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI52" t="n">
+        <v>18960</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>262774,264277</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14546</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>KONDALA JOSHNA</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8143411492</v>
+      </c>
+      <c r="D53" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>18-Nov-2025 10:28:43</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P53" t="n">
+        <v>11000317244031</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1763441830</v>
+      </c>
+      <c r="R53" t="n">
+        <v>108591365446</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI53" t="n">
+        <v>19383</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>266397</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>17371</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AKKURADA ARADHYA</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>8500847900</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16700</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>18-Nov-2025 11:39:14</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>sixteen thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P54" t="n">
+        <v>11000317263208</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1763446046</v>
+      </c>
+      <c r="R54" t="n">
+        <v>108591734203</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI54" t="n">
+        <v>20090</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>268489,268490</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>2050,2058</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>15938</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>VEDITHI ARPANA CHANDRA</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>9959307771</v>
+      </c>
+      <c r="D55" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>18-Nov-2025 16:41:50</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P55" t="n">
+        <v>11000317317733</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1763464253</v>
+      </c>
+      <c r="R55" t="n">
+        <v>108593680409</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI55" t="n">
+        <v>18863</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>265936</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL55"/>
+  <dimension ref="A1:AL60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8423,7 +8423,9 @@
       <c r="D53" t="n">
         <v>11350</v>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>11350</v>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>18-Nov-2025 10:28:43</t>
@@ -8490,7 +8492,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -8513,15 +8515,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
+      <c r="AA53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC53" t="n">
         <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
       </c>
-      <c r="AE53" t="inlineStr"/>
+      <c r="AE53" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF53" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -8563,13 +8571,19 @@
       <c r="D54" t="n">
         <v>16700</v>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>16700</v>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>18-Nov-2025 11:39:14</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -8630,7 +8644,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -8653,15 +8667,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
+      <c r="AA54" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC54" t="n">
         <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
       </c>
-      <c r="AE54" t="inlineStr"/>
+      <c r="AE54" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF54" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -8703,13 +8723,19 @@
       <c r="D55" t="n">
         <v>8350</v>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>8350</v>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>18-Nov-2025 16:41:50</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -8770,7 +8796,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -8793,15 +8819,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
+      <c r="AA55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC55" t="n">
         <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
       </c>
-      <c r="AE55" t="inlineStr"/>
+      <c r="AE55" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF55" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -8827,6 +8859,718 @@
         </is>
       </c>
       <c r="AL55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>16507</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>POTNURU YELEENA</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>8374132397</v>
+      </c>
+      <c r="D56" t="n">
+        <v>8250</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 09:11:28</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>eight thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P56" t="n">
+        <v>11000317376987</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1763523653</v>
+      </c>
+      <c r="R56" t="n">
+        <v>704101659740</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI56" t="n">
+        <v>18352</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>262241,263682</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>2037,2040</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>16754</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BARLA VENKATA JOSHYA</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>7993557118</v>
+      </c>
+      <c r="D57" t="n">
+        <v>8250</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 13:15:22</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>eight thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P57" t="n">
+        <v>11000317420497</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1763538218</v>
+      </c>
+      <c r="R57" t="n">
+        <v>532374231246</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI57" t="n">
+        <v>18267</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>262050,263641</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>2037,2040</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>17305</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TUPAKULA DIA CHARLIE</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>9014136332</v>
+      </c>
+      <c r="D58" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 15:31:01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P58" t="n">
+        <v>11000317441689</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1763546306</v>
+      </c>
+      <c r="R58" t="n">
+        <v>108599052932</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI58" t="n">
+        <v>20014</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>263375</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>15855</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GANGADA MOKSHITH</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6305803494</v>
+      </c>
+      <c r="D59" t="n">
+        <v>8550</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 16:38:21</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P59" t="n">
+        <v>11000317451362</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1763550487</v>
+      </c>
+      <c r="R59" t="n">
+        <v>355970292562</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI59" t="n">
+        <v>18628</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>262471,264025</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>17197</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KONADA YASHASWINI</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>9881234227</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 21:01:26</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P60" t="n">
+        <v>11000317484251</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1763566147</v>
+      </c>
+      <c r="R60" t="n">
+        <v>108601056706</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI60" t="n">
+        <v>19911</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>265070</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL60"/>
+  <dimension ref="A1:AL70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8875,13 +8875,19 @@
       <c r="D56" t="n">
         <v>8250</v>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>8250</v>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>19-Nov-2025 09:11:28</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -8942,7 +8948,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -8965,15 +8971,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
+      <c r="AA56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC56" t="n">
         <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
       </c>
-      <c r="AE56" t="inlineStr"/>
+      <c r="AE56" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF56" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -9019,13 +9031,19 @@
       <c r="D57" t="n">
         <v>8250</v>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>8250</v>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>19-Nov-2025 13:15:22</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -9086,7 +9104,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -9109,15 +9127,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
+      <c r="AA57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC57" t="n">
         <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
       </c>
-      <c r="AE57" t="inlineStr"/>
+      <c r="AE57" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF57" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -9163,13 +9187,19 @@
       <c r="D58" t="n">
         <v>6750</v>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>6750</v>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>19-Nov-2025 15:31:01</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -9230,7 +9260,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -9253,15 +9283,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
+      <c r="AA58" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC58" t="n">
         <v>0</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
       </c>
-      <c r="AE58" t="inlineStr"/>
+      <c r="AE58" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF58" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -9303,13 +9339,19 @@
       <c r="D59" t="n">
         <v>8550</v>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>8550</v>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>19-Nov-2025 16:38:21</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -9370,7 +9412,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -9393,15 +9435,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="inlineStr"/>
+      <c r="AA59" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC59" t="n">
         <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
       </c>
-      <c r="AE59" t="inlineStr"/>
+      <c r="AE59" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF59" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -9447,13 +9495,19 @@
       <c r="D60" t="n">
         <v>6750</v>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>6750</v>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>19-Nov-2025 21:01:26</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -9514,7 +9568,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -9537,15 +9591,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
+      <c r="AA60" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC60" t="n">
         <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
       </c>
-      <c r="AE60" t="inlineStr"/>
+      <c r="AE60" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF60" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -9571,6 +9631,1414 @@
         </is>
       </c>
       <c r="AL60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>17290</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PATNALA YOSHINI</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>9985244439</v>
+      </c>
+      <c r="D61" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 08:47:32</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P61" t="n">
+        <v>11000317511572</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1763608577</v>
+      </c>
+      <c r="R61" t="n">
+        <v>472308202173</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI61" t="n">
+        <v>20000</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>265468</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>17289</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PATNALA DHARVIK</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>9985244439</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 08:49:38</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P62" t="n">
+        <v>11000317511641</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1763608739</v>
+      </c>
+      <c r="R62" t="n">
+        <v>962022877628</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI62" t="n">
+        <v>19999</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>265256</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>15945</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LEKSHITA LAASYA POTNURU</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>8801573949</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8850</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 11:46:10</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P63" t="n">
+        <v>11000317537894</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1763619330</v>
+      </c>
+      <c r="R63" t="n">
+        <v>881654640858</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI63" t="n">
+        <v>18833</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>262775,264278</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>17277</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EDUBILLI MAHASWIN</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>9618641662</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 13:47:57</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P64" t="n">
+        <v>11000317559740</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1763626601</v>
+      </c>
+      <c r="R64" t="n">
+        <v>108604250147</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI64" t="n">
+        <v>19988</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>263475</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>14888</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SHAIK GOUSIA NASRIN</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7207749584</v>
+      </c>
+      <c r="D65" t="n">
+        <v>11250</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 14:40:36</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>eleven thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P65" t="n">
+        <v>11000317567806</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1763629785</v>
+      </c>
+      <c r="R65" t="n">
+        <v>108604632984</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI65" t="n">
+        <v>19200</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>263115,264618</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>2037,2044</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>16983</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NITHYA EMERALD THOTA</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>8919560551</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8550</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 17:01:38</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P66" t="n">
+        <v>11000317588170</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1763636615</v>
+      </c>
+      <c r="R66" t="n">
+        <v>108605493967</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI66" t="n">
+        <v>18526</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>262171,263959</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>16580</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CHANUKYA APPALACHARYULU MUNUBARTHI</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>9908906244</v>
+      </c>
+      <c r="D67" t="n">
+        <v>8850</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 17:12:41</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P67" t="n">
+        <v>11000317589448</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1763638742</v>
+      </c>
+      <c r="R67" t="n">
+        <v>108605556686</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI67" t="n">
+        <v>18889</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>262808,264311</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>15795</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>YAAKSHITH CHETTI</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>9160018096</v>
+      </c>
+      <c r="D68" t="n">
+        <v>500</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 20:01:56</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>five hundred</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P68" t="n">
+        <v>11000317606868</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1763649005</v>
+      </c>
+      <c r="R68" t="n">
+        <v>185561913245</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI68" t="n">
+        <v>19105</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>262986</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>16617</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>THANU SREE BHOOMIREDDY</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>9573771080</v>
+      </c>
+      <c r="D69" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 20:59:36</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P69" t="n">
+        <v>11000317615031</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1763652458</v>
+      </c>
+      <c r="R69" t="n">
+        <v>108606865688</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI69" t="n">
+        <v>18610</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>265580</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>17149</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MELINDHA BADE</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9989075944</v>
+      </c>
+      <c r="D70" t="n">
+        <v>9150</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 21:49:09</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>nine thousand one hundred fifty</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P70" t="n">
+        <v>11000317619325</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1763655441</v>
+      </c>
+      <c r="R70" t="n">
+        <v>108607082636</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI70" t="n">
+        <v>19852</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>262887,264390</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>2037,2043</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL70"/>
+  <dimension ref="A1:AL77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9482,25 +9482,25 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>17197</v>
+        <v>15595</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KONADA YASHASWINI</t>
+          <t>BHODEEP PEETALA</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9881234227</v>
+        <v>9985727557</v>
       </c>
       <c r="D60" t="n">
-        <v>6750</v>
+        <v>9150</v>
       </c>
       <c r="E60" t="n">
-        <v>6750</v>
+        <v>9150</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>19-Nov-2025 21:01:26</t>
+          <t>19-Nov-2025 18:16:25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>Multi</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>nine thousand one hundred fifty</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -9543,13 +9543,13 @@
         <v>1234</v>
       </c>
       <c r="P60" t="n">
-        <v>11000317484251</v>
+        <v>11000317463739</v>
       </c>
       <c r="Q60" t="n">
-        <v>1763566147</v>
+        <v>1763555959</v>
       </c>
       <c r="R60" t="n">
-        <v>108601056706</v>
+        <v>1.01202532371806e+17</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9563,17 +9563,17 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>ICICI UPI QR</t>
+          <t>BANK OF BARODA FSS</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>SIBL0000899</t>
+          <t>IFSC0000000</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -9606,11 +9606,7 @@
       <c r="AE60" t="n">
         <v>5.9</v>
       </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
-        </is>
-      </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr">
         <is>
@@ -9618,42 +9614,48 @@
         </is>
       </c>
       <c r="AI60" t="n">
-        <v>19911</v>
+        <v>19130</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>265070</t>
+          <t>262998,264501</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2037,2043</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>17290</v>
+        <v>17197</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PATNALA YOSHINI</t>
+          <t>KONADA YASHASWINI</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9985244439</v>
+        <v>9881234227</v>
       </c>
       <c r="D61" t="n">
-        <v>8050</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
+        <v>6750</v>
+      </c>
+      <c r="E61" t="n">
+        <v>6750</v>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20-Nov-2025 08:47:32</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>19-Nov-2025 21:01:26</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -9666,12 +9668,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -9689,13 +9691,13 @@
         <v>1234</v>
       </c>
       <c r="P61" t="n">
-        <v>11000317511572</v>
+        <v>11000317484251</v>
       </c>
       <c r="Q61" t="n">
-        <v>1763608577</v>
+        <v>1763566147</v>
       </c>
       <c r="R61" t="n">
-        <v>472308202173</v>
+        <v>108601056706</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -9714,7 +9716,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -9737,18 +9739,24 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
+      <c r="AA61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC61" t="n">
         <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
       </c>
-      <c r="AE61" t="inlineStr"/>
+      <c r="AE61" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr"/>
@@ -9758,46 +9766,48 @@
         </is>
       </c>
       <c r="AI61" t="n">
-        <v>20000</v>
+        <v>19911</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>265468</t>
+          <t>265070</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>UPI INTENT</t>
-        </is>
-      </c>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>17289</v>
+        <v>17290</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PATNALA DHARVIK</t>
+          <t>PATNALA YOSHINI</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>9985244439</v>
       </c>
       <c r="D62" t="n">
-        <v>7750</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>8050</v>
+      </c>
+      <c r="E62" t="n">
+        <v>8050</v>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20-Nov-2025 08:49:38</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>20-Nov-2025 08:47:32</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -9815,7 +9825,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -9833,13 +9843,13 @@
         <v>1234</v>
       </c>
       <c r="P62" t="n">
-        <v>11000317511641</v>
+        <v>11000317511572</v>
       </c>
       <c r="Q62" t="n">
-        <v>1763608739</v>
+        <v>1763608577</v>
       </c>
       <c r="R62" t="n">
-        <v>962022877628</v>
+        <v>472308202173</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -9858,7 +9868,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -9881,15 +9891,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
+      <c r="AA62" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC62" t="n">
         <v>0</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
       </c>
-      <c r="AE62" t="inlineStr"/>
+      <c r="AE62" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF62" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -9902,16 +9918,16 @@
         </is>
       </c>
       <c r="AI62" t="n">
-        <v>19999</v>
+        <v>20000</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>265256</t>
+          <t>265468</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
@@ -9922,26 +9938,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>15945</v>
+        <v>17289</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LEKSHITA LAASYA POTNURU</t>
+          <t>PATNALA DHARVIK</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8801573949</v>
+        <v>9985244439</v>
       </c>
       <c r="D63" t="n">
-        <v>8850</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>7750</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7750</v>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20-Nov-2025 11:46:10</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>20-Nov-2025 08:49:38</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -9959,7 +9981,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>eight thousand eight hundred fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -9977,13 +9999,13 @@
         <v>1234</v>
       </c>
       <c r="P63" t="n">
-        <v>11000317537894</v>
+        <v>11000317511641</v>
       </c>
       <c r="Q63" t="n">
-        <v>1763619330</v>
+        <v>1763608739</v>
       </c>
       <c r="R63" t="n">
-        <v>881654640858</v>
+        <v>962022877628</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -10002,7 +10024,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -10025,15 +10047,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+      <c r="AA63" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC63" t="n">
         <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
       </c>
-      <c r="AE63" t="inlineStr"/>
+      <c r="AE63" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF63" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -10046,16 +10074,16 @@
         </is>
       </c>
       <c r="AI63" t="n">
-        <v>18833</v>
+        <v>19999</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>262775,264278</t>
+          <t>265256</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>2037,2042</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
@@ -10066,26 +10094,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>17277</v>
+        <v>15945</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EDUBILLI MAHASWIN</t>
+          <t>LEKSHITA LAASYA POTNURU</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9618641662</v>
+        <v>8801573949</v>
       </c>
       <c r="D64" t="n">
-        <v>6750</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>8850</v>
+      </c>
+      <c r="E64" t="n">
+        <v>8850</v>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20-Nov-2025 13:47:57</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>20-Nov-2025 11:46:10</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -10098,12 +10132,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>eight thousand eight hundred fifty</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -10121,13 +10155,13 @@
         <v>1234</v>
       </c>
       <c r="P64" t="n">
-        <v>11000317559740</v>
+        <v>11000317537894</v>
       </c>
       <c r="Q64" t="n">
-        <v>1763626601</v>
+        <v>1763619330</v>
       </c>
       <c r="R64" t="n">
-        <v>108604250147</v>
+        <v>881654640858</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -10146,7 +10180,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -10169,18 +10203,24 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
+      <c r="AA64" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC64" t="n">
         <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
       </c>
-      <c r="AE64" t="inlineStr"/>
+      <c r="AE64" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr"/>
@@ -10190,42 +10230,52 @@
         </is>
       </c>
       <c r="AI64" t="n">
-        <v>19988</v>
+        <v>18833</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>263475</t>
+          <t>262775,264278</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr"/>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>14888</v>
+        <v>17277</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SHAIK GOUSIA NASRIN</t>
+          <t>EDUBILLI MAHASWIN</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7207749584</v>
+        <v>9618641662</v>
       </c>
       <c r="D65" t="n">
-        <v>11250</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>6750</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6750</v>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20-Nov-2025 14:40:36</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>20-Nov-2025 13:47:57</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -10238,12 +10288,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>eleven thousand two hundred fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -10261,13 +10311,13 @@
         <v>1234</v>
       </c>
       <c r="P65" t="n">
-        <v>11000317567806</v>
+        <v>11000317559740</v>
       </c>
       <c r="Q65" t="n">
-        <v>1763629785</v>
+        <v>1763626601</v>
       </c>
       <c r="R65" t="n">
-        <v>108604632984</v>
+        <v>108604250147</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -10286,12 +10336,12 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>IFSC0000000</t>
+          <t>SIBL0000899</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -10309,16 +10359,26 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
+      <c r="AA65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC65" t="n">
         <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
       </c>
-      <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
+      <c r="AE65" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10326,42 +10386,48 @@
         </is>
       </c>
       <c r="AI65" t="n">
-        <v>19200</v>
+        <v>19988</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>263115,264618</t>
+          <t>263475</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>2037,2044</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>16983</v>
+        <v>14888</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NITHYA EMERALD THOTA</t>
+          <t>SHAIK GOUSIA NASRIN</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8919560551</v>
+        <v>7207749584</v>
       </c>
       <c r="D66" t="n">
-        <v>8550</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
+        <v>11250</v>
+      </c>
+      <c r="E66" t="n">
+        <v>11250</v>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20-Nov-2025 17:01:38</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>20-Nov-2025 14:40:36</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -10374,12 +10440,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>Multi</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>eight thousand five hundred fifty</t>
+          <t>eleven thousand two hundred fifty</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -10397,13 +10463,13 @@
         <v>1234</v>
       </c>
       <c r="P66" t="n">
-        <v>11000317588170</v>
+        <v>11000317567806</v>
       </c>
       <c r="Q66" t="n">
-        <v>1763636615</v>
+        <v>1763629785</v>
       </c>
       <c r="R66" t="n">
-        <v>108605493967</v>
+        <v>108604632984</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10422,12 +10488,12 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>SIBL0000899</t>
+          <t>IFSC0000000</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -10445,20 +10511,22 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
+      <c r="AA66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC66" t="n">
         <v>0</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
       </c>
-      <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
-        </is>
-      </c>
+      <c r="AE66" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10466,42 +10534,48 @@
         </is>
       </c>
       <c r="AI66" t="n">
-        <v>18526</v>
+        <v>19200</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>262171,263959</t>
+          <t>263115,264618</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>2037,2041</t>
+          <t>2037,2044</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16580</v>
+        <v>16983</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CHANUKYA APPALACHARYULU MUNUBARTHI</t>
+          <t>NITHYA EMERALD THOTA</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9908906244</v>
+        <v>8919560551</v>
       </c>
       <c r="D67" t="n">
-        <v>8850</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
+        <v>8550</v>
+      </c>
+      <c r="E67" t="n">
+        <v>8550</v>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20-Nov-2025 17:12:41</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>20-Nov-2025 17:01:38</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -10519,7 +10593,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>eight thousand eight hundred fifty</t>
+          <t>eight thousand five hundred fifty</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -10537,13 +10611,13 @@
         <v>1234</v>
       </c>
       <c r="P67" t="n">
-        <v>11000317589448</v>
+        <v>11000317588170</v>
       </c>
       <c r="Q67" t="n">
-        <v>1763638742</v>
+        <v>1763636615</v>
       </c>
       <c r="R67" t="n">
-        <v>108605556686</v>
+        <v>108605493967</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -10562,7 +10636,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -10585,15 +10659,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
+      <c r="AA67" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC67" t="n">
         <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
       </c>
-      <c r="AE67" t="inlineStr"/>
+      <c r="AE67" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF67" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -10606,42 +10686,48 @@
         </is>
       </c>
       <c r="AI67" t="n">
-        <v>18889</v>
+        <v>18526</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>262808,264311</t>
+          <t>262171,263959</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>2037,2042</t>
+          <t>2037,2041</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>15795</v>
+        <v>16580</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YAAKSHITH CHETTI</t>
+          <t>CHANUKYA APPALACHARYULU MUNUBARTHI</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9160018096</v>
+        <v>9908906244</v>
       </c>
       <c r="D68" t="n">
-        <v>500</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+        <v>8850</v>
+      </c>
+      <c r="E68" t="n">
+        <v>8850</v>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20-Nov-2025 20:01:56</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>20-Nov-2025 17:12:41</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -10659,7 +10745,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>five hundred</t>
+          <t>eight thousand eight hundred fifty</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -10677,13 +10763,13 @@
         <v>1234</v>
       </c>
       <c r="P68" t="n">
-        <v>11000317606868</v>
+        <v>11000317589448</v>
       </c>
       <c r="Q68" t="n">
-        <v>1763649005</v>
+        <v>1763638742</v>
       </c>
       <c r="R68" t="n">
-        <v>185561913245</v>
+        <v>108605556686</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -10702,7 +10788,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -10725,15 +10811,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr"/>
-      <c r="AB68" t="inlineStr"/>
+      <c r="AA68" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC68" t="n">
         <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
       </c>
-      <c r="AE68" t="inlineStr"/>
+      <c r="AE68" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF68" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -10746,46 +10838,48 @@
         </is>
       </c>
       <c r="AI68" t="n">
-        <v>19105</v>
+        <v>18889</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>262986</t>
+          <t>262808,264311</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="AL68" t="inlineStr">
-        <is>
-          <t>UPI INTENT</t>
-        </is>
-      </c>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>16617</v>
+        <v>15795</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>THANU SREE BHOOMIREDDY</t>
+          <t>YAAKSHITH CHETTI</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9573771080</v>
+        <v>9160018096</v>
       </c>
       <c r="D69" t="n">
-        <v>8050</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
+        <v>500</v>
+      </c>
+      <c r="E69" t="n">
+        <v>500</v>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20-Nov-2025 20:59:36</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>20-Nov-2025 20:01:56</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -10803,7 +10897,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>five hundred</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -10821,13 +10915,13 @@
         <v>1234</v>
       </c>
       <c r="P69" t="n">
-        <v>11000317615031</v>
+        <v>11000317606868</v>
       </c>
       <c r="Q69" t="n">
-        <v>1763652458</v>
+        <v>1763649005</v>
       </c>
       <c r="R69" t="n">
-        <v>108606865688</v>
+        <v>185561913245</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -10846,7 +10940,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -10869,15 +10963,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr"/>
-      <c r="AB69" t="inlineStr"/>
+      <c r="AA69" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC69" t="n">
         <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
       </c>
-      <c r="AE69" t="inlineStr"/>
+      <c r="AE69" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF69" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -10890,42 +10990,52 @@
         </is>
       </c>
       <c r="AI69" t="n">
-        <v>18610</v>
+        <v>19105</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>265580</t>
+          <t>262986</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="AL69" t="inlineStr"/>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>17149</v>
+        <v>16617</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MELINDHA BADE</t>
+          <t>THANU SREE BHOOMIREDDY</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9989075944</v>
+        <v>9573771080</v>
       </c>
       <c r="D70" t="n">
-        <v>9150</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
+        <v>8050</v>
+      </c>
+      <c r="E70" t="n">
+        <v>8050</v>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20-Nov-2025 21:49:09</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>20-Nov-2025 20:59:36</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -10938,12 +11048,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>nine thousand one hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -10961,13 +11071,13 @@
         <v>1234</v>
       </c>
       <c r="P70" t="n">
-        <v>11000317619325</v>
+        <v>11000317615031</v>
       </c>
       <c r="Q70" t="n">
-        <v>1763655441</v>
+        <v>1763652458</v>
       </c>
       <c r="R70" t="n">
-        <v>108607082636</v>
+        <v>108606865688</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -10986,12 +11096,12 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>IFSC0000000</t>
+          <t>SIBL0000899</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -11009,16 +11119,26 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
+      <c r="AA70" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC70" t="n">
         <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
       </c>
-      <c r="AE70" t="inlineStr"/>
-      <c r="AF70" t="inlineStr"/>
+      <c r="AE70" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11026,19 +11146,1015 @@
         </is>
       </c>
       <c r="AI70" t="n">
+        <v>18610</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>265580</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>17149</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MELINDHA BADE</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>9989075944</v>
+      </c>
+      <c r="D71" t="n">
+        <v>9150</v>
+      </c>
+      <c r="E71" t="n">
+        <v>9150</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 21:49:09</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>nine thousand one hundred fifty</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P71" t="n">
+        <v>11000317619325</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1763655441</v>
+      </c>
+      <c r="R71" t="n">
+        <v>108607082636</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA71" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI71" t="n">
         <v>19852</v>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>262887,264390</t>
         </is>
       </c>
-      <c r="AK70" t="inlineStr">
+      <c r="AK71" t="inlineStr">
         <is>
           <t>2037,2043</t>
         </is>
       </c>
-      <c r="AL70" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>16492</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ASHWATH ADITHYA MUNUBARTHI</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9908906244</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8550</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 07:11:30</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P72" t="n">
+        <v>11000317632962</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1763689095</v>
+      </c>
+      <c r="R72" t="n">
+        <v>108608167999</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI72" t="n">
+        <v>18659</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>262404,264014</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>15898</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MAHENDRA NAIDU VANJARI</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9440280157</v>
+      </c>
+      <c r="D73" t="n">
+        <v>17800</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 09:13:00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>seventeen thousand eight hundred</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P73" t="n">
+        <v>11000317644277</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1763696190</v>
+      </c>
+      <c r="R73" t="n">
+        <v>122941457741</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI73" t="n">
+        <v>19009</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>262983,264486,266136</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>2037,2043,2051</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>15538</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>VENKATA VIGNESWARI SAI VINYA BOTTA</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>6303433178</v>
+      </c>
+      <c r="D74" t="n">
+        <v>8850</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 10:45:33</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P74" t="n">
+        <v>11000317657466</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1763702116</v>
+      </c>
+      <c r="R74" t="n">
+        <v>404578383859</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI74" t="n">
+        <v>18918</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>262741,264244</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>14873</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GNANA VIGNESWARI SAI CHANDRIKA BOTTA</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6303433178</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11250</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 10:46:49</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>eleven thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P75" t="n">
+        <v>11000317657543</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1763702195</v>
+      </c>
+      <c r="R75" t="n">
+        <v>79146114128</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI75" t="n">
+        <v>19244</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>263048,264551</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>2037,2044</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>15096</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>RAYASAM SRI VARNIKA</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7382913422</v>
+      </c>
+      <c r="D76" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 14:41:57</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P76" t="n">
+        <v>11000317695213</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1763715904</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1.012025325918391e+17</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>BANK OF BARODA FSS</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI76" t="n">
+        <v>19483</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>264879</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>16992</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GAUTAM MOOGI</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7207505036</v>
+      </c>
+      <c r="D77" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 17:59:17</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P77" t="n">
+        <v>11000317719673</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1763728005</v>
+      </c>
+      <c r="R77" t="n">
+        <v>108611639217</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI77" t="n">
+        <v>18360</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>265368</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL77"/>
+  <dimension ref="A1:AL86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12156,6 +12156,1278 @@
       </c>
       <c r="AL77" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>16353</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HRIDAYANSH VICTOR RETOJI</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>9395553084</v>
+      </c>
+      <c r="D78" t="n">
+        <v>8550</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 07:12:07</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P78" t="n">
+        <v>11000317752087</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1763775572</v>
+      </c>
+      <c r="R78" t="n">
+        <v>108613908890</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI78" t="n">
+        <v>18469</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>262466,263884</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>15824</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GOLAGANI RITHIK NANDHAN</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>9393123464</v>
+      </c>
+      <c r="D79" t="n">
+        <v>8550</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 08:41:05</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P79" t="n">
+        <v>11000317755959</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1763781049</v>
+      </c>
+      <c r="R79" t="n">
+        <v>722776047390</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI79" t="n">
+        <v>18667</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>262441,264022</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>15009</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GOLAGANI GEETHANJALI</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9393123464</v>
+      </c>
+      <c r="D80" t="n">
+        <v>9150</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 08:44:37</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>nine thousand one hundred fifty</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P80" t="n">
+        <v>11000317756764</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1763781250</v>
+      </c>
+      <c r="R80" t="n">
+        <v>387942566112</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI80" t="n">
+        <v>19026</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>262897,264400</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>2037,2043</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>17316</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SUVVARI JAIDEEP</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>7386363690</v>
+      </c>
+      <c r="D81" t="n">
+        <v>8250</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 09:33:58</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>eight thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P81" t="n">
+        <v>11000317759875</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1763783349</v>
+      </c>
+      <c r="R81" t="n">
+        <v>929606991918</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI81" t="n">
+        <v>20024</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>262633,263603</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>2037,2040</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>16598</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MANASHVI AKKIREDDY</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>8184888497</v>
+      </c>
+      <c r="D82" t="n">
+        <v>8250</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 09:56:00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>eight thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P82" t="n">
+        <v>11000317762419</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1763785456</v>
+      </c>
+      <c r="R82" t="n">
+        <v>108614534365</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI82" t="n">
+        <v>18346</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>262200,263672</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>2037,2040</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>14944</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SRAVAN BHARGAV KADIRI</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9701983320</v>
+      </c>
+      <c r="D83" t="n">
+        <v>11250</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 10:53:07</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>eleven thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P83" t="n">
+        <v>11000317774408</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1763788955</v>
+      </c>
+      <c r="R83" t="n">
+        <v>108614807525</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI83" t="n">
+        <v>19236</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>263139,264642</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>2037,2044</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>17099</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VINDYA SOWDALA</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>7075489300</v>
+      </c>
+      <c r="D84" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 12:23:46</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P84" t="n">
+        <v>11000317789451</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1763794365</v>
+      </c>
+      <c r="R84" t="n">
+        <v>84407133536</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI84" t="n">
+        <v>18095</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>265111</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>17100</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BHAVIYSA SOWDALA</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>7075489300</v>
+      </c>
+      <c r="D85" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 12:26:26</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P85" t="n">
+        <v>11000317789617</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1763794575</v>
+      </c>
+      <c r="R85" t="n">
+        <v>892395505599</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI85" t="n">
+        <v>18638</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>265647</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>16721</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KURMAPU GAGANASHREE</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>9908361635</v>
+      </c>
+      <c r="D86" t="n">
+        <v>8250</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 12:59:10</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>eight thousand two hundred fifty</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P86" t="n">
+        <v>11000317794411</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1763796507</v>
+      </c>
+      <c r="R86" t="n">
+        <v>108615558861</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI86" t="n">
+        <v>18114</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>262147,263524</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>2037,2040</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL86"/>
+  <dimension ref="A1:AL90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11323,13 +11323,19 @@
       <c r="D72" t="n">
         <v>8550</v>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>8550</v>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>21-Nov-2025 07:11:30</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -11390,7 +11396,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -11413,15 +11419,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr"/>
-      <c r="AB72" t="inlineStr"/>
+      <c r="AA72" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC72" t="n">
         <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
       </c>
-      <c r="AE72" t="inlineStr"/>
+      <c r="AE72" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF72" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -11467,13 +11479,19 @@
       <c r="D73" t="n">
         <v>17800</v>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>17800</v>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>21-Nov-2025 09:13:00</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -11534,7 +11552,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -11557,15 +11575,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr"/>
+      <c r="AA73" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC73" t="n">
         <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
       </c>
-      <c r="AE73" t="inlineStr"/>
+      <c r="AE73" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr">
@@ -11607,13 +11631,19 @@
       <c r="D74" t="n">
         <v>8850</v>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>8850</v>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>21-Nov-2025 10:45:33</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -11674,7 +11704,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -11697,15 +11727,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr"/>
-      <c r="AB74" t="inlineStr"/>
+      <c r="AA74" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC74" t="n">
         <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
       </c>
-      <c r="AE74" t="inlineStr"/>
+      <c r="AE74" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF74" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -11751,13 +11787,19 @@
       <c r="D75" t="n">
         <v>11250</v>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>11250</v>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>21-Nov-2025 10:46:49</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -11818,7 +11860,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -11841,15 +11883,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr"/>
-      <c r="AB75" t="inlineStr"/>
+      <c r="AA75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC75" t="n">
         <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
       </c>
-      <c r="AE75" t="inlineStr"/>
+      <c r="AE75" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr">
@@ -11891,7 +11939,9 @@
       <c r="D76" t="n">
         <v>11350</v>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>11350</v>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>21-Nov-2025 14:41:57</t>
@@ -11958,7 +12008,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -11981,15 +12031,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr"/>
-      <c r="AB76" t="inlineStr"/>
+      <c r="AA76" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC76" t="n">
         <v>0</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
-      <c r="AE76" t="inlineStr"/>
+      <c r="AE76" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF76" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -12031,13 +12087,19 @@
       <c r="D77" t="n">
         <v>7750</v>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>7750</v>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>21-Nov-2025 17:59:17</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -12098,7 +12160,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -12121,15 +12183,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
+      <c r="AA77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC77" t="n">
         <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
       </c>
-      <c r="AE77" t="inlineStr"/>
+      <c r="AE77" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF77" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -12171,13 +12239,19 @@
       <c r="D78" t="n">
         <v>8550</v>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>8550</v>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>22-Nov-2025 07:12:07</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -12238,7 +12312,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -12261,15 +12335,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
+      <c r="AA78" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC78" t="n">
         <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
       </c>
-      <c r="AE78" t="inlineStr"/>
+      <c r="AE78" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF78" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -12311,13 +12391,19 @@
       <c r="D79" t="n">
         <v>8550</v>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>8550</v>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>22-Nov-2025 08:41:05</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -12378,7 +12464,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -12401,15 +12487,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+      <c r="AA79" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC79" t="n">
         <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
       </c>
-      <c r="AE79" t="inlineStr"/>
+      <c r="AE79" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF79" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -12455,13 +12547,19 @@
       <c r="D80" t="n">
         <v>9150</v>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="n">
+        <v>9150</v>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>22-Nov-2025 08:44:37</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -12522,7 +12620,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -12545,15 +12643,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+      <c r="AA80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC80" t="n">
         <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
       </c>
-      <c r="AE80" t="inlineStr"/>
+      <c r="AE80" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr">
@@ -12595,13 +12699,19 @@
       <c r="D81" t="n">
         <v>8250</v>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="n">
+        <v>8250</v>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>22-Nov-2025 09:33:58</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -12662,7 +12772,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -12685,15 +12795,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
+      <c r="AA81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC81" t="n">
         <v>0</v>
       </c>
       <c r="AD81" t="n">
         <v>0</v>
       </c>
-      <c r="AE81" t="inlineStr"/>
+      <c r="AE81" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF81" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -12739,13 +12855,19 @@
       <c r="D82" t="n">
         <v>8250</v>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="n">
+        <v>8250</v>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>22-Nov-2025 09:56:00</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -12806,7 +12928,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -12829,15 +12951,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
+      <c r="AA82" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC82" t="n">
         <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
       </c>
-      <c r="AE82" t="inlineStr"/>
+      <c r="AE82" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF82" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -12879,13 +13007,19 @@
       <c r="D83" t="n">
         <v>11250</v>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>11250</v>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>22-Nov-2025 10:53:07</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -12946,7 +13080,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -12969,15 +13103,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr"/>
-      <c r="AB83" t="inlineStr"/>
+      <c r="AA83" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC83" t="n">
         <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
       </c>
-      <c r="AE83" t="inlineStr"/>
+      <c r="AE83" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr">
@@ -13015,13 +13155,19 @@
       <c r="D84" t="n">
         <v>6750</v>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>6750</v>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>22-Nov-2025 12:23:46</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -13082,7 +13228,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -13105,15 +13251,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr"/>
-      <c r="AB84" t="inlineStr"/>
+      <c r="AA84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC84" t="n">
         <v>0</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
       </c>
-      <c r="AE84" t="inlineStr"/>
+      <c r="AE84" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF84" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -13159,13 +13311,19 @@
       <c r="D85" t="n">
         <v>8050</v>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="n">
+        <v>8050</v>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>22-Nov-2025 12:26:26</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -13226,7 +13384,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -13249,15 +13407,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
+      <c r="AA85" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC85" t="n">
         <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
       </c>
-      <c r="AE85" t="inlineStr"/>
+      <c r="AE85" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF85" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -13303,13 +13467,19 @@
       <c r="D86" t="n">
         <v>8250</v>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="n">
+        <v>8250</v>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>22-Nov-2025 12:59:10</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -13370,7 +13540,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -13393,15 +13563,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr"/>
-      <c r="AB86" t="inlineStr"/>
+      <c r="AA86" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC86" t="n">
         <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
       </c>
-      <c r="AE86" t="inlineStr"/>
+      <c r="AE86" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF86" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -13427,6 +13603,562 @@
         </is>
       </c>
       <c r="AL86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>14160</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DHARMAVARAPU CHANDANA RAMYA</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>8374970989</v>
+      </c>
+      <c r="D87" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:01:40</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P87" t="n">
+        <v>11000317917995</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1763951385</v>
+      </c>
+      <c r="R87" t="n">
+        <v>108625745822</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI87" t="n">
+        <v>19571</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>264841</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>14511</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DHARMAVARAPU MADHULICA SRI</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>8374970989</v>
+      </c>
+      <c r="D88" t="n">
+        <v>11850</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:07:11</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>eleven thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P88" t="n">
+        <v>11000317919152</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1763951723</v>
+      </c>
+      <c r="R88" t="n">
+        <v>108625767984</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI88" t="n">
+        <v>19336</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>263218,264721</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>2037,2045</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>17103</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PANDRANKI BHAVITHA SRI</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>6301729629</v>
+      </c>
+      <c r="D89" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:19:39</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P89" t="n">
+        <v>11000317919499</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1763952416</v>
+      </c>
+      <c r="R89" t="n">
+        <v>108625814663</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI89" t="n">
+        <v>18038</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>263436</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>16067</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MOHAMMAD AFZAL</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>9885519010</v>
+      </c>
+      <c r="D90" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 10:20:54</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">twenty two thousand </t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P90" t="n">
+        <v>11000317934837</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1763959817</v>
+      </c>
+      <c r="R90" t="n">
+        <v>694416410395</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI90" t="n">
+        <v>19319</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>263145,264648,266298</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>2037,2044,2052</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL90"/>
+  <dimension ref="A1:AL96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12994,25 +12994,25 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>14944</v>
+        <v>17219</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRAVAN BHARGAV KADIRI</t>
+          <t>VARTIKA KUMARI</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9701983320</v>
+        <v>8369239788</v>
       </c>
       <c r="D83" t="n">
-        <v>11250</v>
+        <v>8250</v>
       </c>
       <c r="E83" t="n">
-        <v>11250</v>
+        <v>8250</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>22-Nov-2025 10:53:07</t>
+          <t>22-Nov-2025 10:44:52</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
+          <t>TRANSACTION IS SUCCESS</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -13032,12 +13032,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>eleven thousand two hundred fifty</t>
+          <t>eight thousand two hundred fifty</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -13055,13 +13055,13 @@
         <v>1234</v>
       </c>
       <c r="P83" t="n">
-        <v>11000317774408</v>
+        <v>11000317773361</v>
       </c>
       <c r="Q83" t="n">
-        <v>1763788955</v>
+        <v>1763788142</v>
       </c>
       <c r="R83" t="n">
-        <v>108614807525</v>
+        <v>104508217364</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -13080,12 +13080,12 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>IFSC0000000</t>
+          <t>SIBL0000899</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>QR_UPI</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
@@ -13118,7 +13118,11 @@
       <c r="AE83" t="n">
         <v>5.9</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13126,41 +13130,45 @@
         </is>
       </c>
       <c r="AI83" t="n">
-        <v>19236</v>
+        <v>19931</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>263139,264642</t>
+          <t>262332,263555</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>2037,2044</t>
-        </is>
-      </c>
-      <c r="AL83" t="inlineStr"/>
+          <t>2037,2040</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>17099</v>
+        <v>14944</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VINDYA SOWDALA</t>
+          <t>SRAVAN BHARGAV KADIRI</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7075489300</v>
+        <v>9701983320</v>
       </c>
       <c r="D84" t="n">
-        <v>6750</v>
+        <v>11250</v>
       </c>
       <c r="E84" t="n">
-        <v>6750</v>
+        <v>11250</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>22-Nov-2025 12:23:46</t>
+          <t>22-Nov-2025 10:53:07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -13180,12 +13188,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>Multi</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>eleven thousand two hundred fifty</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -13203,13 +13211,13 @@
         <v>1234</v>
       </c>
       <c r="P84" t="n">
-        <v>11000317789451</v>
+        <v>11000317774408</v>
       </c>
       <c r="Q84" t="n">
-        <v>1763794365</v>
+        <v>1763788955</v>
       </c>
       <c r="R84" t="n">
-        <v>84407133536</v>
+        <v>108614807525</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -13228,12 +13236,12 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>SIBL0000899</t>
+          <t>IFSC0000000</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -13266,11 +13274,7 @@
       <c r="AE84" t="n">
         <v>5.9</v>
       </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
-        </is>
-      </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr">
         <is>
@@ -13278,45 +13282,41 @@
         </is>
       </c>
       <c r="AI84" t="n">
-        <v>18095</v>
+        <v>19236</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>265111</t>
+          <t>263139,264642</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>UPI INTENT</t>
-        </is>
-      </c>
+          <t>2037,2044</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>17100</v>
+        <v>17099</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BHAVIYSA SOWDALA</t>
+          <t>VINDYA SOWDALA</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>7075489300</v>
       </c>
       <c r="D85" t="n">
-        <v>8050</v>
+        <v>6750</v>
       </c>
       <c r="E85" t="n">
-        <v>8050</v>
+        <v>6750</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>22-Nov-2025 12:26:26</t>
+          <t>22-Nov-2025 12:23:46</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -13359,13 +13359,13 @@
         <v>1234</v>
       </c>
       <c r="P85" t="n">
-        <v>11000317789617</v>
+        <v>11000317789451</v>
       </c>
       <c r="Q85" t="n">
-        <v>1763794575</v>
+        <v>1763794365</v>
       </c>
       <c r="R85" t="n">
-        <v>892395505599</v>
+        <v>84407133536</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG85" t="inlineStr"/>
@@ -13434,16 +13434,16 @@
         </is>
       </c>
       <c r="AI85" t="n">
-        <v>18638</v>
+        <v>18095</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>265647</t>
+          <t>265111</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
@@ -13454,25 +13454,25 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>16721</v>
+        <v>17100</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KURMAPU GAGANASHREE</t>
+          <t>BHAVIYSA SOWDALA</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9908361635</v>
+        <v>7075489300</v>
       </c>
       <c r="D86" t="n">
-        <v>8250</v>
+        <v>8050</v>
       </c>
       <c r="E86" t="n">
-        <v>8250</v>
+        <v>8050</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>22-Nov-2025 12:59:10</t>
+          <t>22-Nov-2025 12:26:26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>eight thousand two hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -13515,13 +13515,13 @@
         <v>1234</v>
       </c>
       <c r="P86" t="n">
-        <v>11000317794411</v>
+        <v>11000317789617</v>
       </c>
       <c r="Q86" t="n">
-        <v>1763796507</v>
+        <v>1763794575</v>
       </c>
       <c r="R86" t="n">
-        <v>108615558861</v>
+        <v>892395505599</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -13590,42 +13590,52 @@
         </is>
       </c>
       <c r="AI86" t="n">
-        <v>18114</v>
+        <v>18638</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>262147,263524</t>
+          <t>265647</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>2037,2040</t>
-        </is>
-      </c>
-      <c r="AL86" t="inlineStr"/>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>14160</v>
+        <v>16721</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DHARMAVARAPU CHANDANA RAMYA</t>
+          <t>KURMAPU GAGANASHREE</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8374970989</v>
+        <v>9908361635</v>
       </c>
       <c r="D87" t="n">
-        <v>11350</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>8250</v>
+      </c>
+      <c r="E87" t="n">
+        <v>8250</v>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>24-Nov-2025 08:01:40</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>22-Nov-2025 12:59:10</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -13638,12 +13648,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>VlllX</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>eleven thousand three hundred fifty</t>
+          <t>eight thousand two hundred fifty</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -13661,13 +13671,13 @@
         <v>1234</v>
       </c>
       <c r="P87" t="n">
-        <v>11000317917995</v>
+        <v>11000317794411</v>
       </c>
       <c r="Q87" t="n">
-        <v>1763951385</v>
+        <v>1763796507</v>
       </c>
       <c r="R87" t="n">
-        <v>108625745822</v>
+        <v>108615558861</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -13686,7 +13696,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -13709,18 +13719,24 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr"/>
-      <c r="AB87" t="inlineStr"/>
+      <c r="AA87" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC87" t="n">
         <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
       </c>
-      <c r="AE87" t="inlineStr"/>
+      <c r="AE87" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr"/>
@@ -13730,39 +13746,41 @@
         </is>
       </c>
       <c r="AI87" t="n">
-        <v>19571</v>
+        <v>18114</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>264841</t>
+          <t>262147,263524</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2037,2040</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>14511</v>
+        <v>14160</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DHARMAVARAPU MADHULICA SRI</t>
+          <t>DHARMAVARAPU CHANDANA RAMYA</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>8374970989</v>
       </c>
       <c r="D88" t="n">
-        <v>11850</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>11350</v>
+      </c>
+      <c r="E88" t="n">
+        <v>11350</v>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>24-Nov-2025 08:07:11</t>
+          <t>24-Nov-2025 08:01:40</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -13778,12 +13796,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>VlllX</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>eleven thousand eight hundred fifty</t>
+          <t>eleven thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -13801,13 +13819,13 @@
         <v>1234</v>
       </c>
       <c r="P88" t="n">
-        <v>11000317919152</v>
+        <v>11000317917995</v>
       </c>
       <c r="Q88" t="n">
-        <v>1763951723</v>
+        <v>1763951385</v>
       </c>
       <c r="R88" t="n">
-        <v>108625767984</v>
+        <v>108625745822</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -13826,12 +13844,12 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>IFSC0000000</t>
+          <t>SIBL0000899</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -13849,16 +13867,26 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
+      <c r="AA88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC88" t="n">
         <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
       </c>
-      <c r="AE88" t="inlineStr"/>
-      <c r="AF88" t="inlineStr"/>
+      <c r="AE88" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr">
         <is>
@@ -13866,42 +13894,48 @@
         </is>
       </c>
       <c r="AI88" t="n">
-        <v>19336</v>
+        <v>19571</v>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>263218,264721</t>
+          <t>264841</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>2037,2045</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>17103</v>
+        <v>14511</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PANDRANKI BHAVITHA SRI</t>
+          <t>DHARMAVARAPU MADHULICA SRI</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6301729629</v>
+        <v>8374970989</v>
       </c>
       <c r="D89" t="n">
-        <v>6750</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
+        <v>11850</v>
+      </c>
+      <c r="E89" t="n">
+        <v>11850</v>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>24-Nov-2025 08:19:39</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>24-Nov-2025 08:07:11</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -13914,12 +13948,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>Multi</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>eleven thousand eight hundred fifty</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -13937,13 +13971,13 @@
         <v>1234</v>
       </c>
       <c r="P89" t="n">
-        <v>11000317919499</v>
+        <v>11000317919152</v>
       </c>
       <c r="Q89" t="n">
-        <v>1763952416</v>
+        <v>1763951723</v>
       </c>
       <c r="R89" t="n">
-        <v>108625814663</v>
+        <v>108625767984</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -13962,12 +13996,12 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>SIBL0000899</t>
+          <t>IFSC0000000</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
@@ -13985,20 +14019,22 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr"/>
+      <c r="AA89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC89" t="n">
         <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
       </c>
-      <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
-        </is>
-      </c>
+      <c r="AE89" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14006,42 +14042,48 @@
         </is>
       </c>
       <c r="AI89" t="n">
-        <v>18038</v>
+        <v>19336</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>263436</t>
+          <t>263218,264721</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2037,2045</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>16067</v>
+        <v>17103</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MOHAMMAD AFZAL</t>
+          <t>PANDRANKI BHAVITHA SRI</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9885519010</v>
+        <v>6301729629</v>
       </c>
       <c r="D90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
+        <v>6750</v>
+      </c>
+      <c r="E90" t="n">
+        <v>6750</v>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>24-Nov-2025 10:20:54</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
+          <t>24-Nov-2025 08:19:39</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -14054,12 +14096,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">twenty two thousand </t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -14077,13 +14119,13 @@
         <v>1234</v>
       </c>
       <c r="P90" t="n">
-        <v>11000317934837</v>
+        <v>11000317919499</v>
       </c>
       <c r="Q90" t="n">
-        <v>1763959817</v>
+        <v>1763952416</v>
       </c>
       <c r="R90" t="n">
-        <v>694416410395</v>
+        <v>108625814663</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -14102,12 +14144,12 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>IFSC0000000</t>
+          <t>SIBL0000899</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -14125,16 +14167,26 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
+      <c r="AA90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC90" t="n">
         <v>0</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
       </c>
-      <c r="AE90" t="inlineStr"/>
-      <c r="AF90" t="inlineStr"/>
+      <c r="AE90" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr">
         <is>
@@ -14142,19 +14194,923 @@
         </is>
       </c>
       <c r="AI90" t="n">
+        <v>18038</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>263436</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>16067</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MOHAMMAD AFZAL</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>9885519010</v>
+      </c>
+      <c r="D91" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E91" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 10:20:54</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">twenty two thousand </t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P91" t="n">
+        <v>11000317934837</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1763959817</v>
+      </c>
+      <c r="R91" t="n">
+        <v>694416410395</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA91" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI91" t="n">
         <v>19319</v>
       </c>
-      <c r="AJ90" t="inlineStr">
+      <c r="AJ91" t="inlineStr">
         <is>
           <t>263145,264648,266298</t>
         </is>
       </c>
-      <c r="AK90" t="inlineStr">
+      <c r="AK91" t="inlineStr">
         <is>
           <t>2037,2044,2052</t>
         </is>
       </c>
-      <c r="AL90" t="inlineStr">
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>16555</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>GANTEDA CHERISHMA</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>9676361548</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8850</v>
+      </c>
+      <c r="E92" t="n">
+        <v>8850</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 09:02:25</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>eight thousand eight hundred fifty</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P92" t="n">
+        <v>11000318061560</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1764041529</v>
+      </c>
+      <c r="R92" t="n">
+        <v>285283553470</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA92" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI92" t="n">
+        <v>18789</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>262103,264102</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>2037,2042</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>15863</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BOMMIDI BALA SURYA BHUVAN</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>6300875193</v>
+      </c>
+      <c r="D93" t="n">
+        <v>8550</v>
+      </c>
+      <c r="E93" t="n">
+        <v>8550</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 12:04:15</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>eight thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P93" t="n">
+        <v>11000318091639</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1764052436</v>
+      </c>
+      <c r="R93" t="n">
+        <v>514342923427</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI93" t="n">
+        <v>18543</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>262382,264003</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>2037,2041</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>17295</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PALAKONDA PUDARJUN</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>9493856632</v>
+      </c>
+      <c r="D94" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E94" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 19:32:34</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P94" t="n">
+        <v>11000318159831</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1764079329</v>
+      </c>
+      <c r="R94" t="n">
+        <v>569509465610</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA94" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI94" t="n">
+        <v>20005</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>265045</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>16196</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BOTTA V K SAMTHOSHI VARSHITHA</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>9059927162</v>
+      </c>
+      <c r="D95" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 13:06:35</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P95" t="n">
+        <v>11000318238042</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1764142579</v>
+      </c>
+      <c r="R95" t="n">
+        <v>779334795869</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI95" t="n">
+        <v>19597</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>261864</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>14874</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BOTTA RAM VIGNESH SANTHOSH SAI RISHIK</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>9059927162</v>
+      </c>
+      <c r="D96" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 13:08:30</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P96" t="n">
+        <v>11000318238143</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1764142689</v>
+      </c>
+      <c r="R96" t="n">
+        <v>640249767855</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI96" t="n">
+        <v>19186</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>261642</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -14843,7 +14843,9 @@
       <c r="D95" t="n">
         <v>11350</v>
       </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>11350</v>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>26-Nov-2025 13:06:35</t>
@@ -14910,7 +14912,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -14933,15 +14935,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr"/>
-      <c r="AB95" t="inlineStr"/>
+      <c r="AA95" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC95" t="n">
         <v>0</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
       </c>
-      <c r="AE95" t="inlineStr"/>
+      <c r="AE95" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF95" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -14987,7 +14995,9 @@
       <c r="D96" t="n">
         <v>10750</v>
       </c>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>10750</v>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>26-Nov-2025 13:08:30</t>
@@ -15054,7 +15064,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
@@ -15077,15 +15087,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr"/>
+      <c r="AA96" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC96" t="n">
         <v>0</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
       </c>
-      <c r="AE96" t="inlineStr"/>
+      <c r="AE96" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF96" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL96"/>
+  <dimension ref="A1:AL97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15132,6 +15132,162 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>16915</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>KOMMANABOINA SOHAM KRISHNA</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>7013724701</v>
+      </c>
+      <c r="D97" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E97" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>30-Nov-2025 19:27:04</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>01-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P97" t="n">
+        <v>11000318681594</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1764510946</v>
+      </c>
+      <c r="R97" t="n">
+        <v>253593820489</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA97" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI97" t="n">
+        <v>18069</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>265116</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL97"/>
+  <dimension ref="A1:AL99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15288,6 +15288,286 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>15962</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BANALA VAIBHAV</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>9248863180</v>
+      </c>
+      <c r="D98" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>02-Dec-2025 10:00:57</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O98" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P98" t="n">
+        <v>11000318889672</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1764649784</v>
+      </c>
+      <c r="R98" t="n">
+        <v>108676570140</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI98" t="n">
+        <v>19562</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>266565</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>17307</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HEYAN RUUDRA RAPOL</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>9991367333</v>
+      </c>
+      <c r="D99" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>02-Dec-2025 11:23:13</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P99" t="n">
+        <v>11000318907761</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1764654572</v>
+      </c>
+      <c r="R99" t="n">
+        <v>108677081867</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI99" t="n">
+        <v>20016</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>265830</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL99"/>
+  <dimension ref="A1:AL101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15303,7 +15303,9 @@
       <c r="D98" t="n">
         <v>11350</v>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="n">
+        <v>11350</v>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>02-Dec-2025 10:00:57</t>
@@ -15370,7 +15372,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
@@ -15393,15 +15395,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr"/>
-      <c r="AB98" t="inlineStr"/>
+      <c r="AA98" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC98" t="n">
         <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
       </c>
-      <c r="AE98" t="inlineStr"/>
+      <c r="AE98" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF98" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -15443,13 +15451,19 @@
       <c r="D99" t="n">
         <v>8350</v>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>8350</v>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>02-Dec-2025 11:23:13</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>03-Dec-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -15510,7 +15524,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -15533,15 +15547,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
+      <c r="AA99" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC99" t="n">
         <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
       </c>
-      <c r="AE99" t="inlineStr"/>
+      <c r="AE99" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF99" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -15567,6 +15587,306 @@
         </is>
       </c>
       <c r="AL99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>17201</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DIMILI GAGAN RISHIT</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>9493942534</v>
+      </c>
+      <c r="D100" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E100" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>03-Dec-2025 12:56:10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>04-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P100" t="n">
+        <v>11000319087080</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1764746759</v>
+      </c>
+      <c r="R100" t="n">
+        <v>104049297773</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA100" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI100" t="n">
+        <v>19915</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>265222</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>16147</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PERARAPU RESHMI SRI THANVI</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>9573851290</v>
+      </c>
+      <c r="D101" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>04-Dec-2025 17:57:16</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P101" t="n">
+        <v>11000319277676</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1764851203</v>
+      </c>
+      <c r="R101" t="n">
+        <v>571789451692</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI101" t="n">
+        <v>18767</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>265790</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -15759,13 +15759,19 @@
       <c r="D101" t="n">
         <v>8350</v>
       </c>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="n">
+        <v>8350</v>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>04-Dec-2025 17:57:16</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>05-Dec-2025 00:00:00</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -15826,7 +15832,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -15849,15 +15855,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA101" t="inlineStr"/>
-      <c r="AB101" t="inlineStr"/>
+      <c r="AA101" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC101" t="n">
         <v>0</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
       </c>
-      <c r="AE101" t="inlineStr"/>
+      <c r="AE101" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF101" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL101"/>
+  <dimension ref="A1:AL105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15900,6 +15900,618 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>15762</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PILAKA VINISHA REDDY</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>9505890135</v>
+      </c>
+      <c r="D102" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E102" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>06-Dec-2025 09:17:33</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P102" t="n">
+        <v>11000319490500</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1764992795</v>
+      </c>
+      <c r="R102" t="n">
+        <v>108703980088</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA102" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI102" t="n">
+        <v>18805</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>265779</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>15868</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MYLABATHULA MEDHANSH</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>9949134987</v>
+      </c>
+      <c r="D103" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E103" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>07-Dec-2025 21:32:51</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P103" t="n">
+        <v>11000319686064</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1765123332</v>
+      </c>
+      <c r="R103" t="n">
+        <v>213323909356</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA103" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI103" t="n">
+        <v>18624</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>265707</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>15533</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SHAIK FARHEEN</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>9652279329</v>
+      </c>
+      <c r="D104" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E104" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 15:32:58</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>09-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P104" t="n">
+        <v>11000319809148</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1765188111</v>
+      </c>
+      <c r="R104" t="n">
+        <v>108719254095</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA104" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI104" t="n">
+        <v>18907</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>265963</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>17179</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BORA LYDIA</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>6309196999</v>
+      </c>
+      <c r="D105" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E105" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 17:43:10</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>09-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P105" t="n">
+        <v>11000319830313</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1765195873</v>
+      </c>
+      <c r="R105" t="n">
+        <v>108720139585</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA105" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI105" t="n">
+        <v>19894</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>264985</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL105"/>
+  <dimension ref="A1:AL129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16512,6 +16512,3678 @@
       </c>
       <c r="AL105" t="inlineStr"/>
     </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>17146</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RONGALI JASMIKA</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>7793910192</v>
+      </c>
+      <c r="D106" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E106" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>12-Dec-2025 10:57:59</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P106" t="n">
+        <v>11000340117361</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1765517263</v>
+      </c>
+      <c r="R106" t="n">
+        <v>534655013098</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA106" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI106" t="n">
+        <v>19849</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>265097</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>17147</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>RONGALI YERNI VENKATA RAKESH</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>7793910192</v>
+      </c>
+      <c r="D107" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E107" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>12-Dec-2025 10:58:54</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P107" t="n">
+        <v>11000340117427</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1765517323</v>
+      </c>
+      <c r="R107" t="n">
+        <v>571217384715</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA107" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI107" t="n">
+        <v>19850</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>265556</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>17370</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>AKKURADA VARUN</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>8500847900</v>
+      </c>
+      <c r="D108" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E108" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>12-Dec-2025 15:19:14</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P108" t="n">
+        <v>11000340161581</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1765532834</v>
+      </c>
+      <c r="R108" t="n">
+        <v>108745991711</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA108" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI108" t="n">
+        <v>20089</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>268484</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>17336</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GOGALAMANDA ASHWIN</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>9133615133</v>
+      </c>
+      <c r="D109" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E109" t="n">
+        <v>10750</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>13-Dec-2025 10:25:13</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P109" t="n">
+        <v>11000340240544</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1765601703</v>
+      </c>
+      <c r="R109" t="n">
+        <v>790303117843</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA109" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI109" t="n">
+        <v>20064</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>266318</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>17367</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>EVAAN CHODAM</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>7995919129</v>
+      </c>
+      <c r="D110" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E110" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>13-Dec-2025 15:24:28</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P110" t="n">
+        <v>11000340278660</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1765619596</v>
+      </c>
+      <c r="R110" t="n">
+        <v>397896712035</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI110" t="n">
+        <v>20086</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>268470</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>16796</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MAHENDRA REDDY GUDLA</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>9948345552</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E111" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 11:57:08</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P111" t="n">
+        <v>11000340453923</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1765779979</v>
+      </c>
+      <c r="R111" t="n">
+        <v>231872222125</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA111" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI111" t="n">
+        <v>19010</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>266145</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>16797</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>YASHWANTH REDDY GUDLA</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>9948345552</v>
+      </c>
+      <c r="D112" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E112" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 11:58:00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>16-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O112" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P112" t="n">
+        <v>11000340456018</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1765780062</v>
+      </c>
+      <c r="R112" t="n">
+        <v>717946201991</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI112" t="n">
+        <v>18786</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>265832</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>16936</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HARIPRIYA RAVADA</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>6305148581</v>
+      </c>
+      <c r="D113" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E113" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>16-Dec-2025 12:06:31</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>17-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P113" t="n">
+        <v>11000340619866</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>1765866976</v>
+      </c>
+      <c r="R113" t="n">
+        <v>690206926885</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI113" t="n">
+        <v>18341</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>265338</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>16906</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RANVITHA SEERA</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>7095076706</v>
+      </c>
+      <c r="D114" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E114" t="n">
+        <v>10750</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>17-Dec-2025 12:40:11</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P114" t="n">
+        <v>11000340759102</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1765955387</v>
+      </c>
+      <c r="R114" t="n">
+        <v>794450161070</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA114" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI114" t="n">
+        <v>19168</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>266241</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>16937</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>VINAYAK KUMAR</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>7396170082</v>
+      </c>
+      <c r="D115" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E115" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>17-Dec-2025 19:39:33</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P115" t="n">
+        <v>11000340813371</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1765980521</v>
+      </c>
+      <c r="R115" t="n">
+        <v>108780945784</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA115" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI115" t="n">
+        <v>18292</v>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>265434</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>15621</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>KEERTHANA MUDDA</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>9573036376</v>
+      </c>
+      <c r="D116" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E116" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 12:09:57</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P116" t="n">
+        <v>11000340878141</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>1766039017</v>
+      </c>
+      <c r="R116" t="n">
+        <v>297705735742</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA116" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI116" t="n">
+        <v>19519</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>266531</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>16914</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SAI SRAVAN PATNAYAK</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>7337422112</v>
+      </c>
+      <c r="D117" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E117" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 17:07:06</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>19-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P117" t="n">
+        <v>11000340919232</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>1766057697</v>
+      </c>
+      <c r="R117" t="n">
+        <v>108787285351</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI117" t="n">
+        <v>18066</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>265129</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>16552</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>GANIREDDY ANUHYA</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>9848537189</v>
+      </c>
+      <c r="D118" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E118" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 20:31:47</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>19-Dec-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P118" t="n">
+        <v>11000340940536</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1766070034</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1.012025352350549e+17</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>BANK OF BARODA FSS</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA118" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI118" t="n">
+        <v>18375</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>265457</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>15824</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>GOLAGANI RITHIK NANDHAN</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>9393123464</v>
+      </c>
+      <c r="D119" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E119" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 07:37:12</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P119" t="n">
+        <v>11000342204411</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>1767145208</v>
+      </c>
+      <c r="R119" t="n">
+        <v>67115244586</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA119" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI119" t="n">
+        <v>18667</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>265672</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>17188</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>REYANA SRIJITH</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>9985925345</v>
+      </c>
+      <c r="D120" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E120" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 19:23:00</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P120" t="n">
+        <v>11000342307101</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1767189156</v>
+      </c>
+      <c r="R120" t="n">
+        <v>108881246730</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI120" t="n">
+        <v>19902</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>265340</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>16104</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>KARRI ABHINAY CHARVIK</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>9177965994</v>
+      </c>
+      <c r="D121" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E121" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 20:40:26</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P121" t="n">
+        <v>11000342315290</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>1767193550</v>
+      </c>
+      <c r="R121" t="n">
+        <v>108881815622</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA121" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI121" t="n">
+        <v>18807</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>267483</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>16974</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>KADAJARI ESHAN ESWAR</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>9885130099</v>
+      </c>
+      <c r="D122" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E122" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 09:00:50</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P122" t="n">
+        <v>11000342341005</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1767238144</v>
+      </c>
+      <c r="R122" t="n">
+        <v>108884026898</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA122" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI122" t="n">
+        <v>18273</v>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>265390</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>17219</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>VARTIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>8369239788</v>
+      </c>
+      <c r="D123" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E123" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 10:46:18</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P123" t="n">
+        <v>11000342354253</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1767244559</v>
+      </c>
+      <c r="R123" t="n">
+        <v>104639698103</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA123" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI123" t="n">
+        <v>19931</v>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>265205</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL123" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>17211</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CHENNA JAIKAR ABHIMANYU</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>8074712848</v>
+      </c>
+      <c r="D124" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E124" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 17:33:21</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>03-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P124" t="n">
+        <v>11000342590071</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1767355353</v>
+      </c>
+      <c r="R124" t="n">
+        <v>108896145112</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA124" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI124" t="n">
+        <v>19925</v>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>265220</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>17211</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CHENNA JAIKAR ABHIMANYU</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>8074712848</v>
+      </c>
+      <c r="D125" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E125" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 17:35:15</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>03-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P125" t="n">
+        <v>11000342590128</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1767355490</v>
+      </c>
+      <c r="R125" t="n">
+        <v>108896159648</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA125" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI125" t="n">
+        <v>19925</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>266870</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>17358</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SAANVI SAHOO</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>8309736856</v>
+      </c>
+      <c r="D126" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E126" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>03-Jan-2026 11:15:36</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>05-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P126" t="n">
+        <v>11000342680749</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>1767419107</v>
+      </c>
+      <c r="R126" t="n">
+        <v>600378887759</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA126" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI126" t="n">
+        <v>20077</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>268294</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>16507</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>POTNURU YELEENA</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>8374132397</v>
+      </c>
+      <c r="D127" t="n">
+        <v>15500</v>
+      </c>
+      <c r="E127" t="n">
+        <v>15500</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>07-Jan-2026 08:41:12</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>08-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fifteen thousand five hundred</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P127" t="n">
+        <v>11000343525514</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1767755445</v>
+      </c>
+      <c r="R127" t="n">
+        <v>279709918647</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA127" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI127" t="n">
+        <v>18352</v>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>265332,266982</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>2048,2056</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>16894</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SUGGI VENKATA SAI VISHNU VARDHAN</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>8500793683</v>
+      </c>
+      <c r="D128" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E128" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>07-Jan-2026 17:04:48</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P128" t="n">
+        <v>11000343669593</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1767785538</v>
+      </c>
+      <c r="R128" t="n">
+        <v>691063181825</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA128" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI128" t="n">
+        <v>19146</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>266163</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>17277</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EDUBILLI MAHASWIN</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>9618641662</v>
+      </c>
+      <c r="D129" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 09:21:38</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P129" t="n">
+        <v>11000344283491</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1768017067</v>
+      </c>
+      <c r="R129" t="n">
+        <v>108952003059</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="inlineStr"/>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI129" t="n">
+        <v>19988</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL129"/>
+  <dimension ref="A1:AL148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20059,13 +20059,19 @@
       <c r="D129" t="n">
         <v>6750</v>
       </c>
-      <c r="E129" t="inlineStr"/>
+      <c r="E129" t="n">
+        <v>6750</v>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
           <t>10-Jan-2026 09:21:38</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>12-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -20126,7 +20132,7 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
@@ -20149,15 +20155,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA129" t="inlineStr"/>
-      <c r="AB129" t="inlineStr"/>
+      <c r="AA129" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC129" t="n">
         <v>0</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
       </c>
-      <c r="AE129" t="inlineStr"/>
+      <c r="AE129" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF129" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -20183,6 +20195,2842 @@
         </is>
       </c>
       <c r="AL129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>17264</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SILUGURI CHIYAN ESHAN VARMA</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>8639375454</v>
+      </c>
+      <c r="D130" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E130" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 12:11:32</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>12-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P130" t="n">
+        <v>11000344351903</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>1768027227</v>
+      </c>
+      <c r="R130" t="n">
+        <v>108953138415</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA130" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI130" t="n">
+        <v>19975</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>265274</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>17264</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SILUGURI CHIYAN ESHAN VARMA</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>8639375454</v>
+      </c>
+      <c r="D131" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E131" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 12:14:02</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>12-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P131" t="n">
+        <v>11000344353254</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1768027340</v>
+      </c>
+      <c r="R131" t="n">
+        <v>108953157494</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA131" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI131" t="n">
+        <v>19975</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>266924</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>16686</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DWARAMPUDI BHUVAN REDDY</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>9505754523</v>
+      </c>
+      <c r="D132" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E132" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 08:07:08</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P132" t="n">
+        <v>11000345867539</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1768790106</v>
+      </c>
+      <c r="R132" t="n">
+        <v>109014543218</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA132" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr"/>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI132" t="n">
+        <v>18393</v>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>267111</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>17175</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DWARAMPUDI MOKSHITA</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>9505754523</v>
+      </c>
+      <c r="D133" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E133" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 08:09:06</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P133" t="n">
+        <v>11000345867589</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>1768790317</v>
+      </c>
+      <c r="R133" t="n">
+        <v>109014551659</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr"/>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI133" t="n">
+        <v>19890</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>266639</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>17316</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SUVVARI JAIDEEP</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>7386363690</v>
+      </c>
+      <c r="D134" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E134" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 10:57:18</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P134" t="n">
+        <v>11000345916088</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>1768799896</v>
+      </c>
+      <c r="R134" t="n">
+        <v>464738387430</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI134" t="n">
+        <v>20024</v>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>265253</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL134" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>16313</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>GANTEDA NIKHIL RAJ</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>9676361548</v>
+      </c>
+      <c r="D135" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E135" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 22:18:56</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P135" t="n">
+        <v>11000346179829</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>1768841237</v>
+      </c>
+      <c r="R135" t="n">
+        <v>899357782103</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA135" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr"/>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI135" t="n">
+        <v>19096</v>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>266126</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>16555</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>GANTEDA CHERISHMA</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>9676361548</v>
+      </c>
+      <c r="D136" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E136" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 17:50:43</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P136" t="n">
+        <v>11000346395565</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1768911627</v>
+      </c>
+      <c r="R136" t="n">
+        <v>306068999759</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA136" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr"/>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI136" t="n">
+        <v>18789</v>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>265752</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL136" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>17268</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SIMMA REGINA</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>9949129798</v>
+      </c>
+      <c r="D137" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E137" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 11:00:25</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P137" t="n">
+        <v>11000346525369</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>1768973323</v>
+      </c>
+      <c r="R137" t="n">
+        <v>655956291842</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr"/>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI137" t="n">
+        <v>19979</v>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>265502</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL137" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>15765</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AAROHI DASARI</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>9848982155</v>
+      </c>
+      <c r="D138" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E138" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 12:31:04</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P138" t="n">
+        <v>11000346568106</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1768978763</v>
+      </c>
+      <c r="R138" t="n">
+        <v>109029876457</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI138" t="n">
+        <v>19022</v>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>266033</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="AL138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>14706</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CHINTAPALLI CHATHAN SWAROOP</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>9985304942</v>
+      </c>
+      <c r="D139" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E139" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 07:56:13</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P139" t="n">
+        <v>11000346670581</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>1769048719</v>
+      </c>
+      <c r="R139" t="n">
+        <v>136130932845</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA139" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr"/>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI139" t="n">
+        <v>19397</v>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>266418</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL139" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>15618</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CHINTAPALLI CHANDINI</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>9985304942</v>
+      </c>
+      <c r="D140" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E140" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 08:14:26</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O140" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P140" t="n">
+        <v>11000346674063</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1769049843</v>
+      </c>
+      <c r="R140" t="n">
+        <v>632058461761</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr"/>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI140" t="n">
+        <v>18866</v>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>265897</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL140" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>16617</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>THANU SREE BHOOMIREDDY</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>9573771080</v>
+      </c>
+      <c r="D141" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E141" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 19:45:38</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P141" t="n">
+        <v>11000346806094</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>1769090880</v>
+      </c>
+      <c r="R141" t="n">
+        <v>109039770569</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr"/>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI141" t="n">
+        <v>18610</v>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>267230</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>15539</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>MUSKHAN KARRI</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>8019731551</v>
+      </c>
+      <c r="D142" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 06:50:59</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P142" t="n">
+        <v>11000346831268</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>1769131185</v>
+      </c>
+      <c r="R142" t="n">
+        <v>638921959953</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="inlineStr"/>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI142" t="n">
+        <v>18875</v>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>267563</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>17270</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SEERLA SURAJ SAI</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>9704836532</v>
+      </c>
+      <c r="D143" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 09:30:36</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P143" t="n">
+        <v>11000346844834</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1769140828</v>
+      </c>
+      <c r="R143" t="n">
+        <v>891843903115</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="inlineStr"/>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI143" t="n">
+        <v>19981</v>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>266915</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>16648</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TALACHINTALA SURYA NIMROD</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>9492203981</v>
+      </c>
+      <c r="D144" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 09:40:57</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O144" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P144" t="n">
+        <v>11000346846448</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>1769141317</v>
+      </c>
+      <c r="R144" t="n">
+        <v>109042639757</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="inlineStr"/>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr"/>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI144" t="n">
+        <v>18172</v>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>266904</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>14569</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PIRATI RISHIKESH VENKATA SAI</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>9985572139</v>
+      </c>
+      <c r="D145" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 10:47:03</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O145" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P145" t="n">
+        <v>11000346858020</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>1769145410</v>
+      </c>
+      <c r="R145" t="n">
+        <v>938830485824</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr"/>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="inlineStr"/>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI145" t="n">
+        <v>19505</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>266608</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>14741</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>JYOTHSNA PILAKA</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>9298052339</v>
+      </c>
+      <c r="D146" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 12:37:15</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P146" t="n">
+        <v>11000346874934</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>1769152013</v>
+      </c>
+      <c r="R146" t="n">
+        <v>744495867933</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI146" t="n">
+        <v>19518</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>266530</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>14319</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SARIPILLI JASWITH</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>7396346993</v>
+      </c>
+      <c r="D147" t="n">
+        <v>22700</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 12:56:31</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>twenty two thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P147" t="n">
+        <v>11000346878686</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>1769169337</v>
+      </c>
+      <c r="R147" t="n">
+        <v>250331567150</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI147" t="n">
+        <v>19498</v>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>266614,268264</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>2053,2061</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>14152</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>GUDLA YAMINI</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>7799277970</v>
+      </c>
+      <c r="D148" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 13:01:25</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O148" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P148" t="n">
+        <v>11000346879346</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>1769153340</v>
+      </c>
+      <c r="R148" t="n">
+        <v>109044037469</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="inlineStr"/>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr"/>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI148" t="n">
+        <v>19353</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>266388</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL148"/>
+  <dimension ref="A1:AL158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23032,6 +23032,1438 @@
       </c>
       <c r="AL148" t="inlineStr"/>
     </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>16496</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>MUTHABATHULA HANISHA</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>9553420014</v>
+      </c>
+      <c r="D149" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 08:45:20</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O149" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P149" t="n">
+        <v>11000346968551</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>1769224504</v>
+      </c>
+      <c r="R149" t="n">
+        <v>302212189815</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="inlineStr"/>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI149" t="n">
+        <v>19380</v>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>266406</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>16460</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>VANUMU TRINAYANI SATYA SRI</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>9885123477</v>
+      </c>
+      <c r="D150" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 08:54:46</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O150" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P150" t="n">
+        <v>11000346968962</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>1769225070</v>
+      </c>
+      <c r="R150" t="n">
+        <v>566245840665</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="inlineStr"/>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI150" t="n">
+        <v>19486</v>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>266548</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>16208</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>MYCHERLA SHASANK</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>7386344393</v>
+      </c>
+      <c r="D151" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 10:04:31</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P151" t="n">
+        <v>11000346977003</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>1769229258</v>
+      </c>
+      <c r="R151" t="n">
+        <v>348778801124</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="inlineStr"/>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI151" t="n">
+        <v>19412</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>266452</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>15253</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CHEBOLU ZANETA</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>9030174782</v>
+      </c>
+      <c r="D152" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 10:08:32</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O152" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P152" t="n">
+        <v>11000346977375</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>1769229450</v>
+      </c>
+      <c r="R152" t="n">
+        <v>697973343000</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="inlineStr"/>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI152" t="n">
+        <v>19356</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>266367</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>16844</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>THUPAKULA AARON RAJ GANGADHAR</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>9440076171</v>
+      </c>
+      <c r="D153" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 10:49:26</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O153" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P153" t="n">
+        <v>11000346985333</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>1769231939</v>
+      </c>
+      <c r="R153" t="n">
+        <v>953155834178</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="inlineStr"/>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI153" t="n">
+        <v>19487</v>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>266613</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>16955</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>TANYA KARNATI</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>9542378388</v>
+      </c>
+      <c r="D154" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 11:06:08</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P154" t="n">
+        <v>11000346988908</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>1769232802</v>
+      </c>
+      <c r="R154" t="n">
+        <v>109049853098</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr"/>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="inlineStr"/>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI154" t="n">
+        <v>18229</v>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>266951</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>14541</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>AKULA SIVA SURYA</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>9052828440</v>
+      </c>
+      <c r="D155" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 11:30:33</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O155" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P155" t="n">
+        <v>11000346993137</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>1769234416</v>
+      </c>
+      <c r="R155" t="n">
+        <v>432003362670</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="inlineStr"/>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI155" t="n">
+        <v>19459</v>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>266435</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>15952</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>AFREEN BEGUM</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>8099960677</v>
+      </c>
+      <c r="D156" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 12:25:49</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O156" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P156" t="n">
+        <v>11000347001524</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>1769237723</v>
+      </c>
+      <c r="R156" t="n">
+        <v>744362088782</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="inlineStr"/>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI156" t="n">
+        <v>19419</v>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>266365</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>14652</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>HEMANTH NAMMI</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>9502806409</v>
+      </c>
+      <c r="D157" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 13:21:28</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O157" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P157" t="n">
+        <v>11000347009869</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>1769240812</v>
+      </c>
+      <c r="R157" t="n">
+        <v>557427391390</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="inlineStr"/>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI157" t="n">
+        <v>19448</v>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>266450</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>17178</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>GUNIPE NIHARIKA</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>9966262514</v>
+      </c>
+      <c r="D158" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 16:27:44</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O158" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P158" t="n">
+        <v>11000347038757</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>1769251908</v>
+      </c>
+      <c r="R158" t="n">
+        <v>109052062295</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr"/>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="inlineStr"/>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI158" t="n">
+        <v>19893</v>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>266835</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL158" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,196 +413,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL158"/>
+  <dimension ref="A1:AL175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>admission_no</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>student_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>net_amount_to_be_paid</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>txn_date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>settlement_date</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>txn_status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>amount_in_rupees</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>customer_acc_no</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>merchant_name</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>merchant_id</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>client_code</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>atom_txn_id</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>merchant_txn_id</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>bank_ref_no</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>txn_type</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>bank_name</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>recon_status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>ifsc_code</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>merchant_type</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>discriminator</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>txn_charges</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>gst_18</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>sb_cess</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>krishi_kalyan_cess</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>total_chargeable</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>beneficiary_name</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>imps_status</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>settlement_type</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>udfex1</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>udfex2</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>udfex3</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>qr_transaction_type</t>
         </is>
@@ -22047,13 +22035,19 @@
       <c r="D142" t="n">
         <v>8350</v>
       </c>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="n">
+        <v>8350</v>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>23-Jan-2026 06:50:59</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -22114,7 +22108,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -22137,15 +22131,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA142" t="inlineStr"/>
-      <c r="AB142" t="inlineStr"/>
+      <c r="AA142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC142" t="n">
         <v>0</v>
       </c>
       <c r="AD142" t="n">
         <v>0</v>
       </c>
-      <c r="AE142" t="inlineStr"/>
+      <c r="AE142" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF142" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -22191,13 +22191,19 @@
       <c r="D143" t="n">
         <v>7750</v>
       </c>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="n">
+        <v>7750</v>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
           <t>23-Jan-2026 09:30:36</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -22258,7 +22264,7 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
@@ -22281,15 +22287,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA143" t="inlineStr"/>
-      <c r="AB143" t="inlineStr"/>
+      <c r="AA143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC143" t="n">
         <v>0</v>
       </c>
       <c r="AD143" t="n">
         <v>0</v>
       </c>
-      <c r="AE143" t="inlineStr"/>
+      <c r="AE143" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF143" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -22335,13 +22347,19 @@
       <c r="D144" t="n">
         <v>7750</v>
       </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="n">
+        <v>7750</v>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
           <t>23-Jan-2026 09:40:57</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -22402,7 +22420,7 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -22425,15 +22443,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA144" t="inlineStr"/>
-      <c r="AB144" t="inlineStr"/>
+      <c r="AA144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC144" t="n">
         <v>0</v>
       </c>
       <c r="AD144" t="n">
         <v>0</v>
       </c>
-      <c r="AE144" t="inlineStr"/>
+      <c r="AE144" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF144" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -22475,7 +22499,9 @@
       <c r="D145" t="n">
         <v>11350</v>
       </c>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="n">
+        <v>11350</v>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>23-Jan-2026 10:47:03</t>
@@ -22542,7 +22568,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
@@ -22565,15 +22591,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA145" t="inlineStr"/>
-      <c r="AB145" t="inlineStr"/>
+      <c r="AA145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC145" t="n">
         <v>0</v>
       </c>
       <c r="AD145" t="n">
         <v>0</v>
       </c>
-      <c r="AE145" t="inlineStr"/>
+      <c r="AE145" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF145" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -22619,7 +22651,9 @@
       <c r="D146" t="n">
         <v>11350</v>
       </c>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="n">
+        <v>11350</v>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>23-Jan-2026 12:37:15</t>
@@ -22686,7 +22720,7 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -22709,15 +22743,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA146" t="inlineStr"/>
-      <c r="AB146" t="inlineStr"/>
+      <c r="AA146" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC146" t="n">
         <v>0</v>
       </c>
       <c r="AD146" t="n">
         <v>0</v>
       </c>
-      <c r="AE146" t="inlineStr"/>
+      <c r="AE146" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF146" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -22763,7 +22803,9 @@
       <c r="D147" t="n">
         <v>22700</v>
       </c>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="n">
+        <v>22700</v>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>23-Jan-2026 12:56:31</t>
@@ -22830,7 +22872,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -22853,15 +22895,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA147" t="inlineStr"/>
-      <c r="AB147" t="inlineStr"/>
+      <c r="AA147" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC147" t="n">
         <v>0</v>
       </c>
       <c r="AD147" t="n">
         <v>0</v>
       </c>
-      <c r="AE147" t="inlineStr"/>
+      <c r="AE147" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF147" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -22907,7 +22955,9 @@
       <c r="D148" t="n">
         <v>11350</v>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="n">
+        <v>11350</v>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>23-Jan-2026 13:01:25</t>
@@ -22974,7 +23024,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
@@ -22997,15 +23047,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA148" t="inlineStr"/>
-      <c r="AB148" t="inlineStr"/>
+      <c r="AA148" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC148" t="n">
         <v>0</v>
       </c>
       <c r="AD148" t="n">
         <v>0</v>
       </c>
-      <c r="AE148" t="inlineStr"/>
+      <c r="AE148" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF148" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -23047,7 +23103,9 @@
       <c r="D149" t="n">
         <v>11350</v>
       </c>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="n">
+        <v>11350</v>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>24-Jan-2026 08:45:20</t>
@@ -23114,7 +23172,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -23137,15 +23195,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA149" t="inlineStr"/>
-      <c r="AB149" t="inlineStr"/>
+      <c r="AA149" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC149" t="n">
         <v>0</v>
       </c>
       <c r="AD149" t="n">
         <v>0</v>
       </c>
-      <c r="AE149" t="inlineStr"/>
+      <c r="AE149" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF149" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -23191,7 +23255,9 @@
       <c r="D150" t="n">
         <v>11350</v>
       </c>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="n">
+        <v>11350</v>
+      </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>24-Jan-2026 08:54:46</t>
@@ -23258,7 +23324,7 @@
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
@@ -23281,15 +23347,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA150" t="inlineStr"/>
-      <c r="AB150" t="inlineStr"/>
+      <c r="AA150" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC150" t="n">
         <v>0</v>
       </c>
       <c r="AD150" t="n">
         <v>0</v>
       </c>
-      <c r="AE150" t="inlineStr"/>
+      <c r="AE150" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF150" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -23335,7 +23407,9 @@
       <c r="D151" t="n">
         <v>11350</v>
       </c>
-      <c r="E151" t="inlineStr"/>
+      <c r="E151" t="n">
+        <v>11350</v>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>24-Jan-2026 10:04:31</t>
@@ -23402,7 +23476,7 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
@@ -23425,15 +23499,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA151" t="inlineStr"/>
-      <c r="AB151" t="inlineStr"/>
+      <c r="AA151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC151" t="n">
         <v>0</v>
       </c>
       <c r="AD151" t="n">
         <v>0</v>
       </c>
-      <c r="AE151" t="inlineStr"/>
+      <c r="AE151" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF151" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -23479,7 +23559,9 @@
       <c r="D152" t="n">
         <v>11350</v>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="n">
+        <v>11350</v>
+      </c>
       <c r="F152" t="inlineStr">
         <is>
           <t>24-Jan-2026 10:08:32</t>
@@ -23546,7 +23628,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
@@ -23569,15 +23651,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA152" t="inlineStr"/>
-      <c r="AB152" t="inlineStr"/>
+      <c r="AA152" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC152" t="n">
         <v>0</v>
       </c>
       <c r="AD152" t="n">
         <v>0</v>
       </c>
-      <c r="AE152" t="inlineStr"/>
+      <c r="AE152" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF152" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -23623,7 +23711,9 @@
       <c r="D153" t="n">
         <v>11350</v>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="n">
+        <v>11350</v>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>24-Jan-2026 10:49:26</t>
@@ -23690,7 +23780,7 @@
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
@@ -23713,15 +23803,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA153" t="inlineStr"/>
-      <c r="AB153" t="inlineStr"/>
+      <c r="AA153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC153" t="n">
         <v>0</v>
       </c>
       <c r="AD153" t="n">
         <v>0</v>
       </c>
-      <c r="AE153" t="inlineStr"/>
+      <c r="AE153" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF153" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -23767,13 +23863,19 @@
       <c r="D154" t="n">
         <v>7750</v>
       </c>
-      <c r="E154" t="inlineStr"/>
+      <c r="E154" t="n">
+        <v>7750</v>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>24-Jan-2026 11:06:08</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H154" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -23834,7 +23936,7 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
@@ -23857,15 +23959,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA154" t="inlineStr"/>
-      <c r="AB154" t="inlineStr"/>
+      <c r="AA154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC154" t="n">
         <v>0</v>
       </c>
       <c r="AD154" t="n">
         <v>0</v>
       </c>
-      <c r="AE154" t="inlineStr"/>
+      <c r="AE154" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF154" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -23907,7 +24015,9 @@
       <c r="D155" t="n">
         <v>11350</v>
       </c>
-      <c r="E155" t="inlineStr"/>
+      <c r="E155" t="n">
+        <v>11350</v>
+      </c>
       <c r="F155" t="inlineStr">
         <is>
           <t>24-Jan-2026 11:30:33</t>
@@ -23974,7 +24084,7 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
@@ -23997,15 +24107,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA155" t="inlineStr"/>
-      <c r="AB155" t="inlineStr"/>
+      <c r="AA155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC155" t="n">
         <v>0</v>
       </c>
       <c r="AD155" t="n">
         <v>0</v>
       </c>
-      <c r="AE155" t="inlineStr"/>
+      <c r="AE155" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF155" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -24051,7 +24167,9 @@
       <c r="D156" t="n">
         <v>11350</v>
       </c>
-      <c r="E156" t="inlineStr"/>
+      <c r="E156" t="n">
+        <v>11350</v>
+      </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>24-Jan-2026 12:25:49</t>
@@ -24118,7 +24236,7 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
@@ -24141,15 +24259,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA156" t="inlineStr"/>
-      <c r="AB156" t="inlineStr"/>
+      <c r="AA156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC156" t="n">
         <v>0</v>
       </c>
       <c r="AD156" t="n">
         <v>0</v>
       </c>
-      <c r="AE156" t="inlineStr"/>
+      <c r="AE156" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF156" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -24195,7 +24319,9 @@
       <c r="D157" t="n">
         <v>11350</v>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="n">
+        <v>11350</v>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
           <t>24-Jan-2026 13:21:28</t>
@@ -24262,7 +24388,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -24285,15 +24411,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA157" t="inlineStr"/>
-      <c r="AB157" t="inlineStr"/>
+      <c r="AA157" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC157" t="n">
         <v>0</v>
       </c>
       <c r="AD157" t="n">
         <v>0</v>
       </c>
-      <c r="AE157" t="inlineStr"/>
+      <c r="AE157" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF157" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -24339,13 +24471,19 @@
       <c r="D158" t="n">
         <v>7750</v>
       </c>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="n">
+        <v>7750</v>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>24-Jan-2026 16:27:44</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -24406,7 +24544,7 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
@@ -24429,15 +24567,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA158" t="inlineStr"/>
-      <c r="AB158" t="inlineStr"/>
+      <c r="AA158" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC158" t="n">
         <v>0</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
       </c>
-      <c r="AE158" t="inlineStr"/>
+      <c r="AE158" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF158" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -24463,6 +24607,2570 @@
         </is>
       </c>
       <c r="AL158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>17163</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ZAYN KHAN</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>8210638795</v>
+      </c>
+      <c r="D159" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E159" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>25-Jan-2026 21:28:07</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O159" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P159" t="n">
+        <v>11000347140427</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>1769356585</v>
+      </c>
+      <c r="R159" t="n">
+        <v>109060546215</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI159" t="n">
+        <v>19878</v>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>265043</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>14872</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PEETHALA V V SAMPATH KRISHNA</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>8897052499</v>
+      </c>
+      <c r="D160" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E160" t="n">
+        <v>10750</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>26-Jan-2026 09:50:19</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O160" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P160" t="n">
+        <v>11000347158162</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>1769401204</v>
+      </c>
+      <c r="R160" t="n">
+        <v>322203571426</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI160" t="n">
+        <v>19238</v>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>266325</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>17164</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SHAIK REHAN SIDDIQUE</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>7569535771</v>
+      </c>
+      <c r="D161" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E161" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>26-Jan-2026 13:21:48</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O161" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P161" t="n">
+        <v>11000347183204</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>1769413872</v>
+      </c>
+      <c r="R161" t="n">
+        <v>109063896797</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI161" t="n">
+        <v>19879</v>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>266789</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>15457</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SHAIK SHAISTA REHMAN</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>8686282343</v>
+      </c>
+      <c r="D162" t="n">
+        <v>43100</v>
+      </c>
+      <c r="E162" t="n">
+        <v>43100</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>26-Jan-2026 15:03:09</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>forty three thousand one hundred</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O162" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P162" t="n">
+        <v>11000347191020</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>1769419950</v>
+      </c>
+      <c r="R162" t="n">
+        <v>150333137683</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI162" t="n">
+        <v>19481</v>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>251562,249074,249075,249076,261922</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>2011,2010,2010,2010,2036</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>15319</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SHAIK UZAIR REHMAN</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>8686282343</v>
+      </c>
+      <c r="D163" t="n">
+        <v>41950</v>
+      </c>
+      <c r="E163" t="n">
+        <v>41950</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>26-Jan-2026 15:07:24</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>forty one thousand nine hundred fifty</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O163" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P163" t="n">
+        <v>11000347191159</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>1769420222</v>
+      </c>
+      <c r="R163" t="n">
+        <v>150742538694</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>IFSC0000000</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI163" t="n">
+        <v>19413</v>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>251492,248794,248795,248796,261845,263317</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>2011,2009,2009,2009,2036,2037</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>14160</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>DHARMAVARAPU CHANDANA RAMYA</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>8374970989</v>
+      </c>
+      <c r="D164" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E164" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 07:55:26</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O164" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P164" t="n">
+        <v>11000347256104</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>1769480567</v>
+      </c>
+      <c r="R164" t="n">
+        <v>109068599127</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI164" t="n">
+        <v>19571</v>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>266491</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>14511</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>DHARMAVARAPU MADHULICA SRI</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>8374970989</v>
+      </c>
+      <c r="D165" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E165" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 08:01:20</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P165" t="n">
+        <v>11000347257195</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>1769480830</v>
+      </c>
+      <c r="R165" t="n">
+        <v>109068627803</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA165" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI165" t="n">
+        <v>19336</v>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>266371</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>16307</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PANIGRAHI PRAVEEN KUMAR</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>9848817272</v>
+      </c>
+      <c r="D166" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E166" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 10:05:54</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O166" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P166" t="n">
+        <v>11000347300849</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>1769488542</v>
+      </c>
+      <c r="R166" t="n">
+        <v>357434084064</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI166" t="n">
+        <v>18587</v>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>265706</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL166" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>14942</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>BHARAT PURNA VENKATA SAI PANIGRAHI</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>9848817272</v>
+      </c>
+      <c r="D167" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E167" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 10:04:33</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O167" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P167" t="n">
+        <v>11000347302220</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>1769488424</v>
+      </c>
+      <c r="R167" t="n">
+        <v>361152503768</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA167" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI167" t="n">
+        <v>19492</v>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>266571</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>14830</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PADAMATA HEMANTH</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>9866835075</v>
+      </c>
+      <c r="D168" t="n">
+        <v>22700</v>
+      </c>
+      <c r="E168" t="n">
+        <v>22700</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 10:26:25</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>twenty two thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O168" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P168" t="n">
+        <v>11000347306175</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>1769489743</v>
+      </c>
+      <c r="R168" t="n">
+        <v>903036563145</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA168" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI168" t="n">
+        <v>19604</v>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>266596,268246</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>2053,2061</t>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>16196</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BOTTA V K SAMTHOSHI VARSHITHA</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>9059927162</v>
+      </c>
+      <c r="D169" t="n">
+        <v>22700</v>
+      </c>
+      <c r="E169" t="n">
+        <v>22700</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 12:00:01</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>twenty two thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O169" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P169" t="n">
+        <v>11000347328943</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>1769495251</v>
+      </c>
+      <c r="R169" t="n">
+        <v>602755092306</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI169" t="n">
+        <v>19597</v>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>264839,266489</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>2045,2053</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>14285</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>JENITH HARSHAVARDHAN BOORILA</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>9550770629</v>
+      </c>
+      <c r="D170" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E170" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 11:59:29</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O170" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P170" t="n">
+        <v>11000347330343</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>1769495348</v>
+      </c>
+      <c r="R170" t="n">
+        <v>30769157583</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr"/>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI170" t="n">
+        <v>19608</v>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>266570</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>16721</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>KURMAPU GAGANASHREE</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>9908361635</v>
+      </c>
+      <c r="D171" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E171" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 12:20:26</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O171" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P171" t="n">
+        <v>11000347341033</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>1769494988</v>
+      </c>
+      <c r="R171" t="n">
+        <v>109070353121</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA171" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr"/>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI171" t="n">
+        <v>18114</v>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>265174</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="AL171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>15823</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>KURMAPU HARINI</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>9908361635</v>
+      </c>
+      <c r="D172" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E172" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 12:34:33</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O172" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P172" t="n">
+        <v>11000347342741</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>1769496975</v>
+      </c>
+      <c r="R172" t="n">
+        <v>109070450811</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA172" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr"/>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI172" t="n">
+        <v>18720</v>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>265773</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>17069</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>GUNTURU VIDYA SRI</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>8885883431</v>
+      </c>
+      <c r="D173" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E173" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 14:58:44</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O173" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P173" t="n">
+        <v>11000347375496</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>1769506096</v>
+      </c>
+      <c r="R173" t="n">
+        <v>900078911921</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA173" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr"/>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI173" t="n">
+        <v>18960</v>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>265927</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>15027</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>KORRAI ROHITH</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>9959370022</v>
+      </c>
+      <c r="D174" t="n">
+        <v>22700</v>
+      </c>
+      <c r="E174" t="n">
+        <v>22700</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 14:55:59</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>twenty two thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O174" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P174" t="n">
+        <v>11000347376357</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>1769505935</v>
+      </c>
+      <c r="R174" t="n">
+        <v>58982183299</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr"/>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI174" t="n">
+        <v>19551</v>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>266582,268232</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>2053,2061</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>17197</v>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="n">
+        <v>9881234227</v>
+      </c>
+      <c r="D175" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 13:17:23</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O175" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P175" t="n">
+        <v>11000347530516</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>1769586348</v>
+      </c>
+      <c r="R175" t="n">
+        <v>109077387932</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr"/>
+      <c r="AB175" t="inlineStr"/>
+      <c r="AC175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="inlineStr"/>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI175" t="n">
+        <v>19911</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>266720</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>2055</v>
+      </c>
+      <c r="AL175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL175"/>
+  <dimension ref="A1:AL184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27051,13 +27051,19 @@
       <c r="D175" t="n">
         <v>6750</v>
       </c>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="n">
+        <v>6750</v>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>28-Jan-2026 13:17:23</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -27118,7 +27124,7 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
@@ -27141,15 +27147,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA175" t="inlineStr"/>
-      <c r="AB175" t="inlineStr"/>
+      <c r="AA175" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC175" t="n">
         <v>0</v>
       </c>
       <c r="AD175" t="n">
         <v>0</v>
       </c>
-      <c r="AE175" t="inlineStr"/>
+      <c r="AE175" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF175" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -27164,13 +27176,1325 @@
       <c r="AI175" t="n">
         <v>19911</v>
       </c>
-      <c r="AJ175" t="n">
-        <v>266720</v>
-      </c>
-      <c r="AK175" t="n">
-        <v>2055</v>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>266720</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
       </c>
       <c r="AL175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>15025</v>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="n">
+        <v>6300436983</v>
+      </c>
+      <c r="D176" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E176" t="n">
+        <v>10750</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 22:57:16</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O176" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P176" t="n">
+        <v>11000347614077</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>1769621069</v>
+      </c>
+      <c r="R176" t="n">
+        <v>109080979496</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA176" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr"/>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI176" t="n">
+        <v>19264</v>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>266312</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>14179</v>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="n">
+        <v>22700</v>
+      </c>
+      <c r="E177" t="n">
+        <v>22700</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 23:22:31</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>twenty two thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O177" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P177" t="n">
+        <v>11000347616233</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>1769622527</v>
+      </c>
+      <c r="R177" t="n">
+        <v>232254793834</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA177" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI177" t="n">
+        <v>19590</v>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>264853,266503</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>2045,2053</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>15938</v>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="n">
+        <v>9959307771</v>
+      </c>
+      <c r="D178" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E178" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 02:05:03</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O178" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P178" t="n">
+        <v>11000347619670</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>1769632447</v>
+      </c>
+      <c r="R178" t="n">
+        <v>109081256624</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA178" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI178" t="n">
+        <v>18863</v>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>267586</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>15237</v>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E179" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 08:02:15</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P179" t="n">
+        <v>11000347624524</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>1769653866</v>
+      </c>
+      <c r="R179" t="n">
+        <v>109082072826</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr"/>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI179" t="n">
+        <v>18984</v>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>266061</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>16148</v>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="n">
+        <v>9573851290</v>
+      </c>
+      <c r="D180" t="n">
+        <v>24650</v>
+      </c>
+      <c r="E180" t="n">
+        <v>24650</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 11:43:37</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>twenty four thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O180" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P180" t="n">
+        <v>11000347665261</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>1769667026</v>
+      </c>
+      <c r="R180" t="n">
+        <v>109083484020</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA180" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr"/>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI180" t="n">
+        <v>18502</v>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>262506,263894,265544,267194</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>2037,2041,2049,2057</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>16147</v>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="n">
+        <v>9573851290</v>
+      </c>
+      <c r="D181" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E181" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 11:48:21</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O181" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P181" t="n">
+        <v>11000347667143</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>1769667469</v>
+      </c>
+      <c r="R181" t="n">
+        <v>109083513527</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI181" t="n">
+        <v>18767</v>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>267440</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>17210</v>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="n">
+        <v>8985833952</v>
+      </c>
+      <c r="D182" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E182" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 18:54:47</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O182" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P182" t="n">
+        <v>11000347735867</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>1769693071</v>
+      </c>
+      <c r="R182" t="n">
+        <v>639543409302</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA182" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr"/>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI182" t="n">
+        <v>19924</v>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>266780</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>17370</v>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="n">
+        <v>8500847900</v>
+      </c>
+      <c r="D183" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 10:20:21</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O183" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P183" t="n">
+        <v>11000347805222</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>1769748539</v>
+      </c>
+      <c r="R183" t="n">
+        <v>782823183812</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr"/>
+      <c r="AB183" t="inlineStr"/>
+      <c r="AC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="inlineStr"/>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr"/>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI183" t="n">
+        <v>20089</v>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>268485</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>17061</v>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="n">
+        <v>9701751097</v>
+      </c>
+      <c r="D184" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 22:49:30</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O184" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P184" t="n">
+        <v>11000347945459</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>1769793554</v>
+      </c>
+      <c r="R184" t="n">
+        <v>603044734989</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="inlineStr"/>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr"/>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI184" t="n">
+        <v>19153</v>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>266251</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL184"/>
+  <dimension ref="A1:AL186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28227,7 +28227,9 @@
       <c r="D183" t="n">
         <v>8050</v>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="n">
+        <v>8050</v>
+      </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>30-Jan-2026 10:20:21</t>
@@ -28294,7 +28296,7 @@
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
@@ -28317,15 +28319,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA183" t="inlineStr"/>
-      <c r="AB183" t="inlineStr"/>
+      <c r="AA183" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC183" t="n">
         <v>0</v>
       </c>
       <c r="AD183" t="n">
         <v>0</v>
       </c>
-      <c r="AE183" t="inlineStr"/>
+      <c r="AE183" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF183" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -28367,7 +28375,9 @@
       <c r="D184" t="n">
         <v>10750</v>
       </c>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="n">
+        <v>10750</v>
+      </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>30-Jan-2026 22:49:30</t>
@@ -28434,7 +28444,7 @@
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
@@ -28457,15 +28467,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA184" t="inlineStr"/>
-      <c r="AB184" t="inlineStr"/>
+      <c r="AA184" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC184" t="n">
         <v>0</v>
       </c>
       <c r="AD184" t="n">
         <v>0</v>
       </c>
-      <c r="AE184" t="inlineStr"/>
+      <c r="AE184" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF184" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -28491,6 +28507,282 @@
         </is>
       </c>
       <c r="AL184" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>16937</v>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="n">
+        <v>7396170082</v>
+      </c>
+      <c r="D185" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 11:39:53</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O185" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P185" t="n">
+        <v>11000347994515</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>1769839734</v>
+      </c>
+      <c r="R185" t="n">
+        <v>109096550984</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr"/>
+      <c r="AB185" t="inlineStr"/>
+      <c r="AC185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="inlineStr"/>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI185" t="n">
+        <v>18292</v>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>267084</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>17295</v>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="n">
+        <v>9676727222</v>
+      </c>
+      <c r="D186" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 12:22:53</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O186" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P186" t="n">
+        <v>11000348002801</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>1769842304</v>
+      </c>
+      <c r="R186" t="n">
+        <v>603137988475</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="inlineStr"/>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr"/>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI186" t="n">
+        <v>20005</v>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>266695</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL186"/>
+  <dimension ref="A1:AL200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28235,7 +28235,11 @@
           <t>30-Jan-2026 10:20:21</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H183" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -28296,7 +28300,7 @@
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
@@ -28523,13 +28527,19 @@
       <c r="D185" t="n">
         <v>7750</v>
       </c>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="n">
+        <v>7750</v>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
           <t>31-Jan-2026 11:39:53</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H185" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -28590,7 +28600,7 @@
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
@@ -28613,15 +28623,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA185" t="inlineStr"/>
-      <c r="AB185" t="inlineStr"/>
+      <c r="AA185" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC185" t="n">
         <v>0</v>
       </c>
       <c r="AD185" t="n">
         <v>0</v>
       </c>
-      <c r="AE185" t="inlineStr"/>
+      <c r="AE185" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF185" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -28659,13 +28675,19 @@
       <c r="D186" t="n">
         <v>6750</v>
       </c>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="n">
+        <v>6750</v>
+      </c>
       <c r="F186" t="inlineStr">
         <is>
           <t>31-Jan-2026 12:22:53</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -28726,7 +28748,7 @@
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
@@ -28749,15 +28771,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA186" t="inlineStr"/>
-      <c r="AB186" t="inlineStr"/>
+      <c r="AA186" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC186" t="n">
         <v>0</v>
       </c>
       <c r="AD186" t="n">
         <v>0</v>
       </c>
-      <c r="AE186" t="inlineStr"/>
+      <c r="AE186" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF186" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -28783,6 +28811,2062 @@
         </is>
       </c>
       <c r="AL186" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>16975</v>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="n">
+        <v>9582803185</v>
+      </c>
+      <c r="D187" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E187" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 18:13:43</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O187" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P187" t="n">
+        <v>11000348058030</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>1769863383</v>
+      </c>
+      <c r="R187" t="n">
+        <v>109099158804</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA187" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr"/>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI187" t="n">
+        <v>18689</v>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>267419</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>17203</v>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="n">
+        <v>9582803185</v>
+      </c>
+      <c r="D188" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E188" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 18:17:11</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O188" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P188" t="n">
+        <v>11000348058210</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>1769863602</v>
+      </c>
+      <c r="R188" t="n">
+        <v>109099182132</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA188" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr"/>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI188" t="n">
+        <v>19917</v>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>267156</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>15610</v>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="n">
+        <v>9494128377</v>
+      </c>
+      <c r="D189" t="n">
+        <v>17200</v>
+      </c>
+      <c r="E189" t="n">
+        <v>17200</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 21:10:07</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>seventeen thousand two hundred</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O189" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P189" t="n">
+        <v>11000348075456</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>1769873832</v>
+      </c>
+      <c r="R189" t="n">
+        <v>211520585120</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA189" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr"/>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI189" t="n">
+        <v>18708</v>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>262434,264169,265819</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>2037,2042,2050</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>17299</v>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="n">
+        <v>9959734686</v>
+      </c>
+      <c r="D190" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E190" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 22:18:47</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O190" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P190" t="n">
+        <v>11000348084444</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>1769878103</v>
+      </c>
+      <c r="R190" t="n">
+        <v>261849315319</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA190" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr"/>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI190" t="n">
+        <v>20008</v>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>263349</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>15237</v>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="n">
+        <v>6300436983</v>
+      </c>
+      <c r="D191" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E191" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 10:10:12</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O191" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P191" t="n">
+        <v>11000348259685</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>1770007167</v>
+      </c>
+      <c r="R191" t="n">
+        <v>109110162417</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr"/>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI191" t="n">
+        <v>18984</v>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>268309</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>15025</v>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="n">
+        <v>6300436983</v>
+      </c>
+      <c r="D192" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E192" t="n">
+        <v>10750</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 10:11:47</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O192" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P192" t="n">
+        <v>11000348259812</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>1770007283</v>
+      </c>
+      <c r="R192" t="n">
+        <v>109110173919</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA192" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr"/>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI192" t="n">
+        <v>19264</v>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>268649</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>17103</v>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="n">
+        <v>6301729629</v>
+      </c>
+      <c r="D193" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E193" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 11:03:20</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O193" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P193" t="n">
+        <v>11000348272865</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>1770010319</v>
+      </c>
+      <c r="R193" t="n">
+        <v>109110496570</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA193" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr"/>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI193" t="n">
+        <v>18038</v>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>265086</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>17278</v>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="n">
+        <v>9030736744</v>
+      </c>
+      <c r="D194" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E194" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 12:37:32</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O194" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P194" t="n">
+        <v>11000348296762</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>1770015969</v>
+      </c>
+      <c r="R194" t="n">
+        <v>603396699255</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA194" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr"/>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI194" t="n">
+        <v>19989</v>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>266791</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>16983</v>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="n">
+        <v>8919560551</v>
+      </c>
+      <c r="D195" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E195" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 12:51:55</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O195" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P195" t="n">
+        <v>11000348300433</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>1770016889</v>
+      </c>
+      <c r="R195" t="n">
+        <v>109111170783</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA195" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI195" t="n">
+        <v>18526</v>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>265609</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>16983</v>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="n">
+        <v>8919560551</v>
+      </c>
+      <c r="D196" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E196" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 15:01:40</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O196" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P196" t="n">
+        <v>11000348327211</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>1770024680</v>
+      </c>
+      <c r="R196" t="n">
+        <v>109112112619</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA196" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr"/>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI196" t="n">
+        <v>18526</v>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>267259</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>16981</v>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="n">
+        <v>8919560551</v>
+      </c>
+      <c r="D197" t="n">
+        <v>15500</v>
+      </c>
+      <c r="E197" t="n">
+        <v>15500</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 15:03:03</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>fifteen thousand five hundred</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O197" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P197" t="n">
+        <v>11000348327327</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>1770024758</v>
+      </c>
+      <c r="R197" t="n">
+        <v>109112123447</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA197" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr"/>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI197" t="n">
+        <v>18142</v>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>265260,266910</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>2048,2056</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>16046</v>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="n">
+        <v>9177919989</v>
+      </c>
+      <c r="D198" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E198" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 18:47:03</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O198" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P198" t="n">
+        <v>11000348365273</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>1770038166</v>
+      </c>
+      <c r="R198" t="n">
+        <v>109113635360</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA198" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr"/>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI198" t="n">
+        <v>18940</v>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>267616</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>17149</v>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="n">
+        <v>9989075944</v>
+      </c>
+      <c r="D199" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 12:28:23</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O199" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P199" t="n">
+        <v>11000348471340</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>1770101732</v>
+      </c>
+      <c r="R199" t="n">
+        <v>109118392390</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="inlineStr"/>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI199" t="n">
+        <v>19852</v>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>266040</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="AL199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>16992</v>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="n">
+        <v>7207505036</v>
+      </c>
+      <c r="D200" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 20:53:32</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O200" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P200" t="n">
+        <v>11000348551835</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>1770132067</v>
+      </c>
+      <c r="R200" t="n">
+        <v>337099556372</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="inlineStr"/>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr"/>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI200" t="n">
+        <v>18360</v>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>267018</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL200"/>
+  <dimension ref="A1:AL204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30607,7 +30607,9 @@
       <c r="D199" t="n">
         <v>8650</v>
       </c>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="n">
+        <v>8650</v>
+      </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>03-Feb-2026 12:28:23</t>
@@ -30674,7 +30676,7 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
@@ -30697,15 +30699,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA199" t="inlineStr"/>
-      <c r="AB199" t="inlineStr"/>
+      <c r="AA199" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC199" t="n">
         <v>0</v>
       </c>
       <c r="AD199" t="n">
         <v>0</v>
       </c>
-      <c r="AE199" t="inlineStr"/>
+      <c r="AE199" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF199" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
@@ -30743,13 +30751,19 @@
       <c r="D200" t="n">
         <v>7750</v>
       </c>
-      <c r="E200" t="inlineStr"/>
+      <c r="E200" t="n">
+        <v>7750</v>
+      </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>03-Feb-2026 20:53:32</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H200" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -30810,7 +30824,7 @@
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
@@ -30833,15 +30847,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA200" t="inlineStr"/>
-      <c r="AB200" t="inlineStr"/>
+      <c r="AA200" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC200" t="n">
         <v>0</v>
       </c>
       <c r="AD200" t="n">
         <v>0</v>
       </c>
-      <c r="AE200" t="inlineStr"/>
+      <c r="AE200" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF200" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -30871,6 +30891,558 @@
           <t>UPI INTENT</t>
         </is>
       </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>17307</v>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="n">
+        <v>9991367333</v>
+      </c>
+      <c r="D201" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 07:05:09</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O201" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P201" t="n">
+        <v>11000348575099</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>1770168829</v>
+      </c>
+      <c r="R201" t="n">
+        <v>109123051045</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="inlineStr"/>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr"/>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI201" t="n">
+        <v>20016</v>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>267480</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>17069</v>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="n">
+        <v>8885883431</v>
+      </c>
+      <c r="D202" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 09:56:04</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O202" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P202" t="n">
+        <v>11000348596178</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>1770179127</v>
+      </c>
+      <c r="R202" t="n">
+        <v>496896024593</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="inlineStr"/>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr"/>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI202" t="n">
+        <v>18960</v>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>267577</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>15728</v>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="n">
+        <v>7893025312</v>
+      </c>
+      <c r="D203" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 10:05:07</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O203" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P203" t="n">
+        <v>11000348597736</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>1770179690</v>
+      </c>
+      <c r="R203" t="n">
+        <v>230527479236</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="inlineStr"/>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr"/>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI203" t="n">
+        <v>19462</v>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>268164</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>15541</v>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="n">
+        <v>9849969449</v>
+      </c>
+      <c r="D204" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 23:05:27</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O204" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P204" t="n">
+        <v>11000348724700</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>1770226187</v>
+      </c>
+      <c r="R204" t="n">
+        <v>109128651847</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="inlineStr"/>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr"/>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI204" t="n">
+        <v>18766</v>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>265813</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -30903,13 +30903,19 @@
       <c r="D201" t="n">
         <v>8350</v>
       </c>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="n">
+        <v>8350</v>
+      </c>
       <c r="F201" t="inlineStr">
         <is>
           <t>04-Feb-2026 07:05:09</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>05-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H201" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -30970,7 +30976,7 @@
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
@@ -30993,15 +30999,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA201" t="inlineStr"/>
-      <c r="AB201" t="inlineStr"/>
+      <c r="AA201" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC201" t="n">
         <v>0</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
       </c>
-      <c r="AE201" t="inlineStr"/>
+      <c r="AE201" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF201" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -31039,13 +31051,19 @@
       <c r="D202" t="n">
         <v>8350</v>
       </c>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="n">
+        <v>8350</v>
+      </c>
       <c r="F202" t="inlineStr">
         <is>
           <t>04-Feb-2026 09:56:04</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>05-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H202" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -31106,7 +31124,7 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
@@ -31129,15 +31147,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA202" t="inlineStr"/>
-      <c r="AB202" t="inlineStr"/>
+      <c r="AA202" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC202" t="n">
         <v>0</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
       </c>
-      <c r="AE202" t="inlineStr"/>
+      <c r="AE202" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF202" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -31179,7 +31203,9 @@
       <c r="D203" t="n">
         <v>11350</v>
       </c>
-      <c r="E203" t="inlineStr"/>
+      <c r="E203" t="n">
+        <v>11350</v>
+      </c>
       <c r="F203" t="inlineStr">
         <is>
           <t>04-Feb-2026 10:05:07</t>
@@ -31246,7 +31272,7 @@
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
@@ -31269,15 +31295,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA203" t="inlineStr"/>
-      <c r="AB203" t="inlineStr"/>
+      <c r="AA203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC203" t="n">
         <v>0</v>
       </c>
       <c r="AD203" t="n">
         <v>0</v>
       </c>
-      <c r="AE203" t="inlineStr"/>
+      <c r="AE203" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF203" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -31319,13 +31351,19 @@
       <c r="D204" t="n">
         <v>8350</v>
       </c>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="n">
+        <v>8350</v>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
           <t>04-Feb-2026 23:05:27</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>05-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H204" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -31386,7 +31424,7 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
@@ -31409,15 +31447,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA204" t="inlineStr"/>
-      <c r="AB204" t="inlineStr"/>
+      <c r="AA204" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC204" t="n">
         <v>0</v>
       </c>
       <c r="AD204" t="n">
         <v>0</v>
       </c>
-      <c r="AE204" t="inlineStr"/>
+      <c r="AE204" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF204" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL204"/>
+  <dimension ref="A1:AL222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31488,6 +31488,2710 @@
       </c>
       <c r="AL204" t="inlineStr"/>
     </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>16400</v>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="n">
+        <v>9542502425</v>
+      </c>
+      <c r="D205" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E205" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>06-Feb-2026 15:42:50</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>07-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O205" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P205" t="n">
+        <v>11000348990079</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>1770372650</v>
+      </c>
+      <c r="R205" t="n">
+        <v>696631043153</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr"/>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI205" t="n">
+        <v>18422</v>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>267145</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>15762</v>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="n">
+        <v>9505890135</v>
+      </c>
+      <c r="D206" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E206" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>07-Feb-2026 11:49:02</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O206" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P206" t="n">
+        <v>11000349086368</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>1770445075</v>
+      </c>
+      <c r="R206" t="n">
+        <v>109145651654</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA206" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr"/>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI206" t="n">
+        <v>18805</v>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>267429</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>17229</v>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="n">
+        <v>9985965602</v>
+      </c>
+      <c r="D207" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E207" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 12:35:23</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O207" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P207" t="n">
+        <v>11000349188445</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>1770534277</v>
+      </c>
+      <c r="R207" t="n">
+        <v>773499900668</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA207" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr"/>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI207" t="n">
+        <v>19941</v>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>267541</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>16342</v>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="n">
+        <v>9866955786</v>
+      </c>
+      <c r="D208" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E208" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 14:40:50</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O208" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P208" t="n">
+        <v>11000349199255</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>1770541823</v>
+      </c>
+      <c r="R208" t="n">
+        <v>89695506546</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA208" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr"/>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI208" t="n">
+        <v>18265</v>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>267000</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>16052</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>GURRALA RUSHABH NARAYAN</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>9704995001</v>
+      </c>
+      <c r="D209" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E209" t="n">
+        <v>10750</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 21:49:08</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O209" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P209" t="n">
+        <v>11000349412641</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>1770653878</v>
+      </c>
+      <c r="R209" t="n">
+        <v>109162303649</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA209" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr"/>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI209" t="n">
+        <v>19325</v>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>268659</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>16167</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>VELAMALA LAKSHITHA</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>8886569151</v>
+      </c>
+      <c r="D210" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E210" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>10-Feb-2026 07:23:05</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O210" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P210" t="n">
+        <v>11000349433264</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>1770688284</v>
+      </c>
+      <c r="R210" t="n">
+        <v>109163767115</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA210" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr"/>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI210" t="n">
+        <v>18687</v>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>265804</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>16353</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>RETOJI HRIDAYANSH VICTOR</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>9395553084</v>
+      </c>
+      <c r="D211" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E211" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>10-Feb-2026 17:03:05</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O211" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P211" t="n">
+        <v>11000349550616</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>1770723058</v>
+      </c>
+      <c r="R211" t="n">
+        <v>109167537406</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA211" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr"/>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI211" t="n">
+        <v>18469</v>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>265534</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>17260</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SIDDI SHANMUKHA SAI MANI DEEPANSH</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>6305761566</v>
+      </c>
+      <c r="D212" t="n">
+        <v>16700</v>
+      </c>
+      <c r="E212" t="n">
+        <v>16700</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 07:45:40</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>12-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>sixteen thousand seven hundred</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O212" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P212" t="n">
+        <v>11000349611971</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>1770776081</v>
+      </c>
+      <c r="R212" t="n">
+        <v>109170679443</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA212" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr"/>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI212" t="n">
+        <v>19972</v>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>265869,267519</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>2050,2058</t>
+        </is>
+      </c>
+      <c r="AL212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>17259</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SIDDI SHANMUKHA SESA SAI DHANUSH</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>6305761566</v>
+      </c>
+      <c r="D213" t="n">
+        <v>21500</v>
+      </c>
+      <c r="E213" t="n">
+        <v>21500</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 08:00:22</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>twenty one thousand five hundred</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O213" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P213" t="n">
+        <v>11000349612523</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>1770776819</v>
+      </c>
+      <c r="R213" t="n">
+        <v>109170756189</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA213" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr"/>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI213" t="n">
+        <v>19971</v>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>266353,268690</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>2052,2062</t>
+        </is>
+      </c>
+      <c r="AL213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>16615</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>RAKESH NAMMI</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>9502806409</v>
+      </c>
+      <c r="D214" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E214" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 08:29:21</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O214" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P214" t="n">
+        <v>11000349933934</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>1770951465</v>
+      </c>
+      <c r="R214" t="n">
+        <v>456479327537</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr"/>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI214" t="n">
+        <v>19097</v>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>268335</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="AL214" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>14652</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>HEMANTH NAMMI</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>9502806409</v>
+      </c>
+      <c r="D215" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E215" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 08:30:55</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O215" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P215" t="n">
+        <v>11000349933992</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>1770951642</v>
+      </c>
+      <c r="R215" t="n">
+        <v>186282312824</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr"/>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI215" t="n">
+        <v>19448</v>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>268100</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>17367</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EVAAN CHODAM</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>7995919129</v>
+      </c>
+      <c r="D216" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E216" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 09:38:08</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>16-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O216" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P216" t="n">
+        <v>11000349945161</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>1770955661</v>
+      </c>
+      <c r="R216" t="n">
+        <v>834632436491</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr"/>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI216" t="n">
+        <v>20086</v>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>268471</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>15952</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>AFREEN BEGUM</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>8099960677</v>
+      </c>
+      <c r="D217" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E217" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 18:18:42</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O217" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P217" t="n">
+        <v>11000350040172</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>1770986795</v>
+      </c>
+      <c r="R217" t="n">
+        <v>321558195549</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr"/>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI217" t="n">
+        <v>19419</v>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>268015</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>15009</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>GOLAGANI GEETHANJALI</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>9393123464</v>
+      </c>
+      <c r="D218" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E218" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>14-Feb-2026 08:24:58</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O218" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P218" t="n">
+        <v>11000350075558</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>1771037667</v>
+      </c>
+      <c r="R218" t="n">
+        <v>759841106307</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr"/>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI218" t="n">
+        <v>19026</v>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>266050</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>15095</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>KORUKONDA KALYANI</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>9885668424</v>
+      </c>
+      <c r="D219" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E219" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>17-Feb-2026 09:06:11</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O219" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P219" t="n">
+        <v>11000350432476</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>1771299354</v>
+      </c>
+      <c r="R219" t="n">
+        <v>387026729931</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA219" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr"/>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI219" t="n">
+        <v>19580</v>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>268160</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>16615</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>RAKESH NAMMI</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>9502806409</v>
+      </c>
+      <c r="D220" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>18-Feb-2026 10:49:40</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O220" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P220" t="n">
+        <v>11000350603509</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>1771391968</v>
+      </c>
+      <c r="R220" t="n">
+        <v>821324645171</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr"/>
+      <c r="AB220" t="inlineStr"/>
+      <c r="AC220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="inlineStr"/>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr"/>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI220" t="n">
+        <v>19097</v>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>266170</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>15618</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>CHINTAPALLI CHANDINI</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>9985304942</v>
+      </c>
+      <c r="D221" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>18-Feb-2026 20:11:30</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O221" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P221" t="n">
+        <v>11000350731551</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>1771425670</v>
+      </c>
+      <c r="R221" t="n">
+        <v>163162136750</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr"/>
+      <c r="AB221" t="inlineStr"/>
+      <c r="AC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="inlineStr"/>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr"/>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI221" t="n">
+        <v>18866</v>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>267547</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>14706</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>CHINTAPALLI CHATHAN SWAROOP</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>9985304942</v>
+      </c>
+      <c r="D222" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>18-Feb-2026 20:13:07</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O222" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P222" t="n">
+        <v>11000350731636</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>1771425769</v>
+      </c>
+      <c r="R222" t="n">
+        <v>842044167452</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr"/>
+      <c r="AB222" t="inlineStr"/>
+      <c r="AC222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="inlineStr"/>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr"/>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI222" t="n">
+        <v>19397</v>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>268068</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL222"/>
+  <dimension ref="A1:AL250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33775,7 +33775,9 @@
       <c r="D220" t="n">
         <v>8650</v>
       </c>
-      <c r="E220" t="inlineStr"/>
+      <c r="E220" t="n">
+        <v>8650</v>
+      </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>18-Feb-2026 10:49:40</t>
@@ -33842,7 +33844,7 @@
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
@@ -33865,15 +33867,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA220" t="inlineStr"/>
-      <c r="AB220" t="inlineStr"/>
+      <c r="AA220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC220" t="n">
         <v>0</v>
       </c>
       <c r="AD220" t="n">
         <v>0</v>
       </c>
-      <c r="AE220" t="inlineStr"/>
+      <c r="AE220" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF220" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
@@ -33919,13 +33927,19 @@
       <c r="D221" t="n">
         <v>8350</v>
       </c>
-      <c r="E221" t="inlineStr"/>
+      <c r="E221" t="n">
+        <v>8350</v>
+      </c>
       <c r="F221" t="inlineStr">
         <is>
           <t>18-Feb-2026 20:11:30</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>20-Feb-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H221" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -33986,7 +34000,7 @@
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
@@ -34009,15 +34023,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA221" t="inlineStr"/>
-      <c r="AB221" t="inlineStr"/>
+      <c r="AA221" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC221" t="n">
         <v>0</v>
       </c>
       <c r="AD221" t="n">
         <v>0</v>
       </c>
-      <c r="AE221" t="inlineStr"/>
+      <c r="AE221" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF221" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -34063,7 +34083,9 @@
       <c r="D222" t="n">
         <v>11350</v>
       </c>
-      <c r="E222" t="inlineStr"/>
+      <c r="E222" t="n">
+        <v>11350</v>
+      </c>
       <c r="F222" t="inlineStr">
         <is>
           <t>18-Feb-2026 20:13:07</t>
@@ -34130,7 +34152,7 @@
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
@@ -34153,15 +34175,21 @@
           <t>kotakschoolvsp@gmail.com</t>
         </is>
       </c>
-      <c r="AA222" t="inlineStr"/>
-      <c r="AB222" t="inlineStr"/>
+      <c r="AA222" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC222" t="n">
         <v>0</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
       </c>
-      <c r="AE222" t="inlineStr"/>
+      <c r="AE222" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF222" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -34187,6 +34215,4230 @@
         </is>
       </c>
       <c r="AL222" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>14888</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SHAIK GOUSIA NASRIN</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>7207749584</v>
+      </c>
+      <c r="D223" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E223" t="n">
+        <v>10750</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>20-Feb-2026 07:56:35</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O223" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P223" t="n">
+        <v>11000350963982</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>1771554340</v>
+      </c>
+      <c r="R223" t="n">
+        <v>109227319525</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA223" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr"/>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI223" t="n">
+        <v>19200</v>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>266268</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>17188</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>REYANA SRIJITH</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>9985925345</v>
+      </c>
+      <c r="D224" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E224" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 12:39:56</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O224" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P224" t="n">
+        <v>11000351187164</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>1771744152</v>
+      </c>
+      <c r="R224" t="n">
+        <v>109240823792</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA224" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr"/>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI224" t="n">
+        <v>19902</v>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>266990</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>16056</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>GANIREDDY AISHWARYA</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>6302459147</v>
+      </c>
+      <c r="D225" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E225" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 22:22:18</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O225" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P225" t="n">
+        <v>11000351226381</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>1771778816</v>
+      </c>
+      <c r="R225" t="n">
+        <v>302542306467</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA225" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr"/>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI225" t="n">
+        <v>19023</v>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>266049</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="AL225" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>16552</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>GANIREDDY ANUHYA</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>9848537189</v>
+      </c>
+      <c r="D226" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E226" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 22:46:16</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O226" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P226" t="n">
+        <v>11000351228098</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>1771779418</v>
+      </c>
+      <c r="R226" t="n">
+        <v>640262345476</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA226" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr"/>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI226" t="n">
+        <v>18375</v>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>267107</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL226" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>16208</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>MYCHERLA SHASANK</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>7386344393</v>
+      </c>
+      <c r="D227" t="n">
+        <v>11350</v>
+      </c>
+      <c r="E227" t="n">
+        <v>11350</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 11:09:23</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>eleven thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O227" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P227" t="n">
+        <v>11000351269193</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>1771825072</v>
+      </c>
+      <c r="R227" t="n">
+        <v>109246378284</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA227" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr"/>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI227" t="n">
+        <v>19412</v>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>268102</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="AL227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>16906</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>RANVITHA SEERA</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>7095076706</v>
+      </c>
+      <c r="D228" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E228" t="n">
+        <v>10750</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 17:39:15</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>ten thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O228" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P228" t="n">
+        <v>11000351328822</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>1771848461</v>
+      </c>
+      <c r="R228" t="n">
+        <v>109248745854</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA228" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr"/>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI228" t="n">
+        <v>19168</v>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>268578</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="AL228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>17099</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>VINDYA SOWDALA</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>7075489300</v>
+      </c>
+      <c r="D229" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E229" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>24-Feb-2026 17:26:28</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O229" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P229" t="n">
+        <v>11000351453145</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>1771934170</v>
+      </c>
+      <c r="R229" t="n">
+        <v>929800159168</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA229" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr"/>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI229" t="n">
+        <v>18095</v>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>266761</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL229" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>17100</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>BHAVIYSA SOWDALA</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>7075489300</v>
+      </c>
+      <c r="D230" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E230" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>24-Feb-2026 17:27:19</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O230" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P230" t="n">
+        <v>11000351454113</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>1771934227</v>
+      </c>
+      <c r="R230" t="n">
+        <v>555789383766</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA230" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr"/>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI230" t="n">
+        <v>18638</v>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>267297</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL230" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>17179</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>BORA LYDIA</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>6309196999</v>
+      </c>
+      <c r="D231" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E231" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>24-Feb-2026 22:50:26</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O231" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P231" t="n">
+        <v>11000351479569</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>1771953532</v>
+      </c>
+      <c r="R231" t="n">
+        <v>145208162</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA231" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr"/>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI231" t="n">
+        <v>19894</v>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>266635</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>16120</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TANDU ROSARY ANTHONY</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>9492868687</v>
+      </c>
+      <c r="D232" t="n">
+        <v>25550</v>
+      </c>
+      <c r="E232" t="n">
+        <v>25550</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 21:19:38</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>26-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>twenty five thousand five hundred fifty</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O232" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P232" t="n">
+        <v>11000351595092</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>1772034489</v>
+      </c>
+      <c r="R232" t="n">
+        <v>109262506265</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA232" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr"/>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI232" t="n">
+        <v>18727</v>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>261176,262330,264151,265801</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>2033,2037,2042,2050</t>
+        </is>
+      </c>
+      <c r="AL232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>16977</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>OMMI NIDHISH NANDAN</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>8008110591</v>
+      </c>
+      <c r="D233" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E233" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>26-Feb-2026 16:35:02</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>27-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O233" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P233" t="n">
+        <v>11000351694708</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>1772103829</v>
+      </c>
+      <c r="R233" t="n">
+        <v>109267256087</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA233" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr"/>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI233" t="n">
+        <v>18105</v>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>266784</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>17105</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>AADHVIK DADIRAO</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>7075570737</v>
+      </c>
+      <c r="D234" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E234" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>26-Feb-2026 20:59:33</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>27-Feb-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O234" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P234" t="n">
+        <v>11000351725842</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>1772119422</v>
+      </c>
+      <c r="R234" t="n">
+        <v>109268695191</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA234" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr"/>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI234" t="n">
+        <v>18096</v>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>266773</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>17219</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>VARTIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>8369239788</v>
+      </c>
+      <c r="D235" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E235" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>27-Feb-2026 19:37:49</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O235" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P235" t="n">
+        <v>11000351864684</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>1772201239</v>
+      </c>
+      <c r="R235" t="n">
+        <v>605864009197</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA235" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr"/>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI235" t="n">
+        <v>19931</v>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>266855</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL235" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>16797</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>YASHWANTH REDDY GUDLA</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>9948345552</v>
+      </c>
+      <c r="D236" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E236" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 08:20:07</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O236" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P236" t="n">
+        <v>11000351909240</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>1772246973</v>
+      </c>
+      <c r="R236" t="n">
+        <v>40471991429</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA236" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr"/>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI236" t="n">
+        <v>18786</v>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>267482</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL236" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>16796</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>MAHENDRA REDDY GUDLA</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>9948345552</v>
+      </c>
+      <c r="D237" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E237" t="n">
+        <v>8650</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 08:21:04</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O237" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P237" t="n">
+        <v>11000351910047</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>1772247054</v>
+      </c>
+      <c r="R237" t="n">
+        <v>146763616167</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA237" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr"/>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI237" t="n">
+        <v>19010</v>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>268450</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="AL237" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>16020</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DUVVU MAHALAKSHMI</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="D238" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E238" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:28:45</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O238" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P238" t="n">
+        <v>11000351924775</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>1772254681</v>
+      </c>
+      <c r="R238" t="n">
+        <v>920094640606</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA238" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr"/>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI238" t="n">
+        <v>18522</v>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>265602</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="AL238" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>16036</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>DUVVU BHARGAVA SRI SAI</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="D239" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E239" t="n">
+        <v>8350</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:27:22</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O239" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P239" t="n">
+        <v>11000351925096</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>1772254577</v>
+      </c>
+      <c r="R239" t="n">
+        <v>866758700772</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA239" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr"/>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI239" t="n">
+        <v>18964</v>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>267620</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL239" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>16020</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DUVVU MAHALAKSHMI</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>9502247535</v>
+      </c>
+      <c r="D240" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E240" t="n">
+        <v>8050</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:38:10</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O240" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P240" t="n">
+        <v>11000351927021</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>1772254751</v>
+      </c>
+      <c r="R240" t="n">
+        <v>469507160708</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA240" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr"/>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI240" t="n">
+        <v>18522</v>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>267252</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL240" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>16914</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SAI SRAVAN PATNAYAK</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>7337422112</v>
+      </c>
+      <c r="D241" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E241" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 11:55:41</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O241" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P241" t="n">
+        <v>11000351942212</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>1772259825</v>
+      </c>
+      <c r="R241" t="n">
+        <v>109278991926</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA241" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr"/>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI241" t="n">
+        <v>18066</v>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>266779</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>15863</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>BOMMIDI BALA SURYA BHUVAN</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>6300875193</v>
+      </c>
+      <c r="D242" t="n">
+        <v>16100</v>
+      </c>
+      <c r="E242" t="n">
+        <v>16100</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 12:55:32</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>sixteen thousand one hundred</t>
+        </is>
+      </c>
+      <c r="L242" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N242" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O242" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P242" t="n">
+        <v>11000351953158</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>1772263454</v>
+      </c>
+      <c r="R242" t="n">
+        <v>109279356760</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA242" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr"/>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI242" t="n">
+        <v>18543</v>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>265653,267303</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>2049,2057</t>
+        </is>
+      </c>
+      <c r="AL242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>17358</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SAANVI SAHOO</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>8309736856</v>
+      </c>
+      <c r="D243" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E243" t="n">
+        <v>7750</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>01-Mar-2026 16:13:35</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O243" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P243" t="n">
+        <v>11000352070361</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>1772361488</v>
+      </c>
+      <c r="R243" t="n">
+        <v>1.012026060690908e+17</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>BANK OF BARODA FSS</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA243" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr"/>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI243" t="n">
+        <v>20077</v>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>268295</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>16031</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>MALLA VAIBHAV SAI</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>9247311340</v>
+      </c>
+      <c r="D244" t="n">
+        <v>8350</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 08:34:02</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>eight thousand three hundred fifty</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O244" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P244" t="n">
+        <v>11000352121038</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>1772420420</v>
+      </c>
+      <c r="R244" t="n">
+        <v>606171974859</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr"/>
+      <c r="AB244" t="inlineStr"/>
+      <c r="AC244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="inlineStr"/>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr"/>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI244" t="n">
+        <v>18978</v>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>267636</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL244" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>17177</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>THUTTA HARI CHARANI</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>7337239208</v>
+      </c>
+      <c r="D245" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 09:34:10</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O245" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P245" t="n">
+        <v>11000352133780</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>1772424238</v>
+      </c>
+      <c r="R245" t="n">
+        <v>805616523520</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr"/>
+      <c r="AB245" t="inlineStr"/>
+      <c r="AC245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="inlineStr"/>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr"/>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI245" t="n">
+        <v>19892</v>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>266661</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>16927</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>THUTTA DHANASHVI</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>7337239208</v>
+      </c>
+      <c r="D246" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 09:33:18</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O246" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P246" t="n">
+        <v>11000352134464</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>1772424160</v>
+      </c>
+      <c r="R246" t="n">
+        <v>778077483731</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr"/>
+      <c r="AB246" t="inlineStr"/>
+      <c r="AC246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="inlineStr"/>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr"/>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI246" t="n">
+        <v>18339</v>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>266997</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL246" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>16974</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>KADAJARI ESHAN ESWAR</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>9885130099</v>
+      </c>
+      <c r="D247" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 11:31:24</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>seven thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O247" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P247" t="n">
+        <v>11000352162203</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>1772431154</v>
+      </c>
+      <c r="R247" t="n">
+        <v>606128095174</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr"/>
+      <c r="AB247" t="inlineStr"/>
+      <c r="AC247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="inlineStr"/>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr"/>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI247" t="n">
+        <v>18273</v>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>267040</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>17147</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>RONGALI YERNI VENKATA RAKESH</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>7793910192</v>
+      </c>
+      <c r="D248" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 12:16:58</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>eight thousand fifty</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O248" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P248" t="n">
+        <v>11000352171807</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>1772433952</v>
+      </c>
+      <c r="R248" t="n">
+        <v>398196116938</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr"/>
+      <c r="AB248" t="inlineStr"/>
+      <c r="AC248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="inlineStr"/>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr"/>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI248" t="n">
+        <v>19850</v>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>267206</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>17146</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>RONGALI JASMIKA</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>7793910192</v>
+      </c>
+      <c r="D249" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 12:12:45</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O249" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P249" t="n">
+        <v>11000352172149</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>1772433686</v>
+      </c>
+      <c r="R249" t="n">
+        <v>201120935621</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr"/>
+      <c r="AB249" t="inlineStr"/>
+      <c r="AC249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="inlineStr"/>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr"/>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI249" t="n">
+        <v>19849</v>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>266747</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>16375</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>AYESHA NAIK</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>9346210583</v>
+      </c>
+      <c r="D250" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 12:59:37</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>eight thousand six hundred fifty</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
+        <v>100000036600</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O250" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P250" t="n">
+        <v>11000352181791</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>1772436554</v>
+      </c>
+      <c r="R250" t="n">
+        <v>102107278836</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>kotakschoolvsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr"/>
+      <c r="AB250" t="inlineStr"/>
+      <c r="AC250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="inlineStr"/>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr"/>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI250" t="n">
+        <v>19024</v>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>268411</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL298"/>
+  <dimension ref="A1:AL299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32934,8 +32934,16 @@
       <c r="A235" t="n">
         <v>17219</v>
       </c>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>V****** K*****</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>83****9788</t>
+        </is>
+      </c>
       <c r="D235" t="n">
         <v>7750</v>
       </c>
@@ -32970,7 +32978,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -33026,7 +33038,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z235" t="inlineStr"/>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA235" t="n">
         <v>5</v>
       </c>
@@ -33076,8 +33092,16 @@
       <c r="A236" t="n">
         <v>16797</v>
       </c>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Y******** R**** G****</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>99****5552</t>
+        </is>
+      </c>
       <c r="D236" t="n">
         <v>8350</v>
       </c>
@@ -33112,7 +33136,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -33168,7 +33196,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z236" t="inlineStr"/>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA236" t="n">
         <v>5</v>
       </c>
@@ -33218,8 +33250,16 @@
       <c r="A237" t="n">
         <v>16796</v>
       </c>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>M******* R**** G****</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>99****5552</t>
+        </is>
+      </c>
       <c r="D237" t="n">
         <v>8650</v>
       </c>
@@ -33250,7 +33290,11 @@
           <t>eight thousand six hundred fifty</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -33306,7 +33350,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z237" t="inlineStr"/>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA237" t="n">
         <v>5</v>
       </c>
@@ -33356,8 +33404,16 @@
       <c r="A238" t="n">
         <v>16020</v>
       </c>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>D**** M**********</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>95****7535</t>
+        </is>
+      </c>
       <c r="D238" t="n">
         <v>8050</v>
       </c>
@@ -33392,7 +33448,11 @@
           <t>eight thousand fifty</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -33448,7 +33508,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z238" t="inlineStr"/>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA238" t="n">
         <v>5</v>
       </c>
@@ -33498,8 +33562,16 @@
       <c r="A239" t="n">
         <v>16036</v>
       </c>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>D**** B******* S** S**</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>95****7535</t>
+        </is>
+      </c>
       <c r="D239" t="n">
         <v>8350</v>
       </c>
@@ -33534,7 +33606,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -33590,7 +33666,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z239" t="inlineStr"/>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA239" t="n">
         <v>5</v>
       </c>
@@ -33640,8 +33720,16 @@
       <c r="A240" t="n">
         <v>16020</v>
       </c>
-      <c r="B240" t="inlineStr"/>
-      <c r="C240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>D**** M**********</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>95****7535</t>
+        </is>
+      </c>
       <c r="D240" t="n">
         <v>8050</v>
       </c>
@@ -33676,7 +33764,11 @@
           <t>eight thousand fifty</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -33732,7 +33824,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z240" t="inlineStr"/>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA240" t="n">
         <v>5</v>
       </c>
@@ -33782,8 +33878,16 @@
       <c r="A241" t="n">
         <v>16914</v>
       </c>
-      <c r="B241" t="inlineStr"/>
-      <c r="C241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>S** S***** P*******</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>73****2112</t>
+        </is>
+      </c>
       <c r="D241" t="n">
         <v>6750</v>
       </c>
@@ -33818,7 +33922,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -33874,7 +33982,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z241" t="inlineStr"/>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA241" t="n">
         <v>5</v>
       </c>
@@ -33920,8 +34032,16 @@
       <c r="A242" t="n">
         <v>15863</v>
       </c>
-      <c r="B242" t="inlineStr"/>
-      <c r="C242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>B****** B*** S**** B*****</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>63****5193</t>
+        </is>
+      </c>
       <c r="D242" t="n">
         <v>16100</v>
       </c>
@@ -33956,7 +34076,11 @@
           <t>sixteen thousand one hundred</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -34012,7 +34136,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z242" t="inlineStr"/>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA242" t="n">
         <v>5</v>
       </c>
@@ -34058,8 +34186,16 @@
       <c r="A243" t="n">
         <v>17358</v>
       </c>
-      <c r="B243" t="inlineStr"/>
-      <c r="C243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>S***** S****</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>83****6856</t>
+        </is>
+      </c>
       <c r="D243" t="n">
         <v>7750</v>
       </c>
@@ -34094,7 +34230,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -34150,7 +34290,11 @@
           <t>DC</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr"/>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA243" t="n">
         <v>5</v>
       </c>
@@ -34196,8 +34340,16 @@
       <c r="A244" t="n">
         <v>16031</v>
       </c>
-      <c r="B244" t="inlineStr"/>
-      <c r="C244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>M**** V****** S**</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>92****1340</t>
+        </is>
+      </c>
       <c r="D244" t="n">
         <v>8350</v>
       </c>
@@ -34232,7 +34384,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -34288,7 +34444,11 @@
           <t>QR_UPI</t>
         </is>
       </c>
-      <c r="Z244" t="inlineStr"/>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA244" t="n">
         <v>5</v>
       </c>
@@ -34338,8 +34498,16 @@
       <c r="A245" t="n">
         <v>17177</v>
       </c>
-      <c r="B245" t="inlineStr"/>
-      <c r="C245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>T***** H*** C******</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>73****9208</t>
+        </is>
+      </c>
       <c r="D245" t="n">
         <v>6750</v>
       </c>
@@ -34374,7 +34542,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -34430,7 +34602,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z245" t="inlineStr"/>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA245" t="n">
         <v>5</v>
       </c>
@@ -34480,8 +34656,16 @@
       <c r="A246" t="n">
         <v>16927</v>
       </c>
-      <c r="B246" t="inlineStr"/>
-      <c r="C246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>T***** D********</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>73****9208</t>
+        </is>
+      </c>
       <c r="D246" t="n">
         <v>7750</v>
       </c>
@@ -34516,7 +34700,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -34572,7 +34760,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z246" t="inlineStr"/>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA246" t="n">
         <v>5</v>
       </c>
@@ -34622,8 +34814,16 @@
       <c r="A247" t="n">
         <v>16974</v>
       </c>
-      <c r="B247" t="inlineStr"/>
-      <c r="C247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>K******* E**** E****</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>98****0099</t>
+        </is>
+      </c>
       <c r="D247" t="n">
         <v>7750</v>
       </c>
@@ -34658,7 +34858,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -34714,7 +34918,11 @@
           <t>QR_UPI</t>
         </is>
       </c>
-      <c r="Z247" t="inlineStr"/>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA247" t="n">
         <v>5</v>
       </c>
@@ -34764,8 +34972,16 @@
       <c r="A248" t="n">
         <v>17147</v>
       </c>
-      <c r="B248" t="inlineStr"/>
-      <c r="C248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>R****** Y**** V****** R*****</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>77****0192</t>
+        </is>
+      </c>
       <c r="D248" t="n">
         <v>8050</v>
       </c>
@@ -34800,7 +35016,11 @@
           <t>eight thousand fifty</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -34856,7 +35076,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z248" t="inlineStr"/>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA248" t="n">
         <v>5</v>
       </c>
@@ -34906,8 +35130,16 @@
       <c r="A249" t="n">
         <v>17146</v>
       </c>
-      <c r="B249" t="inlineStr"/>
-      <c r="C249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>R****** J******</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>77****0192</t>
+        </is>
+      </c>
       <c r="D249" t="n">
         <v>6750</v>
       </c>
@@ -34942,7 +35174,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -34998,7 +35234,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z249" t="inlineStr"/>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA249" t="n">
         <v>5</v>
       </c>
@@ -35048,8 +35288,16 @@
       <c r="A250" t="n">
         <v>16375</v>
       </c>
-      <c r="B250" t="inlineStr"/>
-      <c r="C250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>A***** N***</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>93****0583</t>
+        </is>
+      </c>
       <c r="D250" t="n">
         <v>8650</v>
       </c>
@@ -35080,7 +35328,11 @@
           <t>eight thousand six hundred fifty</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -35136,7 +35388,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z250" t="inlineStr"/>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA250" t="n">
         <v>5</v>
       </c>
@@ -35186,8 +35442,16 @@
       <c r="A251" t="n">
         <v>16580</v>
       </c>
-      <c r="B251" t="inlineStr"/>
-      <c r="C251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>C******* A************* M*********</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>99****6244</t>
+        </is>
+      </c>
       <c r="D251" t="n">
         <v>8350</v>
       </c>
@@ -35222,7 +35486,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -35278,7 +35546,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z251" t="inlineStr"/>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA251" t="n">
         <v>5</v>
       </c>
@@ -35328,8 +35600,16 @@
       <c r="A252" t="n">
         <v>16580</v>
       </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>C******* A************* M*********</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>99****6244</t>
+        </is>
+      </c>
       <c r="D252" t="n">
         <v>8350</v>
       </c>
@@ -35364,7 +35644,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr"/>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -35420,7 +35704,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z252" t="inlineStr"/>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA252" t="n">
         <v>5</v>
       </c>
@@ -35470,8 +35758,16 @@
       <c r="A253" t="n">
         <v>16740</v>
       </c>
-      <c r="B253" t="inlineStr"/>
-      <c r="C253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>S**** Y****</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>81****6234</t>
+        </is>
+      </c>
       <c r="D253" t="n">
         <v>7750</v>
       </c>
@@ -35506,7 +35802,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -35562,7 +35862,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z253" t="inlineStr"/>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA253" t="n">
         <v>5</v>
       </c>
@@ -35612,8 +35916,16 @@
       <c r="A254" t="n">
         <v>16936</v>
       </c>
-      <c r="B254" t="inlineStr"/>
-      <c r="C254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>H******** R*****</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>63****8581</t>
+        </is>
+      </c>
       <c r="D254" t="n">
         <v>7750</v>
       </c>
@@ -35648,7 +35960,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr"/>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -35704,7 +36020,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z254" t="inlineStr"/>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA254" t="n">
         <v>5</v>
       </c>
@@ -35754,8 +36074,16 @@
       <c r="A255" t="n">
         <v>15041</v>
       </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>B**** A****** S***</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>90****9626</t>
+        </is>
+      </c>
       <c r="D255" t="n">
         <v>10750</v>
       </c>
@@ -35786,7 +36114,11 @@
           <t>ten thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -35842,7 +36174,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z255" t="inlineStr"/>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA255" t="n">
         <v>5</v>
       </c>
@@ -35892,8 +36228,16 @@
       <c r="A256" t="n">
         <v>16721</v>
       </c>
-      <c r="B256" t="inlineStr"/>
-      <c r="C256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>K****** G**********</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>99****1635</t>
+        </is>
+      </c>
       <c r="D256" t="n">
         <v>7750</v>
       </c>
@@ -35928,7 +36272,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -35984,7 +36332,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z256" t="inlineStr"/>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA256" t="n">
         <v>5</v>
       </c>
@@ -36034,8 +36386,16 @@
       <c r="A257" t="n">
         <v>15823</v>
       </c>
-      <c r="B257" t="inlineStr"/>
-      <c r="C257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>K****** H*****</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>99****1635</t>
+        </is>
+      </c>
       <c r="D257" t="n">
         <v>8350</v>
       </c>
@@ -36070,7 +36430,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr"/>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -36126,7 +36490,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z257" t="inlineStr"/>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA257" t="n">
         <v>5</v>
       </c>
@@ -36176,8 +36544,16 @@
       <c r="A258" t="n">
         <v>15536</v>
       </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>K**** M*********</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>97****1309</t>
+        </is>
+      </c>
       <c r="D258" t="n">
         <v>8350</v>
       </c>
@@ -36212,7 +36588,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr"/>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -36268,7 +36648,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z258" t="inlineStr"/>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA258" t="n">
         <v>5</v>
       </c>
@@ -36318,8 +36702,16 @@
       <c r="A259" t="n">
         <v>15541</v>
       </c>
-      <c r="B259" t="inlineStr"/>
-      <c r="C259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>R****** V***********</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>98****9449</t>
+        </is>
+      </c>
       <c r="D259" t="n">
         <v>8350</v>
       </c>
@@ -36354,7 +36746,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr"/>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -36410,7 +36806,11 @@
           <t>QR_UPI</t>
         </is>
       </c>
-      <c r="Z259" t="inlineStr"/>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA259" t="n">
         <v>5</v>
       </c>
@@ -36460,8 +36860,16 @@
       <c r="A260" t="n">
         <v>17163</v>
       </c>
-      <c r="B260" t="inlineStr"/>
-      <c r="C260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>M******* Z*** K***</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>82****8795</t>
+        </is>
+      </c>
       <c r="D260" t="n">
         <v>6750</v>
       </c>
@@ -36496,7 +36904,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -36552,7 +36964,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z260" t="inlineStr"/>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA260" t="n">
         <v>5</v>
       </c>
@@ -36602,8 +37018,16 @@
       <c r="A261" t="n">
         <v>15746</v>
       </c>
-      <c r="B261" t="inlineStr"/>
-      <c r="C261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Y**** Y******* N****</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>94****1196</t>
+        </is>
+      </c>
       <c r="D261" t="n">
         <v>16700</v>
       </c>
@@ -36638,7 +37062,11 @@
           <t>sixteen thousand seven hundred</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -36694,7 +37122,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z261" t="inlineStr"/>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA261" t="n">
         <v>5</v>
       </c>
@@ -36744,8 +37176,16 @@
       <c r="A262" t="n">
         <v>14949</v>
       </c>
-      <c r="B262" t="inlineStr"/>
-      <c r="C262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>M***** S******* L****** S** M** R**</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>80****0739</t>
+        </is>
+      </c>
       <c r="D262" t="n">
         <v>10750</v>
       </c>
@@ -36776,7 +37216,11 @@
           <t>ten thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr"/>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -36832,7 +37276,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z262" t="inlineStr"/>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA262" t="n">
         <v>5</v>
       </c>
@@ -36882,8 +37330,16 @@
       <c r="A263" t="n">
         <v>16894</v>
       </c>
-      <c r="B263" t="inlineStr"/>
-      <c r="C263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>S**** V****** S** V***** V******</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>85****3683</t>
+        </is>
+      </c>
       <c r="D263" t="n">
         <v>8650</v>
       </c>
@@ -36914,7 +37370,11 @@
           <t>eight thousand six hundred fifty</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -36970,7 +37430,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z263" t="inlineStr"/>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA263" t="n">
         <v>5</v>
       </c>
@@ -37020,8 +37484,16 @@
       <c r="A264" t="n">
         <v>17103</v>
       </c>
-      <c r="B264" t="inlineStr"/>
-      <c r="C264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>P******** B******* S**</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>63****9629</t>
+        </is>
+      </c>
       <c r="D264" t="n">
         <v>6750</v>
       </c>
@@ -37056,7 +37528,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -37112,7 +37588,11 @@
           <t>QR_UPI</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr"/>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA264" t="n">
         <v>5</v>
       </c>
@@ -37162,8 +37642,16 @@
       <c r="A265" t="n">
         <v>17093</v>
       </c>
-      <c r="B265" t="inlineStr"/>
-      <c r="C265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>S**** A******</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>98****7290</t>
+        </is>
+      </c>
       <c r="D265" t="n">
         <v>6750</v>
       </c>
@@ -37198,7 +37686,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr"/>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -37254,7 +37746,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z265" t="inlineStr"/>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA265" t="n">
         <v>5</v>
       </c>
@@ -37304,8 +37800,16 @@
       <c r="A266" t="n">
         <v>16167</v>
       </c>
-      <c r="B266" t="inlineStr"/>
-      <c r="C266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>V******* L********</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>88****9151</t>
+        </is>
+      </c>
       <c r="D266" t="n">
         <v>8350</v>
       </c>
@@ -37340,7 +37844,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -37396,7 +37904,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr"/>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA266" t="n">
         <v>5</v>
       </c>
@@ -37446,8 +37958,16 @@
       <c r="A267" t="n">
         <v>16353</v>
       </c>
-      <c r="B267" t="inlineStr"/>
-      <c r="C267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>R***** H********* V*****</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>93****3084</t>
+        </is>
+      </c>
       <c r="D267" t="n">
         <v>8050</v>
       </c>
@@ -37482,7 +38002,11 @@
           <t>eight thousand fifty</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -37538,7 +38062,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z267" t="inlineStr"/>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA267" t="n">
         <v>5</v>
       </c>
@@ -37588,8 +38116,16 @@
       <c r="A268" t="n">
         <v>17277</v>
       </c>
-      <c r="B268" t="inlineStr"/>
-      <c r="C268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>E******* M*******</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>96****1662</t>
+        </is>
+      </c>
       <c r="D268" t="n">
         <v>6750</v>
       </c>
@@ -37624,7 +38160,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -37680,7 +38220,11 @@
           <t>QR_UPI</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr"/>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA268" t="n">
         <v>5</v>
       </c>
@@ -37730,8 +38274,16 @@
       <c r="A269" t="n">
         <v>17138</v>
       </c>
-      <c r="B269" t="inlineStr"/>
-      <c r="C269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>S**** B******</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>79****8688</t>
+        </is>
+      </c>
       <c r="D269" t="n">
         <v>7750</v>
       </c>
@@ -37766,7 +38318,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -37822,7 +38378,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z269" t="inlineStr"/>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA269" t="n">
         <v>5</v>
       </c>
@@ -37872,8 +38432,16 @@
       <c r="A270" t="n">
         <v>17139</v>
       </c>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>S**** B********* S**</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>79****8688</t>
+        </is>
+      </c>
       <c r="D270" t="n">
         <v>8350</v>
       </c>
@@ -37908,7 +38476,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr"/>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -37964,7 +38536,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z270" t="inlineStr"/>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA270" t="n">
         <v>5</v>
       </c>
@@ -38014,8 +38590,16 @@
       <c r="A271" t="n">
         <v>16043</v>
       </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>V****** V******* M****</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>76****5088</t>
+        </is>
+      </c>
       <c r="D271" t="n">
         <v>8050</v>
       </c>
@@ -38050,7 +38634,11 @@
           <t>eight thousand fifty</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr"/>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -38106,7 +38694,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z271" t="inlineStr"/>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA271" t="n">
         <v>5</v>
       </c>
@@ -38156,8 +38748,16 @@
       <c r="A272" t="n">
         <v>16548</v>
       </c>
-      <c r="B272" t="inlineStr"/>
-      <c r="C272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>P******* C****** R******</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>90****9830</t>
+        </is>
+      </c>
       <c r="D272" t="n">
         <v>8350</v>
       </c>
@@ -38192,7 +38792,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -38248,7 +38852,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z272" t="inlineStr"/>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA272" t="n">
         <v>5</v>
       </c>
@@ -38298,8 +38906,16 @@
       <c r="A273" t="n">
         <v>16761</v>
       </c>
-      <c r="B273" t="inlineStr"/>
-      <c r="C273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>T**** T*** K****</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>97****8884</t>
+        </is>
+      </c>
       <c r="D273" t="n">
         <v>8650</v>
       </c>
@@ -38330,7 +38946,11 @@
           <t>eight thousand six hundred fifty</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr"/>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -38386,7 +39006,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z273" t="inlineStr"/>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA273" t="n">
         <v>5</v>
       </c>
@@ -38436,8 +39060,16 @@
       <c r="A274" t="n">
         <v>17305</v>
       </c>
-      <c r="B274" t="inlineStr"/>
-      <c r="C274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>T******* D** C******</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>90****6332</t>
+        </is>
+      </c>
       <c r="D274" t="n">
         <v>6750</v>
       </c>
@@ -38472,7 +39104,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr"/>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -38528,7 +39164,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z274" t="inlineStr"/>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA274" t="n">
         <v>5</v>
       </c>
@@ -38578,8 +39218,16 @@
       <c r="A275" t="n">
         <v>16492</v>
       </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>A****** A****** M*********</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>99****6244</t>
+        </is>
+      </c>
       <c r="D275" t="n">
         <v>8050</v>
       </c>
@@ -38614,7 +39262,11 @@
           <t>eight thousand fifty</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr"/>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -38670,7 +39322,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z275" t="inlineStr"/>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA275" t="n">
         <v>5</v>
       </c>
@@ -38720,8 +39376,16 @@
       <c r="A276" t="n">
         <v>16492</v>
       </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>A****** A****** M*********</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>99****6244</t>
+        </is>
+      </c>
       <c r="D276" t="n">
         <v>8050</v>
       </c>
@@ -38756,7 +39420,11 @@
           <t>eight thousand fifty</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr"/>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -38812,7 +39480,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr"/>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA276" t="n">
         <v>5</v>
       </c>
@@ -38862,8 +39534,16 @@
       <c r="A277" t="n">
         <v>16966</v>
       </c>
-      <c r="B277" t="inlineStr"/>
-      <c r="C277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>G******* J***** A***** A******</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>82****6967</t>
+        </is>
+      </c>
       <c r="D277" t="n">
         <v>6750</v>
       </c>
@@ -38898,7 +39578,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr"/>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -38954,7 +39638,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z277" t="inlineStr"/>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA277" t="n">
         <v>5</v>
       </c>
@@ -39004,8 +39692,16 @@
       <c r="A278" t="n">
         <v>16211</v>
       </c>
-      <c r="B278" t="inlineStr"/>
-      <c r="C278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>P******* J*******</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>95****0840</t>
+        </is>
+      </c>
       <c r="D278" t="n">
         <v>8350</v>
       </c>
@@ -39040,7 +39736,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr"/>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -39096,7 +39796,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr"/>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA278" t="n">
         <v>5</v>
       </c>
@@ -39146,8 +39850,16 @@
       <c r="A279" t="n">
         <v>15234</v>
       </c>
-      <c r="B279" t="inlineStr"/>
-      <c r="C279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>M****** P*****</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>99****3424</t>
+        </is>
+      </c>
       <c r="D279" t="n">
         <v>8650</v>
       </c>
@@ -39178,7 +39890,11 @@
           <t>eight thousand six hundred fifty</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -39234,7 +39950,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z279" t="inlineStr"/>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA279" t="n">
         <v>5</v>
       </c>
@@ -39284,8 +40004,16 @@
       <c r="A280" t="n">
         <v>16710</v>
       </c>
-      <c r="B280" t="inlineStr"/>
-      <c r="C280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>B********** H*********</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>98****7129</t>
+        </is>
+      </c>
       <c r="D280" t="n">
         <v>7750</v>
       </c>
@@ -39320,7 +40048,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -39376,7 +40108,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z280" t="inlineStr"/>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA280" t="n">
         <v>5</v>
       </c>
@@ -39426,8 +40162,16 @@
       <c r="A281" t="n">
         <v>15544</v>
       </c>
-      <c r="B281" t="inlineStr"/>
-      <c r="C281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>B********** J** A******** S**** S*****</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>98****7129</t>
+        </is>
+      </c>
       <c r="D281" t="n">
         <v>8350</v>
       </c>
@@ -39462,7 +40206,11 @@
           <t>eight thousand three hundred fifty</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr"/>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -39518,7 +40266,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z281" t="inlineStr"/>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA281" t="n">
         <v>5</v>
       </c>
@@ -39568,8 +40320,16 @@
       <c r="A282" t="n">
         <v>15009</v>
       </c>
-      <c r="B282" t="inlineStr"/>
-      <c r="C282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>G******* G**********</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>93****3464</t>
+        </is>
+      </c>
       <c r="D282" t="n">
         <v>8650</v>
       </c>
@@ -39600,7 +40360,11 @@
           <t>eight thousand six hundred fifty</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr"/>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -39656,7 +40420,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z282" t="inlineStr"/>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA282" t="n">
         <v>5</v>
       </c>
@@ -39706,8 +40474,16 @@
       <c r="A283" t="n">
         <v>15824</v>
       </c>
-      <c r="B283" t="inlineStr"/>
-      <c r="C283" t="inlineStr"/>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>G******* R***** N******</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>93****3464</t>
+        </is>
+      </c>
       <c r="D283" t="n">
         <v>8050</v>
       </c>
@@ -39742,7 +40518,11 @@
           <t>eight thousand fifty</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr"/>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -39798,7 +40578,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z283" t="inlineStr"/>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA283" t="n">
         <v>5</v>
       </c>
@@ -39848,8 +40632,16 @@
       <c r="A284" t="n">
         <v>16885</v>
       </c>
-      <c r="B284" t="inlineStr"/>
-      <c r="C284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>J**** C*****</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>81****3759</t>
+        </is>
+      </c>
       <c r="D284" t="n">
         <v>7750</v>
       </c>
@@ -39884,7 +40676,11 @@
           <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr"/>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -39940,7 +40736,11 @@
           <t>QR_UPI</t>
         </is>
       </c>
-      <c r="Z284" t="inlineStr"/>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA284" t="n">
         <v>5</v>
       </c>
@@ -39990,8 +40790,16 @@
       <c r="A285" t="n">
         <v>17215</v>
       </c>
-      <c r="B285" t="inlineStr"/>
-      <c r="C285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>S********** S*****</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>95****8421</t>
+        </is>
+      </c>
       <c r="D285" t="n">
         <v>6750</v>
       </c>
@@ -40026,7 +40834,11 @@
           <t>six thousand seven hundred fifty</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr"/>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>SALESIAN EDUCATION SOCIETY</t>
@@ -40082,7 +40894,11 @@
           <t>UPI</t>
         </is>
       </c>
-      <c r="Z285" t="inlineStr"/>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
       <c r="AA285" t="n">
         <v>5</v>
       </c>
@@ -42158,6 +42974,164 @@
         </is>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>17187</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>C****** V********</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>88****8971</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E299" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F299" s="1" t="n">
+        <v>46119.49782407407</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>08-Apr-2026 17:44:13</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O299" t="n">
+        <v>1234</v>
+      </c>
+      <c r="P299" t="n">
+        <v>11000357637359</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>1775543193</v>
+      </c>
+      <c r="R299" t="n">
+        <v>115726878456</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA299" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr"/>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI299" t="n">
+        <v>19901</v>
+      </c>
+      <c r="AJ299" t="inlineStr">
+        <is>
+          <t>266636</t>
+        </is>
+      </c>
+      <c r="AK299" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL299" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL299"/>
+  <dimension ref="A1:AL294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32932,35 +32932,35 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>17219</v>
+        <v>16031</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>V****** K*****</t>
+          <t>M**** V****** S**</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>83****9788</t>
+          <t>92****1340</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>7750</v>
+        <v>8350</v>
       </c>
       <c r="E235" t="n">
-        <v>7750</v>
+        <v>8350</v>
       </c>
       <c r="F235" s="1" t="n">
-        <v>46080.81792824074</v>
+        <v>46083.35696759259</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>02-Mar-2026 00:00:00</t>
+          <t>04-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
+          <t>TRANSACTION IS SUCCESS</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -32975,7 +32975,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -32995,13 +32995,13 @@
         <v>1234</v>
       </c>
       <c r="P235" t="n">
-        <v>11000351864684</v>
+        <v>11000352121038</v>
       </c>
       <c r="Q235" t="n">
-        <v>1772201239</v>
+        <v>1772420420</v>
       </c>
       <c r="R235" t="n">
-        <v>605864009197</v>
+        <v>606171974859</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>QR_UPI</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
@@ -33070,50 +33070,50 @@
         </is>
       </c>
       <c r="AI235" t="n">
-        <v>19931</v>
+        <v>18978</v>
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>266855</t>
+          <t>267636</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>UPI INTENT</t>
+          <t>PG QR</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>16797</v>
+        <v>17177</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Y******** R**** G****</t>
+          <t>T***** H*** C******</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>99****5552</t>
+          <t>73****9208</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>8350</v>
+        <v>6750</v>
       </c>
       <c r="E236" t="n">
-        <v>8350</v>
+        <v>6750</v>
       </c>
       <c r="F236" s="1" t="n">
-        <v>46081.34730324074</v>
+        <v>46083.39872685185</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>02-Mar-2026 00:00:00</t>
+          <t>04-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -33128,12 +33128,12 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -33153,13 +33153,13 @@
         <v>1234</v>
       </c>
       <c r="P236" t="n">
-        <v>11000351909240</v>
+        <v>11000352133780</v>
       </c>
       <c r="Q236" t="n">
-        <v>1772246973</v>
+        <v>1772424238</v>
       </c>
       <c r="R236" t="n">
-        <v>40471991429</v>
+        <v>805616523520</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
       </c>
       <c r="AF236" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG236" t="inlineStr"/>
@@ -33228,16 +33228,16 @@
         </is>
       </c>
       <c r="AI236" t="n">
-        <v>18786</v>
+        <v>19892</v>
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>267482</t>
+          <t>266661</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
@@ -33248,28 +33248,32 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>16796</v>
+        <v>16927</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>M******* R**** G****</t>
+          <t>T***** D********</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>99****5552</t>
+          <t>73****9208</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>8650</v>
+        <v>7750</v>
       </c>
       <c r="E237" t="n">
-        <v>8650</v>
+        <v>7750</v>
       </c>
       <c r="F237" s="1" t="n">
-        <v>46081.34796296297</v>
-      </c>
-      <c r="G237" t="inlineStr"/>
+        <v>46083.398125</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>04-Mar-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H237" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -33282,12 +33286,12 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Vll</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>eight thousand six hundred fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -33307,13 +33311,13 @@
         <v>1234</v>
       </c>
       <c r="P237" t="n">
-        <v>11000351910047</v>
+        <v>11000352134464</v>
       </c>
       <c r="Q237" t="n">
-        <v>1772247054</v>
+        <v>1772424160</v>
       </c>
       <c r="R237" t="n">
-        <v>146763616167</v>
+        <v>778077483731</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -33332,7 +33336,7 @@
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
@@ -33372,7 +33376,7 @@
       </c>
       <c r="AF237" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG237" t="inlineStr"/>
@@ -33382,16 +33386,16 @@
         </is>
       </c>
       <c r="AI237" t="n">
-        <v>19010</v>
+        <v>18339</v>
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>268450</t>
+          <t>266997</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
@@ -33402,35 +33406,35 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>16020</v>
+        <v>16974</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>D**** M**********</t>
+          <t>K******* E**** E****</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>95****7535</t>
+          <t>98****0099</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>8050</v>
+        <v>7750</v>
       </c>
       <c r="E238" t="n">
-        <v>8050</v>
+        <v>7750</v>
       </c>
       <c r="F238" s="1" t="n">
-        <v>46081.43663194445</v>
+        <v>46083.48013888889</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>02-Mar-2026 00:00:00</t>
+          <t>04-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
+          <t>TRANSACTION IS SUCCESS</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -33445,7 +33449,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -33465,13 +33469,13 @@
         <v>1234</v>
       </c>
       <c r="P238" t="n">
-        <v>11000351924775</v>
+        <v>11000352162203</v>
       </c>
       <c r="Q238" t="n">
-        <v>1772254681</v>
+        <v>1772431154</v>
       </c>
       <c r="R238" t="n">
-        <v>920094640606</v>
+        <v>606128095174</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -33505,7 +33509,7 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>QR_UPI</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
@@ -33540,50 +33544,50 @@
         </is>
       </c>
       <c r="AI238" t="n">
-        <v>18522</v>
+        <v>18273</v>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>265602</t>
+          <t>267040</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>UPI INTENT</t>
+          <t>PG QR</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>16036</v>
+        <v>17147</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>D**** B******* S** S**</t>
+          <t>R****** Y**** V****** R*****</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>95****7535</t>
+          <t>77****0192</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>8350</v>
+        <v>8050</v>
       </c>
       <c r="E239" t="n">
-        <v>8350</v>
+        <v>8050</v>
       </c>
       <c r="F239" s="1" t="n">
-        <v>46081.4356712963</v>
+        <v>46083.5117824074</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>02-Mar-2026 00:00:00</t>
+          <t>04-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -33603,7 +33607,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -33623,13 +33627,13 @@
         <v>1234</v>
       </c>
       <c r="P239" t="n">
-        <v>11000351925096</v>
+        <v>11000352171807</v>
       </c>
       <c r="Q239" t="n">
-        <v>1772254577</v>
+        <v>1772433952</v>
       </c>
       <c r="R239" t="n">
-        <v>866758700772</v>
+        <v>398196116938</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -33698,16 +33702,16 @@
         </is>
       </c>
       <c r="AI239" t="n">
-        <v>18964</v>
+        <v>19850</v>
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>267620</t>
+          <t>267206</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
@@ -33718,30 +33722,30 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>16020</v>
+        <v>17146</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>D**** M**********</t>
+          <t>R****** J******</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>95****7535</t>
+          <t>77****0192</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>8050</v>
+        <v>6750</v>
       </c>
       <c r="E240" t="n">
-        <v>8050</v>
+        <v>6750</v>
       </c>
       <c r="F240" s="1" t="n">
-        <v>46081.4431712963</v>
+        <v>46083.50885416667</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>02-Mar-2026 00:00:00</t>
+          <t>04-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -33756,12 +33760,12 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -33781,13 +33785,13 @@
         <v>1234</v>
       </c>
       <c r="P240" t="n">
-        <v>11000351927021</v>
+        <v>11000352172149</v>
       </c>
       <c r="Q240" t="n">
-        <v>1772254751</v>
+        <v>1772433686</v>
       </c>
       <c r="R240" t="n">
-        <v>469507160708</v>
+        <v>201120935621</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -33846,7 +33850,7 @@
       </c>
       <c r="AF240" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG240" t="inlineStr"/>
@@ -33856,16 +33860,16 @@
         </is>
       </c>
       <c r="AI240" t="n">
-        <v>18522</v>
+        <v>19849</v>
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>267252</t>
+          <t>266747</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="AL240" t="inlineStr">
@@ -33876,32 +33880,28 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>16914</v>
+        <v>16375</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>S** S***** P*******</t>
+          <t>A***** N***</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>73****2112</t>
+          <t>93****0583</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>6750</v>
+        <v>8650</v>
       </c>
       <c r="E241" t="n">
-        <v>6750</v>
+        <v>8650</v>
       </c>
       <c r="F241" s="1" t="n">
-        <v>46081.49700231481</v>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>02-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46083.54140046296</v>
+      </c>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -33914,12 +33914,12 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>Vll</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>eight thousand six hundred fifty</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -33939,13 +33939,13 @@
         <v>1234</v>
       </c>
       <c r="P241" t="n">
-        <v>11000351942212</v>
+        <v>11000352181791</v>
       </c>
       <c r="Q241" t="n">
-        <v>1772259825</v>
+        <v>1772436554</v>
       </c>
       <c r="R241" t="n">
-        <v>109278991926</v>
+        <v>102107278836</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
@@ -34004,7 +34004,7 @@
       </c>
       <c r="AF241" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
         </is>
       </c>
       <c r="AG241" t="inlineStr"/>
@@ -34014,46 +34014,50 @@
         </is>
       </c>
       <c r="AI241" t="n">
-        <v>18066</v>
+        <v>19024</v>
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>266779</t>
+          <t>268411</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="AL241" t="inlineStr"/>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="AL241" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>15863</v>
+        <v>16580</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>B****** B*** S**** B*****</t>
+          <t>C******* A************* M*********</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>63****5193</t>
+          <t>99****6244</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>16100</v>
+        <v>8350</v>
       </c>
       <c r="E242" t="n">
-        <v>16100</v>
+        <v>8350</v>
       </c>
       <c r="F242" s="1" t="n">
-        <v>46081.53856481481</v>
+        <v>46085.34151620371</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>02-Mar-2026 00:00:00</t>
+          <t>05-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -34073,7 +34077,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>sixteen thousand one hundred</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -34093,13 +34097,13 @@
         <v>1234</v>
       </c>
       <c r="P242" t="n">
-        <v>11000351953158</v>
+        <v>11000352412921</v>
       </c>
       <c r="Q242" t="n">
-        <v>1772263454</v>
+        <v>1772591976</v>
       </c>
       <c r="R242" t="n">
-        <v>109279356760</v>
+        <v>471174884415</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -34168,51 +34172,55 @@
         </is>
       </c>
       <c r="AI242" t="n">
-        <v>18543</v>
+        <v>18889</v>
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>265653,267303</t>
+          <t>265961</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>2049,2057</t>
-        </is>
-      </c>
-      <c r="AL242" t="inlineStr"/>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="AL242" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>17358</v>
+        <v>16580</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>S***** S****</t>
+          <t>C******* A************* M*********</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>83****6856</t>
+          <t>99****6244</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>7750</v>
+        <v>8350</v>
       </c>
       <c r="E243" t="n">
-        <v>7750</v>
+        <v>8350</v>
       </c>
       <c r="F243" s="1" t="n">
-        <v>46082.67609953704</v>
+        <v>46085.34430555555</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>02-Mar-2026 00:00:00</t>
+          <t>05-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
+          <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -34227,7 +34235,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -34247,13 +34255,13 @@
         <v>1234</v>
       </c>
       <c r="P243" t="n">
-        <v>11000352070361</v>
+        <v>11000352414090</v>
       </c>
       <c r="Q243" t="n">
-        <v>1772361488</v>
+        <v>1772592337</v>
       </c>
       <c r="R243" t="n">
-        <v>1.012026060690908e+17</v>
+        <v>841705895977</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -34267,7 +34275,7 @@
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>BANK OF BARODA FSS</t>
+          <t>ICICI UPI QR</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
@@ -34287,7 +34295,7 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>UPI</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
@@ -34322,51 +34330,55 @@
         </is>
       </c>
       <c r="AI243" t="n">
-        <v>20077</v>
+        <v>18889</v>
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>268295</t>
+          <t>267611</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="AL243" t="inlineStr"/>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="AL243" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>16031</v>
+        <v>16740</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>M**** V****** S**</t>
+          <t>S**** Y****</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>92****1340</t>
+          <t>81****6234</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>8350</v>
+        <v>7750</v>
       </c>
       <c r="E244" t="n">
-        <v>8350</v>
+        <v>7750</v>
       </c>
       <c r="F244" s="1" t="n">
-        <v>46083.35696759259</v>
+        <v>46085.51104166666</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>04-Mar-2026 00:00:00</t>
+          <t>05-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESS</t>
+          <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -34381,7 +34393,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -34401,13 +34413,13 @@
         <v>1234</v>
       </c>
       <c r="P244" t="n">
-        <v>11000352121038</v>
+        <v>11000352452868</v>
       </c>
       <c r="Q244" t="n">
-        <v>1772420420</v>
+        <v>1772606734</v>
       </c>
       <c r="R244" t="n">
-        <v>606171974859</v>
+        <v>599097516858</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -34441,7 +34453,7 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>QR_UPI</t>
+          <t>UPI</t>
         </is>
       </c>
       <c r="Z244" t="inlineStr">
@@ -34476,50 +34488,50 @@
         </is>
       </c>
       <c r="AI244" t="n">
-        <v>18978</v>
+        <v>18209</v>
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>267636</t>
+          <t>265271</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="AL244" t="inlineStr">
         <is>
-          <t>PG QR</t>
+          <t>UPI INTENT</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>17177</v>
+        <v>16936</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>T***** H*** C******</t>
+          <t>H******** R*****</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>73****9208</t>
+          <t>63****8581</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>6750</v>
+        <v>7750</v>
       </c>
       <c r="E245" t="n">
-        <v>6750</v>
+        <v>7750</v>
       </c>
       <c r="F245" s="1" t="n">
-        <v>46083.39872685185</v>
+        <v>46085.51019675926</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>04-Mar-2026 00:00:00</t>
+          <t>05-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -34534,12 +34546,12 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -34559,13 +34571,13 @@
         <v>1234</v>
       </c>
       <c r="P245" t="n">
-        <v>11000352133780</v>
+        <v>11000352453019</v>
       </c>
       <c r="Q245" t="n">
-        <v>1772424238</v>
+        <v>1772606665</v>
       </c>
       <c r="R245" t="n">
-        <v>805616523520</v>
+        <v>104032665366</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -34624,7 +34636,7 @@
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG245" t="inlineStr"/>
@@ -34634,16 +34646,16 @@
         </is>
       </c>
       <c r="AI245" t="n">
-        <v>19892</v>
+        <v>18341</v>
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>266661</t>
+          <t>266988</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="AL245" t="inlineStr">
@@ -34654,32 +34666,28 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>16927</v>
+        <v>15041</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>T***** D********</t>
+          <t>B**** A****** S***</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>73****9208</t>
+          <t>90****9626</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>7750</v>
+        <v>10750</v>
       </c>
       <c r="E246" t="n">
-        <v>7750</v>
+        <v>10750</v>
       </c>
       <c r="F246" s="1" t="n">
-        <v>46083.398125</v>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>04-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46085.69237268518</v>
+      </c>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -34692,12 +34700,12 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>VlllX</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>ten thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -34717,13 +34725,13 @@
         <v>1234</v>
       </c>
       <c r="P246" t="n">
-        <v>11000352134464</v>
+        <v>11000352485593</v>
       </c>
       <c r="Q246" t="n">
-        <v>1772424160</v>
+        <v>1772622269</v>
       </c>
       <c r="R246" t="n">
-        <v>778077483731</v>
+        <v>192575940153</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -34742,7 +34750,7 @@
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
@@ -34782,7 +34790,7 @@
       </c>
       <c r="AF246" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
         </is>
       </c>
       <c r="AG246" t="inlineStr"/>
@@ -34792,16 +34800,16 @@
         </is>
       </c>
       <c r="AI246" t="n">
-        <v>18339</v>
+        <v>19287</v>
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>266997</t>
+          <t>266193</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="AL246" t="inlineStr">
@@ -34812,16 +34820,16 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>16974</v>
+        <v>16721</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>K******* E**** E****</t>
+          <t>K****** G**********</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>98****0099</t>
+          <t>99****1635</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -34831,16 +34839,16 @@
         <v>7750</v>
       </c>
       <c r="F247" s="1" t="n">
-        <v>46083.48013888889</v>
+        <v>46086.34107638889</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>04-Mar-2026 00:00:00</t>
+          <t>06-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESS</t>
+          <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -34875,13 +34883,13 @@
         <v>1234</v>
       </c>
       <c r="P247" t="n">
-        <v>11000352162203</v>
+        <v>11000352541449</v>
       </c>
       <c r="Q247" t="n">
-        <v>1772431154</v>
+        <v>1772678341</v>
       </c>
       <c r="R247" t="n">
-        <v>606128095174</v>
+        <v>723742672506</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -34915,7 +34923,7 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>QR_UPI</t>
+          <t>UPI</t>
         </is>
       </c>
       <c r="Z247" t="inlineStr">
@@ -34950,11 +34958,11 @@
         </is>
       </c>
       <c r="AI247" t="n">
-        <v>18273</v>
+        <v>18114</v>
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>267040</t>
+          <t>266824</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -34964,36 +34972,36 @@
       </c>
       <c r="AL247" t="inlineStr">
         <is>
-          <t>PG QR</t>
+          <t>UPI INTENT</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>17147</v>
+        <v>15823</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>R****** Y**** V****** R*****</t>
+          <t>K****** H*****</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>77****0192</t>
+          <t>99****1635</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>8050</v>
+        <v>8350</v>
       </c>
       <c r="E248" t="n">
-        <v>8050</v>
+        <v>8350</v>
       </c>
       <c r="F248" s="1" t="n">
-        <v>46083.5117824074</v>
+        <v>46086.39050925926</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>04-Mar-2026 00:00:00</t>
+          <t>06-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -35013,7 +35021,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -35033,13 +35041,13 @@
         <v>1234</v>
       </c>
       <c r="P248" t="n">
-        <v>11000352171807</v>
+        <v>11000352552409</v>
       </c>
       <c r="Q248" t="n">
-        <v>1772433952</v>
+        <v>1772682729</v>
       </c>
       <c r="R248" t="n">
-        <v>398196116938</v>
+        <v>169051468182</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -35108,16 +35116,16 @@
         </is>
       </c>
       <c r="AI248" t="n">
-        <v>19850</v>
+        <v>18720</v>
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>267206</t>
+          <t>267423</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="AL248" t="inlineStr">
@@ -35128,30 +35136,30 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>17146</v>
+        <v>15536</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>R****** J******</t>
+          <t>K**** M*********</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>77****0192</t>
+          <t>97****1309</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>6750</v>
+        <v>8350</v>
       </c>
       <c r="E249" t="n">
-        <v>6750</v>
+        <v>8350</v>
       </c>
       <c r="F249" s="1" t="n">
-        <v>46083.50885416667</v>
+        <v>46086.54883101852</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>04-Mar-2026 00:00:00</t>
+          <t>06-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -35166,12 +35174,12 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -35191,13 +35199,13 @@
         <v>1234</v>
       </c>
       <c r="P249" t="n">
-        <v>11000352172149</v>
+        <v>11000352602879</v>
       </c>
       <c r="Q249" t="n">
-        <v>1772433686</v>
+        <v>1772696399</v>
       </c>
       <c r="R249" t="n">
-        <v>201120935621</v>
+        <v>594651190291</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -35256,7 +35264,7 @@
       </c>
       <c r="AF249" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG249" t="inlineStr"/>
@@ -35266,16 +35274,16 @@
         </is>
       </c>
       <c r="AI249" t="n">
-        <v>19849</v>
+        <v>18911</v>
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>266747</t>
+          <t>265921</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="AL249" t="inlineStr">
@@ -35286,31 +35294,35 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>16375</v>
+        <v>15541</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>A***** N***</t>
+          <t>R****** V***********</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>93****0583</t>
+          <t>98****9449</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>8650</v>
+        <v>8350</v>
       </c>
       <c r="E250" t="n">
-        <v>8650</v>
+        <v>8350</v>
       </c>
       <c r="F250" s="1" t="n">
-        <v>46083.54140046296</v>
-      </c>
-      <c r="G250" t="inlineStr"/>
+        <v>46086.63582175926</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>06-Mar-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
+          <t>TRANSACTION IS SUCCESS</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -35320,12 +35332,12 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Vll</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>eight thousand six hundred fifty</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -35345,13 +35357,13 @@
         <v>1234</v>
       </c>
       <c r="P250" t="n">
-        <v>11000352181791</v>
+        <v>11000352631037</v>
       </c>
       <c r="Q250" t="n">
-        <v>1772436554</v>
+        <v>1772703916</v>
       </c>
       <c r="R250" t="n">
-        <v>102107278836</v>
+        <v>617759165517</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -35370,7 +35382,7 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
@@ -35385,7 +35397,7 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>QR_UPI</t>
         </is>
       </c>
       <c r="Z250" t="inlineStr">
@@ -35410,7 +35422,7 @@
       </c>
       <c r="AF250" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG250" t="inlineStr"/>
@@ -35420,50 +35432,50 @@
         </is>
       </c>
       <c r="AI250" t="n">
-        <v>19024</v>
+        <v>18766</v>
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>268411</t>
+          <t>267463</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="AL250" t="inlineStr">
         <is>
-          <t>UPI INTENT</t>
+          <t>PG QR</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>16580</v>
+        <v>17163</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>C******* A************* M*********</t>
+          <t>M******* Z*** K***</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>99****6244</t>
+          <t>82****8795</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>8350</v>
+        <v>6750</v>
       </c>
       <c r="E251" t="n">
-        <v>8350</v>
+        <v>6750</v>
       </c>
       <c r="F251" s="1" t="n">
-        <v>46085.34151620371</v>
+        <v>46087.03974537037</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>05-Mar-2026 00:00:00</t>
+          <t>07-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -35478,12 +35490,12 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -35503,13 +35515,13 @@
         <v>1234</v>
       </c>
       <c r="P251" t="n">
-        <v>11000352412921</v>
+        <v>11000352698044</v>
       </c>
       <c r="Q251" t="n">
-        <v>1772591976</v>
+        <v>1772738726</v>
       </c>
       <c r="R251" t="n">
-        <v>471174884415</v>
+        <v>606512772867</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -35568,7 +35580,7 @@
       </c>
       <c r="AF251" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG251" t="inlineStr"/>
@@ -35578,16 +35590,16 @@
         </is>
       </c>
       <c r="AI251" t="n">
-        <v>18889</v>
+        <v>19878</v>
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>265961</t>
+          <t>266693</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="AL251" t="inlineStr">
@@ -35598,30 +35610,30 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>16580</v>
+        <v>15746</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>C******* A************* M*********</t>
+          <t>Y**** Y******* N****</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>99****6244</t>
+          <t>94****1196</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>8350</v>
+        <v>16700</v>
       </c>
       <c r="E252" t="n">
-        <v>8350</v>
+        <v>16700</v>
       </c>
       <c r="F252" s="1" t="n">
-        <v>46085.34430555555</v>
+        <v>46087.39373842593</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>05-Mar-2026 00:00:00</t>
+          <t>07-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -35641,7 +35653,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>sixteen thousand seven hundred</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -35661,13 +35673,13 @@
         <v>1234</v>
       </c>
       <c r="P252" t="n">
-        <v>11000352414090</v>
+        <v>11000352720949</v>
       </c>
       <c r="Q252" t="n">
-        <v>1772592337</v>
+        <v>1772769405</v>
       </c>
       <c r="R252" t="n">
-        <v>841705895977</v>
+        <v>685322950436</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -35736,16 +35748,16 @@
         </is>
       </c>
       <c r="AI252" t="n">
-        <v>18889</v>
+        <v>18731</v>
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>267611</t>
+          <t>265778,267428</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2050,2058</t>
         </is>
       </c>
       <c r="AL252" t="inlineStr">
@@ -35756,32 +35768,28 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>16740</v>
+        <v>14949</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>S**** Y****</t>
+          <t>M***** S******* L****** S** M** R**</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>81****6234</t>
+          <t>80****0739</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>7750</v>
+        <v>10750</v>
       </c>
       <c r="E253" t="n">
-        <v>7750</v>
+        <v>10750</v>
       </c>
       <c r="F253" s="1" t="n">
-        <v>46085.51104166666</v>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>05-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46087.42783564814</v>
+      </c>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -35794,12 +35802,12 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>VlllX</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>ten thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -35819,13 +35827,13 @@
         <v>1234</v>
       </c>
       <c r="P253" t="n">
-        <v>11000352452868</v>
+        <v>11000352730892</v>
       </c>
       <c r="Q253" t="n">
-        <v>1772606734</v>
+        <v>1772772303</v>
       </c>
       <c r="R253" t="n">
-        <v>599097516858</v>
+        <v>606553970981</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -35844,7 +35852,7 @@
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
@@ -35884,7 +35892,7 @@
       </c>
       <c r="AF253" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
         </is>
       </c>
       <c r="AG253" t="inlineStr"/>
@@ -35894,16 +35902,16 @@
         </is>
       </c>
       <c r="AI253" t="n">
-        <v>18209</v>
+        <v>19326</v>
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>265271</t>
+          <t>268631</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="AL253" t="inlineStr">
@@ -35914,32 +35922,28 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>16936</v>
+        <v>16894</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>H******** R*****</t>
+          <t>S**** V****** S** V***** V******</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>63****8581</t>
+          <t>85****3683</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>7750</v>
+        <v>8650</v>
       </c>
       <c r="E254" t="n">
-        <v>7750</v>
+        <v>8650</v>
       </c>
       <c r="F254" s="1" t="n">
-        <v>46085.51019675926</v>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>05-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46087.52810185185</v>
+      </c>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -35952,12 +35956,12 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>Vll</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>eight thousand six hundred fifty</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -35977,13 +35981,13 @@
         <v>1234</v>
       </c>
       <c r="P254" t="n">
-        <v>11000352453019</v>
+        <v>11000352765283</v>
       </c>
       <c r="Q254" t="n">
-        <v>1772606665</v>
+        <v>1772781014</v>
       </c>
       <c r="R254" t="n">
-        <v>104032665366</v>
+        <v>398424860025</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -36002,7 +36006,7 @@
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W254" t="inlineStr">
@@ -36042,7 +36046,7 @@
       </c>
       <c r="AF254" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
         </is>
       </c>
       <c r="AG254" t="inlineStr"/>
@@ -36052,16 +36056,16 @@
         </is>
       </c>
       <c r="AI254" t="n">
-        <v>18341</v>
+        <v>19146</v>
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>266988</t>
+          <t>268377</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="AL254" t="inlineStr">
@@ -36072,31 +36076,35 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>15041</v>
+        <v>17103</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>B**** A****** S***</t>
+          <t>P******** B******* S**</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>90****9626</t>
+          <t>63****9629</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>10750</v>
+        <v>6750</v>
       </c>
       <c r="E255" t="n">
-        <v>10750</v>
+        <v>6750</v>
       </c>
       <c r="F255" s="1" t="n">
-        <v>46085.69237268518</v>
-      </c>
-      <c r="G255" t="inlineStr"/>
+        <v>46087.65532407408</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>07-Mar-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
+          <t>TRANSACTION IS SUCCESS</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -36106,12 +36114,12 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>VlllX</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>ten thousand seven hundred fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -36131,13 +36139,13 @@
         <v>1234</v>
       </c>
       <c r="P255" t="n">
-        <v>11000352485593</v>
+        <v>11000352801097</v>
       </c>
       <c r="Q255" t="n">
-        <v>1772622269</v>
+        <v>1772791561</v>
       </c>
       <c r="R255" t="n">
-        <v>192575940153</v>
+        <v>149006197244</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -36156,7 +36164,7 @@
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
@@ -36171,7 +36179,7 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>QR_UPI</t>
         </is>
       </c>
       <c r="Z255" t="inlineStr">
@@ -36196,7 +36204,7 @@
       </c>
       <c r="AF255" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG255" t="inlineStr"/>
@@ -36206,50 +36214,50 @@
         </is>
       </c>
       <c r="AI255" t="n">
-        <v>19287</v>
+        <v>18038</v>
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>266193</t>
+          <t>266736</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="AL255" t="inlineStr">
         <is>
-          <t>UPI INTENT</t>
+          <t>PG QR</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>16721</v>
+        <v>17093</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>K****** G**********</t>
+          <t>S**** A******</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>99****1635</t>
+          <t>98****7290</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>7750</v>
+        <v>6750</v>
       </c>
       <c r="E256" t="n">
-        <v>7750</v>
+        <v>6750</v>
       </c>
       <c r="F256" s="1" t="n">
-        <v>46086.34107638889</v>
+        <v>46087.65797453704</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>06-Mar-2026 00:00:00</t>
+          <t>07-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -36264,12 +36272,12 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -36289,13 +36297,13 @@
         <v>1234</v>
       </c>
       <c r="P256" t="n">
-        <v>11000352541449</v>
+        <v>11000352801447</v>
       </c>
       <c r="Q256" t="n">
-        <v>1772678341</v>
+        <v>1772792222</v>
       </c>
       <c r="R256" t="n">
-        <v>723742672506</v>
+        <v>600442299844</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -36354,7 +36362,7 @@
       </c>
       <c r="AF256" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG256" t="inlineStr"/>
@@ -36364,16 +36372,16 @@
         </is>
       </c>
       <c r="AI256" t="n">
-        <v>18114</v>
+        <v>18047</v>
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>266824</t>
+          <t>265105</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="AL256" t="inlineStr">
@@ -36384,16 +36392,16 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>15823</v>
+        <v>16167</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>K****** H*****</t>
+          <t>V******* L********</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>99****1635</t>
+          <t>88****9151</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -36403,11 +36411,11 @@
         <v>8350</v>
       </c>
       <c r="F257" s="1" t="n">
-        <v>46086.39050925926</v>
+        <v>46087.65587962963</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>06-Mar-2026 00:00:00</t>
+          <t>07-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -36447,13 +36455,13 @@
         <v>1234</v>
       </c>
       <c r="P257" t="n">
-        <v>11000352552409</v>
+        <v>11000352802158</v>
       </c>
       <c r="Q257" t="n">
-        <v>1772682729</v>
+        <v>1772791748</v>
       </c>
       <c r="R257" t="n">
-        <v>169051468182</v>
+        <v>868411654766</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -36522,11 +36530,11 @@
         </is>
       </c>
       <c r="AI257" t="n">
-        <v>18720</v>
+        <v>18687</v>
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>267423</t>
+          <t>267454</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -36542,30 +36550,30 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>15536</v>
+        <v>16353</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>K**** M*********</t>
+          <t>R***** H********* V*****</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>97****1309</t>
+          <t>93****3084</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>8350</v>
+        <v>8050</v>
       </c>
       <c r="E258" t="n">
-        <v>8350</v>
+        <v>8050</v>
       </c>
       <c r="F258" s="1" t="n">
-        <v>46086.54883101852</v>
+        <v>46088.29915509259</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>06-Mar-2026 00:00:00</t>
+          <t>09-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -36585,7 +36593,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -36605,13 +36613,13 @@
         <v>1234</v>
       </c>
       <c r="P258" t="n">
-        <v>11000352602879</v>
+        <v>11000352862728</v>
       </c>
       <c r="Q258" t="n">
-        <v>1772696399</v>
+        <v>1772847626</v>
       </c>
       <c r="R258" t="n">
-        <v>594651190291</v>
+        <v>813785429091</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -36680,16 +36688,16 @@
         </is>
       </c>
       <c r="AI258" t="n">
-        <v>18911</v>
+        <v>18469</v>
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>265921</t>
+          <t>267184</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="AL258" t="inlineStr">
@@ -36700,30 +36708,30 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>15541</v>
+        <v>17277</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>R****** V***********</t>
+          <t>E******* M*******</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>98****9449</t>
+          <t>96****1662</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>8350</v>
+        <v>6750</v>
       </c>
       <c r="E259" t="n">
-        <v>8350</v>
+        <v>6750</v>
       </c>
       <c r="F259" s="1" t="n">
-        <v>46086.63582175926</v>
+        <v>46088.33313657407</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>06-Mar-2026 00:00:00</t>
+          <t>09-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -36738,12 +36746,12 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -36763,13 +36771,13 @@
         <v>1234</v>
       </c>
       <c r="P259" t="n">
-        <v>11000352631037</v>
+        <v>11000352866337</v>
       </c>
       <c r="Q259" t="n">
-        <v>1772703916</v>
+        <v>1772850462</v>
       </c>
       <c r="R259" t="n">
-        <v>617759165517</v>
+        <v>134637860821</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -36828,7 +36836,7 @@
       </c>
       <c r="AF259" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG259" t="inlineStr"/>
@@ -36838,16 +36846,16 @@
         </is>
       </c>
       <c r="AI259" t="n">
-        <v>18766</v>
+        <v>19988</v>
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>267463</t>
+          <t>266775</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="AL259" t="inlineStr">
@@ -36858,30 +36866,30 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>17163</v>
+        <v>17138</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>M******* Z*** K***</t>
+          <t>S**** B******</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>82****8795</t>
+          <t>79****8688</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>6750</v>
+        <v>7750</v>
       </c>
       <c r="E260" t="n">
-        <v>6750</v>
+        <v>7750</v>
       </c>
       <c r="F260" s="1" t="n">
-        <v>46087.03974537037</v>
+        <v>46088.3565625</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>07-Mar-2026 00:00:00</t>
+          <t>09-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -36896,12 +36904,12 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -36921,13 +36929,13 @@
         <v>1234</v>
       </c>
       <c r="P260" t="n">
-        <v>11000352698044</v>
+        <v>11000352872110</v>
       </c>
       <c r="Q260" t="n">
-        <v>1772738726</v>
+        <v>1772852561</v>
       </c>
       <c r="R260" t="n">
-        <v>606512772867</v>
+        <v>814343009761</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -36986,7 +36994,7 @@
       </c>
       <c r="AF260" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG260" t="inlineStr"/>
@@ -36996,16 +37004,16 @@
         </is>
       </c>
       <c r="AI260" t="n">
-        <v>19878</v>
+        <v>19841</v>
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>266693</t>
+          <t>267077</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="AL260" t="inlineStr">
@@ -37016,30 +37024,30 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>15746</v>
+        <v>17139</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Y**** Y******* N****</t>
+          <t>S**** B********* S**</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>94****1196</t>
+          <t>79****8688</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>16700</v>
+        <v>8350</v>
       </c>
       <c r="E261" t="n">
-        <v>16700</v>
+        <v>8350</v>
       </c>
       <c r="F261" s="1" t="n">
-        <v>46087.39373842593</v>
+        <v>46088.36540509259</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>07-Mar-2026 00:00:00</t>
+          <t>09-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -37059,7 +37067,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>sixteen thousand seven hundred</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -37079,13 +37087,13 @@
         <v>1234</v>
       </c>
       <c r="P261" t="n">
-        <v>11000352720949</v>
+        <v>11000352872904</v>
       </c>
       <c r="Q261" t="n">
-        <v>1772769405</v>
+        <v>1772853355</v>
       </c>
       <c r="R261" t="n">
-        <v>685322950436</v>
+        <v>320147941217</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -37154,16 +37162,16 @@
         </is>
       </c>
       <c r="AI261" t="n">
-        <v>18731</v>
+        <v>19842</v>
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>265778,267428</t>
+          <t>267444</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>2050,2058</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="AL261" t="inlineStr">
@@ -37174,28 +37182,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>14949</v>
+        <v>16043</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>M***** S******* L****** S** M** R**</t>
+          <t>V****** V******* M****</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>80****0739</t>
+          <t>76****5088</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>10750</v>
+        <v>8050</v>
       </c>
       <c r="E262" t="n">
-        <v>10750</v>
+        <v>8050</v>
       </c>
       <c r="F262" s="1" t="n">
-        <v>46087.42783564814</v>
-      </c>
-      <c r="G262" t="inlineStr"/>
+        <v>46088.56111111111</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>09-Mar-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H262" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -37208,12 +37220,12 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>VlllX</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>ten thousand seven hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -37233,13 +37245,13 @@
         <v>1234</v>
       </c>
       <c r="P262" t="n">
-        <v>11000352730892</v>
+        <v>11000352923458</v>
       </c>
       <c r="Q262" t="n">
-        <v>1772772303</v>
+        <v>1772870158</v>
       </c>
       <c r="R262" t="n">
-        <v>606553970981</v>
+        <v>405349185208</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
@@ -37258,7 +37270,7 @@
       </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W262" t="inlineStr">
@@ -37298,7 +37310,7 @@
       </c>
       <c r="AF262" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG262" t="inlineStr"/>
@@ -37308,16 +37320,16 @@
         </is>
       </c>
       <c r="AI262" t="n">
-        <v>19326</v>
+        <v>18574</v>
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>268631</t>
+          <t>267267</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="AL262" t="inlineStr">
@@ -37328,28 +37340,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>16894</v>
+        <v>16548</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>S**** V****** S** V***** V******</t>
+          <t>P******* C****** R******</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>85****3683</t>
+          <t>90****9830</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>8650</v>
+        <v>8350</v>
       </c>
       <c r="E263" t="n">
-        <v>8650</v>
+        <v>8350</v>
       </c>
       <c r="F263" s="1" t="n">
-        <v>46087.52810185185</v>
-      </c>
-      <c r="G263" t="inlineStr"/>
+        <v>46088.56423611111</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>09-Mar-2026 00:00:00</t>
+        </is>
+      </c>
       <c r="H263" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -37362,12 +37378,12 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Vll</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>eight thousand six hundred fifty</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -37387,13 +37403,13 @@
         <v>1234</v>
       </c>
       <c r="P263" t="n">
-        <v>11000352765283</v>
+        <v>11000352924719</v>
       </c>
       <c r="Q263" t="n">
-        <v>1772781014</v>
+        <v>1772870522</v>
       </c>
       <c r="R263" t="n">
-        <v>398424860025</v>
+        <v>800388341317</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -37412,7 +37428,7 @@
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W263" t="inlineStr">
@@ -37452,7 +37468,7 @@
       </c>
       <c r="AF263" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG263" t="inlineStr"/>
@@ -37462,16 +37478,16 @@
         </is>
       </c>
       <c r="AI263" t="n">
-        <v>19146</v>
+        <v>18779</v>
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>268377</t>
+          <t>265858</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="AL263" t="inlineStr">
@@ -37482,35 +37498,31 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>17103</v>
+        <v>16761</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>P******** B******* S**</t>
+          <t>T**** T*** K****</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>63****9629</t>
+          <t>97****8884</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>6750</v>
+        <v>8650</v>
       </c>
       <c r="E264" t="n">
-        <v>6750</v>
+        <v>8650</v>
       </c>
       <c r="F264" s="1" t="n">
-        <v>46087.65532407408</v>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>07-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46088.83385416667</v>
+      </c>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESS</t>
+          <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -37520,12 +37532,12 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>Vll</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>eight thousand six hundred fifty</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -37545,13 +37557,13 @@
         <v>1234</v>
       </c>
       <c r="P264" t="n">
-        <v>11000352801097</v>
+        <v>11000352973663</v>
       </c>
       <c r="Q264" t="n">
-        <v>1772791561</v>
+        <v>1772893755</v>
       </c>
       <c r="R264" t="n">
-        <v>149006197244</v>
+        <v>17268084705</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -37570,7 +37582,7 @@
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W264" t="inlineStr">
@@ -37585,7 +37597,7 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>QR_UPI</t>
+          <t>UPI</t>
         </is>
       </c>
       <c r="Z264" t="inlineStr">
@@ -37610,7 +37622,7 @@
       </c>
       <c r="AF264" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
         </is>
       </c>
       <c r="AG264" t="inlineStr"/>
@@ -37620,36 +37632,36 @@
         </is>
       </c>
       <c r="AI264" t="n">
-        <v>18038</v>
+        <v>19103</v>
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>266736</t>
+          <t>268375</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="AL264" t="inlineStr">
         <is>
-          <t>PG QR</t>
+          <t>UPI INTENT</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>17093</v>
+        <v>17305</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>S**** A******</t>
+          <t>T******* D** C******</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>98****7290</t>
+          <t>90****6332</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -37659,11 +37671,11 @@
         <v>6750</v>
       </c>
       <c r="F265" s="1" t="n">
-        <v>46087.65797453704</v>
+        <v>46089.07493055556</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>07-Mar-2026 00:00:00</t>
+          <t>09-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -37703,13 +37715,13 @@
         <v>1234</v>
       </c>
       <c r="P265" t="n">
-        <v>11000352801447</v>
+        <v>11000352997807</v>
       </c>
       <c r="Q265" t="n">
-        <v>1772792222</v>
+        <v>1772914641</v>
       </c>
       <c r="R265" t="n">
-        <v>600442299844</v>
+        <v>606782833518</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -37778,11 +37790,11 @@
         </is>
       </c>
       <c r="AI265" t="n">
-        <v>18047</v>
+        <v>20014</v>
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>265105</t>
+          <t>265025</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -37798,30 +37810,30 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>16167</v>
+        <v>16492</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>V******* L********</t>
+          <t>A****** A****** M*********</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>88****9151</t>
+          <t>99****6244</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>8350</v>
+        <v>8050</v>
       </c>
       <c r="E266" t="n">
-        <v>8350</v>
+        <v>8050</v>
       </c>
       <c r="F266" s="1" t="n">
-        <v>46087.65587962963</v>
+        <v>46089.90702546296</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>07-Mar-2026 00:00:00</t>
+          <t>09-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -37841,7 +37853,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -37861,13 +37873,13 @@
         <v>1234</v>
       </c>
       <c r="P266" t="n">
-        <v>11000352802158</v>
+        <v>11000353087167</v>
       </c>
       <c r="Q266" t="n">
-        <v>1772791748</v>
+        <v>1772986501</v>
       </c>
       <c r="R266" t="n">
-        <v>868411654766</v>
+        <v>880447423383</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -37936,16 +37948,16 @@
         </is>
       </c>
       <c r="AI266" t="n">
-        <v>18687</v>
+        <v>18659</v>
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>267454</t>
+          <t>265664</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="AL266" t="inlineStr">
@@ -37956,16 +37968,16 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>16353</v>
+        <v>16492</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>R***** H********* V*****</t>
+          <t>A****** A****** M*********</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>93****3084</t>
+          <t>99****6244</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -37975,7 +37987,7 @@
         <v>8050</v>
       </c>
       <c r="F267" s="1" t="n">
-        <v>46088.29915509259</v>
+        <v>46089.96021990741</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -38019,13 +38031,13 @@
         <v>1234</v>
       </c>
       <c r="P267" t="n">
-        <v>11000352862728</v>
+        <v>11000353092917</v>
       </c>
       <c r="Q267" t="n">
-        <v>1772847626</v>
+        <v>1772991149</v>
       </c>
       <c r="R267" t="n">
-        <v>813785429091</v>
+        <v>215590265908</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -38094,11 +38106,11 @@
         </is>
       </c>
       <c r="AI267" t="n">
-        <v>18469</v>
+        <v>18659</v>
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>267184</t>
+          <t>267314</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -38114,16 +38126,16 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>17277</v>
+        <v>16966</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>E******* M*******</t>
+          <t>G******* J***** A***** A******</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>96****1662</t>
+          <t>82****6967</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -38133,16 +38145,16 @@
         <v>6750</v>
       </c>
       <c r="F268" s="1" t="n">
-        <v>46088.33313657407</v>
+        <v>46090.37471064815</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>09-Mar-2026 00:00:00</t>
+          <t>10-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESS</t>
+          <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -38177,13 +38189,13 @@
         <v>1234</v>
       </c>
       <c r="P268" t="n">
-        <v>11000352866337</v>
+        <v>11000353120075</v>
       </c>
       <c r="Q268" t="n">
-        <v>1772850462</v>
+        <v>1773026950</v>
       </c>
       <c r="R268" t="n">
-        <v>134637860821</v>
+        <v>979389190536</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -38217,7 +38229,7 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>QR_UPI</t>
+          <t>UPI</t>
         </is>
       </c>
       <c r="Z268" t="inlineStr">
@@ -38252,50 +38264,50 @@
         </is>
       </c>
       <c r="AI268" t="n">
-        <v>19988</v>
+        <v>18059</v>
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>266775</t>
+          <t>265128</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="AL268" t="inlineStr">
         <is>
-          <t>PG QR</t>
+          <t>UPI INTENT</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>17138</v>
+        <v>16211</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>S**** B******</t>
+          <t>P******* J*******</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>79****8688</t>
+          <t>95****0840</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>7750</v>
+        <v>8350</v>
       </c>
       <c r="E269" t="n">
-        <v>7750</v>
+        <v>8350</v>
       </c>
       <c r="F269" s="1" t="n">
-        <v>46088.3565625</v>
+        <v>46090.59347222222</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>09-Mar-2026 00:00:00</t>
+          <t>10-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -38315,7 +38327,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -38335,13 +38347,13 @@
         <v>1234</v>
       </c>
       <c r="P269" t="n">
-        <v>11000352872110</v>
+        <v>11000353205860</v>
       </c>
       <c r="Q269" t="n">
-        <v>1772852561</v>
+        <v>1773045863</v>
       </c>
       <c r="R269" t="n">
-        <v>814343009761</v>
+        <v>618827188164</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -38410,16 +38422,16 @@
         </is>
       </c>
       <c r="AI269" t="n">
-        <v>19841</v>
+        <v>18814</v>
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>267077</t>
+          <t>267504</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="AL269" t="inlineStr">
@@ -38430,32 +38442,28 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>17139</v>
+        <v>15234</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>S**** B********* S**</t>
+          <t>M****** P*****</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>79****8688</t>
+          <t>99****3424</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>8350</v>
+        <v>8650</v>
       </c>
       <c r="E270" t="n">
-        <v>8350</v>
+        <v>8650</v>
       </c>
       <c r="F270" s="1" t="n">
-        <v>46088.36540509259</v>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>09-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46091.42769675926</v>
+      </c>
+      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -38468,12 +38476,12 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>Vll</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>eight thousand six hundred fifty</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -38493,13 +38501,13 @@
         <v>1234</v>
       </c>
       <c r="P270" t="n">
-        <v>11000352872904</v>
+        <v>11000353339581</v>
       </c>
       <c r="Q270" t="n">
-        <v>1772853355</v>
+        <v>1773117932</v>
       </c>
       <c r="R270" t="n">
-        <v>320147941217</v>
+        <v>596296145743</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -38518,7 +38526,7 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W270" t="inlineStr">
@@ -38558,7 +38566,7 @@
       </c>
       <c r="AF270" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
         </is>
       </c>
       <c r="AG270" t="inlineStr"/>
@@ -38568,16 +38576,16 @@
         </is>
       </c>
       <c r="AI270" t="n">
-        <v>19842</v>
+        <v>18995</v>
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>267444</t>
+          <t>268433</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="AL270" t="inlineStr">
@@ -38588,30 +38596,30 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>16043</v>
+        <v>16710</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>V****** V******* M****</t>
+          <t>B********** H*********</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>76****5088</t>
+          <t>98****7129</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>8050</v>
+        <v>7750</v>
       </c>
       <c r="E271" t="n">
-        <v>8050</v>
+        <v>7750</v>
       </c>
       <c r="F271" s="1" t="n">
-        <v>46088.56111111111</v>
+        <v>46091.81101851852</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>09-Mar-2026 00:00:00</t>
+          <t>11-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -38631,7 +38639,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -38651,13 +38659,13 @@
         <v>1234</v>
       </c>
       <c r="P271" t="n">
-        <v>11000352923458</v>
+        <v>11000353447479</v>
       </c>
       <c r="Q271" t="n">
-        <v>1772870158</v>
+        <v>1773151065</v>
       </c>
       <c r="R271" t="n">
-        <v>405349185208</v>
+        <v>918003035791</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -38726,16 +38734,16 @@
         </is>
       </c>
       <c r="AI271" t="n">
-        <v>18574</v>
+        <v>18184</v>
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>267267</t>
+          <t>266804</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="AL271" t="inlineStr">
@@ -38746,16 +38754,16 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>16548</v>
+        <v>15544</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>P******* C****** R******</t>
+          <t>B********** J** A******** S**** S*****</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>90****9830</t>
+          <t>98****7129</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -38765,11 +38773,11 @@
         <v>8350</v>
       </c>
       <c r="F272" s="1" t="n">
-        <v>46088.56423611111</v>
+        <v>46091.8092824074</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>09-Mar-2026 00:00:00</t>
+          <t>11-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -38809,13 +38817,13 @@
         <v>1234</v>
       </c>
       <c r="P272" t="n">
-        <v>11000352924719</v>
+        <v>11000353448162</v>
       </c>
       <c r="Q272" t="n">
-        <v>1772870522</v>
+        <v>1773150910</v>
       </c>
       <c r="R272" t="n">
-        <v>800388341317</v>
+        <v>178077962511</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -38884,16 +38892,16 @@
         </is>
       </c>
       <c r="AI272" t="n">
-        <v>18779</v>
+        <v>18968</v>
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>265858</t>
+          <t>267601</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="AL272" t="inlineStr">
@@ -38904,16 +38912,16 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>16761</v>
+        <v>15009</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>T**** T*** K****</t>
+          <t>G******* G**********</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>97****8884</t>
+          <t>93****3464</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -38923,7 +38931,7 @@
         <v>8650</v>
       </c>
       <c r="F273" s="1" t="n">
-        <v>46088.83385416667</v>
+        <v>46091.82027777778</v>
       </c>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
@@ -38963,13 +38971,13 @@
         <v>1234</v>
       </c>
       <c r="P273" t="n">
-        <v>11000352973663</v>
+        <v>11000353449523</v>
       </c>
       <c r="Q273" t="n">
-        <v>1772893755</v>
+        <v>1773151862</v>
       </c>
       <c r="R273" t="n">
-        <v>17268084705</v>
+        <v>175290481857</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -39038,11 +39046,11 @@
         </is>
       </c>
       <c r="AI273" t="n">
-        <v>19103</v>
+        <v>19026</v>
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>268375</t>
+          <t>268346</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -39058,30 +39066,30 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>17305</v>
+        <v>15824</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>T******* D** C******</t>
+          <t>G******* R***** N******</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>90****6332</t>
+          <t>93****3464</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>6750</v>
+        <v>8050</v>
       </c>
       <c r="E274" t="n">
-        <v>6750</v>
+        <v>8050</v>
       </c>
       <c r="F274" s="1" t="n">
-        <v>46089.07493055556</v>
+        <v>46091.82071759259</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>09-Mar-2026 00:00:00</t>
+          <t>11-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -39096,12 +39104,12 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -39121,13 +39129,13 @@
         <v>1234</v>
       </c>
       <c r="P274" t="n">
-        <v>11000352997807</v>
+        <v>11000353449577</v>
       </c>
       <c r="Q274" t="n">
-        <v>1772914641</v>
+        <v>1773151901</v>
       </c>
       <c r="R274" t="n">
-        <v>606782833518</v>
+        <v>491365461344</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -39186,7 +39194,7 @@
       </c>
       <c r="AF274" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG274" t="inlineStr"/>
@@ -39196,16 +39204,16 @@
         </is>
       </c>
       <c r="AI274" t="n">
-        <v>20014</v>
+        <v>18667</v>
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>265025</t>
+          <t>267322</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="AL274" t="inlineStr">
@@ -39216,35 +39224,35 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>16492</v>
+        <v>16885</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>A****** A****** M*********</t>
+          <t>J**** C*****</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>99****6244</t>
+          <t>81****3759</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>8050</v>
+        <v>7750</v>
       </c>
       <c r="E275" t="n">
-        <v>8050</v>
+        <v>7750</v>
       </c>
       <c r="F275" s="1" t="n">
-        <v>46089.90702546296</v>
+        <v>46094.40575231481</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>09-Mar-2026 00:00:00</t>
+          <t>16-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
+          <t>TRANSACTION IS SUCCESS</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -39259,7 +39267,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -39279,13 +39287,13 @@
         <v>1234</v>
       </c>
       <c r="P275" t="n">
-        <v>11000353087167</v>
+        <v>11000353846215</v>
       </c>
       <c r="Q275" t="n">
-        <v>1772986501</v>
+        <v>1773374772</v>
       </c>
       <c r="R275" t="n">
-        <v>880447423383</v>
+        <v>69448885379</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -39319,7 +39327,7 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>QR_UPI</t>
         </is>
       </c>
       <c r="Z275" t="inlineStr">
@@ -39354,50 +39362,50 @@
         </is>
       </c>
       <c r="AI275" t="n">
-        <v>18659</v>
+        <v>18185</v>
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>265664</t>
+          <t>266808</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="AL275" t="inlineStr">
         <is>
-          <t>UPI INTENT</t>
+          <t>PG QR</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>16492</v>
+        <v>17215</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>A****** A****** M*********</t>
+          <t>S********** S*****</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>99****6244</t>
+          <t>95****8421</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>8050</v>
+        <v>6750</v>
       </c>
       <c r="E276" t="n">
-        <v>8050</v>
+        <v>6750</v>
       </c>
       <c r="F276" s="1" t="n">
-        <v>46089.96021990741</v>
+        <v>46097.52517361111</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>09-Mar-2026 00:00:00</t>
+          <t>17-Mar-2026 00:00:00</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -39412,12 +39420,12 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -39437,13 +39445,13 @@
         <v>1234</v>
       </c>
       <c r="P276" t="n">
-        <v>11000353092917</v>
+        <v>11000354251494</v>
       </c>
       <c r="Q276" t="n">
-        <v>1772991149</v>
+        <v>1773644702</v>
       </c>
       <c r="R276" t="n">
-        <v>215590265908</v>
+        <v>775940371339</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -39502,7 +39510,7 @@
       </c>
       <c r="AF276" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG276" t="inlineStr"/>
@@ -39512,16 +39520,16 @@
         </is>
       </c>
       <c r="AI276" t="n">
-        <v>18659</v>
+        <v>19928</v>
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>267314</t>
+          <t>266698</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="AL276" t="inlineStr">
@@ -39532,32 +39540,28 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>16966</v>
+        <v>16496</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>G******* J***** A***** A******</t>
+          <t>M*********** H******</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>82****6967</t>
+          <t>95****0014</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>6750</v>
+        <v>11350</v>
       </c>
       <c r="E277" t="n">
-        <v>6750</v>
+        <v>11350</v>
       </c>
       <c r="F277" s="1" t="n">
-        <v>46090.37471064815</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>10-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46098.36436342593</v>
+      </c>
+      <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -39570,12 +39574,12 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>VlllX</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>eleven thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -39595,13 +39599,13 @@
         <v>1234</v>
       </c>
       <c r="P277" t="n">
-        <v>11000353120075</v>
+        <v>11000354365594</v>
       </c>
       <c r="Q277" t="n">
-        <v>1773026950</v>
+        <v>1773717239</v>
       </c>
       <c r="R277" t="n">
-        <v>979389190536</v>
+        <v>465060849781</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
@@ -39620,7 +39624,7 @@
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W277" t="inlineStr">
@@ -39660,7 +39664,7 @@
       </c>
       <c r="AF277" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
         </is>
       </c>
       <c r="AG277" t="inlineStr"/>
@@ -39670,16 +39674,16 @@
         </is>
       </c>
       <c r="AI277" t="n">
-        <v>18059</v>
+        <v>19380</v>
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>265128</t>
+          <t>266406</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="AL277" t="inlineStr">
@@ -39690,30 +39694,30 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>16211</v>
+        <v>15945</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>P******* J*******</t>
+          <t>L******* L***** P******</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>95****0840</t>
+          <t>88****3949</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>8350</v>
+        <v>16700</v>
       </c>
       <c r="E278" t="n">
-        <v>8350</v>
+        <v>16700</v>
       </c>
       <c r="F278" s="1" t="n">
-        <v>46090.59347222222</v>
+        <v>46098.45291666667</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>10-Mar-2026 00:00:00</t>
+          <t>18-Mar-2026 18:00:00</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -39733,7 +39737,7 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>sixteen thousand seven hundred</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -39753,13 +39757,13 @@
         <v>1234</v>
       </c>
       <c r="P278" t="n">
-        <v>11000353205860</v>
+        <v>11000354387853</v>
       </c>
       <c r="Q278" t="n">
-        <v>1773045863</v>
+        <v>1773724912</v>
       </c>
       <c r="R278" t="n">
-        <v>618827188164</v>
+        <v>746680379811</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -39828,16 +39832,16 @@
         </is>
       </c>
       <c r="AI278" t="n">
-        <v>18814</v>
+        <v>18833</v>
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>267504</t>
+          <t>265928,267578</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2050,2058</t>
         </is>
       </c>
       <c r="AL278" t="inlineStr">
@@ -39848,28 +39852,32 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>15234</v>
+        <v>17201</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>M****** P*****</t>
+          <t>D***** G**** R*****</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>99****3424</t>
+          <t>94****2534</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>8650</v>
+        <v>7750</v>
       </c>
       <c r="E279" t="n">
-        <v>8650</v>
+        <v>7750</v>
       </c>
       <c r="F279" s="1" t="n">
-        <v>46091.42769675926</v>
-      </c>
-      <c r="G279" t="inlineStr"/>
+        <v>46098.54799768519</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>18-Mar-2026 18:00:00</t>
+        </is>
+      </c>
       <c r="H279" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -39882,12 +39890,12 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Vll</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>eight thousand six hundred fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -39907,13 +39915,13 @@
         <v>1234</v>
       </c>
       <c r="P279" t="n">
-        <v>11000353339581</v>
+        <v>11000354419936</v>
       </c>
       <c r="Q279" t="n">
-        <v>1773117932</v>
+        <v>1773733117</v>
       </c>
       <c r="R279" t="n">
-        <v>596296145743</v>
+        <v>313163971601</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -39932,7 +39940,7 @@
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W279" t="inlineStr">
@@ -39972,7 +39980,7 @@
       </c>
       <c r="AF279" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG279" t="inlineStr"/>
@@ -39982,16 +39990,16 @@
         </is>
       </c>
       <c r="AI279" t="n">
-        <v>18995</v>
+        <v>19915</v>
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>268433</t>
+          <t>266872</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="AL279" t="inlineStr">
@@ -40002,32 +40010,28 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>16710</v>
+        <v>16067</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>B********** H*********</t>
+          <t>M******* A****</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>98****7129</t>
+          <t>98****9010</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>7750</v>
+        <v>10750</v>
       </c>
       <c r="E280" t="n">
-        <v>7750</v>
+        <v>10750</v>
       </c>
       <c r="F280" s="1" t="n">
-        <v>46091.81101851852</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>11-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46099.20768518518</v>
+      </c>
+      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -40040,12 +40044,12 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>VlllX</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>ten thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -40065,13 +40069,13 @@
         <v>1234</v>
       </c>
       <c r="P280" t="n">
-        <v>11000353447479</v>
+        <v>11000354514309</v>
       </c>
       <c r="Q280" t="n">
-        <v>1773151065</v>
+        <v>1773789986</v>
       </c>
       <c r="R280" t="n">
-        <v>918003035791</v>
+        <v>607716423265</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -40090,7 +40094,7 @@
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W280" t="inlineStr">
@@ -40130,7 +40134,7 @@
       </c>
       <c r="AF280" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
         </is>
       </c>
       <c r="AG280" t="inlineStr"/>
@@ -40140,16 +40144,16 @@
         </is>
       </c>
       <c r="AI280" t="n">
-        <v>18184</v>
+        <v>19319</v>
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>266804</t>
+          <t>268635</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="AL280" t="inlineStr">
@@ -40160,35 +40164,31 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>15544</v>
+        <v>16056</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>B********** J** A******** S**** S*****</t>
+          <t>G******** A********</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>98****7129</t>
+          <t>63****9147</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>8350</v>
+        <v>8650</v>
       </c>
       <c r="E281" t="n">
-        <v>8350</v>
+        <v>8650</v>
       </c>
       <c r="F281" s="1" t="n">
-        <v>46091.8092824074</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>11-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46102.42745370371</v>
+      </c>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -40198,12 +40198,12 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>Vll</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>eight thousand six hundred fifty</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -40223,13 +40223,13 @@
         <v>1234</v>
       </c>
       <c r="P281" t="n">
-        <v>11000353448162</v>
+        <v>11000354923104</v>
       </c>
       <c r="Q281" t="n">
-        <v>1773150910</v>
+        <v>1774067934</v>
       </c>
       <c r="R281" t="n">
-        <v>178077962511</v>
+        <v>1.012026080658317e+17</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
@@ -40243,12 +40243,12 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>ICICI UPI QR</t>
+          <t>BANK OF BARODA FSS</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W281" t="inlineStr">
@@ -40263,7 +40263,7 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>UPI</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="Z281" t="inlineStr">
@@ -40288,7 +40288,7 @@
       </c>
       <c r="AF281" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
         </is>
       </c>
       <c r="AG281" t="inlineStr"/>
@@ -40298,48 +40298,48 @@
         </is>
       </c>
       <c r="AI281" t="n">
-        <v>18968</v>
+        <v>19023</v>
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>267601</t>
+          <t>268408</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
         <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="AL281" t="inlineStr">
-        <is>
-          <t>UPI INTENT</t>
-        </is>
-      </c>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="AL281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>15009</v>
+        <v>17316</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>G******* G**********</t>
+          <t>S****** J******</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>93****3464</t>
+          <t>73****3690</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>8650</v>
+        <v>7750</v>
       </c>
       <c r="E282" t="n">
-        <v>8650</v>
+        <v>7750</v>
       </c>
       <c r="F282" s="1" t="n">
-        <v>46091.82027777778</v>
-      </c>
-      <c r="G282" t="inlineStr"/>
+        <v>46105.38423611111</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>25-Mar-2026 17:30:57</t>
+        </is>
+      </c>
       <c r="H282" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -40352,12 +40352,12 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Vll</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>eight thousand six hundred fifty</t>
+          <t>seven thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -40377,13 +40377,13 @@
         <v>1234</v>
       </c>
       <c r="P282" t="n">
-        <v>11000353449523</v>
+        <v>11000355295020</v>
       </c>
       <c r="Q282" t="n">
-        <v>1773151862</v>
+        <v>1774323693</v>
       </c>
       <c r="R282" t="n">
-        <v>175290481857</v>
+        <v>21770993839</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W282" t="inlineStr">
@@ -40442,7 +40442,7 @@
       </c>
       <c r="AF282" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG282" t="inlineStr"/>
@@ -40452,16 +40452,16 @@
         </is>
       </c>
       <c r="AI282" t="n">
-        <v>19026</v>
+        <v>20024</v>
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>268346</t>
+          <t>266903</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="AL282" t="inlineStr">
@@ -40472,30 +40472,30 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>15824</v>
+        <v>15533</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>G******* R***** N******</t>
+          <t>S**** F******</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>93****3464</t>
+          <t>96****9329</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>8050</v>
+        <v>8350</v>
       </c>
       <c r="E283" t="n">
-        <v>8050</v>
+        <v>8350</v>
       </c>
       <c r="F283" s="1" t="n">
-        <v>46091.82071759259</v>
+        <v>46105.40638888889</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>11-Mar-2026 00:00:00</t>
+          <t>25-Mar-2026 17:30:57</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -40515,7 +40515,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>eight thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -40535,13 +40535,13 @@
         <v>1234</v>
       </c>
       <c r="P283" t="n">
-        <v>11000353449577</v>
+        <v>11000355302248</v>
       </c>
       <c r="Q283" t="n">
-        <v>1773151901</v>
+        <v>1774325618</v>
       </c>
       <c r="R283" t="n">
-        <v>491365461344</v>
+        <v>608344330401</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
@@ -40610,16 +40610,16 @@
         </is>
       </c>
       <c r="AI283" t="n">
-        <v>18667</v>
+        <v>18907</v>
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>267322</t>
+          <t>267613</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="AL283" t="inlineStr">
@@ -40630,35 +40630,31 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>16885</v>
+        <v>14888</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>J**** C*****</t>
+          <t>S**** G***** N*****</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>81****3759</t>
+          <t>72****9584</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>7750</v>
+        <v>10750</v>
       </c>
       <c r="E284" t="n">
-        <v>7750</v>
+        <v>10750</v>
       </c>
       <c r="F284" s="1" t="n">
-        <v>46094.40575231481</v>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>16-Mar-2026 00:00:00</t>
-        </is>
-      </c>
+        <v>46105.42898148148</v>
+      </c>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
-          <t>TRANSACTION IS SUCCESS</t>
+          <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -40668,12 +40664,12 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>VlllX</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>ten thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -40693,13 +40689,13 @@
         <v>1234</v>
       </c>
       <c r="P284" t="n">
-        <v>11000353846215</v>
+        <v>11000355309136</v>
       </c>
       <c r="Q284" t="n">
-        <v>1773374772</v>
+        <v>1774327651</v>
       </c>
       <c r="R284" t="n">
-        <v>69448885379</v>
+        <v>608365505153</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -40718,7 +40714,7 @@
       </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W284" t="inlineStr">
@@ -40733,7 +40729,7 @@
       </c>
       <c r="Y284" t="inlineStr">
         <is>
-          <t>QR_UPI</t>
+          <t>UPI</t>
         </is>
       </c>
       <c r="Z284" t="inlineStr">
@@ -40758,7 +40754,7 @@
       </c>
       <c r="AF284" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
         </is>
       </c>
       <c r="AG284" t="inlineStr"/>
@@ -40768,50 +40764,50 @@
         </is>
       </c>
       <c r="AI284" t="n">
-        <v>18185</v>
+        <v>19200</v>
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>266808</t>
+          <t>268605</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="AL284" t="inlineStr">
         <is>
-          <t>PG QR</t>
+          <t>UPI INTENT</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>17215</v>
+        <v>16795</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>S********** S*****</t>
+          <t>M******* A**** S******</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>95****8421</t>
+          <t>87****5241</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>6750</v>
+        <v>8050</v>
       </c>
       <c r="E285" t="n">
-        <v>6750</v>
+        <v>8050</v>
       </c>
       <c r="F285" s="1" t="n">
-        <v>46097.52517361111</v>
+        <v>46105.45387731482</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>17-Mar-2026 00:00:00</t>
+          <t>25-Mar-2026 17:30:57</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -40826,12 +40822,12 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>PREKGUKG</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>six thousand seven hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -40851,13 +40847,13 @@
         <v>1234</v>
       </c>
       <c r="P285" t="n">
-        <v>11000354251494</v>
+        <v>11000355317590</v>
       </c>
       <c r="Q285" t="n">
-        <v>1773644702</v>
+        <v>1774329724</v>
       </c>
       <c r="R285" t="n">
-        <v>775940371339</v>
+        <v>651577243772</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
@@ -40916,7 +40912,7 @@
       </c>
       <c r="AF285" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG285" t="inlineStr"/>
@@ -40926,16 +40922,16 @@
         </is>
       </c>
       <c r="AI285" t="n">
-        <v>19928</v>
+        <v>18523</v>
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>266698</t>
+          <t>267272</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="AL285" t="inlineStr">
@@ -40946,16 +40942,16 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>16496</v>
+        <v>14152</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>M*********** H******</t>
+          <t>G**** Y*****</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>95****0014</t>
+          <t>77****7970</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -40965,7 +40961,7 @@
         <v>11350</v>
       </c>
       <c r="F286" s="1" t="n">
-        <v>46098.36436342593</v>
+        <v>46105.97925925926</v>
       </c>
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
@@ -41005,13 +41001,13 @@
         <v>1234</v>
       </c>
       <c r="P286" t="n">
-        <v>11000354365594</v>
+        <v>11000355439978</v>
       </c>
       <c r="Q286" t="n">
-        <v>1773717239</v>
+        <v>1774375134</v>
       </c>
       <c r="R286" t="n">
-        <v>465060849781</v>
+        <v>588976324936</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
@@ -41080,16 +41076,16 @@
         </is>
       </c>
       <c r="AI286" t="n">
-        <v>19380</v>
+        <v>19353</v>
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>266406</t>
+          <t>268038</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="AL286" t="inlineStr">
@@ -41100,30 +41096,30 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>15945</v>
+        <v>17337</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>L******* L***** P******</t>
+          <t>V******* R***** V*****</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>88****3949</t>
+          <t>96****2924</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>16700</v>
+        <v>6750</v>
       </c>
       <c r="E287" t="n">
-        <v>16700</v>
+        <v>6750</v>
       </c>
       <c r="F287" s="1" t="n">
-        <v>46098.45291666667</v>
+        <v>46107.40277777778</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>18-Mar-2026 18:00:00</t>
+          <t>27-Mar-2026 17:50:52</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -41138,12 +41134,12 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>sixteen thousand seven hundred</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -41163,13 +41159,13 @@
         <v>1234</v>
       </c>
       <c r="P287" t="n">
-        <v>11000354387853</v>
+        <v>11000355626168</v>
       </c>
       <c r="Q287" t="n">
-        <v>1773724912</v>
+        <v>1774498143</v>
       </c>
       <c r="R287" t="n">
-        <v>746680379811</v>
+        <v>589542582308</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
@@ -41228,7 +41224,7 @@
       </c>
       <c r="AF287" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG287" t="inlineStr"/>
@@ -41238,16 +41234,16 @@
         </is>
       </c>
       <c r="AI287" t="n">
-        <v>18833</v>
+        <v>20052</v>
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>265928,267578</t>
+          <t>265102</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>2050,2058</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="AL287" t="inlineStr">
@@ -41258,30 +41254,30 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>17201</v>
+        <v>17268</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>D***** G**** R*****</t>
+          <t>S**** R*****</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>94****2534</t>
+          <t>99****9798</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>7750</v>
+        <v>8050</v>
       </c>
       <c r="E288" t="n">
-        <v>7750</v>
+        <v>8050</v>
       </c>
       <c r="F288" s="1" t="n">
-        <v>46098.54799768519</v>
+        <v>46107.50657407408</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>18-Mar-2026 18:00:00</t>
+          <t>27-Mar-2026 17:50:52</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -41301,7 +41297,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -41321,13 +41317,13 @@
         <v>1234</v>
       </c>
       <c r="P288" t="n">
-        <v>11000354419936</v>
+        <v>11000355648944</v>
       </c>
       <c r="Q288" t="n">
-        <v>1773733117</v>
+        <v>1774507122</v>
       </c>
       <c r="R288" t="n">
-        <v>313163971601</v>
+        <v>38653151868</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -41396,16 +41392,16 @@
         </is>
       </c>
       <c r="AI288" t="n">
-        <v>19915</v>
+        <v>19979</v>
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>266872</t>
+          <t>267152</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="AL288" t="inlineStr">
@@ -41416,28 +41412,32 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>16067</v>
+        <v>16063</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>M******* A****</t>
+          <t>P****** D****</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>98****9010</t>
+          <t>81****4658</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>10750</v>
+        <v>8050</v>
       </c>
       <c r="E289" t="n">
-        <v>10750</v>
+        <v>8050</v>
       </c>
       <c r="F289" s="1" t="n">
-        <v>46099.20768518518</v>
-      </c>
-      <c r="G289" t="inlineStr"/>
+        <v>46107.52826388889</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>27-Mar-2026 17:50:52</t>
+        </is>
+      </c>
       <c r="H289" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -41450,12 +41450,12 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>VlllX</t>
+          <t>lVl</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>ten thousand seven hundred fifty</t>
+          <t>eight thousand fifty</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -41475,13 +41475,13 @@
         <v>1234</v>
       </c>
       <c r="P289" t="n">
-        <v>11000354514309</v>
+        <v>11000355656009</v>
       </c>
       <c r="Q289" t="n">
-        <v>1773789986</v>
+        <v>1774509019</v>
       </c>
       <c r="R289" t="n">
-        <v>607716423265</v>
+        <v>33120254943</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W289" t="inlineStr">
@@ -41540,7 +41540,7 @@
       </c>
       <c r="AF289" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="AG289" t="inlineStr"/>
@@ -41550,16 +41550,16 @@
         </is>
       </c>
       <c r="AI289" t="n">
-        <v>19319</v>
+        <v>18666</v>
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>268635</t>
+          <t>267358</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="AL289" t="inlineStr">
@@ -41570,31 +41570,35 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>16056</v>
+        <v>17187</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>G******** A********</t>
+          <t>C****** V********</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>63****9147</t>
+          <t>88****8971</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>8650</v>
+        <v>6750</v>
       </c>
       <c r="E290" t="n">
-        <v>8650</v>
+        <v>6750</v>
       </c>
       <c r="F290" s="1" t="n">
-        <v>46102.42745370371</v>
-      </c>
-      <c r="G290" t="inlineStr"/>
+        <v>46119.49782407407</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>08-Apr-2026 17:44:13</t>
+        </is>
+      </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
+          <t>TRANSACTION IS SUCCESSFUL</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -41604,12 +41608,12 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Vll</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>eight thousand six hundred fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -41629,13 +41633,13 @@
         <v>1234</v>
       </c>
       <c r="P290" t="n">
-        <v>11000354923104</v>
+        <v>11000357637359</v>
       </c>
       <c r="Q290" t="n">
-        <v>1774067934</v>
+        <v>1775543193</v>
       </c>
       <c r="R290" t="n">
-        <v>1.012026080658317e+17</v>
+        <v>115726878456</v>
       </c>
       <c r="S290" t="inlineStr">
         <is>
@@ -41649,12 +41653,12 @@
       </c>
       <c r="U290" t="inlineStr">
         <is>
-          <t>BANK OF BARODA FSS</t>
+          <t>ICICI UPI QR</t>
         </is>
       </c>
       <c r="V290" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W290" t="inlineStr">
@@ -41669,7 +41673,7 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>UPI</t>
         </is>
       </c>
       <c r="Z290" t="inlineStr">
@@ -41694,7 +41698,7 @@
       </c>
       <c r="AF290" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG290" t="inlineStr"/>
@@ -41704,46 +41708,50 @@
         </is>
       </c>
       <c r="AI290" t="n">
-        <v>19023</v>
+        <v>19901</v>
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>268408</t>
+          <t>266636</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
         <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="AL290" t="inlineStr"/>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL290" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>17316</v>
+        <v>17305</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>S****** J******</t>
+          <t>T******* D** C******</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>73****3690</t>
+          <t>90****6332</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>7750</v>
+        <v>6750</v>
       </c>
       <c r="E291" t="n">
-        <v>7750</v>
+        <v>6750</v>
       </c>
       <c r="F291" s="1" t="n">
-        <v>46105.38423611111</v>
+        <v>46125.16938657407</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>25-Mar-2026 17:30:57</t>
+          <t>15-Apr-2026 18:56:59</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -41758,12 +41766,12 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>PREKGUKG</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>seven thousand seven hundred fifty</t>
+          <t>six thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -41783,13 +41791,13 @@
         <v>1234</v>
       </c>
       <c r="P291" t="n">
-        <v>11000355295020</v>
+        <v>11000358726442</v>
       </c>
       <c r="Q291" t="n">
-        <v>1774323693</v>
+        <v>1776032165</v>
       </c>
       <c r="R291" t="n">
-        <v>21770993839</v>
+        <v>610345470155</v>
       </c>
       <c r="S291" t="inlineStr">
         <is>
@@ -41848,7 +41856,7 @@
       </c>
       <c r="AF291" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
         </is>
       </c>
       <c r="AG291" t="inlineStr"/>
@@ -41858,16 +41866,16 @@
         </is>
       </c>
       <c r="AI291" t="n">
-        <v>20024</v>
+        <v>20014</v>
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>266903</t>
+          <t>266675</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="AL291" t="inlineStr">
@@ -41878,32 +41886,28 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>15533</v>
+        <v>14449</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>S**** F******</t>
+          <t>M****** R** M***</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>96****9329</t>
+          <t>70****8467</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>8350</v>
+        <v>11350</v>
       </c>
       <c r="E292" t="n">
-        <v>8350</v>
+        <v>11350</v>
       </c>
       <c r="F292" s="1" t="n">
-        <v>46105.40638888889</v>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>25-Mar-2026 17:30:57</t>
-        </is>
-      </c>
+        <v>46160.44135416667</v>
+      </c>
+      <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -41916,12 +41920,12 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>VlllX</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>eight thousand three hundred fifty</t>
+          <t>eleven thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -41941,13 +41945,13 @@
         <v>1234</v>
       </c>
       <c r="P292" t="n">
-        <v>11000355302248</v>
+        <v>11000364281496</v>
       </c>
       <c r="Q292" t="n">
-        <v>1774325618</v>
+        <v>1779080707</v>
       </c>
       <c r="R292" t="n">
-        <v>608344330401</v>
+        <v>942368107439</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
@@ -41966,7 +41970,7 @@
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W292" t="inlineStr">
@@ -42006,7 +42010,7 @@
       </c>
       <c r="AF292" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
         </is>
       </c>
       <c r="AG292" t="inlineStr"/>
@@ -42016,16 +42020,16 @@
         </is>
       </c>
       <c r="AI292" t="n">
-        <v>18907</v>
+        <v>19545</v>
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>267613</t>
+          <t>268237</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="AL292" t="inlineStr">
@@ -42036,26 +42040,26 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>14888</v>
+        <v>14569</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>S**** G***** N*****</t>
+          <t>P***** R******** V****** S**</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>72****9584</t>
+          <t>99****2139</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>10750</v>
+        <v>11350</v>
       </c>
       <c r="E293" t="n">
-        <v>10750</v>
+        <v>11350</v>
       </c>
       <c r="F293" s="1" t="n">
-        <v>46105.42898148148</v>
+        <v>46163.2934375</v>
       </c>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
@@ -42075,7 +42079,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>ten thousand seven hundred fifty</t>
+          <t>eleven thousand three hundred fifty</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -42095,13 +42099,13 @@
         <v>1234</v>
       </c>
       <c r="P293" t="n">
-        <v>11000355309136</v>
+        <v>11000364668065</v>
       </c>
       <c r="Q293" t="n">
-        <v>1774327651</v>
+        <v>1779327111</v>
       </c>
       <c r="R293" t="n">
-        <v>608365505153</v>
+        <v>522315152692</v>
       </c>
       <c r="S293" t="inlineStr">
         <is>
@@ -42170,16 +42174,16 @@
         </is>
       </c>
       <c r="AI293" t="n">
-        <v>19200</v>
+        <v>19505</v>
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>268605</t>
+          <t>268258</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="AL293" t="inlineStr">
@@ -42190,32 +42194,28 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>16795</v>
+        <v>17061</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>M******* A**** S******</t>
+          <t>P**** H********* N****</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>87****5241</t>
+          <t>97****1097</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>8050</v>
+        <v>10750</v>
       </c>
       <c r="E294" t="n">
-        <v>8050</v>
+        <v>10750</v>
       </c>
       <c r="F294" s="1" t="n">
-        <v>46105.45387731482</v>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>25-Mar-2026 17:30:57</t>
-        </is>
-      </c>
+        <v>46164.96425925926</v>
+      </c>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -42228,12 +42228,12 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>lVl</t>
+          <t>VlllX</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>eight thousand fifty</t>
+          <t>ten thousand seven hundred fifty</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -42253,13 +42253,13 @@
         <v>1234</v>
       </c>
       <c r="P294" t="n">
-        <v>11000355317590</v>
+        <v>11000364914421</v>
       </c>
       <c r="Q294" t="n">
-        <v>1774329724</v>
+        <v>1779471487</v>
       </c>
       <c r="R294" t="n">
-        <v>651577243772</v>
+        <v>216518110197</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W294" t="inlineStr">
@@ -42318,7 +42318,7 @@
       </c>
       <c r="AF294" t="inlineStr">
         <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
         </is>
       </c>
       <c r="AG294" t="inlineStr"/>
@@ -42328,805 +42328,19 @@
         </is>
       </c>
       <c r="AI294" t="n">
-        <v>18523</v>
+        <v>19153</v>
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>267272</t>
+          <t>268588</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="AL294" t="inlineStr">
-        <is>
-          <t>UPI INTENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>14152</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>G**** Y*****</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>77****7970</t>
-        </is>
-      </c>
-      <c r="D295" t="n">
-        <v>11350</v>
-      </c>
-      <c r="E295" t="n">
-        <v>11350</v>
-      </c>
-      <c r="F295" s="1" t="n">
-        <v>46105.97925925926</v>
-      </c>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>VlllX</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>eleven thousand three hundred fifty</t>
-        </is>
-      </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t>********6600</t>
-        </is>
-      </c>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>SALESIAN EDUCATION SOCIETY</t>
-        </is>
-      </c>
-      <c r="N295" t="n">
-        <v>753702</v>
-      </c>
-      <c r="O295" t="n">
-        <v>1234</v>
-      </c>
-      <c r="P295" t="n">
-        <v>11000355439978</v>
-      </c>
-      <c r="Q295" t="n">
-        <v>1774375134</v>
-      </c>
-      <c r="R295" t="n">
-        <v>588976324936</v>
-      </c>
-      <c r="S295" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="T295" t="inlineStr">
-        <is>
-          <t>sale</t>
-        </is>
-      </c>
-      <c r="U295" t="inlineStr">
-        <is>
-          <t>ICICI UPI QR</t>
-        </is>
-      </c>
-      <c r="V295" t="inlineStr">
-        <is>
-          <t>RNS</t>
-        </is>
-      </c>
-      <c r="W295" t="inlineStr">
-        <is>
-          <t>SIBL0000899</t>
-        </is>
-      </c>
-      <c r="X295" t="inlineStr">
-        <is>
-          <t>MERCHANT</t>
-        </is>
-      </c>
-      <c r="Y295" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="Z295" t="inlineStr">
-        <is>
-          <t>k*************@gmail.com</t>
-        </is>
-      </c>
-      <c r="AA295" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB295" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC295" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD295" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE295" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AF295" t="inlineStr">
-        <is>
-          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
-        </is>
-      </c>
-      <c r="AG295" t="inlineStr"/>
-      <c r="AH295" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="AI295" t="n">
-        <v>19353</v>
-      </c>
-      <c r="AJ295" t="inlineStr">
-        <is>
-          <t>268038</t>
-        </is>
-      </c>
-      <c r="AK295" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="AL295" t="inlineStr">
-        <is>
-          <t>UPI INTENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>17337</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>V******* R***** V*****</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>96****2924</t>
-        </is>
-      </c>
-      <c r="D296" t="n">
-        <v>6750</v>
-      </c>
-      <c r="E296" t="n">
-        <v>6750</v>
-      </c>
-      <c r="F296" s="1" t="n">
-        <v>46107.40277777778</v>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>27-Mar-2026 17:50:52</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>PREKGUKG</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>six thousand seven hundred fifty</t>
-        </is>
-      </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>********6600</t>
-        </is>
-      </c>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>SALESIAN EDUCATION SOCIETY</t>
-        </is>
-      </c>
-      <c r="N296" t="n">
-        <v>753702</v>
-      </c>
-      <c r="O296" t="n">
-        <v>1234</v>
-      </c>
-      <c r="P296" t="n">
-        <v>11000355626168</v>
-      </c>
-      <c r="Q296" t="n">
-        <v>1774498143</v>
-      </c>
-      <c r="R296" t="n">
-        <v>589542582308</v>
-      </c>
-      <c r="S296" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="T296" t="inlineStr">
-        <is>
-          <t>sale</t>
-        </is>
-      </c>
-      <c r="U296" t="inlineStr">
-        <is>
-          <t>ICICI UPI QR</t>
-        </is>
-      </c>
-      <c r="V296" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="W296" t="inlineStr">
-        <is>
-          <t>SIBL0000899</t>
-        </is>
-      </c>
-      <c r="X296" t="inlineStr">
-        <is>
-          <t>MERCHANT</t>
-        </is>
-      </c>
-      <c r="Y296" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>k*************@gmail.com</t>
-        </is>
-      </c>
-      <c r="AA296" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB296" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC296" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD296" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE296" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AF296" t="inlineStr">
-        <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
-        </is>
-      </c>
-      <c r="AG296" t="inlineStr"/>
-      <c r="AH296" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="AI296" t="n">
-        <v>20052</v>
-      </c>
-      <c r="AJ296" t="inlineStr">
-        <is>
-          <t>265102</t>
-        </is>
-      </c>
-      <c r="AK296" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="AL296" t="inlineStr">
-        <is>
-          <t>UPI INTENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>17268</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>S**** R*****</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>99****9798</t>
-        </is>
-      </c>
-      <c r="D297" t="n">
-        <v>8050</v>
-      </c>
-      <c r="E297" t="n">
-        <v>8050</v>
-      </c>
-      <c r="F297" s="1" t="n">
-        <v>46107.50657407408</v>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>27-Mar-2026 17:50:52</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>lVl</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>eight thousand fifty</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>********6600</t>
-        </is>
-      </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>SALESIAN EDUCATION SOCIETY</t>
-        </is>
-      </c>
-      <c r="N297" t="n">
-        <v>753702</v>
-      </c>
-      <c r="O297" t="n">
-        <v>1234</v>
-      </c>
-      <c r="P297" t="n">
-        <v>11000355648944</v>
-      </c>
-      <c r="Q297" t="n">
-        <v>1774507122</v>
-      </c>
-      <c r="R297" t="n">
-        <v>38653151868</v>
-      </c>
-      <c r="S297" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="T297" t="inlineStr">
-        <is>
-          <t>sale</t>
-        </is>
-      </c>
-      <c r="U297" t="inlineStr">
-        <is>
-          <t>ICICI UPI QR</t>
-        </is>
-      </c>
-      <c r="V297" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="W297" t="inlineStr">
-        <is>
-          <t>SIBL0000899</t>
-        </is>
-      </c>
-      <c r="X297" t="inlineStr">
-        <is>
-          <t>MERCHANT</t>
-        </is>
-      </c>
-      <c r="Y297" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>k*************@gmail.com</t>
-        </is>
-      </c>
-      <c r="AA297" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB297" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC297" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD297" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE297" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AF297" t="inlineStr">
-        <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
-        </is>
-      </c>
-      <c r="AG297" t="inlineStr"/>
-      <c r="AH297" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="AI297" t="n">
-        <v>19979</v>
-      </c>
-      <c r="AJ297" t="inlineStr">
-        <is>
-          <t>267152</t>
-        </is>
-      </c>
-      <c r="AK297" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="AL297" t="inlineStr">
-        <is>
-          <t>UPI INTENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>16063</v>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>P****** D****</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>81****4658</t>
-        </is>
-      </c>
-      <c r="D298" t="n">
-        <v>8050</v>
-      </c>
-      <c r="E298" t="n">
-        <v>8050</v>
-      </c>
-      <c r="F298" s="1" t="n">
-        <v>46107.52826388889</v>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>27-Mar-2026 17:50:52</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>lVl</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>eight thousand fifty</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>********6600</t>
-        </is>
-      </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>SALESIAN EDUCATION SOCIETY</t>
-        </is>
-      </c>
-      <c r="N298" t="n">
-        <v>753702</v>
-      </c>
-      <c r="O298" t="n">
-        <v>1234</v>
-      </c>
-      <c r="P298" t="n">
-        <v>11000355656009</v>
-      </c>
-      <c r="Q298" t="n">
-        <v>1774509019</v>
-      </c>
-      <c r="R298" t="n">
-        <v>33120254943</v>
-      </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="T298" t="inlineStr">
-        <is>
-          <t>sale</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>ICICI UPI QR</t>
-        </is>
-      </c>
-      <c r="V298" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="W298" t="inlineStr">
-        <is>
-          <t>SIBL0000899</t>
-        </is>
-      </c>
-      <c r="X298" t="inlineStr">
-        <is>
-          <t>MERCHANT</t>
-        </is>
-      </c>
-      <c r="Y298" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="Z298" t="inlineStr">
-        <is>
-          <t>k*************@gmail.com</t>
-        </is>
-      </c>
-      <c r="AA298" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB298" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC298" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD298" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE298" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AF298" t="inlineStr">
-        <is>
-          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
-        </is>
-      </c>
-      <c r="AG298" t="inlineStr"/>
-      <c r="AH298" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="AI298" t="n">
-        <v>18666</v>
-      </c>
-      <c r="AJ298" t="inlineStr">
-        <is>
-          <t>267358</t>
-        </is>
-      </c>
-      <c r="AK298" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="AL298" t="inlineStr">
-        <is>
-          <t>UPI INTENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>17187</v>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>C****** V********</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>88****8971</t>
-        </is>
-      </c>
-      <c r="D299" t="n">
-        <v>6750</v>
-      </c>
-      <c r="E299" t="n">
-        <v>6750</v>
-      </c>
-      <c r="F299" s="1" t="n">
-        <v>46119.49782407407</v>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>08-Apr-2026 17:44:13</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>TRANSACTION IS SUCCESSFUL</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>PREKGUKG</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>six thousand seven hundred fifty</t>
-        </is>
-      </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>********6600</t>
-        </is>
-      </c>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>SALESIAN EDUCATION SOCIETY</t>
-        </is>
-      </c>
-      <c r="N299" t="n">
-        <v>753702</v>
-      </c>
-      <c r="O299" t="n">
-        <v>1234</v>
-      </c>
-      <c r="P299" t="n">
-        <v>11000357637359</v>
-      </c>
-      <c r="Q299" t="n">
-        <v>1775543193</v>
-      </c>
-      <c r="R299" t="n">
-        <v>115726878456</v>
-      </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="T299" t="inlineStr">
-        <is>
-          <t>sale</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr">
-        <is>
-          <t>ICICI UPI QR</t>
-        </is>
-      </c>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="W299" t="inlineStr">
-        <is>
-          <t>SIBL0000899</t>
-        </is>
-      </c>
-      <c r="X299" t="inlineStr">
-        <is>
-          <t>MERCHANT</t>
-        </is>
-      </c>
-      <c r="Y299" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>k*************@gmail.com</t>
-        </is>
-      </c>
-      <c r="AA299" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB299" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC299" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD299" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE299" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AF299" t="inlineStr">
-        <is>
-          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
-        </is>
-      </c>
-      <c r="AG299" t="inlineStr"/>
-      <c r="AH299" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="AI299" t="n">
-        <v>19901</v>
-      </c>
-      <c r="AJ299" t="inlineStr">
-        <is>
-          <t>266636</t>
-        </is>
-      </c>
-      <c r="AK299" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="AL299" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL395"/>
+  <dimension ref="A1:AL407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,8 +628,10 @@
       <c r="E2" t="n">
         <v>7750</v>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>45960.51997685185</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30-Oct-2025 12:28:46</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -786,8 +784,10 @@
       <c r="E3" t="n">
         <v>11350</v>
       </c>
-      <c r="F3" s="1" t="n">
-        <v>45960.90091435185</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>30-Oct-2025 21:37:19</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -936,8 +936,10 @@
       <c r="E4" t="n">
         <v>6750</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>45961.37190972222</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>31-Oct-2025 08:55:33</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1094,8 +1096,10 @@
       <c r="E5" t="n">
         <v>8250</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>45961.67337962963</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>31-Oct-2025 16:09:40</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1248,8 +1252,10 @@
       <c r="E6" t="n">
         <v>11250</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>45961.81483796296</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>31-Oct-2025 19:33:22</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1402,8 +1408,10 @@
       <c r="E7" t="n">
         <v>8850</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>45961.81548611111</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31-Oct-2025 19:34:18</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1560,8 +1568,10 @@
       <c r="E8" t="n">
         <v>8050</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>45962.3549537037</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>01-Nov-2025 08:31:08</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1714,8 +1724,10 @@
       <c r="E9" t="n">
         <v>8250</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>45962.77892361111</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>01-Nov-2025 18:41:39</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1868,8 +1880,10 @@
       <c r="E10" t="n">
         <v>8550</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>45962.7806712963</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>01-Nov-2025 18:44:10</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2022,8 +2036,10 @@
       <c r="E11" t="n">
         <v>8250</v>
       </c>
-      <c r="F11" s="1" t="n">
-        <v>45962.79679398148</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>01-Nov-2025 19:07:23</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2176,8 +2192,10 @@
       <c r="E12" t="n">
         <v>6750</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>45962.82130787037</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>01-Nov-2025 19:42:41</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2334,8 +2352,10 @@
       <c r="E13" t="n">
         <v>8850</v>
       </c>
-      <c r="F13" s="1" t="n">
-        <v>45963.27521990741</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>02-Nov-2025 06:36:19</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2492,8 +2512,10 @@
       <c r="E14" t="n">
         <v>8250</v>
       </c>
-      <c r="F14" s="1" t="n">
-        <v>45963.27019675926</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>02-Nov-2025 06:29:05</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2650,8 +2672,10 @@
       <c r="E15" t="n">
         <v>6750</v>
       </c>
-      <c r="F15" s="1" t="n">
-        <v>45963.57991898148</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>02-Nov-2025 13:55:05</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2804,8 +2828,10 @@
       <c r="E16" t="n">
         <v>8050</v>
       </c>
-      <c r="F16" s="1" t="n">
-        <v>45963.57731481481</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>02-Nov-2025 13:51:20</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2958,8 +2984,10 @@
       <c r="E17" t="n">
         <v>6750</v>
       </c>
-      <c r="F17" s="1" t="n">
-        <v>45964.40340277777</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>03-Nov-2025 09:40:54</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3116,8 +3144,10 @@
       <c r="E18" t="n">
         <v>8350</v>
       </c>
-      <c r="F18" s="1" t="n">
-        <v>45964.44721064815</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>03-Nov-2025 10:43:59</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3274,8 +3304,10 @@
       <c r="E19" t="n">
         <v>7750</v>
       </c>
-      <c r="F19" s="1" t="n">
-        <v>45964.47178240741</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>03-Nov-2025 11:19:22</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3428,8 +3460,10 @@
       <c r="E20" t="n">
         <v>500</v>
       </c>
-      <c r="F20" s="1" t="n">
-        <v>45964.47362268518</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>03-Nov-2025 11:22:01</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3582,8 +3616,10 @@
       <c r="E21" t="n">
         <v>6750</v>
       </c>
-      <c r="F21" s="1" t="n">
-        <v>45965.24141203704</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>04-Nov-2025 05:47:38</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3736,8 +3772,10 @@
       <c r="E22" t="n">
         <v>11850</v>
       </c>
-      <c r="F22" s="1" t="n">
-        <v>45965.41743055556</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>04-Nov-2025 10:01:06</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3886,8 +3924,10 @@
       <c r="E23" t="n">
         <v>8550</v>
       </c>
-      <c r="F23" s="1" t="n">
-        <v>45965.50827546296</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>04-Nov-2025 12:11:55</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -4040,8 +4080,10 @@
       <c r="E24" t="n">
         <v>9150</v>
       </c>
-      <c r="F24" s="1" t="n">
-        <v>45965.50665509259</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>04-Nov-2025 12:09:35</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -4190,8 +4232,10 @@
       <c r="E25" t="n">
         <v>7750</v>
       </c>
-      <c r="F25" s="1" t="n">
-        <v>45965.62467592592</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>04-Nov-2025 14:59:32</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4344,8 +4388,10 @@
       <c r="E26" t="n">
         <v>8250</v>
       </c>
-      <c r="F26" s="1" t="n">
-        <v>45965.96628472222</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>04-Nov-2025 23:11:27</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4498,8 +4544,10 @@
       <c r="E27" t="n">
         <v>16000</v>
       </c>
-      <c r="F27" s="1" t="n">
-        <v>45966.32918981482</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>05-Nov-2025 07:54:02</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4652,8 +4700,10 @@
       <c r="E28" t="n">
         <v>8250</v>
       </c>
-      <c r="F28" s="1" t="n">
-        <v>45967.40608796296</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>06-Nov-2025 09:44:46</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4806,8 +4856,10 @@
       <c r="E29" t="n">
         <v>8350</v>
       </c>
-      <c r="F29" s="1" t="n">
-        <v>45967.49935185185</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>06-Nov-2025 11:59:04</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4964,8 +5016,10 @@
       <c r="E30" t="n">
         <v>6750</v>
       </c>
-      <c r="F30" s="1" t="n">
-        <v>45967.78626157407</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>06-Nov-2025 18:52:13</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5118,8 +5172,10 @@
       <c r="E31" t="n">
         <v>6750</v>
       </c>
-      <c r="F31" s="1" t="n">
-        <v>45968.47615740741</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>07-Nov-2025 11:25:40</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -5272,8 +5328,10 @@
       <c r="E32" t="n">
         <v>8350</v>
       </c>
-      <c r="F32" s="1" t="n">
-        <v>45971.39392361111</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10-Nov-2025 09:27:15</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -5426,8 +5484,10 @@
       <c r="E33" t="n">
         <v>10750</v>
       </c>
-      <c r="F33" s="1" t="n">
-        <v>45971.88681712963</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10-Nov-2025 21:17:01</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
@@ -5576,8 +5636,10 @@
       <c r="E34" t="n">
         <v>6750</v>
       </c>
-      <c r="F34" s="1" t="n">
-        <v>45972.2457175926</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>11-Nov-2025 05:53:50</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5734,8 +5796,10 @@
       <c r="E35" t="n">
         <v>8350</v>
       </c>
-      <c r="F35" s="1" t="n">
-        <v>45972.42304398148</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>11-Nov-2025 10:09:11</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5888,8 +5952,10 @@
       <c r="E36" t="n">
         <v>11350</v>
       </c>
-      <c r="F36" s="1" t="n">
-        <v>45972.42407407407</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>11-Nov-2025 10:10:40</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
@@ -6038,8 +6104,10 @@
       <c r="E37" t="n">
         <v>7750</v>
       </c>
-      <c r="F37" s="1" t="n">
-        <v>45972.68189814815</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>11-Nov-2025 16:21:56</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6196,8 +6264,10 @@
       <c r="E38" t="n">
         <v>6750</v>
       </c>
-      <c r="F38" s="1" t="n">
-        <v>45972.68135416666</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11-Nov-2025 16:21:09</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6354,8 +6424,10 @@
       <c r="E39" t="n">
         <v>6750</v>
       </c>
-      <c r="F39" s="1" t="n">
-        <v>45973.383125</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>12-Nov-2025 09:11:42</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6508,8 +6580,10 @@
       <c r="E40" t="n">
         <v>8350</v>
       </c>
-      <c r="F40" s="1" t="n">
-        <v>45973.43945601852</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>12-Nov-2025 10:32:49</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6666,8 +6740,10 @@
       <c r="E41" t="n">
         <v>7750</v>
       </c>
-      <c r="F41" s="1" t="n">
-        <v>45974.34503472222</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>13-Nov-2025 08:16:51</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6820,8 +6896,10 @@
       <c r="E42" t="n">
         <v>6750</v>
       </c>
-      <c r="F42" s="1" t="n">
-        <v>45974.73070601852</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>13-Nov-2025 17:32:13</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6978,8 +7056,10 @@
       <c r="E43" t="n">
         <v>11250</v>
       </c>
-      <c r="F43" s="1" t="n">
-        <v>45974.85033564815</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>13-Nov-2025 20:24:29</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -7128,8 +7208,10 @@
       <c r="E44" t="n">
         <v>8550</v>
       </c>
-      <c r="F44" s="1" t="n">
-        <v>45975.84425925926</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>14-Nov-2025 20:15:44</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7282,8 +7364,10 @@
       <c r="E45" t="n">
         <v>8850</v>
       </c>
-      <c r="F45" s="1" t="n">
-        <v>45975.86135416666</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>14-Nov-2025 20:40:21</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7436,8 +7520,10 @@
       <c r="E46" t="n">
         <v>8350</v>
       </c>
-      <c r="F46" s="1" t="n">
-        <v>45975.86333333333</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>14-Nov-2025 20:43:12</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7590,8 +7676,10 @@
       <c r="E47" t="n">
         <v>8850</v>
       </c>
-      <c r="F47" s="1" t="n">
-        <v>45976.33364583334</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 08:00:27</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7744,8 +7832,10 @@
       <c r="E48" t="n">
         <v>8550</v>
       </c>
-      <c r="F48" s="1" t="n">
-        <v>45976.44155092593</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 10:35:50</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -7898,8 +7988,10 @@
       <c r="E49" t="n">
         <v>8050</v>
       </c>
-      <c r="F49" s="1" t="n">
-        <v>45976.58525462963</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 14:02:46</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -8056,8 +8148,10 @@
       <c r="E50" t="n">
         <v>7750</v>
       </c>
-      <c r="F50" s="1" t="n">
-        <v>45976.59844907407</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 14:21:46</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -8210,8 +8304,10 @@
       <c r="E51" t="n">
         <v>8850</v>
       </c>
-      <c r="F51" s="1" t="n">
-        <v>45976.8278125</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>15-Nov-2025 19:52:03</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -8364,8 +8460,10 @@
       <c r="E52" t="n">
         <v>8850</v>
       </c>
-      <c r="F52" s="1" t="n">
-        <v>45978.64869212963</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>17-Nov-2025 15:34:07</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -8522,8 +8620,10 @@
       <c r="E53" t="n">
         <v>11350</v>
       </c>
-      <c r="F53" s="1" t="n">
-        <v>45979.4366087963</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>18-Nov-2025 10:28:43</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
@@ -8672,8 +8772,10 @@
       <c r="E54" t="n">
         <v>16700</v>
       </c>
-      <c r="F54" s="1" t="n">
-        <v>45979.4855787037</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>18-Nov-2025 11:39:14</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -8826,8 +8928,10 @@
       <c r="E55" t="n">
         <v>8350</v>
       </c>
-      <c r="F55" s="1" t="n">
-        <v>45979.69571759259</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>18-Nov-2025 16:41:50</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -8980,8 +9084,10 @@
       <c r="E56" t="n">
         <v>8250</v>
       </c>
-      <c r="F56" s="1" t="n">
-        <v>45980.38296296296</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 09:11:28</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -9138,8 +9244,10 @@
       <c r="E57" t="n">
         <v>8250</v>
       </c>
-      <c r="F57" s="1" t="n">
-        <v>45980.55233796296</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 13:15:22</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -9296,8 +9404,10 @@
       <c r="E58" t="n">
         <v>6750</v>
       </c>
-      <c r="F58" s="1" t="n">
-        <v>45980.64653935185</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 15:31:01</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -9450,8 +9560,10 @@
       <c r="E59" t="n">
         <v>8550</v>
       </c>
-      <c r="F59" s="1" t="n">
-        <v>45980.69329861111</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 16:38:21</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -9608,8 +9720,10 @@
       <c r="E60" t="n">
         <v>9150</v>
       </c>
-      <c r="F60" s="1" t="n">
-        <v>45980.76140046296</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 18:16:25</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -9758,8 +9872,10 @@
       <c r="E61" t="n">
         <v>6750</v>
       </c>
-      <c r="F61" s="1" t="n">
-        <v>45980.87599537037</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>19-Nov-2025 21:01:26</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -9912,8 +10028,10 @@
       <c r="E62" t="n">
         <v>8050</v>
       </c>
-      <c r="F62" s="1" t="n">
-        <v>45981.36634259259</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 08:47:32</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -10070,8 +10188,10 @@
       <c r="E63" t="n">
         <v>7750</v>
       </c>
-      <c r="F63" s="1" t="n">
-        <v>45981.36780092592</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 08:49:38</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -10228,8 +10348,10 @@
       <c r="E64" t="n">
         <v>8850</v>
       </c>
-      <c r="F64" s="1" t="n">
-        <v>45981.49039351852</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 11:46:10</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -10386,8 +10508,10 @@
       <c r="E65" t="n">
         <v>6750</v>
       </c>
-      <c r="F65" s="1" t="n">
-        <v>45981.57496527778</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 13:47:57</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -10540,8 +10664,10 @@
       <c r="E66" t="n">
         <v>11250</v>
       </c>
-      <c r="F66" s="1" t="n">
-        <v>45981.61152777778</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 14:40:36</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -10690,8 +10816,10 @@
       <c r="E67" t="n">
         <v>8550</v>
       </c>
-      <c r="F67" s="1" t="n">
-        <v>45981.70946759259</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 17:01:38</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -10844,8 +10972,10 @@
       <c r="E68" t="n">
         <v>8850</v>
       </c>
-      <c r="F68" s="1" t="n">
-        <v>45981.71714120371</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 17:12:41</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -10998,8 +11128,10 @@
       <c r="E69" t="n">
         <v>500</v>
       </c>
-      <c r="F69" s="1" t="n">
-        <v>45981.83467592593</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 20:01:56</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -11156,8 +11288,10 @@
       <c r="E70" t="n">
         <v>8050</v>
       </c>
-      <c r="F70" s="1" t="n">
-        <v>45981.87472222222</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 20:59:36</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -11310,8 +11444,10 @@
       <c r="E71" t="n">
         <v>9150</v>
       </c>
-      <c r="F71" s="1" t="n">
-        <v>45981.90913194444</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>20-Nov-2025 21:49:09</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -11460,8 +11596,10 @@
       <c r="E72" t="n">
         <v>8550</v>
       </c>
-      <c r="F72" s="1" t="n">
-        <v>45982.29965277778</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 07:11:30</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -11618,8 +11756,10 @@
       <c r="E73" t="n">
         <v>17800</v>
       </c>
-      <c r="F73" s="1" t="n">
-        <v>45982.38402777778</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 09:13:00</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -11772,8 +11912,10 @@
       <c r="E74" t="n">
         <v>8850</v>
       </c>
-      <c r="F74" s="1" t="n">
-        <v>45982.44829861111</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 10:45:33</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -11930,8 +12072,10 @@
       <c r="E75" t="n">
         <v>11250</v>
       </c>
-      <c r="F75" s="1" t="n">
-        <v>45982.44917824074</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 10:46:49</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -12084,8 +12228,10 @@
       <c r="E76" t="n">
         <v>11350</v>
       </c>
-      <c r="F76" s="1" t="n">
-        <v>45982.61246527778</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 14:41:57</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
@@ -12234,8 +12380,10 @@
       <c r="E77" t="n">
         <v>7750</v>
       </c>
-      <c r="F77" s="1" t="n">
-        <v>45982.74950231481</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>21-Nov-2025 17:59:17</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -12388,8 +12536,10 @@
       <c r="E78" t="n">
         <v>8550</v>
       </c>
-      <c r="F78" s="1" t="n">
-        <v>45983.30008101852</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 07:12:07</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -12542,8 +12692,10 @@
       <c r="E79" t="n">
         <v>8550</v>
       </c>
-      <c r="F79" s="1" t="n">
-        <v>45983.36186342593</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 08:41:05</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -12700,8 +12852,10 @@
       <c r="E80" t="n">
         <v>9150</v>
       </c>
-      <c r="F80" s="1" t="n">
-        <v>45983.36431712963</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 08:44:37</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -12854,8 +13008,10 @@
       <c r="E81" t="n">
         <v>8250</v>
       </c>
-      <c r="F81" s="1" t="n">
-        <v>45983.39858796296</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 09:33:58</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -13012,8 +13168,10 @@
       <c r="E82" t="n">
         <v>8250</v>
       </c>
-      <c r="F82" s="1" t="n">
-        <v>45983.41388888889</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 09:56:00</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -13166,8 +13324,10 @@
       <c r="E83" t="n">
         <v>8250</v>
       </c>
-      <c r="F83" s="1" t="n">
-        <v>45983.44782407407</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 10:44:52</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -13324,8 +13484,10 @@
       <c r="E84" t="n">
         <v>11250</v>
       </c>
-      <c r="F84" s="1" t="n">
-        <v>45983.45355324074</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 10:53:07</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -13474,8 +13636,10 @@
       <c r="E85" t="n">
         <v>6750</v>
       </c>
-      <c r="F85" s="1" t="n">
-        <v>45983.51650462963</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 12:23:46</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -13632,8 +13796,10 @@
       <c r="E86" t="n">
         <v>8050</v>
       </c>
-      <c r="F86" s="1" t="n">
-        <v>45983.51835648148</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 12:26:26</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -13790,8 +13956,10 @@
       <c r="E87" t="n">
         <v>8250</v>
       </c>
-      <c r="F87" s="1" t="n">
-        <v>45983.54108796296</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>22-Nov-2025 12:59:10</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -13944,8 +14112,10 @@
       <c r="E88" t="n">
         <v>11350</v>
       </c>
-      <c r="F88" s="1" t="n">
-        <v>45985.33449074074</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:01:40</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
@@ -14094,8 +14264,10 @@
       <c r="E89" t="n">
         <v>11850</v>
       </c>
-      <c r="F89" s="1" t="n">
-        <v>45985.33832175926</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:07:11</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -14244,8 +14416,10 @@
       <c r="E90" t="n">
         <v>6750</v>
       </c>
-      <c r="F90" s="1" t="n">
-        <v>45985.34697916666</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 08:19:39</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -14398,8 +14572,10 @@
       <c r="E91" t="n">
         <v>22000</v>
       </c>
-      <c r="F91" s="1" t="n">
-        <v>45985.43118055556</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>24-Nov-2025 10:20:54</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -14552,8 +14728,10 @@
       <c r="E92" t="n">
         <v>8850</v>
       </c>
-      <c r="F92" s="1" t="n">
-        <v>45986.37667824074</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 09:02:25</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -14710,8 +14888,10 @@
       <c r="E93" t="n">
         <v>8550</v>
       </c>
-      <c r="F93" s="1" t="n">
-        <v>45986.50295138889</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 12:04:15</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -14868,8 +15048,10 @@
       <c r="E94" t="n">
         <v>6750</v>
       </c>
-      <c r="F94" s="1" t="n">
-        <v>45986.81428240741</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>25-Nov-2025 19:32:34</t>
+        </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -15026,8 +15208,10 @@
       <c r="E95" t="n">
         <v>11350</v>
       </c>
-      <c r="F95" s="1" t="n">
-        <v>45987.54623842592</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 13:06:35</t>
+        </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
@@ -15180,8 +15364,10 @@
       <c r="E96" t="n">
         <v>10750</v>
       </c>
-      <c r="F96" s="1" t="n">
-        <v>45987.54756944445</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>26-Nov-2025 13:08:30</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
@@ -15334,8 +15520,10 @@
       <c r="E97" t="n">
         <v>6750</v>
       </c>
-      <c r="F97" s="1" t="n">
-        <v>45991.81046296296</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>30-Nov-2025 19:27:04</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -15492,8 +15680,10 @@
       <c r="E98" t="n">
         <v>11350</v>
       </c>
-      <c r="F98" s="1" t="n">
-        <v>45993.41732638889</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>02-Dec-2025 10:00:57</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
@@ -15642,8 +15832,10 @@
       <c r="E99" t="n">
         <v>8350</v>
       </c>
-      <c r="F99" s="1" t="n">
-        <v>45993.47445601852</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>02-Dec-2025 11:23:13</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -15796,8 +15988,10 @@
       <c r="E100" t="n">
         <v>7750</v>
       </c>
-      <c r="F100" s="1" t="n">
-        <v>45994.53900462963</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>03-Dec-2025 12:56:10</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -15954,8 +16148,10 @@
       <c r="E101" t="n">
         <v>8350</v>
       </c>
-      <c r="F101" s="1" t="n">
-        <v>45995.74810185185</v>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>04-Dec-2025 17:57:16</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -16104,8 +16300,10 @@
       <c r="E102" t="n">
         <v>8350</v>
       </c>
-      <c r="F102" s="1" t="n">
-        <v>45997.3871875</v>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>06-Dec-2025 09:17:33</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -16250,8 +16448,10 @@
       <c r="E103" t="n">
         <v>8050</v>
       </c>
-      <c r="F103" s="1" t="n">
-        <v>45998.8978125</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>07-Dec-2025 21:32:51</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -16408,8 +16608,10 @@
       <c r="E104" t="n">
         <v>8350</v>
       </c>
-      <c r="F104" s="1" t="n">
-        <v>45999.64789351852</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 15:32:58</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -16562,8 +16764,10 @@
       <c r="E105" t="n">
         <v>6750</v>
       </c>
-      <c r="F105" s="1" t="n">
-        <v>45999.73831018519</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>08-Dec-2025 17:43:10</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -16716,8 +16920,10 @@
       <c r="E106" t="n">
         <v>6750</v>
       </c>
-      <c r="F106" s="1" t="n">
-        <v>46003.45693287037</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>12-Dec-2025 10:57:59</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -16874,8 +17080,10 @@
       <c r="E107" t="n">
         <v>8050</v>
       </c>
-      <c r="F107" s="1" t="n">
-        <v>46003.45756944444</v>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>12-Dec-2025 10:58:54</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -17032,8 +17240,10 @@
       <c r="E108" t="n">
         <v>8050</v>
       </c>
-      <c r="F108" s="1" t="n">
-        <v>46003.63835648148</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>12-Dec-2025 15:19:14</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -17186,8 +17396,10 @@
       <c r="E109" t="n">
         <v>10750</v>
       </c>
-      <c r="F109" s="1" t="n">
-        <v>46004.43417824074</v>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>13-Dec-2025 10:25:13</t>
+        </is>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
@@ -17340,8 +17552,10 @@
       <c r="E110" t="n">
         <v>6750</v>
       </c>
-      <c r="F110" s="1" t="n">
-        <v>46004.64199074074</v>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>13-Dec-2025 15:24:28</t>
+        </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -17498,8 +17712,10 @@
       <c r="E111" t="n">
         <v>8650</v>
       </c>
-      <c r="F111" s="1" t="n">
-        <v>46006.49800925926</v>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 11:57:08</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
@@ -17652,8 +17868,10 @@
       <c r="E112" t="n">
         <v>8350</v>
       </c>
-      <c r="F112" s="1" t="n">
-        <v>46006.49861111111</v>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>15-Dec-2025 11:58:00</t>
+        </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -17810,8 +18028,10 @@
       <c r="E113" t="n">
         <v>7750</v>
       </c>
-      <c r="F113" s="1" t="n">
-        <v>46007.50452546297</v>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>16-Dec-2025 12:06:31</t>
+        </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -17968,8 +18188,10 @@
       <c r="E114" t="n">
         <v>10750</v>
       </c>
-      <c r="F114" s="1" t="n">
-        <v>46008.52790509259</v>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>17-Dec-2025 12:40:11</t>
+        </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
@@ -18122,8 +18344,10 @@
       <c r="E115" t="n">
         <v>7750</v>
       </c>
-      <c r="F115" s="1" t="n">
-        <v>46008.81913194444</v>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>17-Dec-2025 19:39:33</t>
+        </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -18276,8 +18500,10 @@
       <c r="E116" t="n">
         <v>11350</v>
       </c>
-      <c r="F116" s="1" t="n">
-        <v>46009.50690972222</v>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 12:09:57</t>
+        </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
@@ -18430,8 +18656,10 @@
       <c r="E117" t="n">
         <v>6750</v>
       </c>
-      <c r="F117" s="1" t="n">
-        <v>46009.71326388889</v>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 17:07:06</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -18584,8 +18812,10 @@
       <c r="E118" t="n">
         <v>8050</v>
       </c>
-      <c r="F118" s="1" t="n">
-        <v>46009.8554050926</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>18-Dec-2025 20:31:47</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -18738,8 +18968,10 @@
       <c r="E119" t="n">
         <v>8050</v>
       </c>
-      <c r="F119" s="1" t="n">
-        <v>46022.3175</v>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 07:37:12</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -18896,8 +19128,10 @@
       <c r="E120" t="n">
         <v>7750</v>
       </c>
-      <c r="F120" s="1" t="n">
-        <v>46022.80763888889</v>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 19:23:00</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -19050,8 +19284,10 @@
       <c r="E121" t="n">
         <v>8350</v>
       </c>
-      <c r="F121" s="1" t="n">
-        <v>46022.86141203704</v>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>31-Dec-2025 20:40:26</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -19204,8 +19440,10 @@
       <c r="E122" t="n">
         <v>7750</v>
       </c>
-      <c r="F122" s="1" t="n">
-        <v>46023.3755787037</v>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 09:00:50</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -19358,8 +19596,10 @@
       <c r="E123" t="n">
         <v>7750</v>
       </c>
-      <c r="F123" s="1" t="n">
-        <v>46023.44881944444</v>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>01-Jan-2026 10:46:18</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -19516,8 +19756,10 @@
       <c r="E124" t="n">
         <v>7750</v>
       </c>
-      <c r="F124" s="1" t="n">
-        <v>46024.73149305556</v>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 17:33:21</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -19670,8 +19912,10 @@
       <c r="E125" t="n">
         <v>7750</v>
       </c>
-      <c r="F125" s="1" t="n">
-        <v>46024.7328125</v>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>02-Jan-2026 17:35:15</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -19824,8 +20068,10 @@
       <c r="E126" t="n">
         <v>7750</v>
       </c>
-      <c r="F126" s="1" t="n">
-        <v>46025.46916666667</v>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>03-Jan-2026 11:15:36</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -19982,8 +20228,10 @@
       <c r="E127" t="n">
         <v>15500</v>
       </c>
-      <c r="F127" s="1" t="n">
-        <v>46029.36194444444</v>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>07-Jan-2026 08:41:12</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -20140,8 +20388,10 @@
       <c r="E128" t="n">
         <v>8650</v>
       </c>
-      <c r="F128" s="1" t="n">
-        <v>46029.71166666667</v>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>07-Jan-2026 17:04:48</t>
+        </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
@@ -20294,8 +20544,10 @@
       <c r="E129" t="n">
         <v>6750</v>
       </c>
-      <c r="F129" s="1" t="n">
-        <v>46032.39002314815</v>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 09:21:38</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -20448,8 +20700,10 @@
       <c r="E130" t="n">
         <v>7750</v>
       </c>
-      <c r="F130" s="1" t="n">
-        <v>46032.50800925926</v>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 12:11:32</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -20602,8 +20856,10 @@
       <c r="E131" t="n">
         <v>7750</v>
       </c>
-      <c r="F131" s="1" t="n">
-        <v>46032.50974537037</v>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>10-Jan-2026 12:14:02</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -20756,8 +21012,10 @@
       <c r="E132" t="n">
         <v>8050</v>
       </c>
-      <c r="F132" s="1" t="n">
-        <v>46041.33828703704</v>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 08:07:08</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -20910,8 +21168,10 @@
       <c r="E133" t="n">
         <v>6750</v>
       </c>
-      <c r="F133" s="1" t="n">
-        <v>46041.33965277778</v>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 08:09:06</t>
+        </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -21064,8 +21324,10 @@
       <c r="E134" t="n">
         <v>7750</v>
       </c>
-      <c r="F134" s="1" t="n">
-        <v>46041.45645833333</v>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 10:57:18</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -21222,8 +21484,10 @@
       <c r="E135" t="n">
         <v>8650</v>
       </c>
-      <c r="F135" s="1" t="n">
-        <v>46041.92981481482</v>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>19-Jan-2026 22:18:56</t>
+        </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
@@ -21376,8 +21640,10 @@
       <c r="E136" t="n">
         <v>8350</v>
       </c>
-      <c r="F136" s="1" t="n">
-        <v>46042.74355324074</v>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>20-Jan-2026 17:50:43</t>
+        </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -21534,8 +21800,10 @@
       <c r="E137" t="n">
         <v>8050</v>
       </c>
-      <c r="F137" s="1" t="n">
-        <v>46043.45862268518</v>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 11:00:25</t>
+        </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -21692,8 +21960,10 @@
       <c r="E138" t="n">
         <v>8650</v>
       </c>
-      <c r="F138" s="1" t="n">
-        <v>46043.52157407408</v>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>21-Jan-2026 12:31:04</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
@@ -21842,8 +22112,10 @@
       <c r="E139" t="n">
         <v>11350</v>
       </c>
-      <c r="F139" s="1" t="n">
-        <v>46044.33070601852</v>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 07:56:13</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
@@ -21996,8 +22268,10 @@
       <c r="E140" t="n">
         <v>8350</v>
       </c>
-      <c r="F140" s="1" t="n">
-        <v>46044.34335648148</v>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 08:14:26</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -22154,8 +22428,10 @@
       <c r="E141" t="n">
         <v>8050</v>
       </c>
-      <c r="F141" s="1" t="n">
-        <v>46044.82335648148</v>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>22-Jan-2026 19:45:38</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -22308,8 +22584,10 @@
       <c r="E142" t="n">
         <v>8350</v>
       </c>
-      <c r="F142" s="1" t="n">
-        <v>46045.2854050926</v>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 06:50:59</t>
+        </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -22466,8 +22744,10 @@
       <c r="E143" t="n">
         <v>7750</v>
       </c>
-      <c r="F143" s="1" t="n">
-        <v>46045.39625</v>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 09:30:36</t>
+        </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -22624,8 +22904,10 @@
       <c r="E144" t="n">
         <v>7750</v>
       </c>
-      <c r="F144" s="1" t="n">
-        <v>46045.4034375</v>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 09:40:57</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -22778,8 +23060,10 @@
       <c r="E145" t="n">
         <v>11350</v>
       </c>
-      <c r="F145" s="1" t="n">
-        <v>46045.44934027778</v>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 10:47:03</t>
+        </is>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
@@ -22932,8 +23216,10 @@
       <c r="E146" t="n">
         <v>11350</v>
       </c>
-      <c r="F146" s="1" t="n">
-        <v>46045.52586805556</v>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 12:37:15</t>
+        </is>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
@@ -23086,8 +23372,10 @@
       <c r="E147" t="n">
         <v>22700</v>
       </c>
-      <c r="F147" s="1" t="n">
-        <v>46045.53924768518</v>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 12:56:31</t>
+        </is>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
@@ -23240,8 +23528,10 @@
       <c r="E148" t="n">
         <v>11350</v>
       </c>
-      <c r="F148" s="1" t="n">
-        <v>46045.54265046296</v>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>23-Jan-2026 13:01:25</t>
+        </is>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
@@ -23390,8 +23680,10 @@
       <c r="E149" t="n">
         <v>11350</v>
       </c>
-      <c r="F149" s="1" t="n">
-        <v>46046.36481481481</v>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 08:45:20</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
@@ -23544,8 +23836,10 @@
       <c r="E150" t="n">
         <v>11350</v>
       </c>
-      <c r="F150" s="1" t="n">
-        <v>46046.37136574074</v>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 08:54:46</t>
+        </is>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
@@ -23698,8 +23992,10 @@
       <c r="E151" t="n">
         <v>11350</v>
       </c>
-      <c r="F151" s="1" t="n">
-        <v>46046.41980324074</v>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 10:04:31</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
@@ -23852,8 +24148,10 @@
       <c r="E152" t="n">
         <v>11350</v>
       </c>
-      <c r="F152" s="1" t="n">
-        <v>46046.42259259259</v>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 10:08:32</t>
+        </is>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
@@ -24006,8 +24304,10 @@
       <c r="E153" t="n">
         <v>11350</v>
       </c>
-      <c r="F153" s="1" t="n">
-        <v>46046.45099537037</v>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 10:49:26</t>
+        </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
@@ -24160,8 +24460,10 @@
       <c r="E154" t="n">
         <v>7750</v>
       </c>
-      <c r="F154" s="1" t="n">
-        <v>46046.46259259259</v>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 11:06:08</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -24314,8 +24616,10 @@
       <c r="E155" t="n">
         <v>11350</v>
       </c>
-      <c r="F155" s="1" t="n">
-        <v>46046.47954861111</v>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 11:30:33</t>
+        </is>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
@@ -24468,8 +24772,10 @@
       <c r="E156" t="n">
         <v>11350</v>
       </c>
-      <c r="F156" s="1" t="n">
-        <v>46046.51792824074</v>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 12:25:49</t>
+        </is>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
@@ -24622,8 +24928,10 @@
       <c r="E157" t="n">
         <v>11350</v>
       </c>
-      <c r="F157" s="1" t="n">
-        <v>46046.55657407407</v>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 13:21:28</t>
+        </is>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
@@ -24776,8 +25084,10 @@
       <c r="E158" t="n">
         <v>7750</v>
       </c>
-      <c r="F158" s="1" t="n">
-        <v>46046.68592592593</v>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>24-Jan-2026 16:27:44</t>
+        </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -24930,8 +25240,10 @@
       <c r="E159" t="n">
         <v>6750</v>
       </c>
-      <c r="F159" s="1" t="n">
-        <v>46047.89452546297</v>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>25-Jan-2026 21:28:07</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -25084,8 +25396,10 @@
       <c r="E160" t="n">
         <v>10750</v>
       </c>
-      <c r="F160" s="1" t="n">
-        <v>46048.40994212963</v>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>26-Jan-2026 09:50:19</t>
+        </is>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
@@ -25238,8 +25552,10 @@
       <c r="E161" t="n">
         <v>6750</v>
       </c>
-      <c r="F161" s="1" t="n">
-        <v>46048.55680555556</v>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>26-Jan-2026 13:21:48</t>
+        </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -25392,8 +25708,10 @@
       <c r="E162" t="n">
         <v>43100</v>
       </c>
-      <c r="F162" s="1" t="n">
-        <v>46048.6271875</v>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>26-Jan-2026 15:03:09</t>
+        </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -25546,8 +25864,10 @@
       <c r="E163" t="n">
         <v>41950</v>
       </c>
-      <c r="F163" s="1" t="n">
-        <v>46048.63013888889</v>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>26-Jan-2026 15:07:24</t>
+        </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -25700,8 +26020,10 @@
       <c r="E164" t="n">
         <v>11350</v>
       </c>
-      <c r="F164" s="1" t="n">
-        <v>46049.33016203704</v>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 07:55:26</t>
+        </is>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
@@ -25850,8 +26172,10 @@
       <c r="E165" t="n">
         <v>11350</v>
       </c>
-      <c r="F165" s="1" t="n">
-        <v>46049.33425925926</v>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 08:01:20</t>
+        </is>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
@@ -26000,8 +26324,10 @@
       <c r="E166" t="n">
         <v>8050</v>
       </c>
-      <c r="F166" s="1" t="n">
-        <v>46049.42076388889</v>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 10:05:54</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -26158,8 +26484,10 @@
       <c r="E167" t="n">
         <v>11350</v>
       </c>
-      <c r="F167" s="1" t="n">
-        <v>46049.41982638889</v>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 10:04:33</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
@@ -26312,8 +26640,10 @@
       <c r="E168" t="n">
         <v>22700</v>
       </c>
-      <c r="F168" s="1" t="n">
-        <v>46049.43501157407</v>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 10:26:25</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
@@ -26466,8 +26796,10 @@
       <c r="E169" t="n">
         <v>22700</v>
       </c>
-      <c r="F169" s="1" t="n">
-        <v>46049.50001157408</v>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 12:00:01</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
@@ -26620,8 +26952,10 @@
       <c r="E170" t="n">
         <v>11350</v>
       </c>
-      <c r="F170" s="1" t="n">
-        <v>46049.49964120371</v>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 11:59:29</t>
+        </is>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
@@ -26774,8 +27108,10 @@
       <c r="E171" t="n">
         <v>7750</v>
       </c>
-      <c r="F171" s="1" t="n">
-        <v>46049.51418981481</v>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 12:20:26</t>
+        </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -26928,8 +27264,10 @@
       <c r="E172" t="n">
         <v>8350</v>
       </c>
-      <c r="F172" s="1" t="n">
-        <v>46049.52399305555</v>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 12:34:33</t>
+        </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -27082,8 +27420,10 @@
       <c r="E173" t="n">
         <v>8350</v>
       </c>
-      <c r="F173" s="1" t="n">
-        <v>46049.62412037037</v>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 14:58:44</t>
+        </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -27240,8 +27580,10 @@
       <c r="E174" t="n">
         <v>22700</v>
       </c>
-      <c r="F174" s="1" t="n">
-        <v>46049.62221064815</v>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>27-Jan-2026 14:55:59</t>
+        </is>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
@@ -27390,8 +27732,10 @@
       <c r="E175" t="n">
         <v>6750</v>
       </c>
-      <c r="F175" s="1" t="n">
-        <v>46050.55373842592</v>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 13:17:23</t>
+        </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -27540,8 +27884,10 @@
       <c r="E176" t="n">
         <v>10750</v>
       </c>
-      <c r="F176" s="1" t="n">
-        <v>46050.95643518519</v>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 22:57:16</t>
+        </is>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
@@ -27682,8 +28028,10 @@
       <c r="E177" t="n">
         <v>22700</v>
       </c>
-      <c r="F177" s="1" t="n">
-        <v>46050.97396990741</v>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>28-Jan-2026 23:22:31</t>
+        </is>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
@@ -27832,8 +28180,10 @@
       <c r="E178" t="n">
         <v>8350</v>
       </c>
-      <c r="F178" s="1" t="n">
-        <v>46051.08684027778</v>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 02:05:03</t>
+        </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -27978,8 +28328,10 @@
       <c r="E179" t="n">
         <v>8650</v>
       </c>
-      <c r="F179" s="1" t="n">
-        <v>46051.33489583333</v>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 08:02:15</t>
+        </is>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
@@ -28124,8 +28476,10 @@
       <c r="E180" t="n">
         <v>24650</v>
       </c>
-      <c r="F180" s="1" t="n">
-        <v>46051.48862268519</v>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 11:43:37</t>
+        </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -28274,8 +28628,10 @@
       <c r="E181" t="n">
         <v>8350</v>
       </c>
-      <c r="F181" s="1" t="n">
-        <v>46051.49190972222</v>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 11:48:21</t>
+        </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -28424,8 +28780,10 @@
       <c r="E182" t="n">
         <v>6750</v>
       </c>
-      <c r="F182" s="1" t="n">
-        <v>46051.78804398148</v>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>29-Jan-2026 18:54:47</t>
+        </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -28578,8 +28936,10 @@
       <c r="E183" t="n">
         <v>8050</v>
       </c>
-      <c r="F183" s="1" t="n">
-        <v>46052.43079861111</v>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 10:20:21</t>
+        </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -28732,8 +29092,10 @@
       <c r="E184" t="n">
         <v>10750</v>
       </c>
-      <c r="F184" s="1" t="n">
-        <v>46052.95104166667</v>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>30-Jan-2026 22:49:30</t>
+        </is>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
@@ -28882,8 +29244,10 @@
       <c r="E185" t="n">
         <v>7750</v>
       </c>
-      <c r="F185" s="1" t="n">
-        <v>46053.48603009259</v>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 11:39:53</t>
+        </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -29032,8 +29396,10 @@
       <c r="E186" t="n">
         <v>6750</v>
       </c>
-      <c r="F186" s="1" t="n">
-        <v>46053.5158912037</v>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 12:22:53</t>
+        </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -29186,8 +29552,10 @@
       <c r="E187" t="n">
         <v>8350</v>
       </c>
-      <c r="F187" s="1" t="n">
-        <v>46053.75952546296</v>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 18:13:43</t>
+        </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -29336,8 +29704,10 @@
       <c r="E188" t="n">
         <v>8050</v>
       </c>
-      <c r="F188" s="1" t="n">
-        <v>46053.76193287037</v>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 18:17:11</t>
+        </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -29486,8 +29856,10 @@
       <c r="E189" t="n">
         <v>17200</v>
       </c>
-      <c r="F189" s="1" t="n">
-        <v>46053.88202546296</v>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 21:10:07</t>
+        </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -29640,8 +30012,10 @@
       <c r="E190" t="n">
         <v>6750</v>
       </c>
-      <c r="F190" s="1" t="n">
-        <v>46053.92971064815</v>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>31-Jan-2026 22:18:47</t>
+        </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -29794,8 +30168,10 @@
       <c r="E191" t="n">
         <v>8650</v>
       </c>
-      <c r="F191" s="1" t="n">
-        <v>46055.42375</v>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 10:10:12</t>
+        </is>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
@@ -29940,8 +30316,10 @@
       <c r="E192" t="n">
         <v>10750</v>
       </c>
-      <c r="F192" s="1" t="n">
-        <v>46055.42484953703</v>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 10:11:47</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
@@ -30086,8 +30464,10 @@
       <c r="E193" t="n">
         <v>6750</v>
       </c>
-      <c r="F193" s="1" t="n">
-        <v>46055.46064814815</v>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 11:03:20</t>
+        </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -30236,8 +30616,10 @@
       <c r="E194" t="n">
         <v>6750</v>
       </c>
-      <c r="F194" s="1" t="n">
-        <v>46055.52606481482</v>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 12:37:32</t>
+        </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -30390,8 +30772,10 @@
       <c r="E195" t="n">
         <v>8050</v>
       </c>
-      <c r="F195" s="1" t="n">
-        <v>46055.53605324074</v>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 12:51:55</t>
+        </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -30540,8 +30924,10 @@
       <c r="E196" t="n">
         <v>8050</v>
       </c>
-      <c r="F196" s="1" t="n">
-        <v>46055.62615740741</v>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 15:01:40</t>
+        </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -30690,8 +31076,10 @@
       <c r="E197" t="n">
         <v>15500</v>
       </c>
-      <c r="F197" s="1" t="n">
-        <v>46055.62711805556</v>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 15:03:03</t>
+        </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -30840,8 +31228,10 @@
       <c r="E198" t="n">
         <v>8350</v>
       </c>
-      <c r="F198" s="1" t="n">
-        <v>46055.78267361111</v>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>02-Feb-2026 18:47:03</t>
+        </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -30990,8 +31380,10 @@
       <c r="E199" t="n">
         <v>8650</v>
       </c>
-      <c r="F199" s="1" t="n">
-        <v>46056.51971064815</v>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 12:28:23</t>
+        </is>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
@@ -31136,8 +31528,10 @@
       <c r="E200" t="n">
         <v>7750</v>
       </c>
-      <c r="F200" s="1" t="n">
-        <v>46056.87050925926</v>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>03-Feb-2026 20:53:32</t>
+        </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -31290,8 +31684,10 @@
       <c r="E201" t="n">
         <v>8350</v>
       </c>
-      <c r="F201" s="1" t="n">
-        <v>46057.29524305555</v>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 07:05:09</t>
+        </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -31440,8 +31836,10 @@
       <c r="E202" t="n">
         <v>8350</v>
       </c>
-      <c r="F202" s="1" t="n">
-        <v>46057.41393518518</v>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 09:56:04</t>
+        </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -31594,8 +31992,10 @@
       <c r="E203" t="n">
         <v>11350</v>
       </c>
-      <c r="F203" s="1" t="n">
-        <v>46057.42021990741</v>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 10:05:07</t>
+        </is>
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
@@ -31744,8 +32144,10 @@
       <c r="E204" t="n">
         <v>8350</v>
       </c>
-      <c r="F204" s="1" t="n">
-        <v>46057.96211805556</v>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>04-Feb-2026 23:05:27</t>
+        </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -31894,8 +32296,10 @@
       <c r="E205" t="n">
         <v>8050</v>
       </c>
-      <c r="F205" s="1" t="n">
-        <v>46059.65474537037</v>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>06-Feb-2026 15:42:50</t>
+        </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -32048,8 +32452,10 @@
       <c r="E206" t="n">
         <v>8350</v>
       </c>
-      <c r="F206" s="1" t="n">
-        <v>46060.49238425926</v>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>07-Feb-2026 11:49:02</t>
+        </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -32198,8 +32604,10 @@
       <c r="E207" t="n">
         <v>8350</v>
       </c>
-      <c r="F207" s="1" t="n">
-        <v>46061.52457175926</v>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 12:35:23</t>
+        </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -32352,8 +32760,10 @@
       <c r="E208" t="n">
         <v>7750</v>
       </c>
-      <c r="F208" s="1" t="n">
-        <v>46061.61168981482</v>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>08-Feb-2026 14:40:50</t>
+        </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -32510,8 +32920,10 @@
       <c r="E209" t="n">
         <v>10750</v>
       </c>
-      <c r="F209" s="1" t="n">
-        <v>46062.90912037037</v>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>09-Feb-2026 21:49:08</t>
+        </is>
       </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
@@ -32660,8 +33072,10 @@
       <c r="E210" t="n">
         <v>8350</v>
       </c>
-      <c r="F210" s="1" t="n">
-        <v>46063.30769675926</v>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>10-Feb-2026 07:23:05</t>
+        </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -32814,8 +33228,10 @@
       <c r="E211" t="n">
         <v>8050</v>
       </c>
-      <c r="F211" s="1" t="n">
-        <v>46063.71047453704</v>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>10-Feb-2026 17:03:05</t>
+        </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -32968,8 +33384,10 @@
       <c r="E212" t="n">
         <v>16700</v>
       </c>
-      <c r="F212" s="1" t="n">
-        <v>46064.32337962963</v>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 07:45:40</t>
+        </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -33122,8 +33540,10 @@
       <c r="E213" t="n">
         <v>21500</v>
       </c>
-      <c r="F213" s="1" t="n">
-        <v>46064.33358796296</v>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>11-Feb-2026 08:00:22</t>
+        </is>
       </c>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
@@ -33272,8 +33692,10 @@
       <c r="E214" t="n">
         <v>8650</v>
       </c>
-      <c r="F214" s="1" t="n">
-        <v>46066.35371527778</v>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 08:29:21</t>
+        </is>
       </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
@@ -33426,8 +33848,10 @@
       <c r="E215" t="n">
         <v>11350</v>
       </c>
-      <c r="F215" s="1" t="n">
-        <v>46066.35480324074</v>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 08:30:55</t>
+        </is>
       </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
@@ -33580,8 +34004,10 @@
       <c r="E216" t="n">
         <v>6750</v>
       </c>
-      <c r="F216" s="1" t="n">
-        <v>46066.40148148148</v>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 09:38:08</t>
+        </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -33738,8 +34164,10 @@
       <c r="E217" t="n">
         <v>11350</v>
       </c>
-      <c r="F217" s="1" t="n">
-        <v>46066.76298611111</v>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>13-Feb-2026 18:18:42</t>
+        </is>
       </c>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
@@ -33892,8 +34320,10 @@
       <c r="E218" t="n">
         <v>8650</v>
       </c>
-      <c r="F218" s="1" t="n">
-        <v>46067.3506712963</v>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>14-Feb-2026 08:24:58</t>
+        </is>
       </c>
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
@@ -34046,8 +34476,10 @@
       <c r="E219" t="n">
         <v>11350</v>
       </c>
-      <c r="F219" s="1" t="n">
-        <v>46070.37929398148</v>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>17-Feb-2026 09:06:11</t>
+        </is>
       </c>
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
@@ -34200,8 +34632,10 @@
       <c r="E220" t="n">
         <v>8650</v>
       </c>
-      <c r="F220" s="1" t="n">
-        <v>46071.45115740741</v>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>18-Feb-2026 10:49:40</t>
+        </is>
       </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
@@ -34354,8 +34788,10 @@
       <c r="E221" t="n">
         <v>8350</v>
       </c>
-      <c r="F221" s="1" t="n">
-        <v>46071.84131944444</v>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>18-Feb-2026 20:11:30</t>
+        </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -34512,8 +34948,10 @@
       <c r="E222" t="n">
         <v>11350</v>
       </c>
-      <c r="F222" s="1" t="n">
-        <v>46071.84244212963</v>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>18-Feb-2026 20:13:07</t>
+        </is>
       </c>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
@@ -34666,8 +35104,10 @@
       <c r="E223" t="n">
         <v>10750</v>
       </c>
-      <c r="F223" s="1" t="n">
-        <v>46073.33096064815</v>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>20-Feb-2026 07:56:35</t>
+        </is>
       </c>
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
@@ -34816,8 +35256,10 @@
       <c r="E224" t="n">
         <v>7750</v>
       </c>
-      <c r="F224" s="1" t="n">
-        <v>46075.52773148148</v>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 12:39:56</t>
+        </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -34970,8 +35412,10 @@
       <c r="E225" t="n">
         <v>8650</v>
       </c>
-      <c r="F225" s="1" t="n">
-        <v>46075.93215277778</v>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 22:22:18</t>
+        </is>
       </c>
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
@@ -35124,8 +35568,10 @@
       <c r="E226" t="n">
         <v>8050</v>
       </c>
-      <c r="F226" s="1" t="n">
-        <v>46075.9487962963</v>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>22-Feb-2026 22:46:16</t>
+        </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -35282,8 +35728,10 @@
       <c r="E227" t="n">
         <v>11350</v>
       </c>
-      <c r="F227" s="1" t="n">
-        <v>46076.46484953703</v>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 11:09:23</t>
+        </is>
       </c>
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
@@ -35432,8 +35880,10 @@
       <c r="E228" t="n">
         <v>10750</v>
       </c>
-      <c r="F228" s="1" t="n">
-        <v>46076.73559027778</v>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>23-Feb-2026 17:39:15</t>
+        </is>
       </c>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
@@ -35582,8 +36032,10 @@
       <c r="E229" t="n">
         <v>6750</v>
       </c>
-      <c r="F229" s="1" t="n">
-        <v>46077.72671296296</v>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>24-Feb-2026 17:26:28</t>
+        </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -35740,8 +36192,10 @@
       <c r="E230" t="n">
         <v>8050</v>
       </c>
-      <c r="F230" s="1" t="n">
-        <v>46077.72730324074</v>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>24-Feb-2026 17:27:19</t>
+        </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -35898,8 +36352,10 @@
       <c r="E231" t="n">
         <v>6750</v>
       </c>
-      <c r="F231" s="1" t="n">
-        <v>46077.95168981481</v>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>24-Feb-2026 22:50:26</t>
+        </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -36056,8 +36512,10 @@
       <c r="E232" t="n">
         <v>25550</v>
       </c>
-      <c r="F232" s="1" t="n">
-        <v>46078.88863425926</v>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>25-Feb-2026 21:19:38</t>
+        </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -36210,8 +36668,10 @@
       <c r="E233" t="n">
         <v>6750</v>
       </c>
-      <c r="F233" s="1" t="n">
-        <v>46079.69099537037</v>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>26-Feb-2026 16:35:02</t>
+        </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -36364,8 +36824,10 @@
       <c r="E234" t="n">
         <v>6750</v>
       </c>
-      <c r="F234" s="1" t="n">
-        <v>46079.8746875</v>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>26-Feb-2026 20:59:33</t>
+        </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -36518,8 +36980,10 @@
       <c r="E235" t="n">
         <v>7750</v>
       </c>
-      <c r="F235" s="1" t="n">
-        <v>46080.81792824074</v>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>27-Feb-2026 19:37:49</t>
+        </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -36676,8 +37140,10 @@
       <c r="E236" t="n">
         <v>8350</v>
       </c>
-      <c r="F236" s="1" t="n">
-        <v>46081.34730324074</v>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 08:20:07</t>
+        </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -36834,8 +37300,10 @@
       <c r="E237" t="n">
         <v>8650</v>
       </c>
-      <c r="F237" s="1" t="n">
-        <v>46081.34796296297</v>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 08:21:04</t>
+        </is>
       </c>
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
@@ -36988,8 +37456,10 @@
       <c r="E238" t="n">
         <v>8050</v>
       </c>
-      <c r="F238" s="1" t="n">
-        <v>46081.43663194445</v>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:28:45</t>
+        </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -37146,8 +37616,10 @@
       <c r="E239" t="n">
         <v>8350</v>
       </c>
-      <c r="F239" s="1" t="n">
-        <v>46081.4356712963</v>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:27:22</t>
+        </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -37304,8 +37776,10 @@
       <c r="E240" t="n">
         <v>8050</v>
       </c>
-      <c r="F240" s="1" t="n">
-        <v>46081.4431712963</v>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 10:38:10</t>
+        </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -37462,8 +37936,10 @@
       <c r="E241" t="n">
         <v>6750</v>
       </c>
-      <c r="F241" s="1" t="n">
-        <v>46081.49700231481</v>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 11:55:41</t>
+        </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -37616,8 +38092,10 @@
       <c r="E242" t="n">
         <v>16100</v>
       </c>
-      <c r="F242" s="1" t="n">
-        <v>46081.53856481481</v>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>28-Feb-2026 12:55:32</t>
+        </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -37770,8 +38248,10 @@
       <c r="E243" t="n">
         <v>7750</v>
       </c>
-      <c r="F243" s="1" t="n">
-        <v>46082.67609953704</v>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>01-Mar-2026 16:13:35</t>
+        </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -37924,8 +38404,10 @@
       <c r="E244" t="n">
         <v>8350</v>
       </c>
-      <c r="F244" s="1" t="n">
-        <v>46083.35696759259</v>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 08:34:02</t>
+        </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -38082,8 +38564,10 @@
       <c r="E245" t="n">
         <v>6750</v>
       </c>
-      <c r="F245" s="1" t="n">
-        <v>46083.39872685185</v>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 09:34:10</t>
+        </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -38240,8 +38724,10 @@
       <c r="E246" t="n">
         <v>7750</v>
       </c>
-      <c r="F246" s="1" t="n">
-        <v>46083.398125</v>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 09:33:18</t>
+        </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -38398,8 +38884,10 @@
       <c r="E247" t="n">
         <v>7750</v>
       </c>
-      <c r="F247" s="1" t="n">
-        <v>46083.48013888889</v>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 11:31:24</t>
+        </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -38556,8 +39044,10 @@
       <c r="E248" t="n">
         <v>8050</v>
       </c>
-      <c r="F248" s="1" t="n">
-        <v>46083.5117824074</v>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 12:16:58</t>
+        </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -38714,8 +39204,10 @@
       <c r="E249" t="n">
         <v>6750</v>
       </c>
-      <c r="F249" s="1" t="n">
-        <v>46083.50885416667</v>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 12:12:45</t>
+        </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -38872,8 +39364,10 @@
       <c r="E250" t="n">
         <v>8650</v>
       </c>
-      <c r="F250" s="1" t="n">
-        <v>46083.54140046296</v>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>02-Mar-2026 12:59:37</t>
+        </is>
       </c>
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
@@ -39026,8 +39520,10 @@
       <c r="E251" t="n">
         <v>8350</v>
       </c>
-      <c r="F251" s="1" t="n">
-        <v>46085.34151620371</v>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>04-Mar-2026 08:11:47</t>
+        </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -39184,8 +39680,10 @@
       <c r="E252" t="n">
         <v>8350</v>
       </c>
-      <c r="F252" s="1" t="n">
-        <v>46085.34430555555</v>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>04-Mar-2026 08:15:48</t>
+        </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -39342,8 +39840,10 @@
       <c r="E253" t="n">
         <v>7750</v>
       </c>
-      <c r="F253" s="1" t="n">
-        <v>46085.51104166666</v>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>04-Mar-2026 12:15:54</t>
+        </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -39500,8 +40000,10 @@
       <c r="E254" t="n">
         <v>7750</v>
       </c>
-      <c r="F254" s="1" t="n">
-        <v>46085.51019675926</v>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>04-Mar-2026 12:14:41</t>
+        </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -39658,8 +40160,10 @@
       <c r="E255" t="n">
         <v>10750</v>
       </c>
-      <c r="F255" s="1" t="n">
-        <v>46085.69237268518</v>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>04-Mar-2026 16:37:01</t>
+        </is>
       </c>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
@@ -39812,8 +40316,10 @@
       <c r="E256" t="n">
         <v>7750</v>
       </c>
-      <c r="F256" s="1" t="n">
-        <v>46086.34107638889</v>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>05-Mar-2026 08:11:09</t>
+        </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -39970,8 +40476,10 @@
       <c r="E257" t="n">
         <v>8350</v>
       </c>
-      <c r="F257" s="1" t="n">
-        <v>46086.39050925926</v>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>05-Mar-2026 09:22:20</t>
+        </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -40128,8 +40636,10 @@
       <c r="E258" t="n">
         <v>8350</v>
       </c>
-      <c r="F258" s="1" t="n">
-        <v>46086.54883101852</v>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>05-Mar-2026 13:10:19</t>
+        </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -40286,8 +40796,10 @@
       <c r="E259" t="n">
         <v>8350</v>
       </c>
-      <c r="F259" s="1" t="n">
-        <v>46086.63582175926</v>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>05-Mar-2026 15:15:35</t>
+        </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -40444,8 +40956,10 @@
       <c r="E260" t="n">
         <v>6750</v>
       </c>
-      <c r="F260" s="1" t="n">
-        <v>46087.03974537037</v>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>06-Mar-2026 00:57:14</t>
+        </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -40602,8 +41116,10 @@
       <c r="E261" t="n">
         <v>16700</v>
       </c>
-      <c r="F261" s="1" t="n">
-        <v>46087.39373842593</v>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>06-Mar-2026 09:26:59</t>
+        </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -40760,8 +41276,10 @@
       <c r="E262" t="n">
         <v>10750</v>
       </c>
-      <c r="F262" s="1" t="n">
-        <v>46087.42783564814</v>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>06-Mar-2026 10:16:05</t>
+        </is>
       </c>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
@@ -40914,8 +41432,10 @@
       <c r="E263" t="n">
         <v>8650</v>
       </c>
-      <c r="F263" s="1" t="n">
-        <v>46087.52810185185</v>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>06-Mar-2026 12:40:28</t>
+        </is>
       </c>
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
@@ -41068,8 +41588,10 @@
       <c r="E264" t="n">
         <v>6750</v>
       </c>
-      <c r="F264" s="1" t="n">
-        <v>46087.65532407408</v>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>06-Mar-2026 15:43:40</t>
+        </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -41226,8 +41748,10 @@
       <c r="E265" t="n">
         <v>6750</v>
       </c>
-      <c r="F265" s="1" t="n">
-        <v>46087.65797453704</v>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>06-Mar-2026 15:47:29</t>
+        </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -41384,8 +41908,10 @@
       <c r="E266" t="n">
         <v>8350</v>
       </c>
-      <c r="F266" s="1" t="n">
-        <v>46087.65587962963</v>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>06-Mar-2026 15:44:28</t>
+        </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -41542,8 +42068,10 @@
       <c r="E267" t="n">
         <v>8050</v>
       </c>
-      <c r="F267" s="1" t="n">
-        <v>46088.29915509259</v>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>07-Mar-2026 07:10:47</t>
+        </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -41700,8 +42228,10 @@
       <c r="E268" t="n">
         <v>6750</v>
       </c>
-      <c r="F268" s="1" t="n">
-        <v>46088.33313657407</v>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>07-Mar-2026 07:59:43</t>
+        </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -41858,8 +42388,10 @@
       <c r="E269" t="n">
         <v>7750</v>
       </c>
-      <c r="F269" s="1" t="n">
-        <v>46088.3565625</v>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>07-Mar-2026 08:33:27</t>
+        </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -42016,8 +42548,10 @@
       <c r="E270" t="n">
         <v>8350</v>
       </c>
-      <c r="F270" s="1" t="n">
-        <v>46088.36540509259</v>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>07-Mar-2026 08:46:11</t>
+        </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -42174,8 +42708,10 @@
       <c r="E271" t="n">
         <v>8050</v>
       </c>
-      <c r="F271" s="1" t="n">
-        <v>46088.56111111111</v>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>07-Mar-2026 13:28:00</t>
+        </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -42332,8 +42868,10 @@
       <c r="E272" t="n">
         <v>8350</v>
       </c>
-      <c r="F272" s="1" t="n">
-        <v>46088.56423611111</v>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>07-Mar-2026 13:32:30</t>
+        </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -42490,8 +43028,10 @@
       <c r="E273" t="n">
         <v>8650</v>
       </c>
-      <c r="F273" s="1" t="n">
-        <v>46088.83385416667</v>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>07-Mar-2026 20:00:45</t>
+        </is>
       </c>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
@@ -42644,8 +43184,10 @@
       <c r="E274" t="n">
         <v>6750</v>
       </c>
-      <c r="F274" s="1" t="n">
-        <v>46089.07493055556</v>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>08-Mar-2026 01:47:54</t>
+        </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -42802,8 +43344,10 @@
       <c r="E275" t="n">
         <v>8050</v>
       </c>
-      <c r="F275" s="1" t="n">
-        <v>46089.90702546296</v>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>08-Mar-2026 21:46:07</t>
+        </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -42960,8 +43504,10 @@
       <c r="E276" t="n">
         <v>8050</v>
       </c>
-      <c r="F276" s="1" t="n">
-        <v>46089.96021990741</v>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>08-Mar-2026 23:02:43</t>
+        </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -43118,8 +43664,10 @@
       <c r="E277" t="n">
         <v>6750</v>
       </c>
-      <c r="F277" s="1" t="n">
-        <v>46090.37471064815</v>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>09-Mar-2026 08:59:35</t>
+        </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -43276,8 +43824,10 @@
       <c r="E278" t="n">
         <v>8350</v>
       </c>
-      <c r="F278" s="1" t="n">
-        <v>46090.59347222222</v>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>09-Mar-2026 14:14:36</t>
+        </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -43434,8 +43984,10 @@
       <c r="E279" t="n">
         <v>8650</v>
       </c>
-      <c r="F279" s="1" t="n">
-        <v>46091.42769675926</v>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>10-Mar-2026 10:15:53</t>
+        </is>
       </c>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
@@ -43588,8 +44140,10 @@
       <c r="E280" t="n">
         <v>7750</v>
       </c>
-      <c r="F280" s="1" t="n">
-        <v>46091.81101851852</v>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>10-Mar-2026 19:27:52</t>
+        </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -43746,8 +44300,10 @@
       <c r="E281" t="n">
         <v>8350</v>
       </c>
-      <c r="F281" s="1" t="n">
-        <v>46091.8092824074</v>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>10-Mar-2026 19:25:22</t>
+        </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -43904,8 +44460,10 @@
       <c r="E282" t="n">
         <v>8650</v>
       </c>
-      <c r="F282" s="1" t="n">
-        <v>46091.82027777778</v>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>10-Mar-2026 19:41:12</t>
+        </is>
       </c>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
@@ -44058,8 +44616,10 @@
       <c r="E283" t="n">
         <v>8050</v>
       </c>
-      <c r="F283" s="1" t="n">
-        <v>46091.82071759259</v>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>10-Mar-2026 19:41:50</t>
+        </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -44216,8 +44776,10 @@
       <c r="E284" t="n">
         <v>7750</v>
       </c>
-      <c r="F284" s="1" t="n">
-        <v>46094.40575231481</v>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>13-Mar-2026 09:44:17</t>
+        </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -44374,8 +44936,10 @@
       <c r="E285" t="n">
         <v>6750</v>
       </c>
-      <c r="F285" s="1" t="n">
-        <v>46097.52517361111</v>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>16-Mar-2026 12:36:15</t>
+        </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -44532,8 +45096,10 @@
       <c r="E286" t="n">
         <v>11350</v>
       </c>
-      <c r="F286" s="1" t="n">
-        <v>46098.36436342593</v>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>17-Mar-2026 08:44:41</t>
+        </is>
       </c>
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
@@ -44686,8 +45252,10 @@
       <c r="E287" t="n">
         <v>16700</v>
       </c>
-      <c r="F287" s="1" t="n">
-        <v>46098.45291666667</v>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>17-Mar-2026 10:52:12</t>
+        </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -44844,8 +45412,10 @@
       <c r="E288" t="n">
         <v>7750</v>
       </c>
-      <c r="F288" s="1" t="n">
-        <v>46098.54799768519</v>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>17-Mar-2026 13:09:07</t>
+        </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -45002,8 +45572,10 @@
       <c r="E289" t="n">
         <v>10750</v>
       </c>
-      <c r="F289" s="1" t="n">
-        <v>46099.20768518518</v>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>18-Mar-2026 04:59:04</t>
+        </is>
       </c>
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
@@ -45156,8 +45728,10 @@
       <c r="E290" t="n">
         <v>8650</v>
       </c>
-      <c r="F290" s="1" t="n">
-        <v>46102.42745370371</v>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>21-Mar-2026 10:15:32</t>
+        </is>
       </c>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
@@ -45306,8 +45880,10 @@
       <c r="E291" t="n">
         <v>7750</v>
       </c>
-      <c r="F291" s="1" t="n">
-        <v>46105.38423611111</v>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>24-Mar-2026 09:13:18</t>
+        </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -45464,8 +46040,10 @@
       <c r="E292" t="n">
         <v>8350</v>
       </c>
-      <c r="F292" s="1" t="n">
-        <v>46105.40638888889</v>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>24-Mar-2026 09:45:12</t>
+        </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -45622,8 +46200,10 @@
       <c r="E293" t="n">
         <v>10750</v>
       </c>
-      <c r="F293" s="1" t="n">
-        <v>46105.42898148148</v>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>24-Mar-2026 10:17:44</t>
+        </is>
       </c>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
@@ -45776,8 +46356,10 @@
       <c r="E294" t="n">
         <v>8050</v>
       </c>
-      <c r="F294" s="1" t="n">
-        <v>46105.45387731482</v>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>24-Mar-2026 10:53:35</t>
+        </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -45934,8 +46516,10 @@
       <c r="E295" t="n">
         <v>11350</v>
       </c>
-      <c r="F295" s="1" t="n">
-        <v>46105.97925925926</v>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>24-Mar-2026 23:30:08</t>
+        </is>
       </c>
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
@@ -46088,8 +46672,10 @@
       <c r="E296" t="n">
         <v>6750</v>
       </c>
-      <c r="F296" s="1" t="n">
-        <v>46107.40277777778</v>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>26-Mar-2026 09:40:00</t>
+        </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -46246,8 +46832,10 @@
       <c r="E297" t="n">
         <v>8050</v>
       </c>
-      <c r="F297" s="1" t="n">
-        <v>46107.50657407408</v>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>26-Mar-2026 12:09:28</t>
+        </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -46404,8 +46992,10 @@
       <c r="E298" t="n">
         <v>8050</v>
       </c>
-      <c r="F298" s="1" t="n">
-        <v>46107.52826388889</v>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>26-Mar-2026 12:40:42</t>
+        </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -46562,8 +47152,10 @@
       <c r="E299" t="n">
         <v>6750</v>
       </c>
-      <c r="F299" s="1" t="n">
-        <v>46119.49782407407</v>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>07-Apr-2026 11:56:52</t>
+        </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -46720,8 +47312,10 @@
       <c r="E300" t="n">
         <v>6750</v>
       </c>
-      <c r="F300" s="1" t="n">
-        <v>46125.16938657407</v>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>13-Apr-2026 04:03:55</t>
+        </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -46878,8 +47472,10 @@
       <c r="E301" t="n">
         <v>11350</v>
       </c>
-      <c r="F301" s="1" t="n">
-        <v>46160.44135416667</v>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>18-May-2026 10:35:33</t>
+        </is>
       </c>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
@@ -47034,8 +47630,10 @@
       <c r="E302" t="n">
         <v>11350</v>
       </c>
-      <c r="F302" s="1" t="n">
-        <v>46163.2934375</v>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>21-May-2026 07:02:33</t>
+        </is>
       </c>
       <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
@@ -47190,8 +47788,10 @@
       <c r="E303" t="n">
         <v>10750</v>
       </c>
-      <c r="F303" s="1" t="n">
-        <v>46164.96425925926</v>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>22-May-2026 23:08:32</t>
+        </is>
       </c>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
@@ -47346,8 +47946,10 @@
       <c r="E304" t="n">
         <v>11350</v>
       </c>
-      <c r="F304" s="1" t="n">
-        <v>46172.50920138889</v>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>30-May-2026 12:13:15</t>
+        </is>
       </c>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
@@ -47502,8 +48104,10 @@
       <c r="E305" t="n">
         <v>8050</v>
       </c>
-      <c r="F305" s="1" t="n">
-        <v>46175.41075231481</v>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>02-Jun-2026 09:51:29</t>
+        </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -47662,8 +48266,10 @@
       <c r="E306" t="n">
         <v>11350</v>
       </c>
-      <c r="F306" s="1" t="n">
-        <v>46175.53351851852</v>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>02-Jun-2026 12:48:16</t>
+        </is>
       </c>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr">
@@ -47818,8 +48424,10 @@
       <c r="E307" t="n">
         <v>11350</v>
       </c>
-      <c r="F307" s="1" t="n">
-        <v>46179.339375</v>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>06-Jun-2026 08:08:42</t>
+        </is>
       </c>
       <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr">
@@ -47974,8 +48582,10 @@
       <c r="E308" t="n">
         <v>10750</v>
       </c>
-      <c r="F308" s="1" t="n">
-        <v>46179.47453703704</v>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>06-Jun-2026 11:23:20</t>
+        </is>
       </c>
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
@@ -48130,8 +48740,10 @@
       <c r="E309" t="n">
         <v>8700</v>
       </c>
-      <c r="F309" s="1" t="n">
-        <v>46185.86115740741</v>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>12-Jun-2026 20:40:04</t>
+        </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -48290,8 +48902,10 @@
       <c r="E310" t="n">
         <v>7250</v>
       </c>
-      <c r="F310" s="1" t="n">
-        <v>46185.86184027778</v>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>12-Jun-2026 20:41:03</t>
+        </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -48442,8 +49056,10 @@
       <c r="E311" t="n">
         <v>9300</v>
       </c>
-      <c r="F311" s="1" t="n">
-        <v>46186.4884375</v>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>13-Jun-2026 11:43:21</t>
+        </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -48598,8 +49214,10 @@
       <c r="E312" t="n">
         <v>9600</v>
       </c>
-      <c r="F312" s="1" t="n">
-        <v>46186.49135416667</v>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>13-Jun-2026 11:47:33</t>
+        </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -48754,8 +49372,10 @@
       <c r="E313" t="n">
         <v>9300</v>
       </c>
-      <c r="F313" s="1" t="n">
-        <v>46186.92850694444</v>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>13-Jun-2026 22:17:03</t>
+        </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -48910,8 +49530,10 @@
       <c r="E314" t="n">
         <v>600</v>
       </c>
-      <c r="F314" s="1" t="n">
-        <v>46188.27199074074</v>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>15-Jun-2026 06:31:40</t>
+        </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -49066,8 +49688,10 @@
       <c r="E315" t="n">
         <v>8700</v>
       </c>
-      <c r="F315" s="1" t="n">
-        <v>46188.72680555555</v>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>15-Jun-2026 17:26:36</t>
+        </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -49222,8 +49846,10 @@
       <c r="E316" t="n">
         <v>600</v>
       </c>
-      <c r="F316" s="1" t="n">
-        <v>46188.72622685185</v>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>15-Jun-2026 17:25:46</t>
+        </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -49378,8 +50004,10 @@
       <c r="E317" t="n">
         <v>600</v>
       </c>
-      <c r="F317" s="1" t="n">
-        <v>46188.72730324074</v>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>15-Jun-2026 17:27:19</t>
+        </is>
       </c>
       <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
@@ -49530,8 +50158,10 @@
       <c r="E318" t="n">
         <v>9400</v>
       </c>
-      <c r="F318" s="1" t="n">
-        <v>46188.72765046296</v>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>15-Jun-2026 17:27:49</t>
+        </is>
       </c>
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
@@ -49686,8 +50316,10 @@
       <c r="E319" t="n">
         <v>7750</v>
       </c>
-      <c r="F319" s="1" t="n">
-        <v>46189.5666087963</v>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>16-Jun-2026 13:35:55</t>
+        </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -49842,8 +50474,10 @@
       <c r="E320" t="n">
         <v>8700</v>
       </c>
-      <c r="F320" s="1" t="n">
-        <v>46189.73005787037</v>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>16-Jun-2026 17:31:17</t>
+        </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -49998,8 +50632,10 @@
       <c r="E321" t="n">
         <v>600</v>
       </c>
-      <c r="F321" s="1" t="n">
-        <v>46189.74625</v>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>16-Jun-2026 17:54:36</t>
+        </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -50154,8 +50790,10 @@
       <c r="E322" t="n">
         <v>9000</v>
       </c>
-      <c r="F322" s="1" t="n">
-        <v>46189.74707175926</v>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>16-Jun-2026 17:55:47</t>
+        </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -50310,8 +50948,10 @@
       <c r="E323" t="n">
         <v>8700</v>
       </c>
-      <c r="F323" s="1" t="n">
-        <v>46189.74833333334</v>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>16-Jun-2026 17:57:36</t>
+        </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -50466,8 +51106,10 @@
       <c r="E324" t="n">
         <v>600</v>
       </c>
-      <c r="F324" s="1" t="n">
-        <v>46189.74769675926</v>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>16-Jun-2026 17:56:41</t>
+        </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -50626,8 +51268,10 @@
       <c r="E325" t="n">
         <v>9400</v>
       </c>
-      <c r="F325" s="1" t="n">
-        <v>46190.3865625</v>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>17-Jun-2026 09:16:39</t>
+        </is>
       </c>
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
@@ -50778,8 +51422,10 @@
       <c r="E326" t="n">
         <v>600</v>
       </c>
-      <c r="F326" s="1" t="n">
-        <v>46190.68299768519</v>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>17-Jun-2026 16:23:31</t>
+        </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -50934,8 +51580,10 @@
       <c r="E327" t="n">
         <v>7250</v>
       </c>
-      <c r="F327" s="1" t="n">
-        <v>46191.35962962963</v>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>18-Jun-2026 08:37:52</t>
+        </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
@@ -51090,8 +51738,10 @@
       <c r="E328" t="n">
         <v>22700</v>
       </c>
-      <c r="F328" s="1" t="n">
-        <v>46191.55832175926</v>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>18-Jun-2026 13:23:59</t>
+        </is>
       </c>
       <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
@@ -51242,8 +51892,10 @@
       <c r="E329" t="n">
         <v>7250</v>
       </c>
-      <c r="F329" s="1" t="n">
-        <v>46191.75966435186</v>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>18-Jun-2026 18:13:55</t>
+        </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -51398,8 +52050,10 @@
       <c r="E330" t="n">
         <v>10000</v>
       </c>
-      <c r="F330" s="1" t="n">
-        <v>46191.84688657407</v>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>18-Jun-2026 20:19:31</t>
+        </is>
       </c>
       <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
@@ -51550,8 +52204,10 @@
       <c r="E331" t="n">
         <v>7250</v>
       </c>
-      <c r="F331" s="1" t="n">
-        <v>46192.36637731481</v>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>19-Jun-2026 08:47:35</t>
+        </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
@@ -51706,8 +52362,10 @@
       <c r="E332" t="n">
         <v>8700</v>
       </c>
-      <c r="F332" s="1" t="n">
-        <v>46192.57136574074</v>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>19-Jun-2026 13:42:46</t>
+        </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -51862,8 +52520,10 @@
       <c r="E333" t="n">
         <v>9000</v>
       </c>
-      <c r="F333" s="1" t="n">
-        <v>46192.62206018518</v>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>19-Jun-2026 14:55:46</t>
+        </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -52018,8 +52678,10 @@
       <c r="E334" t="n">
         <v>9000</v>
       </c>
-      <c r="F334" s="1" t="n">
-        <v>46193.34774305556</v>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 08:20:45</t>
+        </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -52174,8 +52836,10 @@
       <c r="E335" t="n">
         <v>9300</v>
       </c>
-      <c r="F335" s="1" t="n">
-        <v>46193.36482638889</v>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 08:45:21</t>
+        </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -52330,8 +52994,10 @@
       <c r="E336" t="n">
         <v>7250</v>
       </c>
-      <c r="F336" s="1" t="n">
-        <v>46193.37454861111</v>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 08:59:21</t>
+        </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -52486,8 +53152,10 @@
       <c r="E337" t="n">
         <v>9000</v>
       </c>
-      <c r="F337" s="1" t="n">
-        <v>46193.37730324074</v>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 09:03:19</t>
+        </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -52642,8 +53310,10 @@
       <c r="E338" t="n">
         <v>6500</v>
       </c>
-      <c r="F338" s="1" t="n">
-        <v>46193.40918981482</v>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 09:49:14</t>
+        </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -52794,8 +53464,10 @@
       <c r="E339" t="n">
         <v>9600</v>
       </c>
-      <c r="F339" s="1" t="n">
-        <v>46193.41114583334</v>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 09:52:03</t>
+        </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -52946,8 +53618,10 @@
       <c r="E340" t="n">
         <v>7250</v>
       </c>
-      <c r="F340" s="1" t="n">
-        <v>46193.43824074074</v>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 10:31:04</t>
+        </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -53102,8 +53776,10 @@
       <c r="E341" t="n">
         <v>9000</v>
       </c>
-      <c r="F341" s="1" t="n">
-        <v>46193.44519675926</v>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 10:41:05</t>
+        </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -53254,8 +53930,10 @@
       <c r="E342" t="n">
         <v>8700</v>
       </c>
-      <c r="F342" s="1" t="n">
-        <v>46193.47935185185</v>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 11:30:16</t>
+        </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -53410,8 +54088,10 @@
       <c r="E343" t="n">
         <v>7250</v>
       </c>
-      <c r="F343" s="1" t="n">
-        <v>46193.47743055555</v>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 11:27:30</t>
+        </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -53566,8 +54246,10 @@
       <c r="E344" t="n">
         <v>600</v>
       </c>
-      <c r="F344" s="1" t="n">
-        <v>46193.47863425926</v>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 11:29:14</t>
+        </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -53722,8 +54404,10 @@
       <c r="E345" t="n">
         <v>7250</v>
       </c>
-      <c r="F345" s="1" t="n">
-        <v>46193.51692129629</v>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 12:24:22</t>
+        </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
@@ -53878,8 +54562,10 @@
       <c r="E346" t="n">
         <v>7250</v>
       </c>
-      <c r="F346" s="1" t="n">
-        <v>46193.52335648148</v>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 12:33:38</t>
+        </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
@@ -54034,8 +54720,10 @@
       <c r="E347" t="n">
         <v>7250</v>
       </c>
-      <c r="F347" s="1" t="n">
-        <v>46193.5318287037</v>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 12:45:50</t>
+        </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -54190,8 +54878,10 @@
       <c r="E348" t="n">
         <v>8400</v>
       </c>
-      <c r="F348" s="1" t="n">
-        <v>46193.57649305555</v>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 13:50:09</t>
+        </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -54346,8 +55036,10 @@
       <c r="E349" t="n">
         <v>11350</v>
       </c>
-      <c r="F349" s="1" t="n">
-        <v>46193.5850462963</v>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 14:02:28</t>
+        </is>
       </c>
       <c r="G349" t="inlineStr"/>
       <c r="H349" t="inlineStr">
@@ -54502,8 +55194,10 @@
       <c r="E350" t="n">
         <v>9300</v>
       </c>
-      <c r="F350" s="1" t="n">
-        <v>46193.71818287037</v>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 17:14:11</t>
+        </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
@@ -54654,8 +55348,10 @@
       <c r="E351" t="n">
         <v>7250</v>
       </c>
-      <c r="F351" s="1" t="n">
-        <v>46193.72918981482</v>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 17:30:02</t>
+        </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -54810,8 +55506,10 @@
       <c r="E352" t="n">
         <v>9000</v>
       </c>
-      <c r="F352" s="1" t="n">
-        <v>46193.75885416667</v>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 18:12:45</t>
+        </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
@@ -54966,8 +55664,10 @@
       <c r="E353" t="n">
         <v>8400</v>
       </c>
-      <c r="F353" s="1" t="n">
-        <v>46193.79561342593</v>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 19:05:41</t>
+        </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
@@ -55118,8 +55818,10 @@
       <c r="E354" t="n">
         <v>6500</v>
       </c>
-      <c r="F354" s="1" t="n">
-        <v>46193.79994212963</v>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 19:11:55</t>
+        </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
@@ -55278,8 +55980,10 @@
       <c r="E355" t="n">
         <v>8400</v>
       </c>
-      <c r="F355" s="1" t="n">
-        <v>46193.89258101852</v>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 21:25:19</t>
+        </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -55434,8 +56138,10 @@
       <c r="E356" t="n">
         <v>7250</v>
       </c>
-      <c r="F356" s="1" t="n">
-        <v>46193.9046875</v>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 21:42:45</t>
+        </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
@@ -55590,8 +56296,10 @@
       <c r="E357" t="n">
         <v>8700</v>
       </c>
-      <c r="F357" s="1" t="n">
-        <v>46193.90778935186</v>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 21:47:13</t>
+        </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -55746,8 +56454,10 @@
       <c r="E358" t="n">
         <v>7250</v>
       </c>
-      <c r="F358" s="1" t="n">
-        <v>46193.93408564815</v>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 22:25:05</t>
+        </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
@@ -55902,8 +56612,10 @@
       <c r="E359" t="n">
         <v>9000</v>
       </c>
-      <c r="F359" s="1" t="n">
-        <v>46194.83354166667</v>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>21-Jun-2026 20:00:18</t>
+        </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
@@ -56058,8 +56770,10 @@
       <c r="E360" t="n">
         <v>13500</v>
       </c>
-      <c r="F360" s="1" t="n">
-        <v>46194.97063657407</v>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>21-Jun-2026 23:17:43</t>
+        </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -56210,8 +56924,10 @@
       <c r="E361" t="n">
         <v>7250</v>
       </c>
-      <c r="F361" s="1" t="n">
-        <v>46195.32358796296</v>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 07:45:58</t>
+        </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
@@ -56366,8 +57082,10 @@
       <c r="E362" t="n">
         <v>6500</v>
       </c>
-      <c r="F362" s="1" t="n">
-        <v>46195.36267361111</v>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 08:42:15</t>
+        </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
@@ -56522,8 +57240,10 @@
       <c r="E363" t="n">
         <v>9000</v>
       </c>
-      <c r="F363" s="1" t="n">
-        <v>46195.37136574074</v>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 08:54:46</t>
+        </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
@@ -56678,8 +57398,10 @@
       <c r="E364" t="n">
         <v>7250</v>
       </c>
-      <c r="F364" s="1" t="n">
-        <v>46195.37978009259</v>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 09:06:53</t>
+        </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
@@ -56834,8 +57556,10 @@
       <c r="E365" t="n">
         <v>8400</v>
       </c>
-      <c r="F365" s="1" t="n">
-        <v>46195.39155092592</v>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 09:23:50</t>
+        </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -56990,8 +57714,10 @@
       <c r="E366" t="n">
         <v>6500</v>
       </c>
-      <c r="F366" s="1" t="n">
-        <v>46195.41715277778</v>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 10:00:42</t>
+        </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -57146,8 +57872,10 @@
       <c r="E367" t="n">
         <v>7250</v>
       </c>
-      <c r="F367" s="1" t="n">
-        <v>46195.43804398148</v>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 10:30:47</t>
+        </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
@@ -57302,8 +58030,10 @@
       <c r="E368" t="n">
         <v>8400</v>
       </c>
-      <c r="F368" s="1" t="n">
-        <v>46195.44076388889</v>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 10:34:42</t>
+        </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
@@ -57458,8 +58188,10 @@
       <c r="E369" t="n">
         <v>9000</v>
       </c>
-      <c r="F369" s="1" t="n">
-        <v>46195.5021875</v>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 12:03:09</t>
+        </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -57614,8 +58346,10 @@
       <c r="E370" t="n">
         <v>7250</v>
       </c>
-      <c r="F370" s="1" t="n">
-        <v>46195.54572916667</v>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 13:05:51</t>
+        </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -57770,8 +58504,10 @@
       <c r="E371" t="n">
         <v>9000</v>
       </c>
-      <c r="F371" s="1" t="n">
-        <v>46195.60923611111</v>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 14:37:18</t>
+        </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -57926,8 +58662,10 @@
       <c r="E372" t="n">
         <v>7250</v>
       </c>
-      <c r="F372" s="1" t="n">
-        <v>46195.62024305556</v>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 14:53:09</t>
+        </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
@@ -58082,8 +58820,10 @@
       <c r="E373" t="n">
         <v>7250</v>
       </c>
-      <c r="F373" s="1" t="n">
-        <v>46195.84731481481</v>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 20:20:08</t>
+        </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
@@ -58238,8 +58978,10 @@
       <c r="E374" t="n">
         <v>600</v>
       </c>
-      <c r="F374" s="1" t="n">
-        <v>46195.87861111111</v>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 21:05:12</t>
+        </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
@@ -58394,8 +59136,10 @@
       <c r="E375" t="n">
         <v>9000</v>
       </c>
-      <c r="F375" s="1" t="n">
-        <v>46195.87950231481</v>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 21:06:29</t>
+        </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
@@ -58550,8 +59294,10 @@
       <c r="E376" t="n">
         <v>8400</v>
       </c>
-      <c r="F376" s="1" t="n">
-        <v>46195.93912037037</v>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 22:32:20</t>
+        </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
@@ -58706,8 +59452,10 @@
       <c r="E377" t="n">
         <v>9000</v>
       </c>
-      <c r="F377" s="1" t="n">
-        <v>46196.36197916666</v>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 08:41:15</t>
+        </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
@@ -58862,8 +59610,10 @@
       <c r="E378" t="n">
         <v>7250</v>
       </c>
-      <c r="F378" s="1" t="n">
-        <v>46196.36392361111</v>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 08:44:03</t>
+        </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
@@ -59018,8 +59768,10 @@
       <c r="E379" t="n">
         <v>7250</v>
       </c>
-      <c r="F379" s="1" t="n">
-        <v>46196.41171296296</v>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 09:52:52</t>
+        </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -59174,8 +59926,10 @@
       <c r="E380" t="n">
         <v>9000</v>
       </c>
-      <c r="F380" s="1" t="n">
-        <v>46196.48128472222</v>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 11:33:03</t>
+        </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
@@ -59330,8 +60084,10 @@
       <c r="E381" t="n">
         <v>7250</v>
       </c>
-      <c r="F381" s="1" t="n">
-        <v>46196.64337962963</v>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 15:26:28</t>
+        </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -59486,8 +60242,10 @@
       <c r="E382" t="n">
         <v>8400</v>
       </c>
-      <c r="F382" s="1" t="n">
-        <v>46196.84936342593</v>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 20:23:05</t>
+        </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
@@ -59642,8 +60400,10 @@
       <c r="E383" t="n">
         <v>8700</v>
       </c>
-      <c r="F383" s="1" t="n">
-        <v>46196.85241898148</v>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 20:27:29</t>
+        </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -59794,8 +60554,10 @@
       <c r="E384" t="n">
         <v>6500</v>
       </c>
-      <c r="F384" s="1" t="n">
-        <v>46197.30366898148</v>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 07:17:17</t>
+        </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
@@ -59950,8 +60712,10 @@
       <c r="E385" t="n">
         <v>7250</v>
       </c>
-      <c r="F385" s="1" t="n">
-        <v>46197.37752314815</v>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 09:03:38</t>
+        </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
@@ -60106,8 +60870,10 @@
       <c r="E386" t="n">
         <v>7250</v>
       </c>
-      <c r="F386" s="1" t="n">
-        <v>46197.38700231481</v>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 09:17:17</t>
+        </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
@@ -60262,8 +61028,10 @@
       <c r="E387" t="n">
         <v>8700</v>
       </c>
-      <c r="F387" s="1" t="n">
-        <v>46197.39268518519</v>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 09:25:28</t>
+        </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
@@ -60418,8 +61186,10 @@
       <c r="E388" t="n">
         <v>7250</v>
       </c>
-      <c r="F388" s="1" t="n">
-        <v>46197.50105324074</v>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 12:01:31</t>
+        </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -60574,8 +61344,10 @@
       <c r="E389" t="n">
         <v>6500</v>
       </c>
-      <c r="F389" s="1" t="n">
-        <v>46197.50179398148</v>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 12:02:35</t>
+        </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
@@ -60730,8 +61502,10 @@
       <c r="E390" t="n">
         <v>9400</v>
       </c>
-      <c r="F390" s="1" t="n">
-        <v>46197.53702546296</v>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 12:53:19</t>
+        </is>
       </c>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
@@ -60882,8 +61656,10 @@
       <c r="E391" t="n">
         <v>8400</v>
       </c>
-      <c r="F391" s="1" t="n">
-        <v>46197.64799768518</v>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 15:33:07</t>
+        </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
@@ -61038,8 +61814,10 @@
       <c r="E392" t="n">
         <v>8400</v>
       </c>
-      <c r="F392" s="1" t="n">
-        <v>46197.66087962963</v>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 15:51:40</t>
+        </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
@@ -61191,11 +61969,19 @@
       <c r="D393" t="n">
         <v>7250</v>
       </c>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" s="1" t="n">
-        <v>46199.3871412037</v>
-      </c>
-      <c r="G393" t="inlineStr"/>
+      <c r="E393" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 09:17:29</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 20:01:02</t>
+        </is>
+      </c>
       <c r="H393" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -61260,7 +62046,7 @@
       </c>
       <c r="V393" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W393" t="inlineStr">
@@ -61283,15 +62069,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA393" t="inlineStr"/>
-      <c r="AB393" t="inlineStr"/>
+      <c r="AA393" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB393" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC393" t="n">
         <v>0</v>
       </c>
       <c r="AD393" t="n">
         <v>0</v>
       </c>
-      <c r="AE393" t="inlineStr"/>
+      <c r="AE393" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF393" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -61335,11 +62127,19 @@
       <c r="D394" t="n">
         <v>8400</v>
       </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" s="1" t="n">
-        <v>46200.13666666667</v>
-      </c>
-      <c r="G394" t="inlineStr"/>
+      <c r="E394" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>27-Jun-2026 03:16:48</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 19:58:52</t>
+        </is>
+      </c>
       <c r="H394" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -61404,7 +62204,7 @@
       </c>
       <c r="V394" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W394" t="inlineStr">
@@ -61427,15 +62227,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA394" t="inlineStr"/>
-      <c r="AB394" t="inlineStr"/>
+      <c r="AA394" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB394" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC394" t="n">
         <v>0</v>
       </c>
       <c r="AD394" t="n">
         <v>0</v>
       </c>
-      <c r="AE394" t="inlineStr"/>
+      <c r="AE394" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF394" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -61479,11 +62285,19 @@
       <c r="D395" t="n">
         <v>8700</v>
       </c>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" s="1" t="n">
-        <v>46201.32478009259</v>
-      </c>
-      <c r="G395" t="inlineStr"/>
+      <c r="E395" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>28-Jun-2026 07:47:41</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 19:58:52</t>
+        </is>
+      </c>
       <c r="H395" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -61548,7 +62362,7 @@
       </c>
       <c r="V395" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W395" t="inlineStr">
@@ -61571,15 +62385,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA395" t="inlineStr"/>
-      <c r="AB395" t="inlineStr"/>
+      <c r="AA395" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB395" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC395" t="n">
         <v>0</v>
       </c>
       <c r="AD395" t="n">
         <v>0</v>
       </c>
-      <c r="AE395" t="inlineStr"/>
+      <c r="AE395" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF395" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -61605,6 +62425,1818 @@
         </is>
       </c>
       <c r="AL395" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>17692</v>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>83****1772</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E396" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 10:09:21</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 18:27:13</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>*0436</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N396" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>11000369612164</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>1782707944312</v>
+      </c>
+      <c r="R396" t="n">
+        <v>217639908250</v>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA396" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB396" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC396" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD396" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE396" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF396" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG396" t="inlineStr"/>
+      <c r="AH396" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI396" t="n">
+        <v>20436</v>
+      </c>
+      <c r="AJ396" t="inlineStr">
+        <is>
+          <t>277362</t>
+        </is>
+      </c>
+      <c r="AK396" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL396" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>17691</v>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>83****1772</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E397" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 10:12:08</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 18:27:13</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>*0435</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N397" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>11000369613118</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>1782708098766</v>
+      </c>
+      <c r="R397" t="n">
+        <v>826425736351</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA397" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB397" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE397" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF397" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG397" t="inlineStr"/>
+      <c r="AH397" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI397" t="n">
+        <v>20435</v>
+      </c>
+      <c r="AJ397" t="inlineStr">
+        <is>
+          <t>277360</t>
+        </is>
+      </c>
+      <c r="AK397" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL397" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>17358</v>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>83****6856</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>17400</v>
+      </c>
+      <c r="E398" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 11:09:48</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 18:27:13</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>*0077</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N398" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P398" t="n">
+        <v>11000369624103</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>1782711444773</v>
+      </c>
+      <c r="R398" t="n">
+        <v>618023027174</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y398" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA398" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB398" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC398" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD398" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE398" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF398" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG398" t="inlineStr"/>
+      <c r="AH398" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI398" t="n">
+        <v>20077</v>
+      </c>
+      <c r="AJ398" t="inlineStr">
+        <is>
+          <t>271164,269818,271555</t>
+        </is>
+      </c>
+      <c r="AK398" t="inlineStr">
+        <is>
+          <t>2076,2067,2077</t>
+        </is>
+      </c>
+      <c r="AL398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>17452</v>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>85****4344</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E399" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 13:28:57</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 18:27:13</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>*0176</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N399" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P399" t="n">
+        <v>11000369658343</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>1782719924296</v>
+      </c>
+      <c r="R399" t="n">
+        <v>971601575567</v>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA399" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB399" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC399" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD399" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE399" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF399" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG399" t="inlineStr"/>
+      <c r="AH399" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI399" t="n">
+        <v>20176</v>
+      </c>
+      <c r="AJ399" t="inlineStr">
+        <is>
+          <t>271170</t>
+        </is>
+      </c>
+      <c r="AK399" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL399" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>16344</v>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>99****2239</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E400" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 19:16:18</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 18:27:13</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>*8423</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N400" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P400" t="n">
+        <v>11000369711495</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>1782740763914</v>
+      </c>
+      <c r="R400" t="n">
+        <v>962525516737</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W400" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X400" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y400" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA400" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB400" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE400" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF400" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG400" t="inlineStr"/>
+      <c r="AH400" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI400" t="n">
+        <v>18423</v>
+      </c>
+      <c r="AJ400" t="inlineStr">
+        <is>
+          <t>272506</t>
+        </is>
+      </c>
+      <c r="AK400" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL400" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>17623</v>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>77****3791</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E401" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 21:56:59</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 18:27:13</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>*0342</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N401" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P401" t="n">
+        <v>11000369732362</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>1782750393630</v>
+      </c>
+      <c r="R401" t="n">
+        <v>962338751824</v>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA401" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB401" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC401" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD401" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE401" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF401" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG401" t="inlineStr"/>
+      <c r="AH401" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI401" t="n">
+        <v>20342</v>
+      </c>
+      <c r="AJ401" t="inlineStr">
+        <is>
+          <t>268798,268818</t>
+        </is>
+      </c>
+      <c r="AK401" t="inlineStr">
+        <is>
+          <t>2065,2066</t>
+        </is>
+      </c>
+      <c r="AL401" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>15237</v>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>63****6983</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>11600</v>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 07:03:04</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>*8984</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P402" t="n">
+        <v>11000369749870</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>1782783128318</v>
+      </c>
+      <c r="R402" t="n">
+        <v>103557397611</v>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA402" t="inlineStr"/>
+      <c r="AB402" t="inlineStr"/>
+      <c r="AC402" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD402" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE402" t="inlineStr"/>
+      <c r="AF402" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG402" t="inlineStr"/>
+      <c r="AH402" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI402" t="n">
+        <v>18984</v>
+      </c>
+      <c r="AJ402" t="inlineStr">
+        <is>
+          <t>275368</t>
+        </is>
+      </c>
+      <c r="AK402" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="AL402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>15025</v>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>63****6983</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 07:09:52</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>*9264</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N403" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P403" t="n">
+        <v>11000369750126</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>1782783555661</v>
+      </c>
+      <c r="R403" t="n">
+        <v>103557479945</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W403" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X403" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y403" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA403" t="inlineStr"/>
+      <c r="AB403" t="inlineStr"/>
+      <c r="AC403" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD403" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE403" t="inlineStr"/>
+      <c r="AF403" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG403" t="inlineStr"/>
+      <c r="AH403" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI403" t="n">
+        <v>19264</v>
+      </c>
+      <c r="AJ403" t="inlineStr">
+        <is>
+          <t>276033</t>
+        </is>
+      </c>
+      <c r="AK403" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>17491</v>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>95****4527</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 08:50:05</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>*0210</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N404" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P404" t="n">
+        <v>11000369762744</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>1782789593872</v>
+      </c>
+      <c r="R404" t="n">
+        <v>787099153815</v>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W404" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X404" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y404" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA404" t="inlineStr"/>
+      <c r="AB404" t="inlineStr"/>
+      <c r="AC404" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD404" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE404" t="inlineStr"/>
+      <c r="AF404" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG404" t="inlineStr"/>
+      <c r="AH404" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI404" t="n">
+        <v>20210</v>
+      </c>
+      <c r="AJ404" t="inlineStr">
+        <is>
+          <t>273493</t>
+        </is>
+      </c>
+      <c r="AK404" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL404" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>17684</v>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>63****8534</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 11:59:01</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>*0428</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N405" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P405" t="n">
+        <v>11000369809910</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>1782800926241</v>
+      </c>
+      <c r="R405" t="n">
+        <v>686580296603</v>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y405" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA405" t="inlineStr"/>
+      <c r="AB405" t="inlineStr"/>
+      <c r="AC405" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD405" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE405" t="inlineStr"/>
+      <c r="AF405" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG405" t="inlineStr"/>
+      <c r="AH405" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI405" t="n">
+        <v>20428</v>
+      </c>
+      <c r="AJ405" t="inlineStr">
+        <is>
+          <t>277168</t>
+        </is>
+      </c>
+      <c r="AK405" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="AL405" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>17466</v>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>96****7511</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 15:34:09</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>*0108</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N406" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P406" t="n">
+        <v>11000369870899</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>1782813831326</v>
+      </c>
+      <c r="R406" t="n">
+        <v>806564370851</v>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X406" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y406" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z406" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA406" t="inlineStr"/>
+      <c r="AB406" t="inlineStr"/>
+      <c r="AC406" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD406" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE406" t="inlineStr"/>
+      <c r="AF406" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG406" t="inlineStr"/>
+      <c r="AH406" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI406" t="n">
+        <v>20108</v>
+      </c>
+      <c r="AJ406" t="inlineStr">
+        <is>
+          <t>268814</t>
+        </is>
+      </c>
+      <c r="AK406" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="AL406" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>16997</v>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>62****4352</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 22:08:10</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>*8092</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P407" t="n">
+        <v>11000369952021</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>1782837475003</v>
+      </c>
+      <c r="R407" t="n">
+        <v>529512247535</v>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr"/>
+      <c r="AB407" t="inlineStr"/>
+      <c r="AC407" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD407" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE407" t="inlineStr"/>
+      <c r="AF407" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG407" t="inlineStr"/>
+      <c r="AH407" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI407" t="n">
+        <v>18092</v>
+      </c>
+      <c r="AJ407" t="inlineStr">
+        <is>
+          <t>271350</t>
+        </is>
+      </c>
+      <c r="AK407" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL407" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL407"/>
+  <dimension ref="A1:AL412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63387,7 +63387,9 @@
       <c r="D402" t="n">
         <v>11600</v>
       </c>
-      <c r="E402" t="inlineStr"/>
+      <c r="E402" t="n">
+        <v>11600</v>
+      </c>
       <c r="F402" t="inlineStr">
         <is>
           <t>30-Jun-2026 07:03:04</t>
@@ -63458,7 +63460,7 @@
       </c>
       <c r="V402" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W402" t="inlineStr">
@@ -63481,15 +63483,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA402" t="inlineStr"/>
-      <c r="AB402" t="inlineStr"/>
+      <c r="AA402" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB402" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC402" t="n">
         <v>0</v>
       </c>
       <c r="AD402" t="n">
         <v>0</v>
       </c>
-      <c r="AE402" t="inlineStr"/>
+      <c r="AE402" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF402" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -63529,7 +63537,9 @@
       <c r="D403" t="n">
         <v>12300</v>
       </c>
-      <c r="E403" t="inlineStr"/>
+      <c r="E403" t="n">
+        <v>12300</v>
+      </c>
       <c r="F403" t="inlineStr">
         <is>
           <t>30-Jun-2026 07:09:52</t>
@@ -63600,7 +63610,7 @@
       </c>
       <c r="V403" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W403" t="inlineStr">
@@ -63623,15 +63633,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA403" t="inlineStr"/>
-      <c r="AB403" t="inlineStr"/>
+      <c r="AA403" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB403" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC403" t="n">
         <v>0</v>
       </c>
       <c r="AD403" t="n">
         <v>0</v>
       </c>
-      <c r="AE403" t="inlineStr"/>
+      <c r="AE403" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF403" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -63671,13 +63687,19 @@
       <c r="D404" t="n">
         <v>9000</v>
       </c>
-      <c r="E404" t="inlineStr"/>
+      <c r="E404" t="n">
+        <v>9000</v>
+      </c>
       <c r="F404" t="inlineStr">
         <is>
           <t>30-Jun-2026 08:50:05</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 17:28:21</t>
+        </is>
+      </c>
       <c r="H404" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -63742,7 +63764,7 @@
       </c>
       <c r="V404" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W404" t="inlineStr">
@@ -63765,15 +63787,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA404" t="inlineStr"/>
-      <c r="AB404" t="inlineStr"/>
+      <c r="AA404" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB404" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC404" t="n">
         <v>0</v>
       </c>
       <c r="AD404" t="n">
         <v>0</v>
       </c>
-      <c r="AE404" t="inlineStr"/>
+      <c r="AE404" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF404" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -63817,13 +63845,19 @@
       <c r="D405" t="n">
         <v>6500</v>
       </c>
-      <c r="E405" t="inlineStr"/>
+      <c r="E405" t="n">
+        <v>6500</v>
+      </c>
       <c r="F405" t="inlineStr">
         <is>
           <t>30-Jun-2026 11:59:01</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 17:28:21</t>
+        </is>
+      </c>
       <c r="H405" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -63888,7 +63922,7 @@
       </c>
       <c r="V405" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W405" t="inlineStr">
@@ -63911,15 +63945,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA405" t="inlineStr"/>
-      <c r="AB405" t="inlineStr"/>
+      <c r="AA405" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB405" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC405" t="n">
         <v>0</v>
       </c>
       <c r="AD405" t="n">
         <v>0</v>
       </c>
-      <c r="AE405" t="inlineStr"/>
+      <c r="AE405" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF405" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -63963,13 +64003,19 @@
       <c r="D406" t="n">
         <v>6500</v>
       </c>
-      <c r="E406" t="inlineStr"/>
+      <c r="E406" t="n">
+        <v>6500</v>
+      </c>
       <c r="F406" t="inlineStr">
         <is>
           <t>30-Jun-2026 15:34:09</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 17:28:21</t>
+        </is>
+      </c>
       <c r="H406" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -64034,7 +64080,7 @@
       </c>
       <c r="V406" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W406" t="inlineStr">
@@ -64057,15 +64103,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA406" t="inlineStr"/>
-      <c r="AB406" t="inlineStr"/>
+      <c r="AA406" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB406" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC406" t="n">
         <v>0</v>
       </c>
       <c r="AD406" t="n">
         <v>0</v>
       </c>
-      <c r="AE406" t="inlineStr"/>
+      <c r="AE406" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF406" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -64109,13 +64161,19 @@
       <c r="D407" t="n">
         <v>8400</v>
       </c>
-      <c r="E407" t="inlineStr"/>
+      <c r="E407" t="n">
+        <v>8400</v>
+      </c>
       <c r="F407" t="inlineStr">
         <is>
           <t>30-Jun-2026 22:08:10</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 17:28:21</t>
+        </is>
+      </c>
       <c r="H407" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -64180,7 +64238,7 @@
       </c>
       <c r="V407" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W407" t="inlineStr">
@@ -64203,15 +64261,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA407" t="inlineStr"/>
-      <c r="AB407" t="inlineStr"/>
+      <c r="AA407" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB407" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC407" t="n">
         <v>0</v>
       </c>
       <c r="AD407" t="n">
         <v>0</v>
       </c>
-      <c r="AE407" t="inlineStr"/>
+      <c r="AE407" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF407" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -64237,6 +64301,736 @@
         </is>
       </c>
       <c r="AL407" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>17601</v>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>77****4666</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 07:27:15</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>*0320</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P408" t="n">
+        <v>11000369977078</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>1782871025315</v>
+      </c>
+      <c r="R408" t="n">
+        <v>618246845906</v>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr"/>
+      <c r="AB408" t="inlineStr"/>
+      <c r="AC408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE408" t="inlineStr"/>
+      <c r="AF408" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG408" t="inlineStr"/>
+      <c r="AH408" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI408" t="n">
+        <v>20320</v>
+      </c>
+      <c r="AJ408" t="inlineStr">
+        <is>
+          <t>272249</t>
+        </is>
+      </c>
+      <c r="AK408" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL408" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>17419</v>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>81****0244</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 11:35:41</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>*0150</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P409" t="n">
+        <v>11000370033742</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>1782885927208</v>
+      </c>
+      <c r="R409" t="n">
+        <v>698510463204</v>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr"/>
+      <c r="AB409" t="inlineStr"/>
+      <c r="AC409" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD409" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE409" t="inlineStr"/>
+      <c r="AF409" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG409" t="inlineStr"/>
+      <c r="AH409" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI409" t="n">
+        <v>20150</v>
+      </c>
+      <c r="AJ409" t="inlineStr">
+        <is>
+          <t>269195</t>
+        </is>
+      </c>
+      <c r="AK409" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL409" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>17420</v>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>81****0244</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 11:36:53</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>*0180</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P410" t="n">
+        <v>11000370034713</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>1782886002985</v>
+      </c>
+      <c r="R410" t="n">
+        <v>733221939126</v>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X410" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y410" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z410" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA410" t="inlineStr"/>
+      <c r="AB410" t="inlineStr"/>
+      <c r="AC410" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD410" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE410" t="inlineStr"/>
+      <c r="AF410" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG410" t="inlineStr"/>
+      <c r="AH410" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI410" t="n">
+        <v>20180</v>
+      </c>
+      <c r="AJ410" t="inlineStr">
+        <is>
+          <t>272239</t>
+        </is>
+      </c>
+      <c r="AK410" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL410" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>17636</v>
+      </c>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>96****5335</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>11600</v>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 14:34:28</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>*0419</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N411" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P411" t="n">
+        <v>11000370081456</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>1782896345957</v>
+      </c>
+      <c r="R411" t="n">
+        <v>13289287852</v>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y411" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z411" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA411" t="inlineStr"/>
+      <c r="AB411" t="inlineStr"/>
+      <c r="AC411" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD411" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE411" t="inlineStr"/>
+      <c r="AF411" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG411" t="inlineStr"/>
+      <c r="AH411" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI411" t="n">
+        <v>20419</v>
+      </c>
+      <c r="AJ411" t="inlineStr">
+        <is>
+          <t>277478</t>
+        </is>
+      </c>
+      <c r="AK411" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="AL411" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>17501</v>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>94****7581</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 20:24:30</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>*0220</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P412" t="n">
+        <v>11000370146650</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>1782917649184</v>
+      </c>
+      <c r="R412" t="n">
+        <v>618249656742</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X412" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y412" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z412" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA412" t="inlineStr"/>
+      <c r="AB412" t="inlineStr"/>
+      <c r="AC412" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD412" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE412" t="inlineStr"/>
+      <c r="AF412" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG412" t="inlineStr"/>
+      <c r="AH412" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI412" t="n">
+        <v>20220</v>
+      </c>
+      <c r="AJ412" t="inlineStr">
+        <is>
+          <t>272243</t>
+        </is>
+      </c>
+      <c r="AK412" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL412" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL412"/>
+  <dimension ref="A1:AL414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65036,6 +65036,298 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>17543</v>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>89****6747</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 21:59:43</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>*0262</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P413" t="n">
+        <v>11000370169568</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>1782923360248</v>
+      </c>
+      <c r="R413" t="n">
+        <v>754184729326</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X413" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y413" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z413" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr"/>
+      <c r="AB413" t="inlineStr"/>
+      <c r="AC413" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD413" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE413" t="inlineStr"/>
+      <c r="AF413" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG413" t="inlineStr"/>
+      <c r="AH413" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI413" t="n">
+        <v>20262</v>
+      </c>
+      <c r="AJ413" t="inlineStr">
+        <is>
+          <t>269286</t>
+        </is>
+      </c>
+      <c r="AK413" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL413" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>15011</v>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>99****2276</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>10750</v>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 23:06:14</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>*9283</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P414" t="n">
+        <v>11000370178395</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>1782927354981</v>
+      </c>
+      <c r="R414" t="n">
+        <v>958280570453</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X414" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z414" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA414" t="inlineStr"/>
+      <c r="AB414" t="inlineStr"/>
+      <c r="AC414" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD414" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE414" t="inlineStr"/>
+      <c r="AF414" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG414" t="inlineStr"/>
+      <c r="AH414" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI414" t="n">
+        <v>19283</v>
+      </c>
+      <c r="AJ414" t="inlineStr">
+        <is>
+          <t>266301</t>
+        </is>
+      </c>
+      <c r="AK414" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="AL414" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL414"/>
+  <dimension ref="A1:AL419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64319,13 +64319,19 @@
       <c r="D408" t="n">
         <v>8700</v>
       </c>
-      <c r="E408" t="inlineStr"/>
+      <c r="E408" t="n">
+        <v>8700</v>
+      </c>
       <c r="F408" t="inlineStr">
         <is>
           <t>01-Jul-2026 07:27:15</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 18:33:21</t>
+        </is>
+      </c>
       <c r="H408" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -64390,7 +64396,7 @@
       </c>
       <c r="V408" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W408" t="inlineStr">
@@ -64413,15 +64419,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA408" t="inlineStr"/>
-      <c r="AB408" t="inlineStr"/>
+      <c r="AA408" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB408" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC408" t="n">
         <v>0</v>
       </c>
       <c r="AD408" t="n">
         <v>0</v>
       </c>
-      <c r="AE408" t="inlineStr"/>
+      <c r="AE408" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF408" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -64465,13 +64477,19 @@
       <c r="D409" t="n">
         <v>7250</v>
       </c>
-      <c r="E409" t="inlineStr"/>
+      <c r="E409" t="n">
+        <v>7250</v>
+      </c>
       <c r="F409" t="inlineStr">
         <is>
           <t>01-Jul-2026 11:35:41</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 18:33:21</t>
+        </is>
+      </c>
       <c r="H409" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -64536,7 +64554,7 @@
       </c>
       <c r="V409" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W409" t="inlineStr">
@@ -64559,15 +64577,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA409" t="inlineStr"/>
-      <c r="AB409" t="inlineStr"/>
+      <c r="AA409" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB409" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC409" t="n">
         <v>0</v>
       </c>
       <c r="AD409" t="n">
         <v>0</v>
       </c>
-      <c r="AE409" t="inlineStr"/>
+      <c r="AE409" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF409" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -64611,13 +64635,19 @@
       <c r="D410" t="n">
         <v>8700</v>
       </c>
-      <c r="E410" t="inlineStr"/>
+      <c r="E410" t="n">
+        <v>8700</v>
+      </c>
       <c r="F410" t="inlineStr">
         <is>
           <t>01-Jul-2026 11:36:53</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 18:33:21</t>
+        </is>
+      </c>
       <c r="H410" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -64682,7 +64712,7 @@
       </c>
       <c r="V410" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W410" t="inlineStr">
@@ -64705,15 +64735,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA410" t="inlineStr"/>
-      <c r="AB410" t="inlineStr"/>
+      <c r="AA410" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB410" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC410" t="n">
         <v>0</v>
       </c>
       <c r="AD410" t="n">
         <v>0</v>
       </c>
-      <c r="AE410" t="inlineStr"/>
+      <c r="AE410" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF410" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -64757,7 +64793,9 @@
       <c r="D411" t="n">
         <v>11600</v>
       </c>
-      <c r="E411" t="inlineStr"/>
+      <c r="E411" t="n">
+        <v>11600</v>
+      </c>
       <c r="F411" t="inlineStr">
         <is>
           <t>01-Jul-2026 14:34:28</t>
@@ -64828,7 +64866,7 @@
       </c>
       <c r="V411" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W411" t="inlineStr">
@@ -64851,15 +64889,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA411" t="inlineStr"/>
-      <c r="AB411" t="inlineStr"/>
+      <c r="AA411" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB411" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC411" t="n">
         <v>0</v>
       </c>
       <c r="AD411" t="n">
         <v>0</v>
       </c>
-      <c r="AE411" t="inlineStr"/>
+      <c r="AE411" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF411" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -64903,13 +64947,19 @@
       <c r="D412" t="n">
         <v>8700</v>
       </c>
-      <c r="E412" t="inlineStr"/>
+      <c r="E412" t="n">
+        <v>8700</v>
+      </c>
       <c r="F412" t="inlineStr">
         <is>
           <t>01-Jul-2026 20:24:30</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 18:33:21</t>
+        </is>
+      </c>
       <c r="H412" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -64974,7 +65024,7 @@
       </c>
       <c r="V412" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W412" t="inlineStr">
@@ -64997,15 +65047,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA412" t="inlineStr"/>
-      <c r="AB412" t="inlineStr"/>
+      <c r="AA412" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB412" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC412" t="n">
         <v>0</v>
       </c>
       <c r="AD412" t="n">
         <v>0</v>
       </c>
-      <c r="AE412" t="inlineStr"/>
+      <c r="AE412" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF412" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -65049,13 +65105,19 @@
       <c r="D413" t="n">
         <v>7250</v>
       </c>
-      <c r="E413" t="inlineStr"/>
+      <c r="E413" t="n">
+        <v>7250</v>
+      </c>
       <c r="F413" t="inlineStr">
         <is>
           <t>01-Jul-2026 21:59:43</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 18:33:21</t>
+        </is>
+      </c>
       <c r="H413" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -65120,7 +65182,7 @@
       </c>
       <c r="V413" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W413" t="inlineStr">
@@ -65143,15 +65205,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA413" t="inlineStr"/>
-      <c r="AB413" t="inlineStr"/>
+      <c r="AA413" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB413" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC413" t="n">
         <v>0</v>
       </c>
       <c r="AD413" t="n">
         <v>0</v>
       </c>
-      <c r="AE413" t="inlineStr"/>
+      <c r="AE413" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF413" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -65195,7 +65263,9 @@
       <c r="D414" t="n">
         <v>10750</v>
       </c>
-      <c r="E414" t="inlineStr"/>
+      <c r="E414" t="n">
+        <v>10750</v>
+      </c>
       <c r="F414" t="inlineStr">
         <is>
           <t>01-Jul-2026 23:06:14</t>
@@ -65266,7 +65336,7 @@
       </c>
       <c r="V414" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W414" t="inlineStr">
@@ -65289,15 +65359,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA414" t="inlineStr"/>
-      <c r="AB414" t="inlineStr"/>
+      <c r="AA414" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB414" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC414" t="n">
         <v>0</v>
       </c>
       <c r="AD414" t="n">
         <v>0</v>
       </c>
-      <c r="AE414" t="inlineStr"/>
+      <c r="AE414" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF414" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -65323,6 +65399,736 @@
         </is>
       </c>
       <c r="AL414" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>17364</v>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>95****7755</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 11:42:53</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>*0083</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P415" t="n">
+        <v>11000370248959</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>1782972763606</v>
+      </c>
+      <c r="R415" t="n">
+        <v>280967687505</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W415" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X415" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y415" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z415" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA415" t="inlineStr"/>
+      <c r="AB415" t="inlineStr"/>
+      <c r="AC415" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD415" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE415" t="inlineStr"/>
+      <c r="AF415" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG415" t="inlineStr"/>
+      <c r="AH415" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI415" t="n">
+        <v>20083</v>
+      </c>
+      <c r="AJ415" t="inlineStr">
+        <is>
+          <t>269229</t>
+        </is>
+      </c>
+      <c r="AK415" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL415" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>17289</v>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>99****4439</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 15:41:53</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>*9999</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N416" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P416" t="n">
+        <v>11000370319809</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>1782987061841</v>
+      </c>
+      <c r="R416" t="n">
+        <v>597188350842</v>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z416" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA416" t="inlineStr"/>
+      <c r="AB416" t="inlineStr"/>
+      <c r="AC416" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD416" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE416" t="inlineStr"/>
+      <c r="AF416" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG416" t="inlineStr"/>
+      <c r="AH416" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI416" t="n">
+        <v>19999</v>
+      </c>
+      <c r="AJ416" t="inlineStr">
+        <is>
+          <t>271283</t>
+        </is>
+      </c>
+      <c r="AK416" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL416" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>17290</v>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>99****4439</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 15:39:24</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>*0000</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N417" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P417" t="n">
+        <v>11000370320433</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>1782986940047</v>
+      </c>
+      <c r="R417" t="n">
+        <v>9290791408</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y417" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z417" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA417" t="inlineStr"/>
+      <c r="AB417" t="inlineStr"/>
+      <c r="AC417" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD417" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE417" t="inlineStr"/>
+      <c r="AF417" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG417" t="inlineStr"/>
+      <c r="AH417" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI417" t="n">
+        <v>20000</v>
+      </c>
+      <c r="AJ417" t="inlineStr">
+        <is>
+          <t>272445</t>
+        </is>
+      </c>
+      <c r="AK417" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL417" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>17655</v>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>62****2323</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 16:30:28</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>*0367</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N418" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P418" t="n">
+        <v>11000370330429</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>1782990013017</v>
+      </c>
+      <c r="R418" t="n">
+        <v>992689803205</v>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X418" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y418" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z418" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA418" t="inlineStr"/>
+      <c r="AB418" t="inlineStr"/>
+      <c r="AC418" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD418" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE418" t="inlineStr"/>
+      <c r="AF418" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG418" t="inlineStr"/>
+      <c r="AH418" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI418" t="n">
+        <v>20367</v>
+      </c>
+      <c r="AJ418" t="inlineStr">
+        <is>
+          <t>277171</t>
+        </is>
+      </c>
+      <c r="AK418" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="AL418" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>17559</v>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>96****5577</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>9400</v>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 20:31:23</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>*0278</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N419" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P419" t="n">
+        <v>11000370370340</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>1783004366928</v>
+      </c>
+      <c r="R419" t="n">
+        <v>654938260837</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X419" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y419" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z419" t="inlineStr">
+        <is>
+          <t>s******************@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA419" t="inlineStr"/>
+      <c r="AB419" t="inlineStr"/>
+      <c r="AC419" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD419" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE419" t="inlineStr"/>
+      <c r="AF419" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG419" t="inlineStr"/>
+      <c r="AH419" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI419" t="n">
+        <v>20278</v>
+      </c>
+      <c r="AJ419" t="inlineStr">
+        <is>
+          <t>274739</t>
+        </is>
+      </c>
+      <c r="AK419" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="AL419" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL419"/>
+  <dimension ref="A1:AL427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66134,6 +66134,1174 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>16685</v>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>90****8429</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 09:06:18</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>*8187</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N420" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P420" t="n">
+        <v>11000370431576</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>1783049770348</v>
+      </c>
+      <c r="R420" t="n">
+        <v>733969034401</v>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X420" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y420" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z420" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA420" t="inlineStr"/>
+      <c r="AB420" t="inlineStr"/>
+      <c r="AC420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE420" t="inlineStr"/>
+      <c r="AF420" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG420" t="inlineStr"/>
+      <c r="AH420" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI420" t="n">
+        <v>18187</v>
+      </c>
+      <c r="AJ420" t="inlineStr">
+        <is>
+          <t>271229</t>
+        </is>
+      </c>
+      <c r="AK420" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL420" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>17686</v>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>96****6021</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 10:31:45</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>*0430</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N421" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P421" t="n">
+        <v>11000370450794</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>1783054873260</v>
+      </c>
+      <c r="R421" t="n">
+        <v>368020293955</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA421" t="inlineStr"/>
+      <c r="AB421" t="inlineStr"/>
+      <c r="AC421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE421" t="inlineStr"/>
+      <c r="AF421" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG421" t="inlineStr"/>
+      <c r="AH421" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI421" t="n">
+        <v>20430</v>
+      </c>
+      <c r="AJ421" t="inlineStr">
+        <is>
+          <t>277135</t>
+        </is>
+      </c>
+      <c r="AK421" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL421" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>17396</v>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>93****9042</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 11:14:14</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>*0177</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N422" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P422" t="n">
+        <v>11000370453901</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>1783057438066</v>
+      </c>
+      <c r="R422" t="n">
+        <v>148472668787</v>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z422" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA422" t="inlineStr"/>
+      <c r="AB422" t="inlineStr"/>
+      <c r="AC422" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD422" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE422" t="inlineStr"/>
+      <c r="AF422" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG422" t="inlineStr"/>
+      <c r="AH422" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI422" t="n">
+        <v>20177</v>
+      </c>
+      <c r="AJ422" t="inlineStr">
+        <is>
+          <t>271171</t>
+        </is>
+      </c>
+      <c r="AK422" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL422" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>17197</v>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>98****4227</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 12:42:57</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>*9911</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N423" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P423" t="n">
+        <v>11000370484613</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>1783062761346</v>
+      </c>
+      <c r="R423" t="n">
+        <v>124927393284</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W423" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X423" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y423" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z423" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA423" t="inlineStr"/>
+      <c r="AB423" t="inlineStr"/>
+      <c r="AC423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE423" t="inlineStr"/>
+      <c r="AF423" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG423" t="inlineStr"/>
+      <c r="AH423" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI423" t="n">
+        <v>19911</v>
+      </c>
+      <c r="AJ423" t="inlineStr">
+        <is>
+          <t>271351</t>
+        </is>
+      </c>
+      <c r="AK423" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL423" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>16817</v>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>97****9099</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 12:44:19</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>*9205</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N424" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P424" t="n">
+        <v>11000370484680</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>1783062842596</v>
+      </c>
+      <c r="R424" t="n">
+        <v>655083392718</v>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W424" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X424" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y424" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z424" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA424" t="inlineStr"/>
+      <c r="AB424" t="inlineStr"/>
+      <c r="AC424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE424" t="inlineStr"/>
+      <c r="AF424" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG424" t="inlineStr"/>
+      <c r="AH424" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI424" t="n">
+        <v>19205</v>
+      </c>
+      <c r="AJ424" t="inlineStr">
+        <is>
+          <t>275928</t>
+        </is>
+      </c>
+      <c r="AK424" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL424" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>17446</v>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>98****4227</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 12:49:51</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>*0132</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N425" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P425" t="n">
+        <v>11000370492034</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>1783063117234</v>
+      </c>
+      <c r="R425" t="n">
+        <v>720640497520</v>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z425" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA425" t="inlineStr"/>
+      <c r="AB425" t="inlineStr"/>
+      <c r="AC425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE425" t="inlineStr"/>
+      <c r="AF425" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG425" t="inlineStr"/>
+      <c r="AH425" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI425" t="n">
+        <v>20132</v>
+      </c>
+      <c r="AJ425" t="inlineStr">
+        <is>
+          <t>269244</t>
+        </is>
+      </c>
+      <c r="AK425" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL425" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>17687</v>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>96****6021</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 12:56:09</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>*0431</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N426" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P426" t="n">
+        <v>11000370494791</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>1783063507480</v>
+      </c>
+      <c r="R426" t="n">
+        <v>26494125395</v>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA426" t="inlineStr"/>
+      <c r="AB426" t="inlineStr"/>
+      <c r="AC426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE426" t="inlineStr"/>
+      <c r="AF426" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG426" t="inlineStr"/>
+      <c r="AH426" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI426" t="n">
+        <v>20431</v>
+      </c>
+      <c r="AJ426" t="inlineStr">
+        <is>
+          <t>277130,277131</t>
+        </is>
+      </c>
+      <c r="AK426" t="inlineStr">
+        <is>
+          <t>2067,2076</t>
+        </is>
+      </c>
+      <c r="AL426" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>14947</v>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>90****4050</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 19:39:19</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>*9323</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N427" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P427" t="n">
+        <v>11000370580781</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>1783087733287</v>
+      </c>
+      <c r="R427" t="n">
+        <v>542977851768</v>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y427" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z427" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA427" t="inlineStr"/>
+      <c r="AB427" t="inlineStr"/>
+      <c r="AC427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE427" t="inlineStr"/>
+      <c r="AF427" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG427" t="inlineStr"/>
+      <c r="AH427" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI427" t="n">
+        <v>19323</v>
+      </c>
+      <c r="AJ427" t="inlineStr">
+        <is>
+          <t>276013</t>
+        </is>
+      </c>
+      <c r="AK427" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL427" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL427"/>
+  <dimension ref="A1:AL429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65417,13 +65417,19 @@
       <c r="D415" t="n">
         <v>7250</v>
       </c>
-      <c r="E415" t="inlineStr"/>
+      <c r="E415" t="n">
+        <v>7250</v>
+      </c>
       <c r="F415" t="inlineStr">
         <is>
           <t>02-Jul-2026 11:42:53</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H415" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -65488,7 +65494,7 @@
       </c>
       <c r="V415" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W415" t="inlineStr">
@@ -65511,15 +65517,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA415" t="inlineStr"/>
-      <c r="AB415" t="inlineStr"/>
+      <c r="AA415" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB415" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC415" t="n">
         <v>0</v>
       </c>
       <c r="AD415" t="n">
         <v>0</v>
       </c>
-      <c r="AE415" t="inlineStr"/>
+      <c r="AE415" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF415" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -65563,13 +65575,19 @@
       <c r="D416" t="n">
         <v>8400</v>
       </c>
-      <c r="E416" t="inlineStr"/>
+      <c r="E416" t="n">
+        <v>8400</v>
+      </c>
       <c r="F416" t="inlineStr">
         <is>
           <t>02-Jul-2026 15:41:53</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H416" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -65634,7 +65652,7 @@
       </c>
       <c r="V416" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W416" t="inlineStr">
@@ -65657,15 +65675,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA416" t="inlineStr"/>
-      <c r="AB416" t="inlineStr"/>
+      <c r="AA416" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB416" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC416" t="n">
         <v>0</v>
       </c>
       <c r="AD416" t="n">
         <v>0</v>
       </c>
-      <c r="AE416" t="inlineStr"/>
+      <c r="AE416" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF416" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -65709,13 +65733,19 @@
       <c r="D417" t="n">
         <v>8700</v>
       </c>
-      <c r="E417" t="inlineStr"/>
+      <c r="E417" t="n">
+        <v>8700</v>
+      </c>
       <c r="F417" t="inlineStr">
         <is>
           <t>02-Jul-2026 15:39:24</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H417" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -65780,7 +65810,7 @@
       </c>
       <c r="V417" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W417" t="inlineStr">
@@ -65803,15 +65833,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA417" t="inlineStr"/>
-      <c r="AB417" t="inlineStr"/>
+      <c r="AA417" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB417" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC417" t="n">
         <v>0</v>
       </c>
       <c r="AD417" t="n">
         <v>0</v>
       </c>
-      <c r="AE417" t="inlineStr"/>
+      <c r="AE417" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF417" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -65855,13 +65891,19 @@
       <c r="D418" t="n">
         <v>6500</v>
       </c>
-      <c r="E418" t="inlineStr"/>
+      <c r="E418" t="n">
+        <v>6500</v>
+      </c>
       <c r="F418" t="inlineStr">
         <is>
           <t>02-Jul-2026 16:30:28</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H418" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -65926,7 +65968,7 @@
       </c>
       <c r="V418" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W418" t="inlineStr">
@@ -65949,15 +65991,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA418" t="inlineStr"/>
-      <c r="AB418" t="inlineStr"/>
+      <c r="AA418" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB418" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC418" t="n">
         <v>0</v>
       </c>
       <c r="AD418" t="n">
         <v>0</v>
       </c>
-      <c r="AE418" t="inlineStr"/>
+      <c r="AE418" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF418" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -66001,7 +66049,9 @@
       <c r="D419" t="n">
         <v>9400</v>
       </c>
-      <c r="E419" t="inlineStr"/>
+      <c r="E419" t="n">
+        <v>9400</v>
+      </c>
       <c r="F419" t="inlineStr">
         <is>
           <t>02-Jul-2026 20:31:23</t>
@@ -66072,7 +66122,7 @@
       </c>
       <c r="V419" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W419" t="inlineStr">
@@ -66095,15 +66145,21 @@
           <t>s******************@gmail.com</t>
         </is>
       </c>
-      <c r="AA419" t="inlineStr"/>
-      <c r="AB419" t="inlineStr"/>
+      <c r="AA419" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB419" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC419" t="n">
         <v>0</v>
       </c>
       <c r="AD419" t="n">
         <v>0</v>
       </c>
-      <c r="AE419" t="inlineStr"/>
+      <c r="AE419" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF419" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
@@ -66147,13 +66203,19 @@
       <c r="D420" t="n">
         <v>8400</v>
       </c>
-      <c r="E420" t="inlineStr"/>
+      <c r="E420" t="n">
+        <v>8400</v>
+      </c>
       <c r="F420" t="inlineStr">
         <is>
           <t>03-Jul-2026 09:06:18</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H420" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -66218,7 +66280,7 @@
       </c>
       <c r="V420" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W420" t="inlineStr">
@@ -66241,15 +66303,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA420" t="inlineStr"/>
-      <c r="AB420" t="inlineStr"/>
+      <c r="AA420" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB420" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC420" t="n">
         <v>0</v>
       </c>
       <c r="AD420" t="n">
         <v>0</v>
       </c>
-      <c r="AE420" t="inlineStr"/>
+      <c r="AE420" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF420" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -66293,13 +66361,19 @@
       <c r="D421" t="n">
         <v>7250</v>
       </c>
-      <c r="E421" t="inlineStr"/>
+      <c r="E421" t="n">
+        <v>7250</v>
+      </c>
       <c r="F421" t="inlineStr">
         <is>
           <t>03-Jul-2026 10:31:45</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H421" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -66364,7 +66438,7 @@
       </c>
       <c r="V421" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W421" t="inlineStr">
@@ -66387,15 +66461,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA421" t="inlineStr"/>
-      <c r="AB421" t="inlineStr"/>
+      <c r="AA421" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB421" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC421" t="n">
         <v>0</v>
       </c>
       <c r="AD421" t="n">
         <v>0</v>
       </c>
-      <c r="AE421" t="inlineStr"/>
+      <c r="AE421" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF421" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -66439,13 +66519,19 @@
       <c r="D422" t="n">
         <v>8400</v>
       </c>
-      <c r="E422" t="inlineStr"/>
+      <c r="E422" t="n">
+        <v>8400</v>
+      </c>
       <c r="F422" t="inlineStr">
         <is>
           <t>03-Jul-2026 11:14:14</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H422" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -66510,7 +66596,7 @@
       </c>
       <c r="V422" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W422" t="inlineStr">
@@ -66533,15 +66619,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA422" t="inlineStr"/>
-      <c r="AB422" t="inlineStr"/>
+      <c r="AA422" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB422" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC422" t="n">
         <v>0</v>
       </c>
       <c r="AD422" t="n">
         <v>0</v>
       </c>
-      <c r="AE422" t="inlineStr"/>
+      <c r="AE422" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF422" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -66585,13 +66677,19 @@
       <c r="D423" t="n">
         <v>8400</v>
       </c>
-      <c r="E423" t="inlineStr"/>
+      <c r="E423" t="n">
+        <v>8400</v>
+      </c>
       <c r="F423" t="inlineStr">
         <is>
           <t>03-Jul-2026 12:42:57</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H423" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -66656,7 +66754,7 @@
       </c>
       <c r="V423" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W423" t="inlineStr">
@@ -66679,15 +66777,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA423" t="inlineStr"/>
-      <c r="AB423" t="inlineStr"/>
+      <c r="AA423" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB423" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC423" t="n">
         <v>0</v>
       </c>
       <c r="AD423" t="n">
         <v>0</v>
       </c>
-      <c r="AE423" t="inlineStr"/>
+      <c r="AE423" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF423" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -66731,7 +66835,9 @@
       <c r="D424" t="n">
         <v>12300</v>
       </c>
-      <c r="E424" t="inlineStr"/>
+      <c r="E424" t="n">
+        <v>12300</v>
+      </c>
       <c r="F424" t="inlineStr">
         <is>
           <t>03-Jul-2026 12:44:19</t>
@@ -66802,7 +66908,7 @@
       </c>
       <c r="V424" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W424" t="inlineStr">
@@ -66825,15 +66931,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA424" t="inlineStr"/>
-      <c r="AB424" t="inlineStr"/>
+      <c r="AA424" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB424" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC424" t="n">
         <v>0</v>
       </c>
       <c r="AD424" t="n">
         <v>0</v>
       </c>
-      <c r="AE424" t="inlineStr"/>
+      <c r="AE424" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF424" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -66877,13 +66989,19 @@
       <c r="D425" t="n">
         <v>7250</v>
       </c>
-      <c r="E425" t="inlineStr"/>
+      <c r="E425" t="n">
+        <v>7250</v>
+      </c>
       <c r="F425" t="inlineStr">
         <is>
           <t>03-Jul-2026 12:49:51</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H425" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -66948,7 +67066,7 @@
       </c>
       <c r="V425" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W425" t="inlineStr">
@@ -66971,15 +67089,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA425" t="inlineStr"/>
-      <c r="AB425" t="inlineStr"/>
+      <c r="AA425" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB425" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC425" t="n">
         <v>0</v>
       </c>
       <c r="AD425" t="n">
         <v>0</v>
       </c>
-      <c r="AE425" t="inlineStr"/>
+      <c r="AE425" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF425" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -67023,13 +67147,19 @@
       <c r="D426" t="n">
         <v>9000</v>
       </c>
-      <c r="E426" t="inlineStr"/>
+      <c r="E426" t="n">
+        <v>9000</v>
+      </c>
       <c r="F426" t="inlineStr">
         <is>
           <t>03-Jul-2026 12:56:09</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 17:40:49</t>
+        </is>
+      </c>
       <c r="H426" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -67094,7 +67224,7 @@
       </c>
       <c r="V426" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W426" t="inlineStr">
@@ -67117,15 +67247,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA426" t="inlineStr"/>
-      <c r="AB426" t="inlineStr"/>
+      <c r="AA426" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB426" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC426" t="n">
         <v>0</v>
       </c>
       <c r="AD426" t="n">
         <v>0</v>
       </c>
-      <c r="AE426" t="inlineStr"/>
+      <c r="AE426" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF426" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -67169,7 +67305,9 @@
       <c r="D427" t="n">
         <v>12300</v>
       </c>
-      <c r="E427" t="inlineStr"/>
+      <c r="E427" t="n">
+        <v>12300</v>
+      </c>
       <c r="F427" t="inlineStr">
         <is>
           <t>03-Jul-2026 19:39:19</t>
@@ -67240,7 +67378,7 @@
       </c>
       <c r="V427" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W427" t="inlineStr">
@@ -67263,15 +67401,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA427" t="inlineStr"/>
-      <c r="AB427" t="inlineStr"/>
+      <c r="AA427" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB427" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC427" t="n">
         <v>0</v>
       </c>
       <c r="AD427" t="n">
         <v>0</v>
       </c>
-      <c r="AE427" t="inlineStr"/>
+      <c r="AE427" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF427" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -67297,6 +67441,298 @@
         </is>
       </c>
       <c r="AL427" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>17454</v>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>88****9604</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 09:23:33</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>*0178</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N428" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P428" t="n">
+        <v>11000370643339</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>1783137199735</v>
+      </c>
+      <c r="R428" t="n">
+        <v>585537977236</v>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W428" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X428" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y428" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z428" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA428" t="inlineStr"/>
+      <c r="AB428" t="inlineStr"/>
+      <c r="AC428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE428" t="inlineStr"/>
+      <c r="AF428" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG428" t="inlineStr"/>
+      <c r="AH428" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI428" t="n">
+        <v>20178</v>
+      </c>
+      <c r="AJ428" t="inlineStr">
+        <is>
+          <t>271172</t>
+        </is>
+      </c>
+      <c r="AK428" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL428" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>17453</v>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>88****9604</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 09:22:26</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>*0161</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N429" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P429" t="n">
+        <v>11000370644112</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>1783137126963</v>
+      </c>
+      <c r="R429" t="n">
+        <v>300718144315</v>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W429" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y429" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z429" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA429" t="inlineStr"/>
+      <c r="AB429" t="inlineStr"/>
+      <c r="AC429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE429" t="inlineStr"/>
+      <c r="AF429" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG429" t="inlineStr"/>
+      <c r="AH429" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI429" t="n">
+        <v>20161</v>
+      </c>
+      <c r="AJ429" t="inlineStr">
+        <is>
+          <t>269276</t>
+        </is>
+      </c>
+      <c r="AK429" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL429" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL429"/>
+  <dimension ref="A1:AL436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67459,13 +67459,19 @@
       <c r="D428" t="n">
         <v>8400</v>
       </c>
-      <c r="E428" t="inlineStr"/>
+      <c r="E428" t="n">
+        <v>8400</v>
+      </c>
       <c r="F428" t="inlineStr">
         <is>
           <t>04-Jul-2026 09:23:33</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 19:18:36</t>
+        </is>
+      </c>
       <c r="H428" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -67530,7 +67536,7 @@
       </c>
       <c r="V428" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W428" t="inlineStr">
@@ -67553,15 +67559,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA428" t="inlineStr"/>
-      <c r="AB428" t="inlineStr"/>
+      <c r="AA428" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB428" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC428" t="n">
         <v>0</v>
       </c>
       <c r="AD428" t="n">
         <v>0</v>
       </c>
-      <c r="AE428" t="inlineStr"/>
+      <c r="AE428" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF428" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -67605,13 +67617,19 @@
       <c r="D429" t="n">
         <v>7250</v>
       </c>
-      <c r="E429" t="inlineStr"/>
+      <c r="E429" t="n">
+        <v>7250</v>
+      </c>
       <c r="F429" t="inlineStr">
         <is>
           <t>04-Jul-2026 09:22:26</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 19:18:36</t>
+        </is>
+      </c>
       <c r="H429" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -67676,7 +67694,7 @@
       </c>
       <c r="V429" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W429" t="inlineStr">
@@ -67699,15 +67717,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA429" t="inlineStr"/>
-      <c r="AB429" t="inlineStr"/>
+      <c r="AA429" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB429" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC429" t="n">
         <v>0</v>
       </c>
       <c r="AD429" t="n">
         <v>0</v>
       </c>
-      <c r="AE429" t="inlineStr"/>
+      <c r="AE429" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF429" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -67733,6 +67757,1040 @@
         </is>
       </c>
       <c r="AL429" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>17483</v>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>83****1036</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E430" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>05-Jul-2026 17:00:08</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 19:18:36</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>*0202</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P430" t="n">
+        <v>11000370877206</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>1783250987122</v>
+      </c>
+      <c r="R430" t="n">
+        <v>37223040900</v>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W430" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y430" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z430" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA430" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB430" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE430" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF430" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG430" t="inlineStr"/>
+      <c r="AH430" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI430" t="n">
+        <v>20202</v>
+      </c>
+      <c r="AJ430" t="inlineStr">
+        <is>
+          <t>269194</t>
+        </is>
+      </c>
+      <c r="AK430" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL430" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>17444</v>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>86****1578</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 10:37:33</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>*0190</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N431" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P431" t="n">
+        <v>11000371012089</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>1783314411903</v>
+      </c>
+      <c r="R431" t="n">
+        <v>69314796085</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W431" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y431" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z431" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA431" t="inlineStr"/>
+      <c r="AB431" t="inlineStr"/>
+      <c r="AC431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE431" t="inlineStr"/>
+      <c r="AF431" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG431" t="inlineStr"/>
+      <c r="AH431" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI431" t="n">
+        <v>20190</v>
+      </c>
+      <c r="AJ431" t="inlineStr">
+        <is>
+          <t>272405</t>
+        </is>
+      </c>
+      <c r="AK431" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL431" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>17611</v>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>70****0144</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 13:33:13</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>*0330</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N432" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P432" t="n">
+        <v>11000371074092</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>1783324979272</v>
+      </c>
+      <c r="R432" t="n">
+        <v>342620024167</v>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W432" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z432" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA432" t="inlineStr"/>
+      <c r="AB432" t="inlineStr"/>
+      <c r="AC432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE432" t="inlineStr"/>
+      <c r="AF432" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG432" t="inlineStr"/>
+      <c r="AH432" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI432" t="n">
+        <v>20330</v>
+      </c>
+      <c r="AJ432" t="inlineStr">
+        <is>
+          <t>268800</t>
+        </is>
+      </c>
+      <c r="AK432" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="AL432" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>17612</v>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>70****0144</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 13:47:26</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>*0331</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N433" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P433" t="n">
+        <v>11000371075957</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>1783325834580</v>
+      </c>
+      <c r="R433" t="n">
+        <v>243303966386</v>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W433" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y433" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z433" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA433" t="inlineStr"/>
+      <c r="AB433" t="inlineStr"/>
+      <c r="AC433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE433" t="inlineStr"/>
+      <c r="AF433" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG433" t="inlineStr"/>
+      <c r="AH433" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI433" t="n">
+        <v>20331</v>
+      </c>
+      <c r="AJ433" t="inlineStr">
+        <is>
+          <t>271335</t>
+        </is>
+      </c>
+      <c r="AK433" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL433" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>17613</v>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>70****0144</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 13:46:26</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>*0332</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N434" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P434" t="n">
+        <v>11000371077229</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>1783325775130</v>
+      </c>
+      <c r="R434" t="n">
+        <v>402945834522</v>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W434" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y434" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z434" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA434" t="inlineStr"/>
+      <c r="AB434" t="inlineStr"/>
+      <c r="AC434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE434" t="inlineStr"/>
+      <c r="AF434" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG434" t="inlineStr"/>
+      <c r="AH434" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI434" t="n">
+        <v>20332</v>
+      </c>
+      <c r="AJ434" t="inlineStr">
+        <is>
+          <t>271336</t>
+        </is>
+      </c>
+      <c r="AK434" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL434" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>17552</v>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>81****4834</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 13:52:23</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>*0271</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N435" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P435" t="n">
+        <v>11000371077783</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>1783326127638</v>
+      </c>
+      <c r="R435" t="n">
+        <v>392228835312</v>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W435" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y435" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z435" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA435" t="inlineStr"/>
+      <c r="AB435" t="inlineStr"/>
+      <c r="AC435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE435" t="inlineStr"/>
+      <c r="AF435" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG435" t="inlineStr"/>
+      <c r="AH435" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI435" t="n">
+        <v>20271</v>
+      </c>
+      <c r="AJ435" t="inlineStr">
+        <is>
+          <t>272414</t>
+        </is>
+      </c>
+      <c r="AK435" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL435" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>16659</v>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>86****0797</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>26700</v>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 18:53:42</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>*8377</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N436" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P436" t="n">
+        <v>11000371141040</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>1783344190471</v>
+      </c>
+      <c r="R436" t="n">
+        <v>883870971584</v>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W436" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z436" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA436" t="inlineStr"/>
+      <c r="AB436" t="inlineStr"/>
+      <c r="AC436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE436" t="inlineStr"/>
+      <c r="AF436" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG436" t="inlineStr"/>
+      <c r="AH436" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI436" t="n">
+        <v>18377</v>
+      </c>
+      <c r="AJ436" t="inlineStr">
+        <is>
+          <t>270169,272780,273092,273404</t>
+        </is>
+      </c>
+      <c r="AK436" t="inlineStr">
+        <is>
+          <t>2067,2081,2082,2083</t>
+        </is>
+      </c>
+      <c r="AL436" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL436"/>
+  <dimension ref="A1:AL438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68796,6 +68796,294 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>16353</v>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>93****3084</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 20:56:28</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>*8469</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N437" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P437" t="n">
+        <v>11000371165679</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>1783351470900</v>
+      </c>
+      <c r="R437" t="n">
+        <v>618726080298</v>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y437" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z437" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA437" t="inlineStr"/>
+      <c r="AB437" t="inlineStr"/>
+      <c r="AC437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE437" t="inlineStr"/>
+      <c r="AF437" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG437" t="inlineStr"/>
+      <c r="AH437" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI437" t="n">
+        <v>18469</v>
+      </c>
+      <c r="AJ437" t="inlineStr">
+        <is>
+          <t>272507</t>
+        </is>
+      </c>
+      <c r="AK437" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>17455</v>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>73****9369</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 21:58:43</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>*0450</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N438" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P438" t="n">
+        <v>11000371178055</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>1783355277549</v>
+      </c>
+      <c r="R438" t="n">
+        <v>298937086055</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W438" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y438" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z438" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA438" t="inlineStr"/>
+      <c r="AB438" t="inlineStr"/>
+      <c r="AC438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE438" t="inlineStr"/>
+      <c r="AF438" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG438" t="inlineStr"/>
+      <c r="AH438" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI438" t="n">
+        <v>20450</v>
+      </c>
+      <c r="AJ438" t="inlineStr">
+        <is>
+          <t>277544</t>
+        </is>
+      </c>
+      <c r="AK438" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL438" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL438"/>
+  <dimension ref="A1:AL449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67933,13 +67933,19 @@
       <c r="D431" t="n">
         <v>8700</v>
       </c>
-      <c r="E431" t="inlineStr"/>
+      <c r="E431" t="n">
+        <v>8700</v>
+      </c>
       <c r="F431" t="inlineStr">
         <is>
           <t>06-Jul-2026 10:37:33</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 19:39:10</t>
+        </is>
+      </c>
       <c r="H431" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -68004,7 +68010,7 @@
       </c>
       <c r="V431" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W431" t="inlineStr">
@@ -68027,15 +68033,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA431" t="inlineStr"/>
-      <c r="AB431" t="inlineStr"/>
+      <c r="AA431" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB431" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC431" t="n">
         <v>0</v>
       </c>
       <c r="AD431" t="n">
         <v>0</v>
       </c>
-      <c r="AE431" t="inlineStr"/>
+      <c r="AE431" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF431" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -68079,13 +68091,19 @@
       <c r="D432" t="n">
         <v>6500</v>
       </c>
-      <c r="E432" t="inlineStr"/>
+      <c r="E432" t="n">
+        <v>6500</v>
+      </c>
       <c r="F432" t="inlineStr">
         <is>
           <t>06-Jul-2026 13:33:13</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 19:30:48</t>
+        </is>
+      </c>
       <c r="H432" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -68150,7 +68168,7 @@
       </c>
       <c r="V432" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W432" t="inlineStr">
@@ -68173,15 +68191,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA432" t="inlineStr"/>
-      <c r="AB432" t="inlineStr"/>
+      <c r="AA432" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB432" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC432" t="n">
         <v>0</v>
       </c>
       <c r="AD432" t="n">
         <v>0</v>
       </c>
-      <c r="AE432" t="inlineStr"/>
+      <c r="AE432" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF432" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -68225,13 +68249,19 @@
       <c r="D433" t="n">
         <v>8400</v>
       </c>
-      <c r="E433" t="inlineStr"/>
+      <c r="E433" t="n">
+        <v>8400</v>
+      </c>
       <c r="F433" t="inlineStr">
         <is>
           <t>06-Jul-2026 13:47:26</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 19:39:10</t>
+        </is>
+      </c>
       <c r="H433" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -68296,7 +68326,7 @@
       </c>
       <c r="V433" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W433" t="inlineStr">
@@ -68319,15 +68349,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA433" t="inlineStr"/>
-      <c r="AB433" t="inlineStr"/>
+      <c r="AA433" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB433" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC433" t="n">
         <v>0</v>
       </c>
       <c r="AD433" t="n">
         <v>0</v>
       </c>
-      <c r="AE433" t="inlineStr"/>
+      <c r="AE433" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF433" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -68371,13 +68407,19 @@
       <c r="D434" t="n">
         <v>8400</v>
       </c>
-      <c r="E434" t="inlineStr"/>
+      <c r="E434" t="n">
+        <v>8400</v>
+      </c>
       <c r="F434" t="inlineStr">
         <is>
           <t>06-Jul-2026 13:46:26</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 19:39:10</t>
+        </is>
+      </c>
       <c r="H434" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -68442,7 +68484,7 @@
       </c>
       <c r="V434" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W434" t="inlineStr">
@@ -68465,15 +68507,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA434" t="inlineStr"/>
-      <c r="AB434" t="inlineStr"/>
+      <c r="AA434" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB434" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC434" t="n">
         <v>0</v>
       </c>
       <c r="AD434" t="n">
         <v>0</v>
       </c>
-      <c r="AE434" t="inlineStr"/>
+      <c r="AE434" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF434" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -68517,13 +68565,19 @@
       <c r="D435" t="n">
         <v>8700</v>
       </c>
-      <c r="E435" t="inlineStr"/>
+      <c r="E435" t="n">
+        <v>8700</v>
+      </c>
       <c r="F435" t="inlineStr">
         <is>
           <t>06-Jul-2026 13:52:23</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 19:39:10</t>
+        </is>
+      </c>
       <c r="H435" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -68588,7 +68642,7 @@
       </c>
       <c r="V435" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W435" t="inlineStr">
@@ -68611,15 +68665,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA435" t="inlineStr"/>
-      <c r="AB435" t="inlineStr"/>
+      <c r="AA435" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB435" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC435" t="n">
         <v>0</v>
       </c>
       <c r="AD435" t="n">
         <v>0</v>
       </c>
-      <c r="AE435" t="inlineStr"/>
+      <c r="AE435" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF435" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -68663,13 +68723,19 @@
       <c r="D436" t="n">
         <v>26700</v>
       </c>
-      <c r="E436" t="inlineStr"/>
+      <c r="E436" t="n">
+        <v>26700</v>
+      </c>
       <c r="F436" t="inlineStr">
         <is>
           <t>06-Jul-2026 18:53:42</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 19:39:10</t>
+        </is>
+      </c>
       <c r="H436" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -68734,7 +68800,7 @@
       </c>
       <c r="V436" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W436" t="inlineStr">
@@ -68757,15 +68823,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA436" t="inlineStr"/>
-      <c r="AB436" t="inlineStr"/>
+      <c r="AA436" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB436" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC436" t="n">
         <v>0</v>
       </c>
       <c r="AD436" t="n">
         <v>0</v>
       </c>
-      <c r="AE436" t="inlineStr"/>
+      <c r="AE436" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF436" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -68809,13 +68881,19 @@
       <c r="D437" t="n">
         <v>8700</v>
       </c>
-      <c r="E437" t="inlineStr"/>
+      <c r="E437" t="n">
+        <v>8700</v>
+      </c>
       <c r="F437" t="inlineStr">
         <is>
           <t>06-Jul-2026 20:56:28</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 19:39:10</t>
+        </is>
+      </c>
       <c r="H437" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -68880,7 +68958,7 @@
       </c>
       <c r="V437" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W437" t="inlineStr">
@@ -68903,15 +68981,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA437" t="inlineStr"/>
-      <c r="AB437" t="inlineStr"/>
+      <c r="AA437" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>18.79</v>
+      </c>
       <c r="AC437" t="n">
         <v>0</v>
       </c>
       <c r="AD437" t="n">
         <v>0</v>
       </c>
-      <c r="AE437" t="inlineStr"/>
+      <c r="AE437" t="n">
+        <v>123.19</v>
+      </c>
       <c r="AF437" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -68951,13 +69035,19 @@
       <c r="D438" t="n">
         <v>8400</v>
       </c>
-      <c r="E438" t="inlineStr"/>
+      <c r="E438" t="n">
+        <v>8400</v>
+      </c>
       <c r="F438" t="inlineStr">
         <is>
           <t>06-Jul-2026 21:58:43</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 19:39:10</t>
+        </is>
+      </c>
       <c r="H438" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -69022,7 +69112,7 @@
       </c>
       <c r="V438" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W438" t="inlineStr">
@@ -69045,15 +69135,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA438" t="inlineStr"/>
-      <c r="AB438" t="inlineStr"/>
+      <c r="AA438" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC438" t="n">
         <v>0</v>
       </c>
       <c r="AD438" t="n">
         <v>0</v>
       </c>
-      <c r="AE438" t="inlineStr"/>
+      <c r="AE438" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF438" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -69079,6 +69175,1700 @@
         </is>
       </c>
       <c r="AL438" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>17209</v>
+      </c>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>81****5789</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E439" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 11:59:23</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 18:04:16</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>*9923</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N439" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P439" t="n">
+        <v>11000371263354</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>1783405749590</v>
+      </c>
+      <c r="R439" t="n">
+        <v>662958196587</v>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y439" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z439" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA439" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF439" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG439" t="inlineStr"/>
+      <c r="AH439" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI439" t="n">
+        <v>19923</v>
+      </c>
+      <c r="AJ439" t="inlineStr">
+        <is>
+          <t>272277</t>
+        </is>
+      </c>
+      <c r="AK439" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL439" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>17581</v>
+      </c>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>81****5789</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E440" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 12:08:22</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 18:04:16</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>*0300</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N440" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P440" t="n">
+        <v>11000371266226</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>1783406256734</v>
+      </c>
+      <c r="R440" t="n">
+        <v>34612834600</v>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z440" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA440" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF440" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG440" t="inlineStr"/>
+      <c r="AH440" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI440" t="n">
+        <v>20300</v>
+      </c>
+      <c r="AJ440" t="inlineStr">
+        <is>
+          <t>269207</t>
+        </is>
+      </c>
+      <c r="AK440" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL440" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>16936</v>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>63****8581</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E441" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 12:38:28</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 18:04:16</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>*8341</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N441" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P441" t="n">
+        <v>11000371276208</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>1783408085251</v>
+      </c>
+      <c r="R441" t="n">
+        <v>172682718910</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z441" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA441" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF441" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG441" t="inlineStr"/>
+      <c r="AH441" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI441" t="n">
+        <v>18341</v>
+      </c>
+      <c r="AJ441" t="inlineStr">
+        <is>
+          <t>272309</t>
+        </is>
+      </c>
+      <c r="AK441" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL441" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>17229</v>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>99****5602</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>9400</v>
+      </c>
+      <c r="E442" t="n">
+        <v>9400</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 13:44:08</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>*9941</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N442" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P442" t="n">
+        <v>11000371292922</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>1783411980424</v>
+      </c>
+      <c r="R442" t="n">
+        <v>462825959313</v>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z442" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA442" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF442" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG442" t="inlineStr"/>
+      <c r="AH442" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI442" t="n">
+        <v>19941</v>
+      </c>
+      <c r="AJ442" t="inlineStr">
+        <is>
+          <t>274759</t>
+        </is>
+      </c>
+      <c r="AK442" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="AL442" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>17499</v>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>99****1533</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E443" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 15:44:44</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 18:04:16</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>*0218</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P443" t="n">
+        <v>11000371319560</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>1783419274653</v>
+      </c>
+      <c r="R443" t="n">
+        <v>548548443878</v>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA443" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF443" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG443" t="inlineStr"/>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI443" t="n">
+        <v>20218</v>
+      </c>
+      <c r="AJ443" t="inlineStr">
+        <is>
+          <t>269280</t>
+        </is>
+      </c>
+      <c r="AK443" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL443" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>17498</v>
+      </c>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>99****1533</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E444" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 15:43:30</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 18:04:16</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>*0217</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N444" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P444" t="n">
+        <v>11000371320159</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>1783419185484</v>
+      </c>
+      <c r="R444" t="n">
+        <v>734999141645</v>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y444" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z444" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA444" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF444" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG444" t="inlineStr"/>
+      <c r="AH444" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI444" t="n">
+        <v>20217</v>
+      </c>
+      <c r="AJ444" t="inlineStr">
+        <is>
+          <t>273647</t>
+        </is>
+      </c>
+      <c r="AK444" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL444" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>17414</v>
+      </c>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>90****4050</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E445" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 16:19:36</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 18:04:16</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>*0185</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N445" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P445" t="n">
+        <v>11000371326188</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>1783421364162</v>
+      </c>
+      <c r="R445" t="n">
+        <v>450385775361</v>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA445" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF445" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG445" t="inlineStr"/>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI445" t="n">
+        <v>20185</v>
+      </c>
+      <c r="AJ445" t="inlineStr">
+        <is>
+          <t>272400</t>
+        </is>
+      </c>
+      <c r="AK445" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL445" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>17179</v>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>63****6999</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E446" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 16:31:18</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 18:04:16</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>*9894</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N446" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P446" t="n">
+        <v>11000371328310</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>1783422032913</v>
+      </c>
+      <c r="R446" t="n">
+        <v>103627157517</v>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W446" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y446" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z446" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA446" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF446" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG446" t="inlineStr"/>
+      <c r="AH446" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI446" t="n">
+        <v>19894</v>
+      </c>
+      <c r="AJ446" t="inlineStr">
+        <is>
+          <t>269296</t>
+        </is>
+      </c>
+      <c r="AK446" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>14546</v>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>81****1492</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 00:29:44</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>*9383</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N447" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P447" t="n">
+        <v>11000371408479</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>1783450749798</v>
+      </c>
+      <c r="R447" t="n">
+        <v>209520783048</v>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA447" t="inlineStr"/>
+      <c r="AB447" t="inlineStr"/>
+      <c r="AC447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE447" t="inlineStr"/>
+      <c r="AF447" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG447" t="inlineStr"/>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI447" t="n">
+        <v>19383</v>
+      </c>
+      <c r="AJ447" t="inlineStr">
+        <is>
+          <t>276114</t>
+        </is>
+      </c>
+      <c r="AK447" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL447" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>17215</v>
+      </c>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>95****8421</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 09:29:59</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>*9928</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N448" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P448" t="n">
+        <v>11000371437749</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>1783483179375</v>
+      </c>
+      <c r="R448" t="n">
+        <v>655544549646</v>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W448" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y448" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA448" t="inlineStr"/>
+      <c r="AB448" t="inlineStr"/>
+      <c r="AC448" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD448" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE448" t="inlineStr"/>
+      <c r="AF448" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG448" t="inlineStr"/>
+      <c r="AH448" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI448" t="n">
+        <v>19928</v>
+      </c>
+      <c r="AJ448" t="inlineStr">
+        <is>
+          <t>269362</t>
+        </is>
+      </c>
+      <c r="AK448" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL448" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>17685</v>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>81****7481</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 10:44:50</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>*0429</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P449" t="n">
+        <v>11000371454936</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>1783487667354</v>
+      </c>
+      <c r="R449" t="n">
+        <v>104516802468</v>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W449" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y449" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA449" t="inlineStr"/>
+      <c r="AB449" t="inlineStr"/>
+      <c r="AC449" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD449" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE449" t="inlineStr"/>
+      <c r="AF449" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG449" t="inlineStr"/>
+      <c r="AH449" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI449" t="n">
+        <v>20429</v>
+      </c>
+      <c r="AJ449" t="inlineStr">
+        <is>
+          <t>277188</t>
+        </is>
+      </c>
+      <c r="AK449" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL449" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL449"/>
+  <dimension ref="A1:AL451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70874,6 +70874,290 @@
         </is>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>17001</v>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>79****8806</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 00:30:51</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>*8090</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N450" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P450" t="n">
+        <v>11000371625455</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>1783537186850</v>
+      </c>
+      <c r="R450" t="n">
+        <v>619021000861</v>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W450" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y450" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z450" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA450" t="inlineStr"/>
+      <c r="AB450" t="inlineStr"/>
+      <c r="AC450" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD450" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE450" t="inlineStr"/>
+      <c r="AF450" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG450" t="inlineStr"/>
+      <c r="AH450" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI450" t="n">
+        <v>18090</v>
+      </c>
+      <c r="AJ450" t="inlineStr">
+        <is>
+          <t>271343</t>
+        </is>
+      </c>
+      <c r="AK450" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>16567</v>
+      </c>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>90****7436</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 00:28:29</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>*8277</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N451" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P451" t="n">
+        <v>11000371626441</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>1783537025732</v>
+      </c>
+      <c r="R451" t="n">
+        <v>619041000858</v>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z451" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA451" t="inlineStr"/>
+      <c r="AB451" t="inlineStr"/>
+      <c r="AC451" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD451" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE451" t="inlineStr"/>
+      <c r="AF451" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG451" t="inlineStr"/>
+      <c r="AH451" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI451" t="n">
+        <v>18277</v>
+      </c>
+      <c r="AJ451" t="inlineStr">
+        <is>
+          <t>272327</t>
+        </is>
+      </c>
+      <c r="AK451" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL451" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL451"/>
+  <dimension ref="A1:AL454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70449,7 +70449,9 @@
       <c r="D447" t="n">
         <v>12300</v>
       </c>
-      <c r="E447" t="inlineStr"/>
+      <c r="E447" t="n">
+        <v>12300</v>
+      </c>
       <c r="F447" t="inlineStr">
         <is>
           <t>08-Jul-2026 00:29:44</t>
@@ -70520,7 +70522,7 @@
       </c>
       <c r="V447" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W447" t="inlineStr">
@@ -70543,15 +70545,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA447" t="inlineStr"/>
-      <c r="AB447" t="inlineStr"/>
+      <c r="AA447" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC447" t="n">
         <v>0</v>
       </c>
       <c r="AD447" t="n">
         <v>0</v>
       </c>
-      <c r="AE447" t="inlineStr"/>
+      <c r="AE447" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF447" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -70595,13 +70603,19 @@
       <c r="D448" t="n">
         <v>7250</v>
       </c>
-      <c r="E448" t="inlineStr"/>
+      <c r="E448" t="n">
+        <v>7250</v>
+      </c>
       <c r="F448" t="inlineStr">
         <is>
           <t>08-Jul-2026 09:29:59</t>
         </is>
       </c>
-      <c r="G448" t="inlineStr"/>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 18:44:40</t>
+        </is>
+      </c>
       <c r="H448" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -70666,7 +70680,7 @@
       </c>
       <c r="V448" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W448" t="inlineStr">
@@ -70689,15 +70703,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA448" t="inlineStr"/>
-      <c r="AB448" t="inlineStr"/>
+      <c r="AA448" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB448" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC448" t="n">
         <v>0</v>
       </c>
       <c r="AD448" t="n">
         <v>0</v>
       </c>
-      <c r="AE448" t="inlineStr"/>
+      <c r="AE448" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF448" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -70741,13 +70761,19 @@
       <c r="D449" t="n">
         <v>7250</v>
       </c>
-      <c r="E449" t="inlineStr"/>
+      <c r="E449" t="n">
+        <v>7250</v>
+      </c>
       <c r="F449" t="inlineStr">
         <is>
           <t>08-Jul-2026 10:44:50</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr"/>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 18:44:40</t>
+        </is>
+      </c>
       <c r="H449" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -70812,7 +70838,7 @@
       </c>
       <c r="V449" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W449" t="inlineStr">
@@ -70835,15 +70861,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA449" t="inlineStr"/>
-      <c r="AB449" t="inlineStr"/>
+      <c r="AA449" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB449" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC449" t="n">
         <v>0</v>
       </c>
       <c r="AD449" t="n">
         <v>0</v>
       </c>
-      <c r="AE449" t="inlineStr"/>
+      <c r="AE449" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF449" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -71158,6 +71190,444 @@
       </c>
       <c r="AL451" t="inlineStr"/>
     </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>14717</v>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>77****7302</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>22700</v>
+      </c>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 11:18:16</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>*9374</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N452" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P452" t="n">
+        <v>11000371680033</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>1783576085008</v>
+      </c>
+      <c r="R452" t="n">
+        <v>898582523480</v>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W452" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y452" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA452" t="inlineStr"/>
+      <c r="AB452" t="inlineStr"/>
+      <c r="AC452" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD452" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE452" t="inlineStr"/>
+      <c r="AF452" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG452" t="inlineStr"/>
+      <c r="AH452" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI452" t="n">
+        <v>19374</v>
+      </c>
+      <c r="AJ452" t="inlineStr">
+        <is>
+          <t>266457,268107</t>
+        </is>
+      </c>
+      <c r="AK452" t="inlineStr">
+        <is>
+          <t>2053,2061</t>
+        </is>
+      </c>
+      <c r="AL452" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>17362</v>
+      </c>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>83****6661</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 12:49:10</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>*0081</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N453" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P453" t="n">
+        <v>11000371713804</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>1783581520890</v>
+      </c>
+      <c r="R453" t="n">
+        <v>562296538515</v>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W453" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y453" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA453" t="inlineStr"/>
+      <c r="AB453" t="inlineStr"/>
+      <c r="AC453" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD453" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE453" t="inlineStr"/>
+      <c r="AF453" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG453" t="inlineStr"/>
+      <c r="AH453" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI453" t="n">
+        <v>20081</v>
+      </c>
+      <c r="AJ453" t="inlineStr">
+        <is>
+          <t>273587</t>
+        </is>
+      </c>
+      <c r="AK453" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL453" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>17654</v>
+      </c>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>81****0759</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 20:19:47</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>*0366</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N454" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P454" t="n">
+        <v>11000371809305</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>1783608575991</v>
+      </c>
+      <c r="R454" t="n">
+        <v>45802753337</v>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W454" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X454" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y454" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z454" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA454" t="inlineStr"/>
+      <c r="AB454" t="inlineStr"/>
+      <c r="AC454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE454" t="inlineStr"/>
+      <c r="AF454" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG454" t="inlineStr"/>
+      <c r="AH454" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI454" t="n">
+        <v>20366</v>
+      </c>
+      <c r="AJ454" t="inlineStr">
+        <is>
+          <t>277170</t>
+        </is>
+      </c>
+      <c r="AK454" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="AL454" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL454"/>
+  <dimension ref="A1:AL461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70919,13 +70919,19 @@
       <c r="D450" t="n">
         <v>8400</v>
       </c>
-      <c r="E450" t="inlineStr"/>
+      <c r="E450" t="n">
+        <v>8400</v>
+      </c>
       <c r="F450" t="inlineStr">
         <is>
           <t>09-Jul-2026 00:30:51</t>
         </is>
       </c>
-      <c r="G450" t="inlineStr"/>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 19:22:13</t>
+        </is>
+      </c>
       <c r="H450" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -70990,7 +70996,7 @@
       </c>
       <c r="V450" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W450" t="inlineStr">
@@ -71013,15 +71019,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA450" t="inlineStr"/>
-      <c r="AB450" t="inlineStr"/>
+      <c r="AA450" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="AB450" t="n">
+        <v>18.14</v>
+      </c>
       <c r="AC450" t="n">
         <v>0</v>
       </c>
       <c r="AD450" t="n">
         <v>0</v>
       </c>
-      <c r="AE450" t="inlineStr"/>
+      <c r="AE450" t="n">
+        <v>118.94</v>
+      </c>
       <c r="AF450" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -71061,13 +71073,19 @@
       <c r="D451" t="n">
         <v>8700</v>
       </c>
-      <c r="E451" t="inlineStr"/>
+      <c r="E451" t="n">
+        <v>8700</v>
+      </c>
       <c r="F451" t="inlineStr">
         <is>
           <t>09-Jul-2026 00:28:29</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr"/>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 19:22:13</t>
+        </is>
+      </c>
       <c r="H451" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -71132,7 +71150,7 @@
       </c>
       <c r="V451" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W451" t="inlineStr">
@@ -71155,15 +71173,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA451" t="inlineStr"/>
-      <c r="AB451" t="inlineStr"/>
+      <c r="AA451" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AB451" t="n">
+        <v>18.79</v>
+      </c>
       <c r="AC451" t="n">
         <v>0</v>
       </c>
       <c r="AD451" t="n">
         <v>0</v>
       </c>
-      <c r="AE451" t="inlineStr"/>
+      <c r="AE451" t="n">
+        <v>123.19</v>
+      </c>
       <c r="AF451" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -71203,7 +71227,9 @@
       <c r="D452" t="n">
         <v>22700</v>
       </c>
-      <c r="E452" t="inlineStr"/>
+      <c r="E452" t="n">
+        <v>22700</v>
+      </c>
       <c r="F452" t="inlineStr">
         <is>
           <t>09-Jul-2026 11:18:16</t>
@@ -71274,7 +71300,7 @@
       </c>
       <c r="V452" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W452" t="inlineStr">
@@ -71297,15 +71323,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA452" t="inlineStr"/>
-      <c r="AB452" t="inlineStr"/>
+      <c r="AA452" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB452" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC452" t="n">
         <v>0</v>
       </c>
       <c r="AD452" t="n">
         <v>0</v>
       </c>
-      <c r="AE452" t="inlineStr"/>
+      <c r="AE452" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF452" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -71349,13 +71381,19 @@
       <c r="D453" t="n">
         <v>9000</v>
       </c>
-      <c r="E453" t="inlineStr"/>
+      <c r="E453" t="n">
+        <v>9000</v>
+      </c>
       <c r="F453" t="inlineStr">
         <is>
           <t>09-Jul-2026 12:49:10</t>
         </is>
       </c>
-      <c r="G453" t="inlineStr"/>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 19:22:13</t>
+        </is>
+      </c>
       <c r="H453" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -71420,7 +71458,7 @@
       </c>
       <c r="V453" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W453" t="inlineStr">
@@ -71443,15 +71481,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA453" t="inlineStr"/>
-      <c r="AB453" t="inlineStr"/>
+      <c r="AA453" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB453" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC453" t="n">
         <v>0</v>
       </c>
       <c r="AD453" t="n">
         <v>0</v>
       </c>
-      <c r="AE453" t="inlineStr"/>
+      <c r="AE453" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF453" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -71495,13 +71539,19 @@
       <c r="D454" t="n">
         <v>6500</v>
       </c>
-      <c r="E454" t="inlineStr"/>
+      <c r="E454" t="n">
+        <v>6500</v>
+      </c>
       <c r="F454" t="inlineStr">
         <is>
           <t>09-Jul-2026 20:19:47</t>
         </is>
       </c>
-      <c r="G454" t="inlineStr"/>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 19:46:32</t>
+        </is>
+      </c>
       <c r="H454" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -71566,7 +71616,7 @@
       </c>
       <c r="V454" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W454" t="inlineStr">
@@ -71589,15 +71639,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA454" t="inlineStr"/>
-      <c r="AB454" t="inlineStr"/>
+      <c r="AA454" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB454" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC454" t="n">
         <v>0</v>
       </c>
       <c r="AD454" t="n">
         <v>0</v>
       </c>
-      <c r="AE454" t="inlineStr"/>
+      <c r="AE454" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF454" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -71627,6 +71683,1016 @@
           <t>UPI INTENT</t>
         </is>
       </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>15434</v>
+      </c>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 07:02:55</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>*9171</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N455" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P455" t="n">
+        <v>11000371846745</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>1783646728961</v>
+      </c>
+      <c r="R455" t="n">
+        <v>619142008454</v>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W455" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y455" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z455" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA455" t="inlineStr"/>
+      <c r="AB455" t="inlineStr"/>
+      <c r="AC455" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD455" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE455" t="inlineStr"/>
+      <c r="AF455" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG455" t="inlineStr"/>
+      <c r="AH455" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI455" t="n">
+        <v>19171</v>
+      </c>
+      <c r="AJ455" t="inlineStr">
+        <is>
+          <t>275997</t>
+        </is>
+      </c>
+      <c r="AK455" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>17190</v>
+      </c>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>73****0446</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 15:32:30</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>*9904</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N456" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P456" t="n">
+        <v>11000371966595</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>1783677728180</v>
+      </c>
+      <c r="R456" t="n">
+        <v>548704658990</v>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W456" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X456" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y456" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z456" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA456" t="inlineStr"/>
+      <c r="AB456" t="inlineStr"/>
+      <c r="AC456" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD456" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE456" t="inlineStr"/>
+      <c r="AF456" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG456" t="inlineStr"/>
+      <c r="AH456" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI456" t="n">
+        <v>19904</v>
+      </c>
+      <c r="AJ456" t="inlineStr">
+        <is>
+          <t>271218</t>
+        </is>
+      </c>
+      <c r="AK456" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL456" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>17191</v>
+      </c>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>73****0446</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 15:36:18</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>*9905</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N457" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P457" t="n">
+        <v>11000371968280</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>1783677957283</v>
+      </c>
+      <c r="R457" t="n">
+        <v>824012705547</v>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W457" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y457" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z457" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA457" t="inlineStr"/>
+      <c r="AB457" t="inlineStr"/>
+      <c r="AC457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE457" t="inlineStr"/>
+      <c r="AF457" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG457" t="inlineStr"/>
+      <c r="AH457" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI457" t="n">
+        <v>19905</v>
+      </c>
+      <c r="AJ457" t="inlineStr">
+        <is>
+          <t>269356</t>
+        </is>
+      </c>
+      <c r="AK457" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL457" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>16981</v>
+      </c>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>89****0551</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 16:20:33</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>*8142</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N458" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P458" t="n">
+        <v>11000371975854</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>1783680620290</v>
+      </c>
+      <c r="R458" t="n">
+        <v>619117235878</v>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W458" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y458" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z458" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA458" t="inlineStr"/>
+      <c r="AB458" t="inlineStr"/>
+      <c r="AC458" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD458" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE458" t="inlineStr"/>
+      <c r="AF458" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG458" t="inlineStr"/>
+      <c r="AH458" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI458" t="n">
+        <v>18142</v>
+      </c>
+      <c r="AJ458" t="inlineStr">
+        <is>
+          <t>271287</t>
+        </is>
+      </c>
+      <c r="AK458" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL458" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>16983</v>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>89****0551</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 16:21:27</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>*8526</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N459" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P459" t="n">
+        <v>11000371977290</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>1783680678738</v>
+      </c>
+      <c r="R459" t="n">
+        <v>619140437820</v>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W459" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y459" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z459" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA459" t="inlineStr"/>
+      <c r="AB459" t="inlineStr"/>
+      <c r="AC459" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD459" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE459" t="inlineStr"/>
+      <c r="AF459" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG459" t="inlineStr"/>
+      <c r="AH459" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI459" t="n">
+        <v>18526</v>
+      </c>
+      <c r="AJ459" t="inlineStr">
+        <is>
+          <t>273534</t>
+        </is>
+      </c>
+      <c r="AK459" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL459" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>17375</v>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>75****9694</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 17:45:46</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>*0096</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N460" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P460" t="n">
+        <v>11000371993652</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>1783685605765</v>
+      </c>
+      <c r="R460" t="n">
+        <v>57807832716</v>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W460" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y460" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z460" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA460" t="inlineStr"/>
+      <c r="AB460" t="inlineStr"/>
+      <c r="AC460" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD460" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE460" t="inlineStr"/>
+      <c r="AF460" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG460" t="inlineStr"/>
+      <c r="AH460" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI460" t="n">
+        <v>20096</v>
+      </c>
+      <c r="AJ460" t="inlineStr">
+        <is>
+          <t>269261</t>
+        </is>
+      </c>
+      <c r="AK460" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL460" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>16052</v>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>97****5001</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 00:12:30</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>*9325</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N461" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P461" t="n">
+        <v>11000372056483</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>1783708816995</v>
+      </c>
+      <c r="R461" t="n">
+        <v>619245000517</v>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W461" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y461" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z461" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA461" t="inlineStr"/>
+      <c r="AB461" t="inlineStr"/>
+      <c r="AC461" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD461" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE461" t="inlineStr"/>
+      <c r="AF461" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG461" t="inlineStr"/>
+      <c r="AH461" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI461" t="n">
+        <v>19325</v>
+      </c>
+      <c r="AJ461" t="inlineStr">
+        <is>
+          <t>276042</t>
+        </is>
+      </c>
+      <c r="AK461" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL461" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL461"/>
+  <dimension ref="A1:AL472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72694,6 +72694,1616 @@
       </c>
       <c r="AL461" t="inlineStr"/>
     </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>17277</v>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>96****1662</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 07:00:18</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>*9988</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N462" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P462" t="n">
+        <v>11000372059838</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>1783733404541</v>
+      </c>
+      <c r="R462" t="n">
+        <v>302708764437</v>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W462" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X462" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y462" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z462" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA462" t="inlineStr"/>
+      <c r="AB462" t="inlineStr"/>
+      <c r="AC462" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD462" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE462" t="inlineStr"/>
+      <c r="AF462" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG462" t="inlineStr"/>
+      <c r="AH462" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI462" t="n">
+        <v>19988</v>
+      </c>
+      <c r="AJ462" t="inlineStr">
+        <is>
+          <t>270330,271405</t>
+        </is>
+      </c>
+      <c r="AK462" t="inlineStr">
+        <is>
+          <t>2067,2076</t>
+        </is>
+      </c>
+      <c r="AL462" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>15321</v>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>90****6416</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>12200</v>
+      </c>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 07:10:05</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>*8997</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N463" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P463" t="n">
+        <v>11000372063015</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>1783733983603</v>
+      </c>
+      <c r="R463" t="n">
+        <v>76530301623</v>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W463" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y463" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z463" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA463" t="inlineStr"/>
+      <c r="AB463" t="inlineStr"/>
+      <c r="AC463" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD463" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE463" t="inlineStr"/>
+      <c r="AF463" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG463" t="inlineStr"/>
+      <c r="AH463" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI463" t="n">
+        <v>18997</v>
+      </c>
+      <c r="AJ463" t="inlineStr">
+        <is>
+          <t>270911,275393</t>
+        </is>
+      </c>
+      <c r="AK463" t="inlineStr">
+        <is>
+          <t>2075,2092</t>
+        </is>
+      </c>
+      <c r="AL463" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>16209</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>V********** N**** S**</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>81****1333</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 08:21:46</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nine thousand </t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N464" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="P464" t="n">
+        <v>11000372067768</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>1783738279</v>
+      </c>
+      <c r="R464" t="n">
+        <v>105959969580</v>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W464" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X464" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y464" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z464" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA464" t="inlineStr"/>
+      <c r="AB464" t="inlineStr"/>
+      <c r="AC464" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD464" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE464" t="inlineStr"/>
+      <c r="AF464" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG464" t="inlineStr"/>
+      <c r="AH464" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI464" t="n">
+        <v>18690</v>
+      </c>
+      <c r="AJ464" t="inlineStr">
+        <is>
+          <t>273722</t>
+        </is>
+      </c>
+      <c r="AK464" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL464" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>14582</v>
+      </c>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>93****9606</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 12:34:57</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>*9354</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N465" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P465" t="n">
+        <v>11000372113886</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>1783753406583</v>
+      </c>
+      <c r="R465" t="n">
+        <v>724009638591</v>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W465" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X465" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y465" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z465" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA465" t="inlineStr"/>
+      <c r="AB465" t="inlineStr"/>
+      <c r="AC465" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD465" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE465" t="inlineStr"/>
+      <c r="AF465" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG465" t="inlineStr"/>
+      <c r="AH465" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI465" t="n">
+        <v>19354</v>
+      </c>
+      <c r="AJ465" t="inlineStr">
+        <is>
+          <t>276079</t>
+        </is>
+      </c>
+      <c r="AK465" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL465" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>15541</v>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>98****9449</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 12:35:19</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>*8766</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N466" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P466" t="n">
+        <v>11000372114900</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>1783753512275</v>
+      </c>
+      <c r="R466" t="n">
+        <v>429700282239</v>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W466" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X466" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y466" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z466" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA466" t="inlineStr"/>
+      <c r="AB466" t="inlineStr"/>
+      <c r="AC466" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD466" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE466" t="inlineStr"/>
+      <c r="AF466" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG466" t="inlineStr"/>
+      <c r="AH466" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI466" t="n">
+        <v>18766</v>
+      </c>
+      <c r="AJ466" t="inlineStr">
+        <is>
+          <t>273735</t>
+        </is>
+      </c>
+      <c r="AK466" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL466" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>15587</v>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>93****9606</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>9400</v>
+      </c>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 12:48:58</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>*8856</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N467" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P467" t="n">
+        <v>11000372117902</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>1783754283667</v>
+      </c>
+      <c r="R467" t="n">
+        <v>999343787537</v>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W467" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X467" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y467" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z467" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA467" t="inlineStr"/>
+      <c r="AB467" t="inlineStr"/>
+      <c r="AC467" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD467" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE467" t="inlineStr"/>
+      <c r="AF467" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG467" t="inlineStr"/>
+      <c r="AH467" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI467" t="n">
+        <v>18856</v>
+      </c>
+      <c r="AJ467" t="inlineStr">
+        <is>
+          <t>274809</t>
+        </is>
+      </c>
+      <c r="AK467" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="AL467" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>17459</v>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>91****3633</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 13:49:46</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>*0171</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N468" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P468" t="n">
+        <v>11000372131404</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>1783757872189</v>
+      </c>
+      <c r="R468" t="n">
+        <v>655863582381</v>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W468" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X468" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y468" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z468" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA468" t="inlineStr"/>
+      <c r="AB468" t="inlineStr"/>
+      <c r="AC468" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD468" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE468" t="inlineStr"/>
+      <c r="AF468" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG468" t="inlineStr"/>
+      <c r="AH468" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI468" t="n">
+        <v>20171</v>
+      </c>
+      <c r="AJ468" t="inlineStr">
+        <is>
+          <t>271165</t>
+        </is>
+      </c>
+      <c r="AK468" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL468" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>15823</v>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>99****1635</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 15:25:36</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>*8720</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N469" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P469" t="n">
+        <v>11000372145896</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>1783763721706</v>
+      </c>
+      <c r="R469" t="n">
+        <v>673975146257</v>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W469" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X469" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y469" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z469" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA469" t="inlineStr"/>
+      <c r="AB469" t="inlineStr"/>
+      <c r="AC469" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD469" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE469" t="inlineStr"/>
+      <c r="AF469" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG469" t="inlineStr"/>
+      <c r="AH469" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI469" t="n">
+        <v>18720</v>
+      </c>
+      <c r="AJ469" t="inlineStr">
+        <is>
+          <t>273694</t>
+        </is>
+      </c>
+      <c r="AK469" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL469" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>16721</v>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>99****1635</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 15:20:17</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>*8114</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N470" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P470" t="n">
+        <v>11000372146568</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>1783763397059</v>
+      </c>
+      <c r="R470" t="n">
+        <v>482482929627</v>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W470" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X470" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y470" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z470" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA470" t="inlineStr"/>
+      <c r="AB470" t="inlineStr"/>
+      <c r="AC470" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD470" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE470" t="inlineStr"/>
+      <c r="AF470" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG470" t="inlineStr"/>
+      <c r="AH470" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI470" t="n">
+        <v>18114</v>
+      </c>
+      <c r="AJ470" t="inlineStr">
+        <is>
+          <t>271206</t>
+        </is>
+      </c>
+      <c r="AK470" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL470" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>16476</v>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>99****3153</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>9400</v>
+      </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 19:44:08</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>*8969</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N471" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P471" t="n">
+        <v>11000372181653</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>1783779230077</v>
+      </c>
+      <c r="R471" t="n">
+        <v>663341327002</v>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W471" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X471" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y471" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z471" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA471" t="inlineStr"/>
+      <c r="AB471" t="inlineStr"/>
+      <c r="AC471" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD471" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE471" t="inlineStr"/>
+      <c r="AF471" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG471" t="inlineStr"/>
+      <c r="AH471" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI471" t="n">
+        <v>18969</v>
+      </c>
+      <c r="AJ471" t="inlineStr">
+        <is>
+          <t>274865</t>
+        </is>
+      </c>
+      <c r="AK471" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="AL471" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>16475</v>
+      </c>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>99****3153</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 19:46:59</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>*8788</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N472" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P472" t="n">
+        <v>11000372182083</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>1783779407447</v>
+      </c>
+      <c r="R472" t="n">
+        <v>381430784071</v>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W472" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X472" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y472" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z472" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA472" t="inlineStr"/>
+      <c r="AB472" t="inlineStr"/>
+      <c r="AC472" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD472" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE472" t="inlineStr"/>
+      <c r="AF472" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG472" t="inlineStr"/>
+      <c r="AH472" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI472" t="n">
+        <v>18788</v>
+      </c>
+      <c r="AJ472" t="inlineStr">
+        <is>
+          <t>273686</t>
+        </is>
+      </c>
+      <c r="AK472" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL472" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL472"/>
+  <dimension ref="A1:AL473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74304,6 +74304,152 @@
         </is>
       </c>
     </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>17219</v>
+      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>83****9788</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>12-Jul-2026 13:25:18</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>*9931</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N473" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P473" t="n">
+        <v>11000372261199</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>1783842905483</v>
+      </c>
+      <c r="R473" t="n">
+        <v>136649511585</v>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W473" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X473" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y473" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z473" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA473" t="inlineStr"/>
+      <c r="AB473" t="inlineStr"/>
+      <c r="AC473" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD473" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE473" t="inlineStr"/>
+      <c r="AF473" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG473" t="inlineStr"/>
+      <c r="AH473" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI473" t="n">
+        <v>19931</v>
+      </c>
+      <c r="AJ473" t="inlineStr">
+        <is>
+          <t>271238</t>
+        </is>
+      </c>
+      <c r="AK473" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL473" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL473"/>
+  <dimension ref="A1:AL488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71693,7 +71693,9 @@
       <c r="D455" t="n">
         <v>12300</v>
       </c>
-      <c r="E455" t="inlineStr"/>
+      <c r="E455" t="n">
+        <v>12300</v>
+      </c>
       <c r="F455" t="inlineStr">
         <is>
           <t>10-Jul-2026 07:02:55</t>
@@ -71764,7 +71766,7 @@
       </c>
       <c r="V455" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W455" t="inlineStr">
@@ -71787,15 +71789,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA455" t="inlineStr"/>
-      <c r="AB455" t="inlineStr"/>
+      <c r="AA455" t="n">
+        <v>166.05</v>
+      </c>
+      <c r="AB455" t="n">
+        <v>29.89</v>
+      </c>
       <c r="AC455" t="n">
         <v>0</v>
       </c>
       <c r="AD455" t="n">
         <v>0</v>
       </c>
-      <c r="AE455" t="inlineStr"/>
+      <c r="AE455" t="n">
+        <v>195.94</v>
+      </c>
       <c r="AF455" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -71835,13 +71843,19 @@
       <c r="D456" t="n">
         <v>8400</v>
       </c>
-      <c r="E456" t="inlineStr"/>
+      <c r="E456" t="n">
+        <v>8400</v>
+      </c>
       <c r="F456" t="inlineStr">
         <is>
           <t>10-Jul-2026 15:32:30</t>
         </is>
       </c>
-      <c r="G456" t="inlineStr"/>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H456" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -71906,7 +71920,7 @@
       </c>
       <c r="V456" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W456" t="inlineStr">
@@ -71929,15 +71943,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA456" t="inlineStr"/>
-      <c r="AB456" t="inlineStr"/>
+      <c r="AA456" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB456" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC456" t="n">
         <v>0</v>
       </c>
       <c r="AD456" t="n">
         <v>0</v>
       </c>
-      <c r="AE456" t="inlineStr"/>
+      <c r="AE456" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF456" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -71981,13 +72001,19 @@
       <c r="D457" t="n">
         <v>7250</v>
       </c>
-      <c r="E457" t="inlineStr"/>
+      <c r="E457" t="n">
+        <v>7250</v>
+      </c>
       <c r="F457" t="inlineStr">
         <is>
           <t>10-Jul-2026 15:36:18</t>
         </is>
       </c>
-      <c r="G457" t="inlineStr"/>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H457" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -72052,7 +72078,7 @@
       </c>
       <c r="V457" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W457" t="inlineStr">
@@ -72075,15 +72101,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA457" t="inlineStr"/>
-      <c r="AB457" t="inlineStr"/>
+      <c r="AA457" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB457" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC457" t="n">
         <v>0</v>
       </c>
       <c r="AD457" t="n">
         <v>0</v>
       </c>
-      <c r="AE457" t="inlineStr"/>
+      <c r="AE457" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF457" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -72127,13 +72159,19 @@
       <c r="D458" t="n">
         <v>8400</v>
       </c>
-      <c r="E458" t="inlineStr"/>
+      <c r="E458" t="n">
+        <v>8400</v>
+      </c>
       <c r="F458" t="inlineStr">
         <is>
           <t>10-Jul-2026 16:20:33</t>
         </is>
       </c>
-      <c r="G458" t="inlineStr"/>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H458" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -72198,7 +72236,7 @@
       </c>
       <c r="V458" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W458" t="inlineStr">
@@ -72221,15 +72259,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA458" t="inlineStr"/>
-      <c r="AB458" t="inlineStr"/>
+      <c r="AA458" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB458" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC458" t="n">
         <v>0</v>
       </c>
       <c r="AD458" t="n">
         <v>0</v>
       </c>
-      <c r="AE458" t="inlineStr"/>
+      <c r="AE458" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF458" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -72273,13 +72317,19 @@
       <c r="D459" t="n">
         <v>9000</v>
       </c>
-      <c r="E459" t="inlineStr"/>
+      <c r="E459" t="n">
+        <v>9000</v>
+      </c>
       <c r="F459" t="inlineStr">
         <is>
           <t>10-Jul-2026 16:21:27</t>
         </is>
       </c>
-      <c r="G459" t="inlineStr"/>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H459" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -72344,7 +72394,7 @@
       </c>
       <c r="V459" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W459" t="inlineStr">
@@ -72367,15 +72417,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA459" t="inlineStr"/>
-      <c r="AB459" t="inlineStr"/>
+      <c r="AA459" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB459" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC459" t="n">
         <v>0</v>
       </c>
       <c r="AD459" t="n">
         <v>0</v>
       </c>
-      <c r="AE459" t="inlineStr"/>
+      <c r="AE459" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF459" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -72419,13 +72475,19 @@
       <c r="D460" t="n">
         <v>7250</v>
       </c>
-      <c r="E460" t="inlineStr"/>
+      <c r="E460" t="n">
+        <v>7250</v>
+      </c>
       <c r="F460" t="inlineStr">
         <is>
           <t>10-Jul-2026 17:45:46</t>
         </is>
       </c>
-      <c r="G460" t="inlineStr"/>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H460" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -72490,7 +72552,7 @@
       </c>
       <c r="V460" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W460" t="inlineStr">
@@ -72513,15 +72575,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA460" t="inlineStr"/>
-      <c r="AB460" t="inlineStr"/>
+      <c r="AA460" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB460" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC460" t="n">
         <v>0</v>
       </c>
       <c r="AD460" t="n">
         <v>0</v>
       </c>
-      <c r="AE460" t="inlineStr"/>
+      <c r="AE460" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF460" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -72565,7 +72633,9 @@
       <c r="D461" t="n">
         <v>12300</v>
       </c>
-      <c r="E461" t="inlineStr"/>
+      <c r="E461" t="n">
+        <v>12300</v>
+      </c>
       <c r="F461" t="inlineStr">
         <is>
           <t>11-Jul-2026 00:12:30</t>
@@ -72636,7 +72706,7 @@
       </c>
       <c r="V461" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W461" t="inlineStr">
@@ -72659,15 +72729,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA461" t="inlineStr"/>
-      <c r="AB461" t="inlineStr"/>
+      <c r="AA461" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="AB461" t="n">
+        <v>26.57</v>
+      </c>
       <c r="AC461" t="n">
         <v>0</v>
       </c>
       <c r="AD461" t="n">
         <v>0</v>
       </c>
-      <c r="AE461" t="inlineStr"/>
+      <c r="AE461" t="n">
+        <v>174.17</v>
+      </c>
       <c r="AF461" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -72707,13 +72783,19 @@
       <c r="D462" t="n">
         <v>9000</v>
       </c>
-      <c r="E462" t="inlineStr"/>
+      <c r="E462" t="n">
+        <v>9000</v>
+      </c>
       <c r="F462" t="inlineStr">
         <is>
           <t>11-Jul-2026 07:00:18</t>
         </is>
       </c>
-      <c r="G462" t="inlineStr"/>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H462" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -72778,7 +72860,7 @@
       </c>
       <c r="V462" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W462" t="inlineStr">
@@ -72801,15 +72883,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA462" t="inlineStr"/>
-      <c r="AB462" t="inlineStr"/>
+      <c r="AA462" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB462" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC462" t="n">
         <v>0</v>
       </c>
       <c r="AD462" t="n">
         <v>0</v>
       </c>
-      <c r="AE462" t="inlineStr"/>
+      <c r="AE462" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF462" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -72853,7 +72941,9 @@
       <c r="D463" t="n">
         <v>12200</v>
       </c>
-      <c r="E463" t="inlineStr"/>
+      <c r="E463" t="n">
+        <v>12200</v>
+      </c>
       <c r="F463" t="inlineStr">
         <is>
           <t>11-Jul-2026 07:10:05</t>
@@ -72924,7 +73014,7 @@
       </c>
       <c r="V463" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W463" t="inlineStr">
@@ -72947,15 +73037,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA463" t="inlineStr"/>
-      <c r="AB463" t="inlineStr"/>
+      <c r="AA463" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB463" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC463" t="n">
         <v>0</v>
       </c>
       <c r="AD463" t="n">
         <v>0</v>
       </c>
-      <c r="AE463" t="inlineStr"/>
+      <c r="AE463" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF463" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -73003,13 +73099,19 @@
       <c r="D464" t="n">
         <v>9000</v>
       </c>
-      <c r="E464" t="inlineStr"/>
+      <c r="E464" t="n">
+        <v>9000</v>
+      </c>
       <c r="F464" t="inlineStr">
         <is>
           <t>11-Jul-2026 08:21:46</t>
         </is>
       </c>
-      <c r="G464" t="inlineStr"/>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H464" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -73074,7 +73176,7 @@
       </c>
       <c r="V464" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W464" t="inlineStr">
@@ -73097,15 +73199,21 @@
           <t>k*************@gmail.com</t>
         </is>
       </c>
-      <c r="AA464" t="inlineStr"/>
-      <c r="AB464" t="inlineStr"/>
+      <c r="AA464" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB464" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC464" t="n">
         <v>0</v>
       </c>
       <c r="AD464" t="n">
         <v>0</v>
       </c>
-      <c r="AE464" t="inlineStr"/>
+      <c r="AE464" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF464" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -73149,7 +73257,9 @@
       <c r="D465" t="n">
         <v>12300</v>
       </c>
-      <c r="E465" t="inlineStr"/>
+      <c r="E465" t="n">
+        <v>12300</v>
+      </c>
       <c r="F465" t="inlineStr">
         <is>
           <t>11-Jul-2026 12:34:57</t>
@@ -73220,7 +73330,7 @@
       </c>
       <c r="V465" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W465" t="inlineStr">
@@ -73243,15 +73353,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA465" t="inlineStr"/>
-      <c r="AB465" t="inlineStr"/>
+      <c r="AA465" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB465" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC465" t="n">
         <v>0</v>
       </c>
       <c r="AD465" t="n">
         <v>0</v>
       </c>
-      <c r="AE465" t="inlineStr"/>
+      <c r="AE465" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF465" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -73295,13 +73411,19 @@
       <c r="D466" t="n">
         <v>9000</v>
       </c>
-      <c r="E466" t="inlineStr"/>
+      <c r="E466" t="n">
+        <v>9000</v>
+      </c>
       <c r="F466" t="inlineStr">
         <is>
           <t>11-Jul-2026 12:35:19</t>
         </is>
       </c>
-      <c r="G466" t="inlineStr"/>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H466" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -73366,7 +73488,7 @@
       </c>
       <c r="V466" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W466" t="inlineStr">
@@ -73389,15 +73511,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA466" t="inlineStr"/>
-      <c r="AB466" t="inlineStr"/>
+      <c r="AA466" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB466" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC466" t="n">
         <v>0</v>
       </c>
       <c r="AD466" t="n">
         <v>0</v>
       </c>
-      <c r="AE466" t="inlineStr"/>
+      <c r="AE466" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF466" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -73441,7 +73569,9 @@
       <c r="D467" t="n">
         <v>9400</v>
       </c>
-      <c r="E467" t="inlineStr"/>
+      <c r="E467" t="n">
+        <v>9400</v>
+      </c>
       <c r="F467" t="inlineStr">
         <is>
           <t>11-Jul-2026 12:48:58</t>
@@ -73512,7 +73642,7 @@
       </c>
       <c r="V467" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W467" t="inlineStr">
@@ -73535,15 +73665,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA467" t="inlineStr"/>
-      <c r="AB467" t="inlineStr"/>
+      <c r="AA467" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB467" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC467" t="n">
         <v>0</v>
       </c>
       <c r="AD467" t="n">
         <v>0</v>
       </c>
-      <c r="AE467" t="inlineStr"/>
+      <c r="AE467" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF467" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
@@ -73587,13 +73723,19 @@
       <c r="D468" t="n">
         <v>8400</v>
       </c>
-      <c r="E468" t="inlineStr"/>
+      <c r="E468" t="n">
+        <v>8400</v>
+      </c>
       <c r="F468" t="inlineStr">
         <is>
           <t>11-Jul-2026 13:49:46</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr"/>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H468" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -73658,7 +73800,7 @@
       </c>
       <c r="V468" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W468" t="inlineStr">
@@ -73681,15 +73823,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA468" t="inlineStr"/>
-      <c r="AB468" t="inlineStr"/>
+      <c r="AA468" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB468" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC468" t="n">
         <v>0</v>
       </c>
       <c r="AD468" t="n">
         <v>0</v>
       </c>
-      <c r="AE468" t="inlineStr"/>
+      <c r="AE468" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF468" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -73733,13 +73881,19 @@
       <c r="D469" t="n">
         <v>9000</v>
       </c>
-      <c r="E469" t="inlineStr"/>
+      <c r="E469" t="n">
+        <v>9000</v>
+      </c>
       <c r="F469" t="inlineStr">
         <is>
           <t>11-Jul-2026 15:25:36</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr"/>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H469" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -73804,7 +73958,7 @@
       </c>
       <c r="V469" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W469" t="inlineStr">
@@ -73827,15 +73981,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA469" t="inlineStr"/>
-      <c r="AB469" t="inlineStr"/>
+      <c r="AA469" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB469" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC469" t="n">
         <v>0</v>
       </c>
       <c r="AD469" t="n">
         <v>0</v>
       </c>
-      <c r="AE469" t="inlineStr"/>
+      <c r="AE469" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF469" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -73879,13 +74039,19 @@
       <c r="D470" t="n">
         <v>8400</v>
       </c>
-      <c r="E470" t="inlineStr"/>
+      <c r="E470" t="n">
+        <v>8400</v>
+      </c>
       <c r="F470" t="inlineStr">
         <is>
           <t>11-Jul-2026 15:20:17</t>
         </is>
       </c>
-      <c r="G470" t="inlineStr"/>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H470" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -73950,7 +74116,7 @@
       </c>
       <c r="V470" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W470" t="inlineStr">
@@ -73973,15 +74139,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA470" t="inlineStr"/>
-      <c r="AB470" t="inlineStr"/>
+      <c r="AA470" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB470" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC470" t="n">
         <v>0</v>
       </c>
       <c r="AD470" t="n">
         <v>0</v>
       </c>
-      <c r="AE470" t="inlineStr"/>
+      <c r="AE470" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF470" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -74025,7 +74197,9 @@
       <c r="D471" t="n">
         <v>9400</v>
       </c>
-      <c r="E471" t="inlineStr"/>
+      <c r="E471" t="n">
+        <v>9400</v>
+      </c>
       <c r="F471" t="inlineStr">
         <is>
           <t>11-Jul-2026 19:44:08</t>
@@ -74096,7 +74270,7 @@
       </c>
       <c r="V471" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W471" t="inlineStr">
@@ -74119,15 +74293,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA471" t="inlineStr"/>
-      <c r="AB471" t="inlineStr"/>
+      <c r="AA471" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB471" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC471" t="n">
         <v>0</v>
       </c>
       <c r="AD471" t="n">
         <v>0</v>
       </c>
-      <c r="AE471" t="inlineStr"/>
+      <c r="AE471" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF471" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
@@ -74171,13 +74351,19 @@
       <c r="D472" t="n">
         <v>9000</v>
       </c>
-      <c r="E472" t="inlineStr"/>
+      <c r="E472" t="n">
+        <v>9000</v>
+      </c>
       <c r="F472" t="inlineStr">
         <is>
           <t>11-Jul-2026 19:46:59</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr"/>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H472" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -74242,7 +74428,7 @@
       </c>
       <c r="V472" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W472" t="inlineStr">
@@ -74265,15 +74451,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA472" t="inlineStr"/>
-      <c r="AB472" t="inlineStr"/>
+      <c r="AA472" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB472" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC472" t="n">
         <v>0</v>
       </c>
       <c r="AD472" t="n">
         <v>0</v>
       </c>
-      <c r="AE472" t="inlineStr"/>
+      <c r="AE472" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF472" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -74317,13 +74509,19 @@
       <c r="D473" t="n">
         <v>8400</v>
       </c>
-      <c r="E473" t="inlineStr"/>
+      <c r="E473" t="n">
+        <v>8400</v>
+      </c>
       <c r="F473" t="inlineStr">
         <is>
           <t>12-Jul-2026 13:25:18</t>
         </is>
       </c>
-      <c r="G473" t="inlineStr"/>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
       <c r="H473" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -74388,7 +74586,7 @@
       </c>
       <c r="V473" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W473" t="inlineStr">
@@ -74411,15 +74609,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA473" t="inlineStr"/>
-      <c r="AB473" t="inlineStr"/>
+      <c r="AA473" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB473" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC473" t="n">
         <v>0</v>
       </c>
       <c r="AD473" t="n">
         <v>0</v>
       </c>
-      <c r="AE473" t="inlineStr"/>
+      <c r="AE473" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF473" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -74449,6 +74653,2240 @@
           <t>UPI INTENT</t>
         </is>
       </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>16552</v>
+      </c>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>98****7189</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E474" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>12-Jul-2026 14:46:57</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>*8375</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N474" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P474" t="n">
+        <v>11000372271363</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>1783847740793</v>
+      </c>
+      <c r="R474" t="n">
+        <v>900975042052</v>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W474" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X474" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y474" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z474" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA474" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB474" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC474" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD474" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE474" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF474" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG474" t="inlineStr"/>
+      <c r="AH474" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI474" t="n">
+        <v>18375</v>
+      </c>
+      <c r="AJ474" t="inlineStr">
+        <is>
+          <t>272434</t>
+        </is>
+      </c>
+      <c r="AK474" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL474" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>17417</v>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>83****4561</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E475" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>12-Jul-2026 15:28:40</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>*0447</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N475" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P475" t="n">
+        <v>11000372274677</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>1783850310406</v>
+      </c>
+      <c r="R475" t="n">
+        <v>199681789218</v>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W475" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X475" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y475" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z475" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA475" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB475" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC475" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD475" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE475" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF475" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG475" t="inlineStr"/>
+      <c r="AH475" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI475" t="n">
+        <v>20447</v>
+      </c>
+      <c r="AJ475" t="inlineStr">
+        <is>
+          <t>277531</t>
+        </is>
+      </c>
+      <c r="AK475" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="AL475" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>15915</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>K******* J*****</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>81****8482</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E476" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>12-Jul-2026 15:36:35</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nine thousand </t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N476" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="P476" t="n">
+        <v>11000372274949</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>1783850726</v>
+      </c>
+      <c r="R476" t="n">
+        <v>619341050138</v>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W476" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X476" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y476" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="Z476" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA476" t="n">
+        <v>81</v>
+      </c>
+      <c r="AB476" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="AC476" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD476" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE476" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="AF476" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG476" t="inlineStr"/>
+      <c r="AH476" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI476" t="n">
+        <v>18704</v>
+      </c>
+      <c r="AJ476" t="inlineStr">
+        <is>
+          <t>273773</t>
+        </is>
+      </c>
+      <c r="AK476" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>17477</v>
+      </c>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>92****7887</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E477" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>12-Jul-2026 18:44:55</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>*0151</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N477" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P477" t="n">
+        <v>11000372295469</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>1783862052004</v>
+      </c>
+      <c r="R477" t="n">
+        <v>619302536692</v>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W477" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X477" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y477" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z477" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA477" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB477" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC477" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD477" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE477" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF477" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG477" t="inlineStr"/>
+      <c r="AH477" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI477" t="n">
+        <v>20151</v>
+      </c>
+      <c r="AJ477" t="inlineStr">
+        <is>
+          <t>269266</t>
+        </is>
+      </c>
+      <c r="AK477" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL477" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>17476</v>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>92****7887</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E478" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>12-Jul-2026 18:55:19</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:11:05</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>*0193</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N478" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P478" t="n">
+        <v>11000372295995</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>1783862507456</v>
+      </c>
+      <c r="R478" t="n">
+        <v>619323086570</v>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W478" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X478" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y478" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z478" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA478" t="n">
+        <v>108</v>
+      </c>
+      <c r="AB478" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="AC478" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD478" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE478" t="n">
+        <v>127.44</v>
+      </c>
+      <c r="AF478" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG478" t="inlineStr"/>
+      <c r="AH478" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI478" t="n">
+        <v>20193</v>
+      </c>
+      <c r="AJ478" t="inlineStr">
+        <is>
+          <t>273486</t>
+        </is>
+      </c>
+      <c r="AK478" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>14988</v>
+      </c>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>99****1686</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 08:43:44</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>*9209</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N479" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P479" t="n">
+        <v>11000372366091</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>1783912411054</v>
+      </c>
+      <c r="R479" t="n">
+        <v>534781613024</v>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W479" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X479" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y479" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z479" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA479" t="inlineStr"/>
+      <c r="AB479" t="inlineStr"/>
+      <c r="AC479" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD479" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE479" t="inlineStr"/>
+      <c r="AF479" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG479" t="inlineStr"/>
+      <c r="AH479" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI479" t="n">
+        <v>19209</v>
+      </c>
+      <c r="AJ479" t="inlineStr">
+        <is>
+          <t>275933</t>
+        </is>
+      </c>
+      <c r="AK479" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL479" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>17645</v>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>85****2836</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 08:50:31</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>*0410</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N480" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P480" t="n">
+        <v>11000372367339</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>1783912802746</v>
+      </c>
+      <c r="R480" t="n">
+        <v>927027233779</v>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W480" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X480" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y480" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z480" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA480" t="inlineStr"/>
+      <c r="AB480" t="inlineStr"/>
+      <c r="AC480" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD480" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE480" t="inlineStr"/>
+      <c r="AF480" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG480" t="inlineStr"/>
+      <c r="AH480" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI480" t="n">
+        <v>20410</v>
+      </c>
+      <c r="AJ480" t="inlineStr">
+        <is>
+          <t>277380</t>
+        </is>
+      </c>
+      <c r="AK480" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL480" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>14944</v>
+      </c>
+      <c r="B481" t="inlineStr"/>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>97****3320</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 09:46:23</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>*9236</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N481" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P481" t="n">
+        <v>11000372375804</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>1783916164452</v>
+      </c>
+      <c r="R481" t="n">
+        <v>815132583286</v>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W481" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X481" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y481" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z481" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA481" t="inlineStr"/>
+      <c r="AB481" t="inlineStr"/>
+      <c r="AC481" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD481" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE481" t="inlineStr"/>
+      <c r="AF481" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG481" t="inlineStr"/>
+      <c r="AH481" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI481" t="n">
+        <v>19236</v>
+      </c>
+      <c r="AJ481" t="inlineStr">
+        <is>
+          <t>276015</t>
+        </is>
+      </c>
+      <c r="AK481" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL481" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>17413</v>
+      </c>
+      <c r="B482" t="inlineStr"/>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>90****4050</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 13:15:08</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr"/>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>*0153</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N482" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P482" t="n">
+        <v>11000372439451</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>1783928695480</v>
+      </c>
+      <c r="R482" t="n">
+        <v>628026794280</v>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W482" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X482" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y482" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z482" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA482" t="inlineStr"/>
+      <c r="AB482" t="inlineStr"/>
+      <c r="AC482" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD482" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE482" t="inlineStr"/>
+      <c r="AF482" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG482" t="inlineStr"/>
+      <c r="AH482" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI482" t="n">
+        <v>20153</v>
+      </c>
+      <c r="AJ482" t="inlineStr">
+        <is>
+          <t>269268</t>
+        </is>
+      </c>
+      <c r="AK482" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL482" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>16211</v>
+      </c>
+      <c r="B483" t="inlineStr"/>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>95****0840</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 15:50:31</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>*8814</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N483" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P483" t="n">
+        <v>11000372485711</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>1783938007306</v>
+      </c>
+      <c r="R483" t="n">
+        <v>523129640767</v>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W483" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X483" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y483" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z483" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA483" t="inlineStr"/>
+      <c r="AB483" t="inlineStr"/>
+      <c r="AC483" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD483" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE483" t="inlineStr"/>
+      <c r="AF483" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG483" t="inlineStr"/>
+      <c r="AH483" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI483" t="n">
+        <v>18814</v>
+      </c>
+      <c r="AJ483" t="inlineStr">
+        <is>
+          <t>273774</t>
+        </is>
+      </c>
+      <c r="AK483" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL483" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>15367</v>
+      </c>
+      <c r="B484" t="inlineStr"/>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>97****8094</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>11600</v>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 16:43:37</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>*9001</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N484" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P484" t="n">
+        <v>11000372496635</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>1783941124068</v>
+      </c>
+      <c r="R484" t="n">
+        <v>619444062662</v>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W484" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X484" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y484" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z484" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA484" t="inlineStr"/>
+      <c r="AB484" t="inlineStr"/>
+      <c r="AC484" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD484" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE484" t="inlineStr"/>
+      <c r="AF484" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG484" t="inlineStr"/>
+      <c r="AH484" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI484" t="n">
+        <v>19001</v>
+      </c>
+      <c r="AJ484" t="inlineStr">
+        <is>
+          <t>275417</t>
+        </is>
+      </c>
+      <c r="AK484" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="AL484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>14949</v>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>98****7093</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>12900</v>
+      </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 17:06:10</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>*9326</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N485" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P485" t="n">
+        <v>11000372499979</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>1783942555328</v>
+      </c>
+      <c r="R485" t="n">
+        <v>998912050238</v>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W485" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X485" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y485" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z485" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA485" t="inlineStr"/>
+      <c r="AB485" t="inlineStr"/>
+      <c r="AC485" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD485" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE485" t="inlineStr"/>
+      <c r="AF485" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG485" t="inlineStr"/>
+      <c r="AH485" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI485" t="n">
+        <v>19326</v>
+      </c>
+      <c r="AJ485" t="inlineStr">
+        <is>
+          <t>271103,276017</t>
+        </is>
+      </c>
+      <c r="AK485" t="inlineStr">
+        <is>
+          <t>2075,2096</t>
+        </is>
+      </c>
+      <c r="AL485" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>14576</v>
+      </c>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>98****7093</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 17:09:58</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>*9456</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N486" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P486" t="n">
+        <v>11000372503211</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>1783942788406</v>
+      </c>
+      <c r="R486" t="n">
+        <v>907449229278</v>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W486" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X486" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y486" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z486" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA486" t="inlineStr"/>
+      <c r="AB486" t="inlineStr"/>
+      <c r="AC486" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD486" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE486" t="inlineStr"/>
+      <c r="AF486" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG486" t="inlineStr"/>
+      <c r="AH486" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI486" t="n">
+        <v>19456</v>
+      </c>
+      <c r="AJ486" t="inlineStr">
+        <is>
+          <t>276151</t>
+        </is>
+      </c>
+      <c r="AK486" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL486" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>15549</v>
+      </c>
+      <c r="B487" t="inlineStr"/>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>89****0483</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 19:47:02</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>*8714</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N487" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P487" t="n">
+        <v>11000372534162</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>1783952132104</v>
+      </c>
+      <c r="R487" t="n">
+        <v>619435057338</v>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W487" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X487" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y487" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z487" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA487" t="inlineStr"/>
+      <c r="AB487" t="inlineStr"/>
+      <c r="AC487" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD487" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE487" t="inlineStr"/>
+      <c r="AF487" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG487" t="inlineStr"/>
+      <c r="AH487" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI487" t="n">
+        <v>18714</v>
+      </c>
+      <c r="AJ487" t="inlineStr">
+        <is>
+          <t>273680</t>
+        </is>
+      </c>
+      <c r="AK487" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>17678</v>
+      </c>
+      <c r="B488" t="inlineStr"/>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>90****3128</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 20:43:31</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr"/>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>*0423</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N488" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P488" t="n">
+        <v>11000372542814</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>1783955557362</v>
+      </c>
+      <c r="R488" t="n">
+        <v>619433095379</v>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W488" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X488" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y488" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z488" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA488" t="inlineStr"/>
+      <c r="AB488" t="inlineStr"/>
+      <c r="AC488" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD488" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE488" t="inlineStr"/>
+      <c r="AF488" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG488" t="inlineStr"/>
+      <c r="AH488" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI488" t="n">
+        <v>20423</v>
+      </c>
+      <c r="AJ488" t="inlineStr">
+        <is>
+          <t>277276</t>
+        </is>
+      </c>
+      <c r="AK488" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL488" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL488"/>
+  <dimension ref="A1:AL489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76888,6 +76888,152 @@
       </c>
       <c r="AL488" t="inlineStr"/>
     </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>16600</v>
+      </c>
+      <c r="B489" t="inlineStr"/>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>78****9830</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 06:24:44</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr"/>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>*8417</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N489" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P489" t="n">
+        <v>11000372581514</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>1783990473035</v>
+      </c>
+      <c r="R489" t="n">
+        <v>744464417704</v>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W489" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X489" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y489" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z489" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA489" t="inlineStr"/>
+      <c r="AB489" t="inlineStr"/>
+      <c r="AC489" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD489" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE489" t="inlineStr"/>
+      <c r="AF489" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG489" t="inlineStr"/>
+      <c r="AH489" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI489" t="n">
+        <v>18417</v>
+      </c>
+      <c r="AJ489" t="inlineStr">
+        <is>
+          <t>272464</t>
+        </is>
+      </c>
+      <c r="AK489" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL489" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL489"/>
+  <dimension ref="A1:AL507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75453,7 +75453,9 @@
       <c r="D479" t="n">
         <v>12300</v>
       </c>
-      <c r="E479" t="inlineStr"/>
+      <c r="E479" t="n">
+        <v>12300</v>
+      </c>
       <c r="F479" t="inlineStr">
         <is>
           <t>13-Jul-2026 08:43:44</t>
@@ -75524,7 +75526,7 @@
       </c>
       <c r="V479" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W479" t="inlineStr">
@@ -75547,15 +75549,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA479" t="inlineStr"/>
-      <c r="AB479" t="inlineStr"/>
+      <c r="AA479" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB479" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC479" t="n">
         <v>0</v>
       </c>
       <c r="AD479" t="n">
         <v>0</v>
       </c>
-      <c r="AE479" t="inlineStr"/>
+      <c r="AE479" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF479" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -75599,13 +75607,19 @@
       <c r="D480" t="n">
         <v>9000</v>
       </c>
-      <c r="E480" t="inlineStr"/>
+      <c r="E480" t="n">
+        <v>9000</v>
+      </c>
       <c r="F480" t="inlineStr">
         <is>
           <t>13-Jul-2026 08:50:31</t>
         </is>
       </c>
-      <c r="G480" t="inlineStr"/>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 18:54:43</t>
+        </is>
+      </c>
       <c r="H480" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -75670,7 +75684,7 @@
       </c>
       <c r="V480" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W480" t="inlineStr">
@@ -75693,15 +75707,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA480" t="inlineStr"/>
-      <c r="AB480" t="inlineStr"/>
+      <c r="AA480" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB480" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC480" t="n">
         <v>0</v>
       </c>
       <c r="AD480" t="n">
         <v>0</v>
       </c>
-      <c r="AE480" t="inlineStr"/>
+      <c r="AE480" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF480" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -75745,7 +75765,9 @@
       <c r="D481" t="n">
         <v>12300</v>
       </c>
-      <c r="E481" t="inlineStr"/>
+      <c r="E481" t="n">
+        <v>12300</v>
+      </c>
       <c r="F481" t="inlineStr">
         <is>
           <t>13-Jul-2026 09:46:23</t>
@@ -75816,7 +75838,7 @@
       </c>
       <c r="V481" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W481" t="inlineStr">
@@ -75839,15 +75861,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA481" t="inlineStr"/>
-      <c r="AB481" t="inlineStr"/>
+      <c r="AA481" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB481" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC481" t="n">
         <v>0</v>
       </c>
       <c r="AD481" t="n">
         <v>0</v>
       </c>
-      <c r="AE481" t="inlineStr"/>
+      <c r="AE481" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF481" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -75891,13 +75919,19 @@
       <c r="D482" t="n">
         <v>7250</v>
       </c>
-      <c r="E482" t="inlineStr"/>
+      <c r="E482" t="n">
+        <v>7250</v>
+      </c>
       <c r="F482" t="inlineStr">
         <is>
           <t>13-Jul-2026 13:15:08</t>
         </is>
       </c>
-      <c r="G482" t="inlineStr"/>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 18:54:43</t>
+        </is>
+      </c>
       <c r="H482" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -75962,7 +75996,7 @@
       </c>
       <c r="V482" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W482" t="inlineStr">
@@ -75985,15 +76019,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA482" t="inlineStr"/>
-      <c r="AB482" t="inlineStr"/>
+      <c r="AA482" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB482" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC482" t="n">
         <v>0</v>
       </c>
       <c r="AD482" t="n">
         <v>0</v>
       </c>
-      <c r="AE482" t="inlineStr"/>
+      <c r="AE482" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF482" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -76037,13 +76077,19 @@
       <c r="D483" t="n">
         <v>9000</v>
       </c>
-      <c r="E483" t="inlineStr"/>
+      <c r="E483" t="n">
+        <v>9000</v>
+      </c>
       <c r="F483" t="inlineStr">
         <is>
           <t>13-Jul-2026 15:50:31</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr"/>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 18:54:43</t>
+        </is>
+      </c>
       <c r="H483" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -76108,7 +76154,7 @@
       </c>
       <c r="V483" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W483" t="inlineStr">
@@ -76131,15 +76177,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA483" t="inlineStr"/>
-      <c r="AB483" t="inlineStr"/>
+      <c r="AA483" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB483" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC483" t="n">
         <v>0</v>
       </c>
       <c r="AD483" t="n">
         <v>0</v>
       </c>
-      <c r="AE483" t="inlineStr"/>
+      <c r="AE483" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF483" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -76183,7 +76235,9 @@
       <c r="D484" t="n">
         <v>11600</v>
       </c>
-      <c r="E484" t="inlineStr"/>
+      <c r="E484" t="n">
+        <v>11600</v>
+      </c>
       <c r="F484" t="inlineStr">
         <is>
           <t>13-Jul-2026 16:43:37</t>
@@ -76254,7 +76308,7 @@
       </c>
       <c r="V484" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W484" t="inlineStr">
@@ -76277,15 +76331,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA484" t="inlineStr"/>
-      <c r="AB484" t="inlineStr"/>
+      <c r="AA484" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="AB484" t="n">
+        <v>25.06</v>
+      </c>
       <c r="AC484" t="n">
         <v>0</v>
       </c>
       <c r="AD484" t="n">
         <v>0</v>
       </c>
-      <c r="AE484" t="inlineStr"/>
+      <c r="AE484" t="n">
+        <v>164.26</v>
+      </c>
       <c r="AF484" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -76325,7 +76385,9 @@
       <c r="D485" t="n">
         <v>12900</v>
       </c>
-      <c r="E485" t="inlineStr"/>
+      <c r="E485" t="n">
+        <v>12900</v>
+      </c>
       <c r="F485" t="inlineStr">
         <is>
           <t>13-Jul-2026 17:06:10</t>
@@ -76396,7 +76458,7 @@
       </c>
       <c r="V485" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W485" t="inlineStr">
@@ -76419,15 +76481,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA485" t="inlineStr"/>
-      <c r="AB485" t="inlineStr"/>
+      <c r="AA485" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB485" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC485" t="n">
         <v>0</v>
       </c>
       <c r="AD485" t="n">
         <v>0</v>
       </c>
-      <c r="AE485" t="inlineStr"/>
+      <c r="AE485" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF485" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -76471,7 +76539,9 @@
       <c r="D486" t="n">
         <v>12300</v>
       </c>
-      <c r="E486" t="inlineStr"/>
+      <c r="E486" t="n">
+        <v>12300</v>
+      </c>
       <c r="F486" t="inlineStr">
         <is>
           <t>13-Jul-2026 17:09:58</t>
@@ -76542,7 +76612,7 @@
       </c>
       <c r="V486" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W486" t="inlineStr">
@@ -76565,15 +76635,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA486" t="inlineStr"/>
-      <c r="AB486" t="inlineStr"/>
+      <c r="AA486" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB486" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC486" t="n">
         <v>0</v>
       </c>
       <c r="AD486" t="n">
         <v>0</v>
       </c>
-      <c r="AE486" t="inlineStr"/>
+      <c r="AE486" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF486" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -76617,13 +76693,19 @@
       <c r="D487" t="n">
         <v>9000</v>
       </c>
-      <c r="E487" t="inlineStr"/>
+      <c r="E487" t="n">
+        <v>9000</v>
+      </c>
       <c r="F487" t="inlineStr">
         <is>
           <t>13-Jul-2026 19:47:02</t>
         </is>
       </c>
-      <c r="G487" t="inlineStr"/>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 18:54:43</t>
+        </is>
+      </c>
       <c r="H487" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -76688,7 +76770,7 @@
       </c>
       <c r="V487" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W487" t="inlineStr">
@@ -76711,15 +76793,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA487" t="inlineStr"/>
-      <c r="AB487" t="inlineStr"/>
+      <c r="AA487" t="n">
+        <v>108</v>
+      </c>
+      <c r="AB487" t="n">
+        <v>19.44</v>
+      </c>
       <c r="AC487" t="n">
         <v>0</v>
       </c>
       <c r="AD487" t="n">
         <v>0</v>
       </c>
-      <c r="AE487" t="inlineStr"/>
+      <c r="AE487" t="n">
+        <v>127.44</v>
+      </c>
       <c r="AF487" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -76759,13 +76847,19 @@
       <c r="D488" t="n">
         <v>8400</v>
       </c>
-      <c r="E488" t="inlineStr"/>
+      <c r="E488" t="n">
+        <v>8400</v>
+      </c>
       <c r="F488" t="inlineStr">
         <is>
           <t>13-Jul-2026 20:43:31</t>
         </is>
       </c>
-      <c r="G488" t="inlineStr"/>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 18:54:43</t>
+        </is>
+      </c>
       <c r="H488" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -76830,7 +76924,7 @@
       </c>
       <c r="V488" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W488" t="inlineStr">
@@ -76853,15 +76947,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA488" t="inlineStr"/>
-      <c r="AB488" t="inlineStr"/>
+      <c r="AA488" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="AB488" t="n">
+        <v>20.41</v>
+      </c>
       <c r="AC488" t="n">
         <v>0</v>
       </c>
       <c r="AD488" t="n">
         <v>0</v>
       </c>
-      <c r="AE488" t="inlineStr"/>
+      <c r="AE488" t="n">
+        <v>133.81</v>
+      </c>
       <c r="AF488" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -77034,6 +77134,2626 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>16210</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>V********** H****** K****</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>81****1333</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>11600</v>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 08:19:45</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>eleven thousand six hundred</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N490" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="P490" t="n">
+        <v>11000372592904</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>1783997365</v>
+      </c>
+      <c r="R490" t="n">
+        <v>970216478702</v>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W490" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y490" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z490" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA490" t="inlineStr"/>
+      <c r="AB490" t="inlineStr"/>
+      <c r="AC490" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD490" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE490" t="inlineStr"/>
+      <c r="AF490" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG490" t="inlineStr"/>
+      <c r="AH490" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI490" t="n">
+        <v>19051</v>
+      </c>
+      <c r="AJ490" t="inlineStr">
+        <is>
+          <t>275475</t>
+        </is>
+      </c>
+      <c r="AK490" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="AL490" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>16754</v>
+      </c>
+      <c r="B491" t="inlineStr"/>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>79****7118</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 08:32:00</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr"/>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>*8267</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N491" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P491" t="n">
+        <v>11000372593846</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>1783998111697</v>
+      </c>
+      <c r="R491" t="n">
+        <v>656134982093</v>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W491" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y491" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z491" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA491" t="inlineStr"/>
+      <c r="AB491" t="inlineStr"/>
+      <c r="AC491" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD491" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE491" t="inlineStr"/>
+      <c r="AF491" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG491" t="inlineStr"/>
+      <c r="AH491" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI491" t="n">
+        <v>18267</v>
+      </c>
+      <c r="AJ491" t="inlineStr">
+        <is>
+          <t>272264</t>
+        </is>
+      </c>
+      <c r="AK491" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL491" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>17474</v>
+      </c>
+      <c r="B492" t="inlineStr"/>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>95****0855</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 08:55:10</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>*0440</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N492" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P492" t="n">
+        <v>11000372597439</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>1783999483660</v>
+      </c>
+      <c r="R492" t="n">
+        <v>163139316836</v>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W492" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y492" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z492" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA492" t="inlineStr"/>
+      <c r="AB492" t="inlineStr"/>
+      <c r="AC492" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD492" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE492" t="inlineStr"/>
+      <c r="AF492" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG492" t="inlineStr"/>
+      <c r="AH492" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI492" t="n">
+        <v>20440</v>
+      </c>
+      <c r="AJ492" t="inlineStr">
+        <is>
+          <t>277500</t>
+        </is>
+      </c>
+      <c r="AK492" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL492" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>17635</v>
+      </c>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>95****1386</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>9300</v>
+      </c>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 09:17:53</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>*0439</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N493" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P493" t="n">
+        <v>11000372602280</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>1784000839883</v>
+      </c>
+      <c r="R493" t="n">
+        <v>586045885504</v>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W493" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y493" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z493" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA493" t="inlineStr"/>
+      <c r="AB493" t="inlineStr"/>
+      <c r="AC493" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD493" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE493" t="inlineStr"/>
+      <c r="AF493" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG493" t="inlineStr"/>
+      <c r="AH493" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI493" t="n">
+        <v>20439</v>
+      </c>
+      <c r="AJ493" t="inlineStr">
+        <is>
+          <t>277157,277158</t>
+        </is>
+      </c>
+      <c r="AK493" t="inlineStr">
+        <is>
+          <t>2067,2080</t>
+        </is>
+      </c>
+      <c r="AL493" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>15946</v>
+      </c>
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>99****3270</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>600</v>
+      </c>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 10:38:53</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>*8582</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N494" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P494" t="n">
+        <v>11000372621189</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>1784005658818</v>
+      </c>
+      <c r="R494" t="n">
+        <v>279854132977</v>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W494" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y494" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z494" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA494" t="inlineStr"/>
+      <c r="AB494" t="inlineStr"/>
+      <c r="AC494" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD494" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE494" t="inlineStr"/>
+      <c r="AF494" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG494" t="inlineStr"/>
+      <c r="AH494" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI494" t="n">
+        <v>18582</v>
+      </c>
+      <c r="AJ494" t="inlineStr">
+        <is>
+          <t>270376</t>
+        </is>
+      </c>
+      <c r="AK494" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="AL494" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>14595</v>
+      </c>
+      <c r="B495" t="inlineStr"/>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>97****3026</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 12:01:07</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr"/>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>*9376</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N495" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P495" t="n">
+        <v>11000372647475</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>1784010645253</v>
+      </c>
+      <c r="R495" t="n">
+        <v>303738269768</v>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W495" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y495" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z495" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA495" t="inlineStr"/>
+      <c r="AB495" t="inlineStr"/>
+      <c r="AC495" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD495" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE495" t="inlineStr"/>
+      <c r="AF495" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG495" t="inlineStr"/>
+      <c r="AH495" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI495" t="n">
+        <v>19376</v>
+      </c>
+      <c r="AJ495" t="inlineStr">
+        <is>
+          <t>276103</t>
+        </is>
+      </c>
+      <c r="AK495" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL495" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>14972</v>
+      </c>
+      <c r="B496" t="inlineStr"/>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>97****3026</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 12:07:44</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>*9310</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N496" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P496" t="n">
+        <v>11000372651223</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>1784011047137</v>
+      </c>
+      <c r="R496" t="n">
+        <v>442912257699</v>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W496" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y496" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z496" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA496" t="inlineStr"/>
+      <c r="AB496" t="inlineStr"/>
+      <c r="AC496" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD496" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE496" t="inlineStr"/>
+      <c r="AF496" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG496" t="inlineStr"/>
+      <c r="AH496" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI496" t="n">
+        <v>19310</v>
+      </c>
+      <c r="AJ496" t="inlineStr">
+        <is>
+          <t>276056</t>
+        </is>
+      </c>
+      <c r="AK496" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL496" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>16308</v>
+      </c>
+      <c r="B497" t="inlineStr"/>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>88****7880</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 15:58:15</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>*8443</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N497" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P497" t="n">
+        <v>11000372709836</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>1784024636491</v>
+      </c>
+      <c r="R497" t="n">
+        <v>619545045871</v>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W497" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y497" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z497" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA497" t="inlineStr"/>
+      <c r="AB497" t="inlineStr"/>
+      <c r="AC497" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD497" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE497" t="inlineStr"/>
+      <c r="AF497" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG497" t="inlineStr"/>
+      <c r="AH497" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI497" t="n">
+        <v>18443</v>
+      </c>
+      <c r="AJ497" t="inlineStr">
+        <is>
+          <t>272490</t>
+        </is>
+      </c>
+      <c r="AK497" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>16636</v>
+      </c>
+      <c r="B498" t="inlineStr"/>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>88****7880</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 16:01:05</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>*8297</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N498" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P498" t="n">
+        <v>11000372711014</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>1784024987288</v>
+      </c>
+      <c r="R498" t="n">
+        <v>619533061786</v>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W498" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y498" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z498" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA498" t="inlineStr"/>
+      <c r="AB498" t="inlineStr"/>
+      <c r="AC498" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD498" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE498" t="inlineStr"/>
+      <c r="AF498" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG498" t="inlineStr"/>
+      <c r="AH498" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI498" t="n">
+        <v>18297</v>
+      </c>
+      <c r="AJ498" t="inlineStr">
+        <is>
+          <t>272276</t>
+        </is>
+      </c>
+      <c r="AK498" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>16946</v>
+      </c>
+      <c r="B499" t="inlineStr"/>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>97****7601</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 17:52:35</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>*8263</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N499" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P499" t="n">
+        <v>11000372732102</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>1784031726449</v>
+      </c>
+      <c r="R499" t="n">
+        <v>621816203512</v>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>HDFC BANK UPI</t>
+        </is>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W499" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y499" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z499" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA499" t="inlineStr"/>
+      <c r="AB499" t="inlineStr"/>
+      <c r="AC499" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD499" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE499" t="inlineStr"/>
+      <c r="AF499" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG499" t="inlineStr"/>
+      <c r="AH499" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI499" t="n">
+        <v>18263</v>
+      </c>
+      <c r="AJ499" t="inlineStr">
+        <is>
+          <t>272310</t>
+        </is>
+      </c>
+      <c r="AK499" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL499" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>17259</v>
+      </c>
+      <c r="B500" t="inlineStr"/>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>63****1566</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 18:40:49</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>*9971</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N500" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P500" t="n">
+        <v>11000372738767</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>1784034633473</v>
+      </c>
+      <c r="R500" t="n">
+        <v>619572737176</v>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W500" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y500" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z500" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA500" t="inlineStr"/>
+      <c r="AB500" t="inlineStr"/>
+      <c r="AC500" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD500" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE500" t="inlineStr"/>
+      <c r="AF500" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG500" t="inlineStr"/>
+      <c r="AH500" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI500" t="n">
+        <v>19971</v>
+      </c>
+      <c r="AJ500" t="inlineStr">
+        <is>
+          <t>276072</t>
+        </is>
+      </c>
+      <c r="AK500" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL500" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>17260</v>
+      </c>
+      <c r="B501" t="inlineStr"/>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>63****1566</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 18:43:00</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>*9972</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N501" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P501" t="n">
+        <v>11000372739801</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>1784034760455</v>
+      </c>
+      <c r="R501" t="n">
+        <v>619535244605</v>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W501" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y501" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z501" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA501" t="inlineStr"/>
+      <c r="AB501" t="inlineStr"/>
+      <c r="AC501" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD501" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE501" t="inlineStr"/>
+      <c r="AF501" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG501" t="inlineStr"/>
+      <c r="AH501" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI501" t="n">
+        <v>19972</v>
+      </c>
+      <c r="AJ501" t="inlineStr">
+        <is>
+          <t>273787</t>
+        </is>
+      </c>
+      <c r="AK501" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL501" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>17305</v>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>70****3690</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 19:25:25</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>*0014</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N502" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P502" t="n">
+        <v>11000372748134</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>1784037291694</v>
+      </c>
+      <c r="R502" t="n">
+        <v>619523487211</v>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W502" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y502" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z502" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA502" t="inlineStr"/>
+      <c r="AB502" t="inlineStr"/>
+      <c r="AC502" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD502" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE502" t="inlineStr"/>
+      <c r="AF502" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG502" t="inlineStr"/>
+      <c r="AH502" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI502" t="n">
+        <v>20014</v>
+      </c>
+      <c r="AJ502" t="inlineStr">
+        <is>
+          <t>269340</t>
+        </is>
+      </c>
+      <c r="AK502" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL502" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>16184</v>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>98****4994</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 21:50:45</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>*8643</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N503" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P503" t="n">
+        <v>11000372774187</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>1784045939391</v>
+      </c>
+      <c r="R503" t="n">
+        <v>619526086181</v>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W503" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y503" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z503" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA503" t="inlineStr"/>
+      <c r="AB503" t="inlineStr"/>
+      <c r="AC503" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD503" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE503" t="inlineStr"/>
+      <c r="AF503" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG503" t="inlineStr"/>
+      <c r="AH503" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI503" t="n">
+        <v>18643</v>
+      </c>
+      <c r="AJ503" t="inlineStr">
+        <is>
+          <t>273525</t>
+        </is>
+      </c>
+      <c r="AK503" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>17139</v>
+      </c>
+      <c r="B504" t="inlineStr"/>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>79****8688</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 22:23:39</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>*9842</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N504" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P504" t="n">
+        <v>11000372787749</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>1784047981963</v>
+      </c>
+      <c r="R504" t="n">
+        <v>619566785107</v>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W504" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y504" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z504" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA504" t="inlineStr"/>
+      <c r="AB504" t="inlineStr"/>
+      <c r="AC504" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD504" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE504" t="inlineStr"/>
+      <c r="AF504" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG504" t="inlineStr"/>
+      <c r="AH504" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI504" t="n">
+        <v>19842</v>
+      </c>
+      <c r="AJ504" t="inlineStr">
+        <is>
+          <t>273716</t>
+        </is>
+      </c>
+      <c r="AK504" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL504" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>17138</v>
+      </c>
+      <c r="B505" t="inlineStr"/>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>79****8688</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E505" t="inlineStr"/>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 22:25:50</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESS</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>*9841</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N505" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P505" t="n">
+        <v>11000372788739</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>1784048132165</v>
+      </c>
+      <c r="R505" t="n">
+        <v>126301595397</v>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W505" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y505" t="inlineStr">
+        <is>
+          <t>QR_UPI</t>
+        </is>
+      </c>
+      <c r="Z505" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA505" t="inlineStr"/>
+      <c r="AB505" t="inlineStr"/>
+      <c r="AC505" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD505" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE505" t="inlineStr"/>
+      <c r="AF505" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG505" t="inlineStr"/>
+      <c r="AH505" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI505" t="n">
+        <v>19841</v>
+      </c>
+      <c r="AJ505" t="inlineStr">
+        <is>
+          <t>272388</t>
+        </is>
+      </c>
+      <c r="AK505" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL505" t="inlineStr">
+        <is>
+          <t>PG QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>16056</v>
+      </c>
+      <c r="B506" t="inlineStr"/>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>63****9147</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>11600</v>
+      </c>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 23:02:15</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>*9023</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N506" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P506" t="n">
+        <v>11000372794165</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>1784050323852</v>
+      </c>
+      <c r="R506" t="n">
+        <v>207509877173</v>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W506" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y506" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z506" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA506" t="inlineStr"/>
+      <c r="AB506" t="inlineStr"/>
+      <c r="AC506" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD506" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE506" t="inlineStr"/>
+      <c r="AF506" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG506" t="inlineStr"/>
+      <c r="AH506" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI506" t="n">
+        <v>19023</v>
+      </c>
+      <c r="AJ506" t="inlineStr">
+        <is>
+          <t>275357</t>
+        </is>
+      </c>
+      <c r="AK506" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="AL506" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>15011</v>
+      </c>
+      <c r="B507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>99****2276</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 06:38:13</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr"/>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>*9283</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N507" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P507" t="n">
+        <v>11000372803936</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>1784077528625</v>
+      </c>
+      <c r="R507" t="n">
+        <v>82502943802</v>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W507" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y507" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z507" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA507" t="inlineStr"/>
+      <c r="AB507" t="inlineStr"/>
+      <c r="AC507" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD507" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE507" t="inlineStr"/>
+      <c r="AF507" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG507" t="inlineStr"/>
+      <c r="AH507" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI507" t="n">
+        <v>19283</v>
+      </c>
+      <c r="AJ507" t="inlineStr">
+        <is>
+          <t>276023</t>
+        </is>
+      </c>
+      <c r="AK507" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL507" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL507"/>
+  <dimension ref="A1:AL522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77001,13 +77001,19 @@
       <c r="D489" t="n">
         <v>8700</v>
       </c>
-      <c r="E489" t="inlineStr"/>
+      <c r="E489" t="n">
+        <v>8700</v>
+      </c>
       <c r="F489" t="inlineStr">
         <is>
           <t>14-Jul-2026 06:24:44</t>
         </is>
       </c>
-      <c r="G489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H489" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -77072,7 +77078,7 @@
       </c>
       <c r="V489" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W489" t="inlineStr">
@@ -77095,15 +77101,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA489" t="inlineStr"/>
-      <c r="AB489" t="inlineStr"/>
+      <c r="AA489" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB489" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC489" t="n">
         <v>0</v>
       </c>
       <c r="AD489" t="n">
         <v>0</v>
       </c>
-      <c r="AE489" t="inlineStr"/>
+      <c r="AE489" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF489" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -77151,7 +77163,9 @@
       <c r="D490" t="n">
         <v>11600</v>
       </c>
-      <c r="E490" t="inlineStr"/>
+      <c r="E490" t="n">
+        <v>11600</v>
+      </c>
       <c r="F490" t="inlineStr">
         <is>
           <t>14-Jul-2026 08:19:45</t>
@@ -77222,7 +77236,7 @@
       </c>
       <c r="V490" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W490" t="inlineStr">
@@ -77245,15 +77259,21 @@
           <t>k*************@gmail.com</t>
         </is>
       </c>
-      <c r="AA490" t="inlineStr"/>
-      <c r="AB490" t="inlineStr"/>
+      <c r="AA490" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB490" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC490" t="n">
         <v>0</v>
       </c>
       <c r="AD490" t="n">
         <v>0</v>
       </c>
-      <c r="AE490" t="inlineStr"/>
+      <c r="AE490" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF490" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -77297,13 +77317,19 @@
       <c r="D491" t="n">
         <v>8700</v>
       </c>
-      <c r="E491" t="inlineStr"/>
+      <c r="E491" t="n">
+        <v>8700</v>
+      </c>
       <c r="F491" t="inlineStr">
         <is>
           <t>14-Jul-2026 08:32:00</t>
         </is>
       </c>
-      <c r="G491" t="inlineStr"/>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H491" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -77368,7 +77394,7 @@
       </c>
       <c r="V491" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W491" t="inlineStr">
@@ -77391,15 +77417,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA491" t="inlineStr"/>
-      <c r="AB491" t="inlineStr"/>
+      <c r="AA491" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB491" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC491" t="n">
         <v>0</v>
       </c>
       <c r="AD491" t="n">
         <v>0</v>
       </c>
-      <c r="AE491" t="inlineStr"/>
+      <c r="AE491" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF491" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -77443,13 +77475,19 @@
       <c r="D492" t="n">
         <v>9000</v>
       </c>
-      <c r="E492" t="inlineStr"/>
+      <c r="E492" t="n">
+        <v>9000</v>
+      </c>
       <c r="F492" t="inlineStr">
         <is>
           <t>14-Jul-2026 08:55:10</t>
         </is>
       </c>
-      <c r="G492" t="inlineStr"/>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H492" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -77514,7 +77552,7 @@
       </c>
       <c r="V492" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W492" t="inlineStr">
@@ -77537,15 +77575,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA492" t="inlineStr"/>
-      <c r="AB492" t="inlineStr"/>
+      <c r="AA492" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB492" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC492" t="n">
         <v>0</v>
       </c>
       <c r="AD492" t="n">
         <v>0</v>
       </c>
-      <c r="AE492" t="inlineStr"/>
+      <c r="AE492" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF492" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -77589,13 +77633,19 @@
       <c r="D493" t="n">
         <v>9300</v>
       </c>
-      <c r="E493" t="inlineStr"/>
+      <c r="E493" t="n">
+        <v>9300</v>
+      </c>
       <c r="F493" t="inlineStr">
         <is>
           <t>14-Jul-2026 09:17:53</t>
         </is>
       </c>
-      <c r="G493" t="inlineStr"/>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H493" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -77660,7 +77710,7 @@
       </c>
       <c r="V493" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W493" t="inlineStr">
@@ -77683,15 +77733,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA493" t="inlineStr"/>
-      <c r="AB493" t="inlineStr"/>
+      <c r="AA493" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB493" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC493" t="n">
         <v>0</v>
       </c>
       <c r="AD493" t="n">
         <v>0</v>
       </c>
-      <c r="AE493" t="inlineStr"/>
+      <c r="AE493" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF493" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -77735,13 +77791,19 @@
       <c r="D494" t="n">
         <v>600</v>
       </c>
-      <c r="E494" t="inlineStr"/>
+      <c r="E494" t="n">
+        <v>600</v>
+      </c>
       <c r="F494" t="inlineStr">
         <is>
           <t>14-Jul-2026 10:38:53</t>
         </is>
       </c>
-      <c r="G494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H494" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -77806,7 +77868,7 @@
       </c>
       <c r="V494" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W494" t="inlineStr">
@@ -77829,15 +77891,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA494" t="inlineStr"/>
-      <c r="AB494" t="inlineStr"/>
+      <c r="AA494" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB494" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC494" t="n">
         <v>0</v>
       </c>
       <c r="AD494" t="n">
         <v>0</v>
       </c>
-      <c r="AE494" t="inlineStr"/>
+      <c r="AE494" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF494" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -77881,7 +77949,9 @@
       <c r="D495" t="n">
         <v>12300</v>
       </c>
-      <c r="E495" t="inlineStr"/>
+      <c r="E495" t="n">
+        <v>12300</v>
+      </c>
       <c r="F495" t="inlineStr">
         <is>
           <t>14-Jul-2026 12:01:07</t>
@@ -77952,7 +78022,7 @@
       </c>
       <c r="V495" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W495" t="inlineStr">
@@ -77975,15 +78045,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA495" t="inlineStr"/>
-      <c r="AB495" t="inlineStr"/>
+      <c r="AA495" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB495" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC495" t="n">
         <v>0</v>
       </c>
       <c r="AD495" t="n">
         <v>0</v>
       </c>
-      <c r="AE495" t="inlineStr"/>
+      <c r="AE495" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF495" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -78027,7 +78103,9 @@
       <c r="D496" t="n">
         <v>12300</v>
       </c>
-      <c r="E496" t="inlineStr"/>
+      <c r="E496" t="n">
+        <v>12300</v>
+      </c>
       <c r="F496" t="inlineStr">
         <is>
           <t>14-Jul-2026 12:07:44</t>
@@ -78098,7 +78176,7 @@
       </c>
       <c r="V496" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W496" t="inlineStr">
@@ -78121,15 +78199,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA496" t="inlineStr"/>
-      <c r="AB496" t="inlineStr"/>
+      <c r="AA496" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB496" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC496" t="n">
         <v>0</v>
       </c>
       <c r="AD496" t="n">
         <v>0</v>
       </c>
-      <c r="AE496" t="inlineStr"/>
+      <c r="AE496" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF496" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -78173,13 +78257,19 @@
       <c r="D497" t="n">
         <v>8700</v>
       </c>
-      <c r="E497" t="inlineStr"/>
+      <c r="E497" t="n">
+        <v>8700</v>
+      </c>
       <c r="F497" t="inlineStr">
         <is>
           <t>14-Jul-2026 15:58:15</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr"/>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H497" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -78244,7 +78334,7 @@
       </c>
       <c r="V497" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W497" t="inlineStr">
@@ -78267,15 +78357,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA497" t="inlineStr"/>
-      <c r="AB497" t="inlineStr"/>
+      <c r="AA497" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AB497" t="n">
+        <v>18.79</v>
+      </c>
       <c r="AC497" t="n">
         <v>0</v>
       </c>
       <c r="AD497" t="n">
         <v>0</v>
       </c>
-      <c r="AE497" t="inlineStr"/>
+      <c r="AE497" t="n">
+        <v>123.19</v>
+      </c>
       <c r="AF497" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -78315,13 +78411,19 @@
       <c r="D498" t="n">
         <v>8700</v>
       </c>
-      <c r="E498" t="inlineStr"/>
+      <c r="E498" t="n">
+        <v>8700</v>
+      </c>
       <c r="F498" t="inlineStr">
         <is>
           <t>14-Jul-2026 16:01:05</t>
         </is>
       </c>
-      <c r="G498" t="inlineStr"/>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H498" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -78386,7 +78488,7 @@
       </c>
       <c r="V498" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W498" t="inlineStr">
@@ -78409,15 +78511,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA498" t="inlineStr"/>
-      <c r="AB498" t="inlineStr"/>
+      <c r="AA498" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AB498" t="n">
+        <v>18.79</v>
+      </c>
       <c r="AC498" t="n">
         <v>0</v>
       </c>
       <c r="AD498" t="n">
         <v>0</v>
       </c>
-      <c r="AE498" t="inlineStr"/>
+      <c r="AE498" t="n">
+        <v>123.19</v>
+      </c>
       <c r="AF498" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -78457,13 +78565,19 @@
       <c r="D499" t="n">
         <v>8700</v>
       </c>
-      <c r="E499" t="inlineStr"/>
+      <c r="E499" t="n">
+        <v>8700</v>
+      </c>
       <c r="F499" t="inlineStr">
         <is>
           <t>14-Jul-2026 17:52:35</t>
         </is>
       </c>
-      <c r="G499" t="inlineStr"/>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H499" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -78528,7 +78642,7 @@
       </c>
       <c r="V499" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W499" t="inlineStr">
@@ -78551,15 +78665,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA499" t="inlineStr"/>
-      <c r="AB499" t="inlineStr"/>
+      <c r="AA499" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB499" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC499" t="n">
         <v>0</v>
       </c>
       <c r="AD499" t="n">
         <v>0</v>
       </c>
-      <c r="AE499" t="inlineStr"/>
+      <c r="AE499" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF499" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -78603,7 +78723,9 @@
       <c r="D500" t="n">
         <v>12300</v>
       </c>
-      <c r="E500" t="inlineStr"/>
+      <c r="E500" t="n">
+        <v>12300</v>
+      </c>
       <c r="F500" t="inlineStr">
         <is>
           <t>14-Jul-2026 18:40:49</t>
@@ -78674,7 +78796,7 @@
       </c>
       <c r="V500" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W500" t="inlineStr">
@@ -78697,15 +78819,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA500" t="inlineStr"/>
-      <c r="AB500" t="inlineStr"/>
+      <c r="AA500" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB500" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC500" t="n">
         <v>0</v>
       </c>
       <c r="AD500" t="n">
         <v>0</v>
       </c>
-      <c r="AE500" t="inlineStr"/>
+      <c r="AE500" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF500" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -78749,13 +78877,19 @@
       <c r="D501" t="n">
         <v>9000</v>
       </c>
-      <c r="E501" t="inlineStr"/>
+      <c r="E501" t="n">
+        <v>9000</v>
+      </c>
       <c r="F501" t="inlineStr">
         <is>
           <t>14-Jul-2026 18:43:00</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr"/>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H501" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -78820,7 +78954,7 @@
       </c>
       <c r="V501" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W501" t="inlineStr">
@@ -78843,15 +78977,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA501" t="inlineStr"/>
-      <c r="AB501" t="inlineStr"/>
+      <c r="AA501" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB501" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC501" t="n">
         <v>0</v>
       </c>
       <c r="AD501" t="n">
         <v>0</v>
       </c>
-      <c r="AE501" t="inlineStr"/>
+      <c r="AE501" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF501" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -78895,13 +79035,19 @@
       <c r="D502" t="n">
         <v>7250</v>
       </c>
-      <c r="E502" t="inlineStr"/>
+      <c r="E502" t="n">
+        <v>7250</v>
+      </c>
       <c r="F502" t="inlineStr">
         <is>
           <t>14-Jul-2026 19:25:25</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr"/>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H502" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -78966,7 +79112,7 @@
       </c>
       <c r="V502" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W502" t="inlineStr">
@@ -78989,15 +79135,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA502" t="inlineStr"/>
-      <c r="AB502" t="inlineStr"/>
+      <c r="AA502" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB502" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC502" t="n">
         <v>0</v>
       </c>
       <c r="AD502" t="n">
         <v>0</v>
       </c>
-      <c r="AE502" t="inlineStr"/>
+      <c r="AE502" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF502" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -79041,13 +79193,19 @@
       <c r="D503" t="n">
         <v>9000</v>
       </c>
-      <c r="E503" t="inlineStr"/>
+      <c r="E503" t="n">
+        <v>9000</v>
+      </c>
       <c r="F503" t="inlineStr">
         <is>
           <t>14-Jul-2026 21:50:45</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H503" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -79112,7 +79270,7 @@
       </c>
       <c r="V503" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W503" t="inlineStr">
@@ -79135,15 +79293,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA503" t="inlineStr"/>
-      <c r="AB503" t="inlineStr"/>
+      <c r="AA503" t="n">
+        <v>108</v>
+      </c>
+      <c r="AB503" t="n">
+        <v>19.44</v>
+      </c>
       <c r="AC503" t="n">
         <v>0</v>
       </c>
       <c r="AD503" t="n">
         <v>0</v>
       </c>
-      <c r="AE503" t="inlineStr"/>
+      <c r="AE503" t="n">
+        <v>127.44</v>
+      </c>
       <c r="AF503" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -79183,13 +79347,19 @@
       <c r="D504" t="n">
         <v>9000</v>
       </c>
-      <c r="E504" t="inlineStr"/>
+      <c r="E504" t="n">
+        <v>9000</v>
+      </c>
       <c r="F504" t="inlineStr">
         <is>
           <t>14-Jul-2026 22:23:39</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H504" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESS</t>
@@ -79254,7 +79424,7 @@
       </c>
       <c r="V504" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W504" t="inlineStr">
@@ -79277,15 +79447,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA504" t="inlineStr"/>
-      <c r="AB504" t="inlineStr"/>
+      <c r="AA504" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB504" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC504" t="n">
         <v>0</v>
       </c>
       <c r="AD504" t="n">
         <v>0</v>
       </c>
-      <c r="AE504" t="inlineStr"/>
+      <c r="AE504" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF504" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -79329,13 +79505,19 @@
       <c r="D505" t="n">
         <v>8700</v>
       </c>
-      <c r="E505" t="inlineStr"/>
+      <c r="E505" t="n">
+        <v>8700</v>
+      </c>
       <c r="F505" t="inlineStr">
         <is>
           <t>14-Jul-2026 22:25:50</t>
         </is>
       </c>
-      <c r="G505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 17:54:32</t>
+        </is>
+      </c>
       <c r="H505" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESS</t>
@@ -79400,7 +79582,7 @@
       </c>
       <c r="V505" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W505" t="inlineStr">
@@ -79423,15 +79605,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA505" t="inlineStr"/>
-      <c r="AB505" t="inlineStr"/>
+      <c r="AA505" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB505" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC505" t="n">
         <v>0</v>
       </c>
       <c r="AD505" t="n">
         <v>0</v>
       </c>
-      <c r="AE505" t="inlineStr"/>
+      <c r="AE505" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF505" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -79475,7 +79663,9 @@
       <c r="D506" t="n">
         <v>11600</v>
       </c>
-      <c r="E506" t="inlineStr"/>
+      <c r="E506" t="n">
+        <v>11600</v>
+      </c>
       <c r="F506" t="inlineStr">
         <is>
           <t>14-Jul-2026 23:02:15</t>
@@ -79546,7 +79736,7 @@
       </c>
       <c r="V506" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W506" t="inlineStr">
@@ -79569,15 +79759,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA506" t="inlineStr"/>
-      <c r="AB506" t="inlineStr"/>
+      <c r="AA506" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB506" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC506" t="n">
         <v>0</v>
       </c>
       <c r="AD506" t="n">
         <v>0</v>
       </c>
-      <c r="AE506" t="inlineStr"/>
+      <c r="AE506" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF506" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -79753,6 +79949,2192 @@
           <t>UPI INTENT</t>
         </is>
       </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>17595</v>
+      </c>
+      <c r="B508" t="inlineStr"/>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>83****2419</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E508" t="inlineStr"/>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 07:06:53</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr"/>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>*0314</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N508" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P508" t="n">
+        <v>11000372806721</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>1784079402320</v>
+      </c>
+      <c r="R508" t="n">
+        <v>109042362519</v>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W508" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y508" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z508" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA508" t="inlineStr"/>
+      <c r="AB508" t="inlineStr"/>
+      <c r="AC508" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD508" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE508" t="inlineStr"/>
+      <c r="AF508" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG508" t="inlineStr"/>
+      <c r="AH508" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI508" t="n">
+        <v>20314</v>
+      </c>
+      <c r="AJ508" t="inlineStr">
+        <is>
+          <t>273655</t>
+        </is>
+      </c>
+      <c r="AK508" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL508" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>17596</v>
+      </c>
+      <c r="B509" t="inlineStr"/>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>83****2419</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>9400</v>
+      </c>
+      <c r="E509" t="inlineStr"/>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 07:08:31</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>*0315</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N509" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P509" t="n">
+        <v>11000372806821</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>1784079502710</v>
+      </c>
+      <c r="R509" t="n">
+        <v>501835994354</v>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W509" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y509" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z509" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA509" t="inlineStr"/>
+      <c r="AB509" t="inlineStr"/>
+      <c r="AC509" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD509" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE509" t="inlineStr"/>
+      <c r="AF509" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG509" t="inlineStr"/>
+      <c r="AH509" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI509" t="n">
+        <v>20315</v>
+      </c>
+      <c r="AJ509" t="inlineStr">
+        <is>
+          <t>274742</t>
+        </is>
+      </c>
+      <c r="AK509" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="AL509" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>16782</v>
+      </c>
+      <c r="B510" t="inlineStr"/>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>63****2843</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>11600</v>
+      </c>
+      <c r="E510" t="inlineStr"/>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 07:35:47</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>*9079</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N510" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P510" t="n">
+        <v>11000372811593</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>1784081129004</v>
+      </c>
+      <c r="R510" t="n">
+        <v>619641890897</v>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W510" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y510" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z510" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA510" t="inlineStr"/>
+      <c r="AB510" t="inlineStr"/>
+      <c r="AC510" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD510" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE510" t="inlineStr"/>
+      <c r="AF510" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG510" t="inlineStr"/>
+      <c r="AH510" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI510" t="n">
+        <v>19079</v>
+      </c>
+      <c r="AJ510" t="inlineStr">
+        <is>
+          <t>275413</t>
+        </is>
+      </c>
+      <c r="AK510" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="AL510" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>16783</v>
+      </c>
+      <c r="B511" t="inlineStr"/>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>63****2843</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E511" t="inlineStr"/>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 07:37:12</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr"/>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>*8559</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N511" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P511" t="n">
+        <v>11000372811793</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>1784081222752</v>
+      </c>
+      <c r="R511" t="n">
+        <v>619636383557</v>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W511" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y511" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z511" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA511" t="inlineStr"/>
+      <c r="AB511" t="inlineStr"/>
+      <c r="AC511" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD511" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE511" t="inlineStr"/>
+      <c r="AF511" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG511" t="inlineStr"/>
+      <c r="AH511" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI511" t="n">
+        <v>18559</v>
+      </c>
+      <c r="AJ511" t="inlineStr">
+        <is>
+          <t>273564</t>
+        </is>
+      </c>
+      <c r="AK511" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL511" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>16934</v>
+      </c>
+      <c r="B512" t="inlineStr"/>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>73****0623</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E512" t="inlineStr"/>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 09:13:39</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>*8063</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N512" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P512" t="n">
+        <v>11000372831197</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>1784086996179</v>
+      </c>
+      <c r="R512" t="n">
+        <v>122321756433</v>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W512" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y512" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z512" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA512" t="inlineStr"/>
+      <c r="AB512" t="inlineStr"/>
+      <c r="AC512" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD512" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE512" t="inlineStr"/>
+      <c r="AF512" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG512" t="inlineStr"/>
+      <c r="AH512" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI512" t="n">
+        <v>18063</v>
+      </c>
+      <c r="AJ512" t="inlineStr">
+        <is>
+          <t>271403</t>
+        </is>
+      </c>
+      <c r="AK512" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL512" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>17051</v>
+      </c>
+      <c r="B513" t="inlineStr"/>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>73****0623</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 09:18:21</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>*8700</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N513" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P513" t="n">
+        <v>11000372832257</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>1784087211347</v>
+      </c>
+      <c r="R513" t="n">
+        <v>943665380156</v>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W513" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y513" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z513" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA513" t="inlineStr"/>
+      <c r="AB513" t="inlineStr"/>
+      <c r="AC513" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD513" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE513" t="inlineStr"/>
+      <c r="AF513" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG513" t="inlineStr"/>
+      <c r="AH513" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI513" t="n">
+        <v>18700</v>
+      </c>
+      <c r="AJ513" t="inlineStr">
+        <is>
+          <t>273733</t>
+        </is>
+      </c>
+      <c r="AK513" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL513" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>16572</v>
+      </c>
+      <c r="B514" t="inlineStr"/>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>99****9977</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>9400</v>
+      </c>
+      <c r="E514" t="inlineStr"/>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 10:42:37</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>*8977</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N514" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P514" t="n">
+        <v>11000372853210</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>1784092322989</v>
+      </c>
+      <c r="R514" t="n">
+        <v>204571823197</v>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W514" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y514" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z514" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA514" t="inlineStr"/>
+      <c r="AB514" t="inlineStr"/>
+      <c r="AC514" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD514" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE514" t="inlineStr"/>
+      <c r="AF514" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG514" t="inlineStr"/>
+      <c r="AH514" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI514" t="n">
+        <v>18977</v>
+      </c>
+      <c r="AJ514" t="inlineStr">
+        <is>
+          <t>274858</t>
+        </is>
+      </c>
+      <c r="AK514" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="AL514" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>16571</v>
+      </c>
+      <c r="B515" t="inlineStr"/>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>99****9977</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 10:44:51</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr"/>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>*9204</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N515" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P515" t="n">
+        <v>11000372854188</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>1784092481421</v>
+      </c>
+      <c r="R515" t="n">
+        <v>27098224180</v>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V515" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W515" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y515" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z515" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA515" t="inlineStr"/>
+      <c r="AB515" t="inlineStr"/>
+      <c r="AC515" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD515" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE515" t="inlineStr"/>
+      <c r="AF515" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG515" t="inlineStr"/>
+      <c r="AH515" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI515" t="n">
+        <v>19204</v>
+      </c>
+      <c r="AJ515" t="inlineStr">
+        <is>
+          <t>275975</t>
+        </is>
+      </c>
+      <c r="AK515" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL515" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>17577</v>
+      </c>
+      <c r="B516" t="inlineStr"/>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>95****1640</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 13:35:56</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>*0296</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N516" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P516" t="n">
+        <v>11000372928457</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>1784102716449</v>
+      </c>
+      <c r="R516" t="n">
+        <v>743878369192</v>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W516" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y516" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z516" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA516" t="inlineStr"/>
+      <c r="AB516" t="inlineStr"/>
+      <c r="AC516" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD516" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE516" t="inlineStr"/>
+      <c r="AF516" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG516" t="inlineStr"/>
+      <c r="AH516" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI516" t="n">
+        <v>20296</v>
+      </c>
+      <c r="AJ516" t="inlineStr">
+        <is>
+          <t>273652</t>
+        </is>
+      </c>
+      <c r="AK516" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL516" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>17576</v>
+      </c>
+      <c r="B517" t="inlineStr"/>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>95****1640</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 13:34:37</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>*0295</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N517" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P517" t="n">
+        <v>11000372929322</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>1784102668153</v>
+      </c>
+      <c r="R517" t="n">
+        <v>310715703195</v>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W517" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y517" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z517" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA517" t="inlineStr"/>
+      <c r="AB517" t="inlineStr"/>
+      <c r="AC517" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD517" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE517" t="inlineStr"/>
+      <c r="AF517" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG517" t="inlineStr"/>
+      <c r="AH517" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI517" t="n">
+        <v>20295</v>
+      </c>
+      <c r="AJ517" t="inlineStr">
+        <is>
+          <t>272416</t>
+        </is>
+      </c>
+      <c r="AK517" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL517" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>15866</v>
+      </c>
+      <c r="B518" t="inlineStr"/>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>83****1596</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 14:52:10</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>*8617</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N518" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P518" t="n">
+        <v>11000372954049</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>1784107318823</v>
+      </c>
+      <c r="R518" t="n">
+        <v>959857018282</v>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V518" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W518" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y518" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z518" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA518" t="inlineStr"/>
+      <c r="AB518" t="inlineStr"/>
+      <c r="AC518" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD518" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE518" t="inlineStr"/>
+      <c r="AF518" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG518" t="inlineStr"/>
+      <c r="AH518" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI518" t="n">
+        <v>18617</v>
+      </c>
+      <c r="AJ518" t="inlineStr">
+        <is>
+          <t>273586</t>
+        </is>
+      </c>
+      <c r="AK518" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL518" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>17315</v>
+      </c>
+      <c r="B519" t="inlineStr"/>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>83****2524</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 15:36:05</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>*0023</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N519" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P519" t="n">
+        <v>11000372961520</v>
+      </c>
+      <c r="Q519" t="n">
+        <v>1784111204911</v>
+      </c>
+      <c r="R519" t="n">
+        <v>550381119890</v>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W519" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y519" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z519" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA519" t="inlineStr"/>
+      <c r="AB519" t="inlineStr"/>
+      <c r="AC519" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD519" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE519" t="inlineStr"/>
+      <c r="AF519" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG519" t="inlineStr"/>
+      <c r="AH519" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI519" t="n">
+        <v>20023</v>
+      </c>
+      <c r="AJ519" t="inlineStr">
+        <is>
+          <t>271428</t>
+        </is>
+      </c>
+      <c r="AK519" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL519" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>17597</v>
+      </c>
+      <c r="B520" t="inlineStr"/>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>83****2524</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 15:41:19</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>*0316</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N520" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P520" t="n">
+        <v>11000372961777</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>1784111565572</v>
+      </c>
+      <c r="R520" t="n">
+        <v>807149121170</v>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V520" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W520" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y520" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z520" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA520" t="inlineStr"/>
+      <c r="AB520" t="inlineStr"/>
+      <c r="AC520" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD520" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE520" t="inlineStr"/>
+      <c r="AF520" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG520" t="inlineStr"/>
+      <c r="AH520" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI520" t="n">
+        <v>20316</v>
+      </c>
+      <c r="AJ520" t="inlineStr">
+        <is>
+          <t>269214</t>
+        </is>
+      </c>
+      <c r="AK520" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL520" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>17661</v>
+      </c>
+      <c r="B521" t="inlineStr"/>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>70****0341</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 18:21:38</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>*0383</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N521" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P521" t="n">
+        <v>11000372996670</v>
+      </c>
+      <c r="Q521" t="n">
+        <v>1784119874839</v>
+      </c>
+      <c r="R521" t="n">
+        <v>377647234780</v>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V521" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W521" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y521" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z521" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA521" t="inlineStr"/>
+      <c r="AB521" t="inlineStr"/>
+      <c r="AC521" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD521" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE521" t="inlineStr"/>
+      <c r="AF521" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG521" t="inlineStr"/>
+      <c r="AH521" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI521" t="n">
+        <v>20383</v>
+      </c>
+      <c r="AJ521" t="inlineStr">
+        <is>
+          <t>277204</t>
+        </is>
+      </c>
+      <c r="AK521" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL521" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>17523</v>
+      </c>
+      <c r="B522" t="inlineStr"/>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>77****9882</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>18600</v>
+      </c>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 19:46:28</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>*0242</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N522" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P522" t="n">
+        <v>11000373011586</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>1784124848978</v>
+      </c>
+      <c r="R522" t="n">
+        <v>619631055262</v>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T522" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V522" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W522" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y522" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z522" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA522" t="inlineStr"/>
+      <c r="AB522" t="inlineStr"/>
+      <c r="AC522" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD522" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE522" t="inlineStr"/>
+      <c r="AF522" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG522" t="inlineStr"/>
+      <c r="AH522" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI522" t="n">
+        <v>20242</v>
+      </c>
+      <c r="AJ522" t="inlineStr">
+        <is>
+          <t>273497,269878,273810</t>
+        </is>
+      </c>
+      <c r="AK522" t="inlineStr">
+        <is>
+          <t>2084,2067,2085</t>
+        </is>
+      </c>
+      <c r="AL522" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL522"/>
+  <dimension ref="A1:AL527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79817,7 +79817,9 @@
       <c r="D507" t="n">
         <v>12300</v>
       </c>
-      <c r="E507" t="inlineStr"/>
+      <c r="E507" t="n">
+        <v>12300</v>
+      </c>
       <c r="F507" t="inlineStr">
         <is>
           <t>15-Jul-2026 06:38:13</t>
@@ -79888,7 +79890,7 @@
       </c>
       <c r="V507" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W507" t="inlineStr">
@@ -79911,15 +79913,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA507" t="inlineStr"/>
-      <c r="AB507" t="inlineStr"/>
+      <c r="AA507" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB507" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC507" t="n">
         <v>0</v>
       </c>
       <c r="AD507" t="n">
         <v>0</v>
       </c>
-      <c r="AE507" t="inlineStr"/>
+      <c r="AE507" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF507" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -79963,13 +79971,19 @@
       <c r="D508" t="n">
         <v>9000</v>
       </c>
-      <c r="E508" t="inlineStr"/>
+      <c r="E508" t="n">
+        <v>9000</v>
+      </c>
       <c r="F508" t="inlineStr">
         <is>
           <t>15-Jul-2026 07:06:53</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H508" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -80034,7 +80048,7 @@
       </c>
       <c r="V508" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W508" t="inlineStr">
@@ -80057,15 +80071,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA508" t="inlineStr"/>
-      <c r="AB508" t="inlineStr"/>
+      <c r="AA508" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB508" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC508" t="n">
         <v>0</v>
       </c>
       <c r="AD508" t="n">
         <v>0</v>
       </c>
-      <c r="AE508" t="inlineStr"/>
+      <c r="AE508" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF508" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -80109,7 +80129,9 @@
       <c r="D509" t="n">
         <v>9400</v>
       </c>
-      <c r="E509" t="inlineStr"/>
+      <c r="E509" t="n">
+        <v>9400</v>
+      </c>
       <c r="F509" t="inlineStr">
         <is>
           <t>15-Jul-2026 07:08:31</t>
@@ -80180,7 +80202,7 @@
       </c>
       <c r="V509" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W509" t="inlineStr">
@@ -80203,15 +80225,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA509" t="inlineStr"/>
-      <c r="AB509" t="inlineStr"/>
+      <c r="AA509" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB509" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC509" t="n">
         <v>0</v>
       </c>
       <c r="AD509" t="n">
         <v>0</v>
       </c>
-      <c r="AE509" t="inlineStr"/>
+      <c r="AE509" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF509" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
@@ -80255,7 +80283,9 @@
       <c r="D510" t="n">
         <v>11600</v>
       </c>
-      <c r="E510" t="inlineStr"/>
+      <c r="E510" t="n">
+        <v>11600</v>
+      </c>
       <c r="F510" t="inlineStr">
         <is>
           <t>15-Jul-2026 07:35:47</t>
@@ -80326,7 +80356,7 @@
       </c>
       <c r="V510" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W510" t="inlineStr">
@@ -80349,15 +80379,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA510" t="inlineStr"/>
-      <c r="AB510" t="inlineStr"/>
+      <c r="AA510" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB510" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC510" t="n">
         <v>0</v>
       </c>
       <c r="AD510" t="n">
         <v>0</v>
       </c>
-      <c r="AE510" t="inlineStr"/>
+      <c r="AE510" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF510" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -80401,13 +80437,19 @@
       <c r="D511" t="n">
         <v>9000</v>
       </c>
-      <c r="E511" t="inlineStr"/>
+      <c r="E511" t="n">
+        <v>9000</v>
+      </c>
       <c r="F511" t="inlineStr">
         <is>
           <t>15-Jul-2026 07:37:12</t>
         </is>
       </c>
-      <c r="G511" t="inlineStr"/>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H511" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -80472,7 +80514,7 @@
       </c>
       <c r="V511" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W511" t="inlineStr">
@@ -80495,15 +80537,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA511" t="inlineStr"/>
-      <c r="AB511" t="inlineStr"/>
+      <c r="AA511" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB511" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC511" t="n">
         <v>0</v>
       </c>
       <c r="AD511" t="n">
         <v>0</v>
       </c>
-      <c r="AE511" t="inlineStr"/>
+      <c r="AE511" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF511" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -80547,13 +80595,19 @@
       <c r="D512" t="n">
         <v>8400</v>
       </c>
-      <c r="E512" t="inlineStr"/>
+      <c r="E512" t="n">
+        <v>8400</v>
+      </c>
       <c r="F512" t="inlineStr">
         <is>
           <t>15-Jul-2026 09:13:39</t>
         </is>
       </c>
-      <c r="G512" t="inlineStr"/>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H512" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -80618,7 +80672,7 @@
       </c>
       <c r="V512" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W512" t="inlineStr">
@@ -80641,15 +80695,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA512" t="inlineStr"/>
-      <c r="AB512" t="inlineStr"/>
+      <c r="AA512" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB512" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC512" t="n">
         <v>0</v>
       </c>
       <c r="AD512" t="n">
         <v>0</v>
       </c>
-      <c r="AE512" t="inlineStr"/>
+      <c r="AE512" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF512" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -80693,13 +80753,19 @@
       <c r="D513" t="n">
         <v>9000</v>
       </c>
-      <c r="E513" t="inlineStr"/>
+      <c r="E513" t="n">
+        <v>9000</v>
+      </c>
       <c r="F513" t="inlineStr">
         <is>
           <t>15-Jul-2026 09:18:21</t>
         </is>
       </c>
-      <c r="G513" t="inlineStr"/>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H513" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -80764,7 +80830,7 @@
       </c>
       <c r="V513" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W513" t="inlineStr">
@@ -80787,15 +80853,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA513" t="inlineStr"/>
-      <c r="AB513" t="inlineStr"/>
+      <c r="AA513" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB513" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC513" t="n">
         <v>0</v>
       </c>
       <c r="AD513" t="n">
         <v>0</v>
       </c>
-      <c r="AE513" t="inlineStr"/>
+      <c r="AE513" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF513" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -80839,7 +80911,9 @@
       <c r="D514" t="n">
         <v>9400</v>
       </c>
-      <c r="E514" t="inlineStr"/>
+      <c r="E514" t="n">
+        <v>9400</v>
+      </c>
       <c r="F514" t="inlineStr">
         <is>
           <t>15-Jul-2026 10:42:37</t>
@@ -80910,7 +80984,7 @@
       </c>
       <c r="V514" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W514" t="inlineStr">
@@ -80933,15 +81007,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA514" t="inlineStr"/>
-      <c r="AB514" t="inlineStr"/>
+      <c r="AA514" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB514" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC514" t="n">
         <v>0</v>
       </c>
       <c r="AD514" t="n">
         <v>0</v>
       </c>
-      <c r="AE514" t="inlineStr"/>
+      <c r="AE514" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF514" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
@@ -80985,7 +81065,9 @@
       <c r="D515" t="n">
         <v>12300</v>
       </c>
-      <c r="E515" t="inlineStr"/>
+      <c r="E515" t="n">
+        <v>12300</v>
+      </c>
       <c r="F515" t="inlineStr">
         <is>
           <t>15-Jul-2026 10:44:51</t>
@@ -81056,7 +81138,7 @@
       </c>
       <c r="V515" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W515" t="inlineStr">
@@ -81079,15 +81161,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA515" t="inlineStr"/>
-      <c r="AB515" t="inlineStr"/>
+      <c r="AA515" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB515" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC515" t="n">
         <v>0</v>
       </c>
       <c r="AD515" t="n">
         <v>0</v>
       </c>
-      <c r="AE515" t="inlineStr"/>
+      <c r="AE515" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF515" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -81131,13 +81219,19 @@
       <c r="D516" t="n">
         <v>9000</v>
       </c>
-      <c r="E516" t="inlineStr"/>
+      <c r="E516" t="n">
+        <v>9000</v>
+      </c>
       <c r="F516" t="inlineStr">
         <is>
           <t>15-Jul-2026 13:35:56</t>
         </is>
       </c>
-      <c r="G516" t="inlineStr"/>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H516" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -81202,7 +81296,7 @@
       </c>
       <c r="V516" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W516" t="inlineStr">
@@ -81225,15 +81319,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA516" t="inlineStr"/>
-      <c r="AB516" t="inlineStr"/>
+      <c r="AA516" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB516" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC516" t="n">
         <v>0</v>
       </c>
       <c r="AD516" t="n">
         <v>0</v>
       </c>
-      <c r="AE516" t="inlineStr"/>
+      <c r="AE516" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF516" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -81277,13 +81377,19 @@
       <c r="D517" t="n">
         <v>8700</v>
       </c>
-      <c r="E517" t="inlineStr"/>
+      <c r="E517" t="n">
+        <v>8700</v>
+      </c>
       <c r="F517" t="inlineStr">
         <is>
           <t>15-Jul-2026 13:34:37</t>
         </is>
       </c>
-      <c r="G517" t="inlineStr"/>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H517" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -81348,7 +81454,7 @@
       </c>
       <c r="V517" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W517" t="inlineStr">
@@ -81371,15 +81477,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA517" t="inlineStr"/>
-      <c r="AB517" t="inlineStr"/>
+      <c r="AA517" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB517" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC517" t="n">
         <v>0</v>
       </c>
       <c r="AD517" t="n">
         <v>0</v>
       </c>
-      <c r="AE517" t="inlineStr"/>
+      <c r="AE517" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF517" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -81423,13 +81535,19 @@
       <c r="D518" t="n">
         <v>9000</v>
       </c>
-      <c r="E518" t="inlineStr"/>
+      <c r="E518" t="n">
+        <v>9000</v>
+      </c>
       <c r="F518" t="inlineStr">
         <is>
           <t>15-Jul-2026 14:52:10</t>
         </is>
       </c>
-      <c r="G518" t="inlineStr"/>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H518" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -81494,7 +81612,7 @@
       </c>
       <c r="V518" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W518" t="inlineStr">
@@ -81517,15 +81635,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA518" t="inlineStr"/>
-      <c r="AB518" t="inlineStr"/>
+      <c r="AA518" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB518" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC518" t="n">
         <v>0</v>
       </c>
       <c r="AD518" t="n">
         <v>0</v>
       </c>
-      <c r="AE518" t="inlineStr"/>
+      <c r="AE518" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF518" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -81569,13 +81693,19 @@
       <c r="D519" t="n">
         <v>8400</v>
       </c>
-      <c r="E519" t="inlineStr"/>
+      <c r="E519" t="n">
+        <v>8400</v>
+      </c>
       <c r="F519" t="inlineStr">
         <is>
           <t>15-Jul-2026 15:36:05</t>
         </is>
       </c>
-      <c r="G519" t="inlineStr"/>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H519" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -81640,7 +81770,7 @@
       </c>
       <c r="V519" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W519" t="inlineStr">
@@ -81663,15 +81793,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA519" t="inlineStr"/>
-      <c r="AB519" t="inlineStr"/>
+      <c r="AA519" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB519" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC519" t="n">
         <v>0</v>
       </c>
       <c r="AD519" t="n">
         <v>0</v>
       </c>
-      <c r="AE519" t="inlineStr"/>
+      <c r="AE519" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF519" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -81715,13 +81851,19 @@
       <c r="D520" t="n">
         <v>7250</v>
       </c>
-      <c r="E520" t="inlineStr"/>
+      <c r="E520" t="n">
+        <v>7250</v>
+      </c>
       <c r="F520" t="inlineStr">
         <is>
           <t>15-Jul-2026 15:41:19</t>
         </is>
       </c>
-      <c r="G520" t="inlineStr"/>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H520" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -81786,7 +81928,7 @@
       </c>
       <c r="V520" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W520" t="inlineStr">
@@ -81809,15 +81951,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA520" t="inlineStr"/>
-      <c r="AB520" t="inlineStr"/>
+      <c r="AA520" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB520" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC520" t="n">
         <v>0</v>
       </c>
       <c r="AD520" t="n">
         <v>0</v>
       </c>
-      <c r="AE520" t="inlineStr"/>
+      <c r="AE520" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF520" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -81861,13 +82009,19 @@
       <c r="D521" t="n">
         <v>7250</v>
       </c>
-      <c r="E521" t="inlineStr"/>
+      <c r="E521" t="n">
+        <v>7250</v>
+      </c>
       <c r="F521" t="inlineStr">
         <is>
           <t>15-Jul-2026 18:21:38</t>
         </is>
       </c>
-      <c r="G521" t="inlineStr"/>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H521" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -81932,7 +82086,7 @@
       </c>
       <c r="V521" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W521" t="inlineStr">
@@ -81955,15 +82109,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA521" t="inlineStr"/>
-      <c r="AB521" t="inlineStr"/>
+      <c r="AA521" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB521" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC521" t="n">
         <v>0</v>
       </c>
       <c r="AD521" t="n">
         <v>0</v>
       </c>
-      <c r="AE521" t="inlineStr"/>
+      <c r="AE521" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF521" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -82007,13 +82167,19 @@
       <c r="D522" t="n">
         <v>18600</v>
       </c>
-      <c r="E522" t="inlineStr"/>
+      <c r="E522" t="n">
+        <v>18600</v>
+      </c>
       <c r="F522" t="inlineStr">
         <is>
           <t>15-Jul-2026 19:46:28</t>
         </is>
       </c>
-      <c r="G522" t="inlineStr"/>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 18:46:23</t>
+        </is>
+      </c>
       <c r="H522" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -82078,7 +82244,7 @@
       </c>
       <c r="V522" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W522" t="inlineStr">
@@ -82101,15 +82267,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA522" t="inlineStr"/>
-      <c r="AB522" t="inlineStr"/>
+      <c r="AA522" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="AB522" t="n">
+        <v>40.18</v>
+      </c>
       <c r="AC522" t="n">
         <v>0</v>
       </c>
       <c r="AD522" t="n">
         <v>0</v>
       </c>
-      <c r="AE522" t="inlineStr"/>
+      <c r="AE522" t="n">
+        <v>263.38</v>
+      </c>
       <c r="AF522" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -82135,6 +82307,728 @@
         </is>
       </c>
       <c r="AL522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>17573</v>
+      </c>
+      <c r="B523" t="inlineStr"/>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>96****5143</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 09:10:49</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>*0292</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N523" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P523" t="n">
+        <v>11000373097760</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>1784173225479</v>
+      </c>
+      <c r="R523" t="n">
+        <v>983036771377</v>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T523" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V523" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W523" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y523" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z523" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA523" t="inlineStr"/>
+      <c r="AB523" t="inlineStr"/>
+      <c r="AC523" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD523" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE523" t="inlineStr"/>
+      <c r="AF523" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG523" t="inlineStr"/>
+      <c r="AH523" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI523" t="n">
+        <v>20292</v>
+      </c>
+      <c r="AJ523" t="inlineStr">
+        <is>
+          <t>272415</t>
+        </is>
+      </c>
+      <c r="AK523" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL523" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>15960</v>
+      </c>
+      <c r="B524" t="inlineStr"/>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>89****4468</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 11:23:39</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>*8680</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N524" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P524" t="n">
+        <v>11000373132456</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>1784181209075</v>
+      </c>
+      <c r="R524" t="n">
+        <v>142055713821</v>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T524" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V524" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W524" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y524" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z524" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA524" t="inlineStr"/>
+      <c r="AB524" t="inlineStr"/>
+      <c r="AC524" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD524" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE524" t="inlineStr"/>
+      <c r="AF524" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG524" t="inlineStr"/>
+      <c r="AH524" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI524" t="n">
+        <v>18680</v>
+      </c>
+      <c r="AJ524" t="inlineStr">
+        <is>
+          <t>273713</t>
+        </is>
+      </c>
+      <c r="AK524" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL524" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>17043</v>
+      </c>
+      <c r="B525" t="inlineStr"/>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>76****8914</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E525" t="inlineStr"/>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 11:53:37</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr"/>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>*8665</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N525" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P525" t="n">
+        <v>11000373141841</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>1784182897436</v>
+      </c>
+      <c r="R525" t="n">
+        <v>619722026199</v>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T525" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V525" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W525" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y525" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z525" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA525" t="inlineStr"/>
+      <c r="AB525" t="inlineStr"/>
+      <c r="AC525" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD525" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE525" t="inlineStr"/>
+      <c r="AF525" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG525" t="inlineStr"/>
+      <c r="AH525" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI525" t="n">
+        <v>18665</v>
+      </c>
+      <c r="AJ525" t="inlineStr">
+        <is>
+          <t>273602</t>
+        </is>
+      </c>
+      <c r="AK525" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>17565</v>
+      </c>
+      <c r="B526" t="inlineStr"/>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>98****9526</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 12:07:38</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>*0284</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N526" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P526" t="n">
+        <v>11000373148327</v>
+      </c>
+      <c r="Q526" t="n">
+        <v>1784183847348</v>
+      </c>
+      <c r="R526" t="n">
+        <v>266781393508</v>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V526" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W526" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y526" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z526" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA526" t="inlineStr"/>
+      <c r="AB526" t="inlineStr"/>
+      <c r="AC526" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD526" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE526" t="inlineStr"/>
+      <c r="AF526" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG526" t="inlineStr"/>
+      <c r="AH526" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI526" t="n">
+        <v>20284</v>
+      </c>
+      <c r="AJ526" t="inlineStr">
+        <is>
+          <t>269289</t>
+        </is>
+      </c>
+      <c r="AK526" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL526" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>17617</v>
+      </c>
+      <c r="B527" t="inlineStr"/>
+      <c r="C527" t="inlineStr"/>
+      <c r="D527" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 14:35:35</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>*0336</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N527" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P527" t="n">
+        <v>11000373198795</v>
+      </c>
+      <c r="Q527" t="n">
+        <v>1784192638889</v>
+      </c>
+      <c r="R527" t="n">
+        <v>790239938877</v>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T527" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V527" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W527" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y527" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z527" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA527" t="inlineStr"/>
+      <c r="AB527" t="inlineStr"/>
+      <c r="AC527" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD527" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE527" t="inlineStr"/>
+      <c r="AF527" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG527" t="inlineStr"/>
+      <c r="AH527" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI527" t="n">
+        <v>20336</v>
+      </c>
+      <c r="AJ527" t="inlineStr">
+        <is>
+          <t>271337</t>
+        </is>
+      </c>
+      <c r="AK527" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL527" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL527"/>
+  <dimension ref="A1:AL528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82321,7 +82321,9 @@
       <c r="D523" t="n">
         <v>8700</v>
       </c>
-      <c r="E523" t="inlineStr"/>
+      <c r="E523" t="n">
+        <v>8700</v>
+      </c>
       <c r="F523" t="inlineStr">
         <is>
           <t>16-Jul-2026 09:10:49</t>
@@ -82392,7 +82394,7 @@
       </c>
       <c r="V523" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W523" t="inlineStr">
@@ -82415,15 +82417,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA523" t="inlineStr"/>
-      <c r="AB523" t="inlineStr"/>
+      <c r="AA523" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB523" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC523" t="n">
         <v>0</v>
       </c>
       <c r="AD523" t="n">
         <v>0</v>
       </c>
-      <c r="AE523" t="inlineStr"/>
+      <c r="AE523" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF523" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -82467,7 +82475,9 @@
       <c r="D524" t="n">
         <v>9000</v>
       </c>
-      <c r="E524" t="inlineStr"/>
+      <c r="E524" t="n">
+        <v>9000</v>
+      </c>
       <c r="F524" t="inlineStr">
         <is>
           <t>16-Jul-2026 11:23:39</t>
@@ -82538,7 +82548,7 @@
       </c>
       <c r="V524" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W524" t="inlineStr">
@@ -82561,15 +82571,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA524" t="inlineStr"/>
-      <c r="AB524" t="inlineStr"/>
+      <c r="AA524" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB524" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC524" t="n">
         <v>0</v>
       </c>
       <c r="AD524" t="n">
         <v>0</v>
       </c>
-      <c r="AE524" t="inlineStr"/>
+      <c r="AE524" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF524" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -82613,7 +82629,9 @@
       <c r="D525" t="n">
         <v>9000</v>
       </c>
-      <c r="E525" t="inlineStr"/>
+      <c r="E525" t="n">
+        <v>9000</v>
+      </c>
       <c r="F525" t="inlineStr">
         <is>
           <t>16-Jul-2026 11:53:37</t>
@@ -82684,7 +82702,7 @@
       </c>
       <c r="V525" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W525" t="inlineStr">
@@ -82707,15 +82725,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA525" t="inlineStr"/>
-      <c r="AB525" t="inlineStr"/>
+      <c r="AA525" t="n">
+        <v>108</v>
+      </c>
+      <c r="AB525" t="n">
+        <v>19.44</v>
+      </c>
       <c r="AC525" t="n">
         <v>0</v>
       </c>
       <c r="AD525" t="n">
         <v>0</v>
       </c>
-      <c r="AE525" t="inlineStr"/>
+      <c r="AE525" t="n">
+        <v>127.44</v>
+      </c>
       <c r="AF525" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -82755,7 +82779,9 @@
       <c r="D526" t="n">
         <v>7250</v>
       </c>
-      <c r="E526" t="inlineStr"/>
+      <c r="E526" t="n">
+        <v>7250</v>
+      </c>
       <c r="F526" t="inlineStr">
         <is>
           <t>16-Jul-2026 12:07:38</t>
@@ -82826,7 +82852,7 @@
       </c>
       <c r="V526" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W526" t="inlineStr">
@@ -82849,15 +82875,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA526" t="inlineStr"/>
-      <c r="AB526" t="inlineStr"/>
+      <c r="AA526" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB526" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC526" t="n">
         <v>0</v>
       </c>
       <c r="AD526" t="n">
         <v>0</v>
       </c>
-      <c r="AE526" t="inlineStr"/>
+      <c r="AE526" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF526" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -82897,7 +82929,9 @@
       <c r="D527" t="n">
         <v>8400</v>
       </c>
-      <c r="E527" t="inlineStr"/>
+      <c r="E527" t="n">
+        <v>8400</v>
+      </c>
       <c r="F527" t="inlineStr">
         <is>
           <t>16-Jul-2026 14:35:35</t>
@@ -82968,7 +83002,7 @@
       </c>
       <c r="V527" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W527" t="inlineStr">
@@ -82991,15 +83025,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA527" t="inlineStr"/>
-      <c r="AB527" t="inlineStr"/>
+      <c r="AA527" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB527" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC527" t="n">
         <v>0</v>
       </c>
       <c r="AD527" t="n">
         <v>0</v>
       </c>
-      <c r="AE527" t="inlineStr"/>
+      <c r="AE527" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF527" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -83025,6 +83065,152 @@
         </is>
       </c>
       <c r="AL527" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>17633</v>
+      </c>
+      <c r="B528" t="inlineStr"/>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>73****3777</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>17-Jul-2026 17:16:04</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>*0377</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N528" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P528" t="n">
+        <v>11000373484907</v>
+      </c>
+      <c r="Q528" t="n">
+        <v>1784288751850</v>
+      </c>
+      <c r="R528" t="n">
+        <v>760702566589</v>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T528" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V528" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W528" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y528" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z528" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA528" t="inlineStr"/>
+      <c r="AB528" t="inlineStr"/>
+      <c r="AC528" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD528" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE528" t="inlineStr"/>
+      <c r="AF528" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG528" t="inlineStr"/>
+      <c r="AH528" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI528" t="n">
+        <v>20377</v>
+      </c>
+      <c r="AJ528" t="inlineStr">
+        <is>
+          <t>277205</t>
+        </is>
+      </c>
+      <c r="AK528" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL528" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL530"/>
+  <dimension ref="A1:AL532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83540,6 +83540,298 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>17163</v>
+      </c>
+      <c r="B531" t="inlineStr"/>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>82****8795</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>18-Jul-2026 23:36:28</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>*9878</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N531" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P531" t="n">
+        <v>11000373792011</v>
+      </c>
+      <c r="Q531" t="n">
+        <v>1784397874065</v>
+      </c>
+      <c r="R531" t="n">
+        <v>656573924792</v>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V531" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W531" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y531" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z531" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA531" t="inlineStr"/>
+      <c r="AB531" t="inlineStr"/>
+      <c r="AC531" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD531" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE531" t="inlineStr"/>
+      <c r="AF531" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG531" t="inlineStr"/>
+      <c r="AH531" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI531" t="n">
+        <v>19878</v>
+      </c>
+      <c r="AJ531" t="inlineStr">
+        <is>
+          <t>269357</t>
+        </is>
+      </c>
+      <c r="AK531" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL531" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>15974</v>
+      </c>
+      <c r="B532" t="inlineStr"/>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>99****4605</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>19-Jul-2026 12:14:18</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>*9352</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N532" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P532" t="n">
+        <v>11000373829949</v>
+      </c>
+      <c r="Q532" t="n">
+        <v>1784443438932</v>
+      </c>
+      <c r="R532" t="n">
+        <v>495905674100</v>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T532" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V532" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W532" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y532" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z532" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA532" t="inlineStr"/>
+      <c r="AB532" t="inlineStr"/>
+      <c r="AC532" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD532" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE532" t="inlineStr"/>
+      <c r="AF532" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG532" t="inlineStr"/>
+      <c r="AH532" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI532" t="n">
+        <v>19352</v>
+      </c>
+      <c r="AJ532" t="inlineStr">
+        <is>
+          <t>276141</t>
+        </is>
+      </c>
+      <c r="AK532" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL532" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL532"/>
+  <dimension ref="A1:AL534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83261,13 +83261,19 @@
       <c r="D529" t="n">
         <v>6500</v>
       </c>
-      <c r="E529" t="inlineStr"/>
+      <c r="E529" t="n">
+        <v>6500</v>
+      </c>
       <c r="F529" t="inlineStr">
         <is>
           <t>18-Jul-2026 09:19:43</t>
         </is>
       </c>
-      <c r="G529" t="inlineStr"/>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>20-Jul-2026 19:00:28</t>
+        </is>
+      </c>
       <c r="H529" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -83332,7 +83338,7 @@
       </c>
       <c r="V529" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W529" t="inlineStr">
@@ -83355,15 +83361,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA529" t="inlineStr"/>
-      <c r="AB529" t="inlineStr"/>
+      <c r="AA529" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB529" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC529" t="n">
         <v>0</v>
       </c>
       <c r="AD529" t="n">
         <v>0</v>
       </c>
-      <c r="AE529" t="inlineStr"/>
+      <c r="AE529" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF529" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -83407,7 +83419,9 @@
       <c r="D530" t="n">
         <v>11600</v>
       </c>
-      <c r="E530" t="inlineStr"/>
+      <c r="E530" t="n">
+        <v>11600</v>
+      </c>
       <c r="F530" t="inlineStr">
         <is>
           <t>18-Jul-2026 10:46:55</t>
@@ -83478,7 +83492,7 @@
       </c>
       <c r="V530" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W530" t="inlineStr">
@@ -83501,15 +83515,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA530" t="inlineStr"/>
-      <c r="AB530" t="inlineStr"/>
+      <c r="AA530" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB530" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC530" t="n">
         <v>0</v>
       </c>
       <c r="AD530" t="n">
         <v>0</v>
       </c>
-      <c r="AE530" t="inlineStr"/>
+      <c r="AE530" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF530" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -83553,13 +83573,19 @@
       <c r="D531" t="n">
         <v>7250</v>
       </c>
-      <c r="E531" t="inlineStr"/>
+      <c r="E531" t="n">
+        <v>7250</v>
+      </c>
       <c r="F531" t="inlineStr">
         <is>
           <t>18-Jul-2026 23:36:28</t>
         </is>
       </c>
-      <c r="G531" t="inlineStr"/>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>20-Jul-2026 19:00:28</t>
+        </is>
+      </c>
       <c r="H531" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -83624,7 +83650,7 @@
       </c>
       <c r="V531" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W531" t="inlineStr">
@@ -83647,15 +83673,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA531" t="inlineStr"/>
-      <c r="AB531" t="inlineStr"/>
+      <c r="AA531" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB531" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC531" t="n">
         <v>0</v>
       </c>
       <c r="AD531" t="n">
         <v>0</v>
       </c>
-      <c r="AE531" t="inlineStr"/>
+      <c r="AE531" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF531" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -83699,7 +83731,9 @@
       <c r="D532" t="n">
         <v>12300</v>
       </c>
-      <c r="E532" t="inlineStr"/>
+      <c r="E532" t="n">
+        <v>12300</v>
+      </c>
       <c r="F532" t="inlineStr">
         <is>
           <t>19-Jul-2026 12:14:18</t>
@@ -83770,7 +83804,7 @@
       </c>
       <c r="V532" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W532" t="inlineStr">
@@ -83793,15 +83827,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA532" t="inlineStr"/>
-      <c r="AB532" t="inlineStr"/>
+      <c r="AA532" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB532" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC532" t="n">
         <v>0</v>
       </c>
       <c r="AD532" t="n">
         <v>0</v>
       </c>
-      <c r="AE532" t="inlineStr"/>
+      <c r="AE532" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF532" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -83827,6 +83867,298 @@
         </is>
       </c>
       <c r="AL532" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>17569</v>
+      </c>
+      <c r="B533" t="inlineStr"/>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>94****7600</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>9400</v>
+      </c>
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>20-Jul-2026 06:37:47</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>*0288</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N533" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P533" t="n">
+        <v>11000373932307</v>
+      </c>
+      <c r="Q533" t="n">
+        <v>1784509645092</v>
+      </c>
+      <c r="R533" t="n">
+        <v>656708555309</v>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V533" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W533" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y533" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z533" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA533" t="inlineStr"/>
+      <c r="AB533" t="inlineStr"/>
+      <c r="AC533" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD533" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE533" t="inlineStr"/>
+      <c r="AF533" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG533" t="inlineStr"/>
+      <c r="AH533" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI533" t="n">
+        <v>20288</v>
+      </c>
+      <c r="AJ533" t="inlineStr">
+        <is>
+          <t>274740</t>
+        </is>
+      </c>
+      <c r="AK533" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="AL533" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>17568</v>
+      </c>
+      <c r="B534" t="inlineStr"/>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>94****7600</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>20-Jul-2026 06:43:50</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>*0287</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N534" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P534" t="n">
+        <v>11000373932413</v>
+      </c>
+      <c r="Q534" t="n">
+        <v>1784510019670</v>
+      </c>
+      <c r="R534" t="n">
+        <v>656703552786</v>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V534" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W534" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y534" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z534" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA534" t="inlineStr"/>
+      <c r="AB534" t="inlineStr"/>
+      <c r="AC534" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD534" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE534" t="inlineStr"/>
+      <c r="AF534" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG534" t="inlineStr"/>
+      <c r="AH534" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI534" t="n">
+        <v>20287</v>
+      </c>
+      <c r="AJ534" t="inlineStr">
+        <is>
+          <t>271331</t>
+        </is>
+      </c>
+      <c r="AK534" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL534" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL534"/>
+  <dimension ref="A1:AL535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84164,6 +84164,152 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>17464</v>
+      </c>
+      <c r="B535" t="inlineStr"/>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>81****4454</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>20-Jul-2026 21:46:59</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>*0147</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N535" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P535" t="n">
+        <v>11000374170898</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>1784564204653</v>
+      </c>
+      <c r="R535" t="n">
+        <v>177810809921</v>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V535" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W535" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y535" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z535" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA535" t="inlineStr"/>
+      <c r="AB535" t="inlineStr"/>
+      <c r="AC535" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD535" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE535" t="inlineStr"/>
+      <c r="AF535" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG535" t="inlineStr"/>
+      <c r="AH535" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI535" t="n">
+        <v>20147</v>
+      </c>
+      <c r="AJ535" t="inlineStr">
+        <is>
+          <t>269188</t>
+        </is>
+      </c>
+      <c r="AK535" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL535" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL535"/>
+  <dimension ref="A1:AL543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83885,7 +83885,9 @@
       <c r="D533" t="n">
         <v>9400</v>
       </c>
-      <c r="E533" t="inlineStr"/>
+      <c r="E533" t="n">
+        <v>9400</v>
+      </c>
       <c r="F533" t="inlineStr">
         <is>
           <t>20-Jul-2026 06:37:47</t>
@@ -83956,7 +83958,7 @@
       </c>
       <c r="V533" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W533" t="inlineStr">
@@ -83979,15 +83981,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA533" t="inlineStr"/>
-      <c r="AB533" t="inlineStr"/>
+      <c r="AA533" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB533" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC533" t="n">
         <v>0</v>
       </c>
       <c r="AD533" t="n">
         <v>0</v>
       </c>
-      <c r="AE533" t="inlineStr"/>
+      <c r="AE533" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF533" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
@@ -84031,7 +84039,9 @@
       <c r="D534" t="n">
         <v>8400</v>
       </c>
-      <c r="E534" t="inlineStr"/>
+      <c r="E534" t="n">
+        <v>8400</v>
+      </c>
       <c r="F534" t="inlineStr">
         <is>
           <t>20-Jul-2026 06:43:50</t>
@@ -84102,7 +84112,7 @@
       </c>
       <c r="V534" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W534" t="inlineStr">
@@ -84125,15 +84135,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA534" t="inlineStr"/>
-      <c r="AB534" t="inlineStr"/>
+      <c r="AA534" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB534" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC534" t="n">
         <v>0</v>
       </c>
       <c r="AD534" t="n">
         <v>0</v>
       </c>
-      <c r="AE534" t="inlineStr"/>
+      <c r="AE534" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF534" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -84177,7 +84193,9 @@
       <c r="D535" t="n">
         <v>7250</v>
       </c>
-      <c r="E535" t="inlineStr"/>
+      <c r="E535" t="n">
+        <v>7250</v>
+      </c>
       <c r="F535" t="inlineStr">
         <is>
           <t>20-Jul-2026 21:46:59</t>
@@ -84248,7 +84266,7 @@
       </c>
       <c r="V535" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W535" t="inlineStr">
@@ -84271,15 +84289,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA535" t="inlineStr"/>
-      <c r="AB535" t="inlineStr"/>
+      <c r="AA535" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB535" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC535" t="n">
         <v>0</v>
       </c>
       <c r="AD535" t="n">
         <v>0</v>
       </c>
-      <c r="AE535" t="inlineStr"/>
+      <c r="AE535" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF535" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -84305,6 +84329,1166 @@
         </is>
       </c>
       <c r="AL535" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>17401</v>
+      </c>
+      <c r="B536" t="inlineStr"/>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>93****7628</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 11:29:01</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>*0135</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N536" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P536" t="n">
+        <v>11000374269061</v>
+      </c>
+      <c r="Q536" t="n">
+        <v>1784613431057</v>
+      </c>
+      <c r="R536" t="n">
+        <v>620245023420</v>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V536" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W536" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y536" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z536" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA536" t="inlineStr"/>
+      <c r="AB536" t="inlineStr"/>
+      <c r="AC536" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD536" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE536" t="inlineStr"/>
+      <c r="AF536" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG536" t="inlineStr"/>
+      <c r="AH536" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI536" t="n">
+        <v>20135</v>
+      </c>
+      <c r="AJ536" t="inlineStr">
+        <is>
+          <t>269241</t>
+        </is>
+      </c>
+      <c r="AK536" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>17423</v>
+      </c>
+      <c r="B537" t="inlineStr"/>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>90****5456</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E537" t="inlineStr"/>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 11:32:08</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>*0141</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N537" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P537" t="n">
+        <v>11000374270731</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>1784613682204</v>
+      </c>
+      <c r="R537" t="n">
+        <v>994943925028</v>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T537" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V537" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W537" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y537" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z537" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA537" t="inlineStr"/>
+      <c r="AB537" t="inlineStr"/>
+      <c r="AC537" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD537" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE537" t="inlineStr"/>
+      <c r="AF537" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG537" t="inlineStr"/>
+      <c r="AH537" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI537" t="n">
+        <v>20141</v>
+      </c>
+      <c r="AJ537" t="inlineStr">
+        <is>
+          <t>269204</t>
+        </is>
+      </c>
+      <c r="AK537" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL537" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>17424</v>
+      </c>
+      <c r="B538" t="inlineStr"/>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>90****5456</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 11:33:06</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>*0107</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N538" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P538" t="n">
+        <v>11000374271394</v>
+      </c>
+      <c r="Q538" t="n">
+        <v>1784613776249</v>
+      </c>
+      <c r="R538" t="n">
+        <v>543334519190</v>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V538" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W538" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y538" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z538" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA538" t="inlineStr"/>
+      <c r="AB538" t="inlineStr"/>
+      <c r="AC538" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD538" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE538" t="inlineStr"/>
+      <c r="AF538" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG538" t="inlineStr"/>
+      <c r="AH538" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI538" t="n">
+        <v>20107</v>
+      </c>
+      <c r="AJ538" t="inlineStr">
+        <is>
+          <t>268815</t>
+        </is>
+      </c>
+      <c r="AK538" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="AL538" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>16831</v>
+      </c>
+      <c r="B539" t="inlineStr"/>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>90****3866</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 11:38:20</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>*8157</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N539" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P539" t="n">
+        <v>11000374272652</v>
+      </c>
+      <c r="Q539" t="n">
+        <v>1784614007034</v>
+      </c>
+      <c r="R539" t="n">
+        <v>620221019147</v>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T539" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V539" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W539" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y539" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z539" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA539" t="inlineStr"/>
+      <c r="AB539" t="inlineStr"/>
+      <c r="AC539" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD539" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE539" t="inlineStr"/>
+      <c r="AF539" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG539" t="inlineStr"/>
+      <c r="AH539" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI539" t="n">
+        <v>18157</v>
+      </c>
+      <c r="AJ539" t="inlineStr">
+        <is>
+          <t>271246</t>
+        </is>
+      </c>
+      <c r="AK539" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>17590</v>
+      </c>
+      <c r="B540" t="inlineStr"/>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>83****3772</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 11:46:18</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>*0309</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N540" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P540" t="n">
+        <v>11000374273904</v>
+      </c>
+      <c r="Q540" t="n">
+        <v>1784614556907</v>
+      </c>
+      <c r="R540" t="n">
+        <v>394620749288</v>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V540" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W540" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y540" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z540" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA540" t="inlineStr"/>
+      <c r="AB540" t="inlineStr"/>
+      <c r="AC540" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD540" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE540" t="inlineStr"/>
+      <c r="AF540" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG540" t="inlineStr"/>
+      <c r="AH540" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI540" t="n">
+        <v>20309</v>
+      </c>
+      <c r="AJ540" t="inlineStr">
+        <is>
+          <t>269215</t>
+        </is>
+      </c>
+      <c r="AK540" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL540" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>17562</v>
+      </c>
+      <c r="B541" t="inlineStr"/>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>83****1458</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 15:22:03</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>*0281</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N541" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P541" t="n">
+        <v>11000374323565</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>1784627435926</v>
+      </c>
+      <c r="R541" t="n">
+        <v>883328878441</v>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V541" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W541" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y541" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z541" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA541" t="inlineStr"/>
+      <c r="AB541" t="inlineStr"/>
+      <c r="AC541" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD541" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE541" t="inlineStr"/>
+      <c r="AF541" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG541" t="inlineStr"/>
+      <c r="AH541" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI541" t="n">
+        <v>20281</v>
+      </c>
+      <c r="AJ541" t="inlineStr">
+        <is>
+          <t>269220</t>
+        </is>
+      </c>
+      <c r="AK541" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL541" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>16966</v>
+      </c>
+      <c r="B542" t="inlineStr"/>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>63****3349</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 16:08:19</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr"/>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>*8059</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N542" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P542" t="n">
+        <v>11000374330041</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>1784630283155</v>
+      </c>
+      <c r="R542" t="n">
+        <v>924627519371</v>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T542" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V542" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W542" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y542" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z542" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA542" t="inlineStr"/>
+      <c r="AB542" t="inlineStr"/>
+      <c r="AC542" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD542" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE542" t="inlineStr"/>
+      <c r="AF542" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG542" t="inlineStr"/>
+      <c r="AH542" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI542" t="n">
+        <v>18059</v>
+      </c>
+      <c r="AJ542" t="inlineStr">
+        <is>
+          <t>266778</t>
+        </is>
+      </c>
+      <c r="AK542" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="AL542" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>17201</v>
+      </c>
+      <c r="B543" t="inlineStr"/>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>94****2534</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 16:47:48</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>*9915</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N543" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P543" t="n">
+        <v>11000374344315</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>1784632510787</v>
+      </c>
+      <c r="R543" t="n">
+        <v>881128805043</v>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V543" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W543" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y543" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z543" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA543" t="inlineStr"/>
+      <c r="AB543" t="inlineStr"/>
+      <c r="AC543" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD543" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE543" t="inlineStr"/>
+      <c r="AF543" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG543" t="inlineStr"/>
+      <c r="AH543" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI543" t="n">
+        <v>19915</v>
+      </c>
+      <c r="AJ543" t="inlineStr">
+        <is>
+          <t>271252</t>
+        </is>
+      </c>
+      <c r="AK543" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL543" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL543"/>
+  <dimension ref="A1:AL557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84047,7 +84047,11 @@
           <t>20-Jul-2026 06:43:50</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr"/>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 18:50:53</t>
+        </is>
+      </c>
       <c r="H534" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -84112,7 +84116,7 @@
       </c>
       <c r="V534" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W534" t="inlineStr">
@@ -84201,7 +84205,11 @@
           <t>20-Jul-2026 21:46:59</t>
         </is>
       </c>
-      <c r="G535" t="inlineStr"/>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>21-Jul-2026 18:50:53</t>
+        </is>
+      </c>
       <c r="H535" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -84266,7 +84274,7 @@
       </c>
       <c r="V535" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W535" t="inlineStr">
@@ -84347,13 +84355,19 @@
       <c r="D536" t="n">
         <v>7250</v>
       </c>
-      <c r="E536" t="inlineStr"/>
+      <c r="E536" t="n">
+        <v>7250</v>
+      </c>
       <c r="F536" t="inlineStr">
         <is>
           <t>21-Jul-2026 11:29:01</t>
         </is>
       </c>
-      <c r="G536" t="inlineStr"/>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 18:45:58</t>
+        </is>
+      </c>
       <c r="H536" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -84418,7 +84432,7 @@
       </c>
       <c r="V536" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W536" t="inlineStr">
@@ -84441,15 +84455,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA536" t="inlineStr"/>
-      <c r="AB536" t="inlineStr"/>
+      <c r="AA536" t="n">
+        <v>87</v>
+      </c>
+      <c r="AB536" t="n">
+        <v>15.66</v>
+      </c>
       <c r="AC536" t="n">
         <v>0</v>
       </c>
       <c r="AD536" t="n">
         <v>0</v>
       </c>
-      <c r="AE536" t="inlineStr"/>
+      <c r="AE536" t="n">
+        <v>102.66</v>
+      </c>
       <c r="AF536" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -84489,13 +84509,19 @@
       <c r="D537" t="n">
         <v>7250</v>
       </c>
-      <c r="E537" t="inlineStr"/>
+      <c r="E537" t="n">
+        <v>7250</v>
+      </c>
       <c r="F537" t="inlineStr">
         <is>
           <t>21-Jul-2026 11:32:08</t>
         </is>
       </c>
-      <c r="G537" t="inlineStr"/>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 18:45:58</t>
+        </is>
+      </c>
       <c r="H537" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -84560,7 +84586,7 @@
       </c>
       <c r="V537" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W537" t="inlineStr">
@@ -84583,15 +84609,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA537" t="inlineStr"/>
-      <c r="AB537" t="inlineStr"/>
+      <c r="AA537" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB537" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC537" t="n">
         <v>0</v>
       </c>
       <c r="AD537" t="n">
         <v>0</v>
       </c>
-      <c r="AE537" t="inlineStr"/>
+      <c r="AE537" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF537" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -84635,13 +84667,19 @@
       <c r="D538" t="n">
         <v>6500</v>
       </c>
-      <c r="E538" t="inlineStr"/>
+      <c r="E538" t="n">
+        <v>6500</v>
+      </c>
       <c r="F538" t="inlineStr">
         <is>
           <t>21-Jul-2026 11:33:06</t>
         </is>
       </c>
-      <c r="G538" t="inlineStr"/>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 18:45:58</t>
+        </is>
+      </c>
       <c r="H538" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -84706,7 +84744,7 @@
       </c>
       <c r="V538" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W538" t="inlineStr">
@@ -84729,15 +84767,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA538" t="inlineStr"/>
-      <c r="AB538" t="inlineStr"/>
+      <c r="AA538" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB538" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC538" t="n">
         <v>0</v>
       </c>
       <c r="AD538" t="n">
         <v>0</v>
       </c>
-      <c r="AE538" t="inlineStr"/>
+      <c r="AE538" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF538" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -84781,13 +84825,19 @@
       <c r="D539" t="n">
         <v>8400</v>
       </c>
-      <c r="E539" t="inlineStr"/>
+      <c r="E539" t="n">
+        <v>8400</v>
+      </c>
       <c r="F539" t="inlineStr">
         <is>
           <t>21-Jul-2026 11:38:20</t>
         </is>
       </c>
-      <c r="G539" t="inlineStr"/>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 18:45:58</t>
+        </is>
+      </c>
       <c r="H539" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -84852,7 +84902,7 @@
       </c>
       <c r="V539" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W539" t="inlineStr">
@@ -84875,15 +84925,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA539" t="inlineStr"/>
-      <c r="AB539" t="inlineStr"/>
+      <c r="AA539" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="AB539" t="n">
+        <v>18.14</v>
+      </c>
       <c r="AC539" t="n">
         <v>0</v>
       </c>
       <c r="AD539" t="n">
         <v>0</v>
       </c>
-      <c r="AE539" t="inlineStr"/>
+      <c r="AE539" t="n">
+        <v>118.94</v>
+      </c>
       <c r="AF539" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -84923,13 +84979,19 @@
       <c r="D540" t="n">
         <v>7250</v>
       </c>
-      <c r="E540" t="inlineStr"/>
+      <c r="E540" t="n">
+        <v>7250</v>
+      </c>
       <c r="F540" t="inlineStr">
         <is>
           <t>21-Jul-2026 11:46:18</t>
         </is>
       </c>
-      <c r="G540" t="inlineStr"/>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 18:45:58</t>
+        </is>
+      </c>
       <c r="H540" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -84994,7 +85056,7 @@
       </c>
       <c r="V540" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W540" t="inlineStr">
@@ -85017,15 +85079,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA540" t="inlineStr"/>
-      <c r="AB540" t="inlineStr"/>
+      <c r="AA540" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB540" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC540" t="n">
         <v>0</v>
       </c>
       <c r="AD540" t="n">
         <v>0</v>
       </c>
-      <c r="AE540" t="inlineStr"/>
+      <c r="AE540" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF540" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -85069,13 +85137,19 @@
       <c r="D541" t="n">
         <v>7250</v>
       </c>
-      <c r="E541" t="inlineStr"/>
+      <c r="E541" t="n">
+        <v>7250</v>
+      </c>
       <c r="F541" t="inlineStr">
         <is>
           <t>21-Jul-2026 15:22:03</t>
         </is>
       </c>
-      <c r="G541" t="inlineStr"/>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 18:45:58</t>
+        </is>
+      </c>
       <c r="H541" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -85140,7 +85214,7 @@
       </c>
       <c r="V541" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W541" t="inlineStr">
@@ -85163,15 +85237,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA541" t="inlineStr"/>
-      <c r="AB541" t="inlineStr"/>
+      <c r="AA541" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB541" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC541" t="n">
         <v>0</v>
       </c>
       <c r="AD541" t="n">
         <v>0</v>
       </c>
-      <c r="AE541" t="inlineStr"/>
+      <c r="AE541" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF541" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -85215,13 +85295,19 @@
       <c r="D542" t="n">
         <v>6750</v>
       </c>
-      <c r="E542" t="inlineStr"/>
+      <c r="E542" t="n">
+        <v>6750</v>
+      </c>
       <c r="F542" t="inlineStr">
         <is>
           <t>21-Jul-2026 16:08:19</t>
         </is>
       </c>
-      <c r="G542" t="inlineStr"/>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 18:45:58</t>
+        </is>
+      </c>
       <c r="H542" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -85286,7 +85372,7 @@
       </c>
       <c r="V542" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W542" t="inlineStr">
@@ -85309,15 +85395,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA542" t="inlineStr"/>
-      <c r="AB542" t="inlineStr"/>
+      <c r="AA542" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB542" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC542" t="n">
         <v>0</v>
       </c>
       <c r="AD542" t="n">
         <v>0</v>
       </c>
-      <c r="AE542" t="inlineStr"/>
+      <c r="AE542" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF542" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -85361,13 +85453,19 @@
       <c r="D543" t="n">
         <v>8400</v>
       </c>
-      <c r="E543" t="inlineStr"/>
+      <c r="E543" t="n">
+        <v>8400</v>
+      </c>
       <c r="F543" t="inlineStr">
         <is>
           <t>21-Jul-2026 16:47:48</t>
         </is>
       </c>
-      <c r="G543" t="inlineStr"/>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 18:45:58</t>
+        </is>
+      </c>
       <c r="H543" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -85432,7 +85530,7 @@
       </c>
       <c r="V543" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W543" t="inlineStr">
@@ -85455,15 +85553,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA543" t="inlineStr"/>
-      <c r="AB543" t="inlineStr"/>
+      <c r="AA543" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB543" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC543" t="n">
         <v>0</v>
       </c>
       <c r="AD543" t="n">
         <v>0</v>
       </c>
-      <c r="AE543" t="inlineStr"/>
+      <c r="AE543" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF543" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -85489,6 +85593,2042 @@
         </is>
       </c>
       <c r="AL543" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>16208</v>
+      </c>
+      <c r="B544" t="inlineStr"/>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>73****4393</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E544" t="inlineStr"/>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 07:35:22</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>*9412</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N544" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P544" t="n">
+        <v>11000374402910</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>1784685905649</v>
+      </c>
+      <c r="R544" t="n">
+        <v>467270522142</v>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V544" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W544" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y544" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z544" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA544" t="inlineStr"/>
+      <c r="AB544" t="inlineStr"/>
+      <c r="AC544" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD544" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE544" t="inlineStr"/>
+      <c r="AF544" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG544" t="inlineStr"/>
+      <c r="AH544" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI544" t="n">
+        <v>19412</v>
+      </c>
+      <c r="AJ544" t="inlineStr">
+        <is>
+          <t>276168</t>
+        </is>
+      </c>
+      <c r="AK544" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL544" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>17470</v>
+      </c>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>62****9288</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 08:52:26</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>*0154</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N545" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P545" t="n">
+        <v>11000374410889</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>1784690526265</v>
+      </c>
+      <c r="R545" t="n">
+        <v>74635998191</v>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V545" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W545" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y545" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z545" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA545" t="inlineStr"/>
+      <c r="AB545" t="inlineStr"/>
+      <c r="AC545" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD545" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE545" t="inlineStr"/>
+      <c r="AF545" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG545" t="inlineStr"/>
+      <c r="AH545" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI545" t="n">
+        <v>20154</v>
+      </c>
+      <c r="AJ545" t="inlineStr">
+        <is>
+          <t>269269</t>
+        </is>
+      </c>
+      <c r="AK545" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL545" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>15824</v>
+      </c>
+      <c r="B546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>93****3464</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>600</v>
+      </c>
+      <c r="E546" t="inlineStr"/>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 10:31:04</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>*8667</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N546" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P546" t="n">
+        <v>11000374425269</v>
+      </c>
+      <c r="Q546" t="n">
+        <v>1784696449005</v>
+      </c>
+      <c r="R546" t="n">
+        <v>620374657715</v>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V546" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W546" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y546" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z546" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA546" t="inlineStr"/>
+      <c r="AB546" t="inlineStr"/>
+      <c r="AC546" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD546" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE546" t="inlineStr"/>
+      <c r="AF546" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG546" t="inlineStr"/>
+      <c r="AH546" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI546" t="n">
+        <v>18667</v>
+      </c>
+      <c r="AJ546" t="inlineStr">
+        <is>
+          <t>270324</t>
+        </is>
+      </c>
+      <c r="AK546" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="AL546" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>15824</v>
+      </c>
+      <c r="B547" t="inlineStr"/>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>93****3464</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E547" t="inlineStr"/>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 10:29:52</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>*8667</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N547" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P547" t="n">
+        <v>11000374425570</v>
+      </c>
+      <c r="Q547" t="n">
+        <v>1784696371161</v>
+      </c>
+      <c r="R547" t="n">
+        <v>620359661427</v>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T547" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V547" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W547" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y547" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z547" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA547" t="inlineStr"/>
+      <c r="AB547" t="inlineStr"/>
+      <c r="AC547" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD547" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE547" t="inlineStr"/>
+      <c r="AF547" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG547" t="inlineStr"/>
+      <c r="AH547" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI547" t="n">
+        <v>18667</v>
+      </c>
+      <c r="AJ547" t="inlineStr">
+        <is>
+          <t>273595</t>
+        </is>
+      </c>
+      <c r="AK547" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL547" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>17658</v>
+      </c>
+      <c r="B548" t="inlineStr"/>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>81****7834</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E548" t="inlineStr"/>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 11:59:04</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>*0373</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N548" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P548" t="n">
+        <v>11000374445012</v>
+      </c>
+      <c r="Q548" t="n">
+        <v>1784701729121</v>
+      </c>
+      <c r="R548" t="n">
+        <v>918463970227</v>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V548" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W548" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y548" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z548" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA548" t="inlineStr"/>
+      <c r="AB548" t="inlineStr"/>
+      <c r="AC548" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD548" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE548" t="inlineStr"/>
+      <c r="AF548" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG548" t="inlineStr"/>
+      <c r="AH548" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI548" t="n">
+        <v>20373</v>
+      </c>
+      <c r="AJ548" t="inlineStr">
+        <is>
+          <t>277191</t>
+        </is>
+      </c>
+      <c r="AK548" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL548" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>16548</v>
+      </c>
+      <c r="B549" t="inlineStr"/>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>90****9830</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E549" t="inlineStr"/>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 12:04:09</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>*8779</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N549" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P549" t="n">
+        <v>11000374445892</v>
+      </c>
+      <c r="Q549" t="n">
+        <v>1784701908784</v>
+      </c>
+      <c r="R549" t="n">
+        <v>620322024266</v>
+      </c>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T549" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V549" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W549" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y549" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z549" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA549" t="inlineStr"/>
+      <c r="AB549" t="inlineStr"/>
+      <c r="AC549" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD549" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE549" t="inlineStr"/>
+      <c r="AF549" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG549" t="inlineStr"/>
+      <c r="AH549" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI549" t="n">
+        <v>18779</v>
+      </c>
+      <c r="AJ549" t="inlineStr">
+        <is>
+          <t>273778</t>
+        </is>
+      </c>
+      <c r="AK549" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>17676</v>
+      </c>
+      <c r="B550" t="inlineStr"/>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>90****9830</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E550" t="inlineStr"/>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 12:08:07</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr"/>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>*0421</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N550" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P550" t="n">
+        <v>11000374447782</v>
+      </c>
+      <c r="Q550" t="n">
+        <v>1784702236405</v>
+      </c>
+      <c r="R550" t="n">
+        <v>620343032033</v>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V550" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W550" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y550" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z550" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA550" t="inlineStr"/>
+      <c r="AB550" t="inlineStr"/>
+      <c r="AC550" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD550" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE550" t="inlineStr"/>
+      <c r="AF550" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG550" t="inlineStr"/>
+      <c r="AH550" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI550" t="n">
+        <v>20421</v>
+      </c>
+      <c r="AJ550" t="inlineStr">
+        <is>
+          <t>277199</t>
+        </is>
+      </c>
+      <c r="AK550" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>17634</v>
+      </c>
+      <c r="B551" t="inlineStr"/>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>83****3383</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E551" t="inlineStr"/>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 12:16:29</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>*0385</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N551" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P551" t="n">
+        <v>11000374449988</v>
+      </c>
+      <c r="Q551" t="n">
+        <v>1784702772292</v>
+      </c>
+      <c r="R551" t="n">
+        <v>821448646444</v>
+      </c>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V551" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W551" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y551" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z551" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA551" t="inlineStr"/>
+      <c r="AB551" t="inlineStr"/>
+      <c r="AC551" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD551" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE551" t="inlineStr"/>
+      <c r="AF551" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG551" t="inlineStr"/>
+      <c r="AH551" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI551" t="n">
+        <v>20385</v>
+      </c>
+      <c r="AJ551" t="inlineStr">
+        <is>
+          <t>277283</t>
+        </is>
+      </c>
+      <c r="AK551" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL551" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>17201</v>
+      </c>
+      <c r="B552" t="inlineStr"/>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>94****2534</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E552" t="inlineStr"/>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 13:26:28</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr"/>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>*9915</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N552" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P552" t="n">
+        <v>11000374470710</v>
+      </c>
+      <c r="Q552" t="n">
+        <v>1784706974539</v>
+      </c>
+      <c r="R552" t="n">
+        <v>24166548769</v>
+      </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V552" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W552" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y552" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z552" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA552" t="inlineStr"/>
+      <c r="AB552" t="inlineStr"/>
+      <c r="AC552" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD552" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE552" t="inlineStr"/>
+      <c r="AF552" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG552" t="inlineStr"/>
+      <c r="AH552" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI552" t="n">
+        <v>19915</v>
+      </c>
+      <c r="AJ552" t="inlineStr">
+        <is>
+          <t>271646</t>
+        </is>
+      </c>
+      <c r="AK552" t="inlineStr">
+        <is>
+          <t>2077</t>
+        </is>
+      </c>
+      <c r="AL552" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>15329</v>
+      </c>
+      <c r="B553" t="inlineStr"/>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>95****2142</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E553" t="inlineStr"/>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 15:48:33</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr"/>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>*9453</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N553" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P553" t="n">
+        <v>11000374501506</v>
+      </c>
+      <c r="Q553" t="n">
+        <v>1784715500879</v>
+      </c>
+      <c r="R553" t="n">
+        <v>258353587436</v>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V553" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W553" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y553" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z553" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA553" t="inlineStr"/>
+      <c r="AB553" t="inlineStr"/>
+      <c r="AC553" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD553" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE553" t="inlineStr"/>
+      <c r="AF553" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG553" t="inlineStr"/>
+      <c r="AH553" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI553" t="n">
+        <v>19453</v>
+      </c>
+      <c r="AJ553" t="inlineStr">
+        <is>
+          <t>276164</t>
+        </is>
+      </c>
+      <c r="AK553" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL553" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>14717</v>
+      </c>
+      <c r="B554" t="inlineStr"/>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>77****7302</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E554" t="inlineStr"/>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 16:04:34</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr"/>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>*9374</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N554" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P554" t="n">
+        <v>11000374503102</v>
+      </c>
+      <c r="Q554" t="n">
+        <v>1784716463382</v>
+      </c>
+      <c r="R554" t="n">
+        <v>30463883736</v>
+      </c>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V554" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W554" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y554" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z554" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA554" t="inlineStr"/>
+      <c r="AB554" t="inlineStr"/>
+      <c r="AC554" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD554" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE554" t="inlineStr"/>
+      <c r="AF554" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG554" t="inlineStr"/>
+      <c r="AH554" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI554" t="n">
+        <v>19374</v>
+      </c>
+      <c r="AJ554" t="inlineStr">
+        <is>
+          <t>276173</t>
+        </is>
+      </c>
+      <c r="AK554" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL554" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>17698</v>
+      </c>
+      <c r="B555" t="inlineStr"/>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>96****8422</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E555" t="inlineStr"/>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 18:10:52</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr"/>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>*0452</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N555" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P555" t="n">
+        <v>11000374521392</v>
+      </c>
+      <c r="Q555" t="n">
+        <v>1784724024218</v>
+      </c>
+      <c r="R555" t="n">
+        <v>620339982296</v>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V555" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W555" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y555" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z555" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA555" t="inlineStr"/>
+      <c r="AB555" t="inlineStr"/>
+      <c r="AC555" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD555" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE555" t="inlineStr"/>
+      <c r="AF555" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG555" t="inlineStr"/>
+      <c r="AH555" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI555" t="n">
+        <v>20452</v>
+      </c>
+      <c r="AJ555" t="inlineStr">
+        <is>
+          <t>277553</t>
+        </is>
+      </c>
+      <c r="AK555" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL555" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>16974</v>
+      </c>
+      <c r="B556" t="inlineStr"/>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>98****0099</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E556" t="inlineStr"/>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 19:27:59</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr"/>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>*8273</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N556" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P556" t="n">
+        <v>11000374532416</v>
+      </c>
+      <c r="Q556" t="n">
+        <v>1784728665573</v>
+      </c>
+      <c r="R556" t="n">
+        <v>498137399796</v>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V556" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W556" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y556" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z556" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA556" t="inlineStr"/>
+      <c r="AB556" t="inlineStr"/>
+      <c r="AC556" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD556" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE556" t="inlineStr"/>
+      <c r="AF556" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG556" t="inlineStr"/>
+      <c r="AH556" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI556" t="n">
+        <v>18273</v>
+      </c>
+      <c r="AJ556" t="inlineStr">
+        <is>
+          <t>272356</t>
+        </is>
+      </c>
+      <c r="AK556" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL556" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>17400</v>
+      </c>
+      <c r="B557" t="inlineStr"/>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>96****1718</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E557" t="inlineStr"/>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 21:23:33</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr"/>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>*0120</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N557" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P557" t="n">
+        <v>11000374543686</v>
+      </c>
+      <c r="Q557" t="n">
+        <v>1784735602083</v>
+      </c>
+      <c r="R557" t="n">
+        <v>25367472515</v>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V557" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W557" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y557" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z557" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA557" t="inlineStr"/>
+      <c r="AB557" t="inlineStr"/>
+      <c r="AC557" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD557" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE557" t="inlineStr"/>
+      <c r="AF557" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG557" t="inlineStr"/>
+      <c r="AH557" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI557" t="n">
+        <v>20120</v>
+      </c>
+      <c r="AJ557" t="inlineStr">
+        <is>
+          <t>269235</t>
+        </is>
+      </c>
+      <c r="AK557" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL557" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -87811,7 +87811,11 @@
           <t>23-Jul-2026 09:48:54</t>
         </is>
       </c>
-      <c r="G558" t="inlineStr"/>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 18:56:45</t>
+        </is>
+      </c>
       <c r="H558" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -87876,7 +87880,7 @@
       </c>
       <c r="V558" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W558" t="inlineStr">
@@ -87965,7 +87969,11 @@
           <t>23-Jul-2026 12:01:04</t>
         </is>
       </c>
-      <c r="G559" t="inlineStr"/>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 18:56:45</t>
+        </is>
+      </c>
       <c r="H559" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -88030,7 +88038,7 @@
       </c>
       <c r="V559" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W559" t="inlineStr">
@@ -88119,7 +88127,11 @@
           <t>23-Jul-2026 11:59:43</t>
         </is>
       </c>
-      <c r="G560" t="inlineStr"/>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 18:56:45</t>
+        </is>
+      </c>
       <c r="H560" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -88184,7 +88196,7 @@
       </c>
       <c r="V560" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W560" t="inlineStr">
@@ -88273,7 +88285,11 @@
           <t>23-Jul-2026 12:33:37</t>
         </is>
       </c>
-      <c r="G561" t="inlineStr"/>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 18:56:45</t>
+        </is>
+      </c>
       <c r="H561" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -88338,7 +88354,7 @@
       </c>
       <c r="V561" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W561" t="inlineStr">
@@ -88581,7 +88597,11 @@
           <t>23-Jul-2026 12:44:14</t>
         </is>
       </c>
-      <c r="G563" t="inlineStr"/>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 18:56:45</t>
+        </is>
+      </c>
       <c r="H563" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -88646,7 +88666,7 @@
       </c>
       <c r="V563" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W563" t="inlineStr">
@@ -88735,7 +88755,11 @@
           <t>23-Jul-2026 13:22:42</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr"/>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 18:56:45</t>
+        </is>
+      </c>
       <c r="H564" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -88800,7 +88824,7 @@
       </c>
       <c r="V564" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W564" t="inlineStr">
@@ -88889,7 +88913,11 @@
           <t>23-Jul-2026 16:10:13</t>
         </is>
       </c>
-      <c r="G565" t="inlineStr"/>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 18:56:45</t>
+        </is>
+      </c>
       <c r="H565" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -88954,7 +88982,7 @@
       </c>
       <c r="V565" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W565" t="inlineStr">
@@ -89043,7 +89071,11 @@
           <t>23-Jul-2026 18:59:23</t>
         </is>
       </c>
-      <c r="G566" t="inlineStr"/>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 18:56:45</t>
+        </is>
+      </c>
       <c r="H566" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -89108,7 +89140,7 @@
       </c>
       <c r="V566" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W566" t="inlineStr">

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL566"/>
+  <dimension ref="A1:AL572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89208,6 +89208,882 @@
         </is>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>17247</v>
+      </c>
+      <c r="B567" t="inlineStr"/>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>98****4144</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E567" t="inlineStr"/>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>25-Jul-2026 08:23:40</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr"/>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>*9959</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N567" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P567" t="n">
+        <v>11000374898465</v>
+      </c>
+      <c r="Q567" t="n">
+        <v>1784948006490</v>
+      </c>
+      <c r="R567" t="n">
+        <v>3077259763</v>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V567" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W567" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X567" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y567" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z567" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA567" t="inlineStr"/>
+      <c r="AB567" t="inlineStr"/>
+      <c r="AC567" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD567" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE567" t="inlineStr"/>
+      <c r="AF567" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG567" t="inlineStr"/>
+      <c r="AH567" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI567" t="n">
+        <v>19959</v>
+      </c>
+      <c r="AJ567" t="inlineStr">
+        <is>
+          <t>271271</t>
+        </is>
+      </c>
+      <c r="AK567" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL567" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>16351</v>
+      </c>
+      <c r="B568" t="inlineStr"/>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>95****4297</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E568" t="inlineStr"/>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>25-Jul-2026 10:20:06</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr"/>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>*8369</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N568" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P568" t="n">
+        <v>11000374910056</v>
+      </c>
+      <c r="Q568" t="n">
+        <v>1784954977603</v>
+      </c>
+      <c r="R568" t="n">
+        <v>1214918255</v>
+      </c>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V568" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W568" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X568" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y568" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z568" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA568" t="inlineStr"/>
+      <c r="AB568" t="inlineStr"/>
+      <c r="AC568" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD568" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE568" t="inlineStr"/>
+      <c r="AF568" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG568" t="inlineStr"/>
+      <c r="AH568" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI568" t="n">
+        <v>18369</v>
+      </c>
+      <c r="AJ568" t="inlineStr">
+        <is>
+          <t>272342</t>
+        </is>
+      </c>
+      <c r="AK568" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL568" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>14152</v>
+      </c>
+      <c r="B569" t="inlineStr"/>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>77****7970</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E569" t="inlineStr"/>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>25-Jul-2026 10:51:44</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>*9353</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N569" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P569" t="n">
+        <v>11000374915744</v>
+      </c>
+      <c r="Q569" t="n">
+        <v>1784956884079</v>
+      </c>
+      <c r="R569" t="n">
+        <v>814665494707</v>
+      </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V569" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W569" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X569" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y569" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z569" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA569" t="inlineStr"/>
+      <c r="AB569" t="inlineStr"/>
+      <c r="AC569" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD569" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE569" t="inlineStr"/>
+      <c r="AF569" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG569" t="inlineStr"/>
+      <c r="AH569" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI569" t="n">
+        <v>19353</v>
+      </c>
+      <c r="AJ569" t="inlineStr">
+        <is>
+          <t>276105</t>
+        </is>
+      </c>
+      <c r="AK569" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL569" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>16404</v>
+      </c>
+      <c r="B570" t="inlineStr"/>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>77****6258</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E570" t="inlineStr"/>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>25-Jul-2026 12:29:38</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr"/>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>*8546</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N570" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P570" t="n">
+        <v>11000374938004</v>
+      </c>
+      <c r="Q570" t="n">
+        <v>1784962754414</v>
+      </c>
+      <c r="R570" t="n">
+        <v>150236443436</v>
+      </c>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V570" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W570" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X570" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y570" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z570" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA570" t="inlineStr"/>
+      <c r="AB570" t="inlineStr"/>
+      <c r="AC570" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD570" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE570" t="inlineStr"/>
+      <c r="AF570" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG570" t="inlineStr"/>
+      <c r="AH570" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI570" t="n">
+        <v>18546</v>
+      </c>
+      <c r="AJ570" t="inlineStr">
+        <is>
+          <t>267319</t>
+        </is>
+      </c>
+      <c r="AK570" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="AL570" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>17609</v>
+      </c>
+      <c r="B571" t="inlineStr"/>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>83****2537</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E571" t="inlineStr"/>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>25-Jul-2026 12:56:37</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr"/>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>*0328</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N571" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P571" t="n">
+        <v>11000374944254</v>
+      </c>
+      <c r="Q571" t="n">
+        <v>1784964385508</v>
+      </c>
+      <c r="R571" t="n">
+        <v>198902843986</v>
+      </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V571" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W571" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X571" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y571" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z571" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA571" t="inlineStr"/>
+      <c r="AB571" t="inlineStr"/>
+      <c r="AC571" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD571" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE571" t="inlineStr"/>
+      <c r="AF571" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG571" t="inlineStr"/>
+      <c r="AH571" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI571" t="n">
+        <v>20328</v>
+      </c>
+      <c r="AJ571" t="inlineStr">
+        <is>
+          <t>277548</t>
+        </is>
+      </c>
+      <c r="AK571" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="AL571" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>17524</v>
+      </c>
+      <c r="B572" t="inlineStr"/>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>63****8718</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E572" t="inlineStr"/>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>25-Jul-2026 13:32:31</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr"/>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>*0243</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N572" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P572" t="n">
+        <v>11000374952523</v>
+      </c>
+      <c r="Q572" t="n">
+        <v>1784966535315</v>
+      </c>
+      <c r="R572" t="n">
+        <v>441622965891</v>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V572" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W572" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X572" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y572" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z572" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA572" t="inlineStr"/>
+      <c r="AB572" t="inlineStr"/>
+      <c r="AC572" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD572" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE572" t="inlineStr"/>
+      <c r="AF572" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG572" t="inlineStr"/>
+      <c r="AH572" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI572" t="n">
+        <v>20243</v>
+      </c>
+      <c r="AJ572" t="inlineStr">
+        <is>
+          <t>272411</t>
+        </is>
+      </c>
+      <c r="AK572" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL572" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL572"/>
+  <dimension ref="A1:AL574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90084,6 +90084,298 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>16673</v>
+      </c>
+      <c r="B573" t="inlineStr"/>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>90****3576</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E573" t="inlineStr"/>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>26-Jul-2026 00:28:26</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>*8166</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N573" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P573" t="n">
+        <v>11000375016744</v>
+      </c>
+      <c r="Q573" t="n">
+        <v>1785005874009</v>
+      </c>
+      <c r="R573" t="n">
+        <v>653353524103</v>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V573" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W573" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y573" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z573" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA573" t="inlineStr"/>
+      <c r="AB573" t="inlineStr"/>
+      <c r="AC573" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD573" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE573" t="inlineStr"/>
+      <c r="AF573" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG573" t="inlineStr"/>
+      <c r="AH573" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI573" t="n">
+        <v>18166</v>
+      </c>
+      <c r="AJ573" t="inlineStr">
+        <is>
+          <t>271281</t>
+        </is>
+      </c>
+      <c r="AK573" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL573" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>16398</v>
+      </c>
+      <c r="B574" t="inlineStr"/>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>91****2954</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>9400</v>
+      </c>
+      <c r="E574" t="inlineStr"/>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>26-Jul-2026 14:17:35</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr"/>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>*8886</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N574" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P574" t="n">
+        <v>11000375055101</v>
+      </c>
+      <c r="Q574" t="n">
+        <v>1785055641129</v>
+      </c>
+      <c r="R574" t="n">
+        <v>310058895026</v>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V574" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W574" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y574" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z574" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA574" t="inlineStr"/>
+      <c r="AB574" t="inlineStr"/>
+      <c r="AC574" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD574" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE574" t="inlineStr"/>
+      <c r="AF574" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG574" t="inlineStr"/>
+      <c r="AH574" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI574" t="n">
+        <v>18886</v>
+      </c>
+      <c r="AJ574" t="inlineStr">
+        <is>
+          <t>274826</t>
+        </is>
+      </c>
+      <c r="AK574" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="AL574" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL574"/>
+  <dimension ref="A1:AL582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89221,13 +89221,19 @@
       <c r="D567" t="n">
         <v>8400</v>
       </c>
-      <c r="E567" t="inlineStr"/>
+      <c r="E567" t="n">
+        <v>8400</v>
+      </c>
       <c r="F567" t="inlineStr">
         <is>
           <t>25-Jul-2026 08:23:40</t>
         </is>
       </c>
-      <c r="G567" t="inlineStr"/>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>27-Jul-2026 19:26:55</t>
+        </is>
+      </c>
       <c r="H567" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -89292,7 +89298,7 @@
       </c>
       <c r="V567" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W567" t="inlineStr">
@@ -89315,15 +89321,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA567" t="inlineStr"/>
-      <c r="AB567" t="inlineStr"/>
+      <c r="AA567" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB567" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC567" t="n">
         <v>0</v>
       </c>
       <c r="AD567" t="n">
         <v>0</v>
       </c>
-      <c r="AE567" t="inlineStr"/>
+      <c r="AE567" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF567" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -89367,13 +89379,19 @@
       <c r="D568" t="n">
         <v>8700</v>
       </c>
-      <c r="E568" t="inlineStr"/>
+      <c r="E568" t="n">
+        <v>8700</v>
+      </c>
       <c r="F568" t="inlineStr">
         <is>
           <t>25-Jul-2026 10:20:06</t>
         </is>
       </c>
-      <c r="G568" t="inlineStr"/>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>27-Jul-2026 19:26:55</t>
+        </is>
+      </c>
       <c r="H568" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -89438,7 +89456,7 @@
       </c>
       <c r="V568" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W568" t="inlineStr">
@@ -89461,15 +89479,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA568" t="inlineStr"/>
-      <c r="AB568" t="inlineStr"/>
+      <c r="AA568" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB568" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC568" t="n">
         <v>0</v>
       </c>
       <c r="AD568" t="n">
         <v>0</v>
       </c>
-      <c r="AE568" t="inlineStr"/>
+      <c r="AE568" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF568" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -89513,7 +89537,9 @@
       <c r="D569" t="n">
         <v>12300</v>
       </c>
-      <c r="E569" t="inlineStr"/>
+      <c r="E569" t="n">
+        <v>12300</v>
+      </c>
       <c r="F569" t="inlineStr">
         <is>
           <t>25-Jul-2026 10:51:44</t>
@@ -89584,7 +89610,7 @@
       </c>
       <c r="V569" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W569" t="inlineStr">
@@ -89607,15 +89633,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA569" t="inlineStr"/>
-      <c r="AB569" t="inlineStr"/>
+      <c r="AA569" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB569" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC569" t="n">
         <v>0</v>
       </c>
       <c r="AD569" t="n">
         <v>0</v>
       </c>
-      <c r="AE569" t="inlineStr"/>
+      <c r="AE569" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF569" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
@@ -89659,13 +89691,19 @@
       <c r="D570" t="n">
         <v>8050</v>
       </c>
-      <c r="E570" t="inlineStr"/>
+      <c r="E570" t="n">
+        <v>8050</v>
+      </c>
       <c r="F570" t="inlineStr">
         <is>
           <t>25-Jul-2026 12:29:38</t>
         </is>
       </c>
-      <c r="G570" t="inlineStr"/>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>27-Jul-2026 19:26:55</t>
+        </is>
+      </c>
       <c r="H570" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -89730,7 +89768,7 @@
       </c>
       <c r="V570" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W570" t="inlineStr">
@@ -89753,15 +89791,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA570" t="inlineStr"/>
-      <c r="AB570" t="inlineStr"/>
+      <c r="AA570" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB570" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC570" t="n">
         <v>0</v>
       </c>
       <c r="AD570" t="n">
         <v>0</v>
       </c>
-      <c r="AE570" t="inlineStr"/>
+      <c r="AE570" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF570" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -89805,13 +89849,19 @@
       <c r="D571" t="n">
         <v>6500</v>
       </c>
-      <c r="E571" t="inlineStr"/>
+      <c r="E571" t="n">
+        <v>6500</v>
+      </c>
       <c r="F571" t="inlineStr">
         <is>
           <t>25-Jul-2026 12:56:37</t>
         </is>
       </c>
-      <c r="G571" t="inlineStr"/>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>27-Jul-2026 19:26:55</t>
+        </is>
+      </c>
       <c r="H571" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -89876,7 +89926,7 @@
       </c>
       <c r="V571" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W571" t="inlineStr">
@@ -89899,15 +89949,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA571" t="inlineStr"/>
-      <c r="AB571" t="inlineStr"/>
+      <c r="AA571" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB571" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC571" t="n">
         <v>0</v>
       </c>
       <c r="AD571" t="n">
         <v>0</v>
       </c>
-      <c r="AE571" t="inlineStr"/>
+      <c r="AE571" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF571" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
@@ -89951,13 +90007,19 @@
       <c r="D572" t="n">
         <v>8700</v>
       </c>
-      <c r="E572" t="inlineStr"/>
+      <c r="E572" t="n">
+        <v>8700</v>
+      </c>
       <c r="F572" t="inlineStr">
         <is>
           <t>25-Jul-2026 13:32:31</t>
         </is>
       </c>
-      <c r="G572" t="inlineStr"/>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>27-Jul-2026 19:26:55</t>
+        </is>
+      </c>
       <c r="H572" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -90022,7 +90084,7 @@
       </c>
       <c r="V572" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W572" t="inlineStr">
@@ -90045,15 +90107,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA572" t="inlineStr"/>
-      <c r="AB572" t="inlineStr"/>
+      <c r="AA572" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB572" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC572" t="n">
         <v>0</v>
       </c>
       <c r="AD572" t="n">
         <v>0</v>
       </c>
-      <c r="AE572" t="inlineStr"/>
+      <c r="AE572" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF572" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -90097,13 +90165,19 @@
       <c r="D573" t="n">
         <v>8400</v>
       </c>
-      <c r="E573" t="inlineStr"/>
+      <c r="E573" t="n">
+        <v>8400</v>
+      </c>
       <c r="F573" t="inlineStr">
         <is>
           <t>26-Jul-2026 00:28:26</t>
         </is>
       </c>
-      <c r="G573" t="inlineStr"/>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>27-Jul-2026 19:26:55</t>
+        </is>
+      </c>
       <c r="H573" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -90168,7 +90242,7 @@
       </c>
       <c r="V573" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W573" t="inlineStr">
@@ -90191,15 +90265,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA573" t="inlineStr"/>
-      <c r="AB573" t="inlineStr"/>
+      <c r="AA573" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB573" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC573" t="n">
         <v>0</v>
       </c>
       <c r="AD573" t="n">
         <v>0</v>
       </c>
-      <c r="AE573" t="inlineStr"/>
+      <c r="AE573" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF573" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -90243,7 +90323,9 @@
       <c r="D574" t="n">
         <v>9400</v>
       </c>
-      <c r="E574" t="inlineStr"/>
+      <c r="E574" t="n">
+        <v>9400</v>
+      </c>
       <c r="F574" t="inlineStr">
         <is>
           <t>26-Jul-2026 14:17:35</t>
@@ -90314,7 +90396,7 @@
       </c>
       <c r="V574" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="W574" t="inlineStr">
@@ -90337,15 +90419,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA574" t="inlineStr"/>
-      <c r="AB574" t="inlineStr"/>
+      <c r="AA574" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB574" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC574" t="n">
         <v>0</v>
       </c>
       <c r="AD574" t="n">
         <v>0</v>
       </c>
-      <c r="AE574" t="inlineStr"/>
+      <c r="AE574" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF574" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
@@ -90371,6 +90459,1238 @@
         </is>
       </c>
       <c r="AL574" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>15509</v>
+      </c>
+      <c r="B575" t="inlineStr"/>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>81****2047</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E575" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>28-Jul-2026 11:23:55</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr"/>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>Vll</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>*8975</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N575" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P575" t="n">
+        <v>11000375310135</v>
+      </c>
+      <c r="Q575" t="n">
+        <v>1785217942546</v>
+      </c>
+      <c r="R575" t="n">
+        <v>620935016217</v>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V575" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W575" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y575" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="Z575" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA575" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB575" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="AC575" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD575" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE575" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="AF575" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN HIGH SCHOOL SSC</t>
+        </is>
+      </c>
+      <c r="AG575" t="inlineStr"/>
+      <c r="AH575" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI575" t="n">
+        <v>18975</v>
+      </c>
+      <c r="AJ575" t="inlineStr">
+        <is>
+          <t>270833,275013</t>
+        </is>
+      </c>
+      <c r="AK575" t="inlineStr">
+        <is>
+          <t>2074,2089</t>
+        </is>
+      </c>
+      <c r="AL575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>16989</v>
+      </c>
+      <c r="B576" t="inlineStr"/>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>80****0599</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>8700</v>
+      </c>
+      <c r="E576" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>28-Jul-2026 11:54:19</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>29-Jul-2026 18:59:49</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>*8303</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N576" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P576" t="n">
+        <v>11000375320298</v>
+      </c>
+      <c r="Q576" t="n">
+        <v>1785219843680</v>
+      </c>
+      <c r="R576" t="n">
+        <v>188832104200</v>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V576" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W576" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y576" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z576" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA576" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB576" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC576" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD576" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE576" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF576" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG576" t="inlineStr"/>
+      <c r="AH576" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI576" t="n">
+        <v>18303</v>
+      </c>
+      <c r="AJ576" t="inlineStr">
+        <is>
+          <t>272293</t>
+        </is>
+      </c>
+      <c r="AK576" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="AL576" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>16220</v>
+      </c>
+      <c r="B577" t="inlineStr"/>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>80****0599</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E577" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>28-Jul-2026 11:56:35</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>29-Jul-2026 18:59:49</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>*8695</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N577" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P577" t="n">
+        <v>11000375323139</v>
+      </c>
+      <c r="Q577" t="n">
+        <v>1785219984190</v>
+      </c>
+      <c r="R577" t="n">
+        <v>56256987921</v>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V577" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W577" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y577" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z577" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA577" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB577" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC577" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD577" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE577" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF577" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG577" t="inlineStr"/>
+      <c r="AH577" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI577" t="n">
+        <v>18695</v>
+      </c>
+      <c r="AJ577" t="inlineStr">
+        <is>
+          <t>273784</t>
+        </is>
+      </c>
+      <c r="AK577" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL577" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>17454</v>
+      </c>
+      <c r="B578" t="inlineStr"/>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>88****9604</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E578" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>28-Jul-2026 12:37:03</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>29-Jul-2026 18:59:49</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>*0178</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N578" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P578" t="n">
+        <v>11000375336242</v>
+      </c>
+      <c r="Q578" t="n">
+        <v>1785222406923</v>
+      </c>
+      <c r="R578" t="n">
+        <v>223648763398</v>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V578" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W578" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y578" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z578" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA578" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB578" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC578" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD578" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE578" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF578" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG578" t="inlineStr"/>
+      <c r="AH578" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI578" t="n">
+        <v>20178</v>
+      </c>
+      <c r="AJ578" t="inlineStr">
+        <is>
+          <t>271565</t>
+        </is>
+      </c>
+      <c r="AK578" t="inlineStr">
+        <is>
+          <t>2077</t>
+        </is>
+      </c>
+      <c r="AL578" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>17453</v>
+      </c>
+      <c r="B579" t="inlineStr"/>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>88****9604</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E579" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>28-Jul-2026 12:38:21</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>29-Jul-2026 19:06:03</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>*0161</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N579" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P579" t="n">
+        <v>11000375338199</v>
+      </c>
+      <c r="Q579" t="n">
+        <v>1785222486969</v>
+      </c>
+      <c r="R579" t="n">
+        <v>990740713105</v>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V579" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W579" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y579" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z579" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA579" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB579" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC579" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD579" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE579" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF579" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG579" t="inlineStr"/>
+      <c r="AH579" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI579" t="n">
+        <v>20161</v>
+      </c>
+      <c r="AJ579" t="inlineStr">
+        <is>
+          <t>277035</t>
+        </is>
+      </c>
+      <c r="AK579" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="AL579" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>17643</v>
+      </c>
+      <c r="B580" t="inlineStr"/>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>70****0325</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E580" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>28-Jul-2026 15:48:12</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>29-Jul-2026 19:06:03</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>*0379</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N580" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P580" t="n">
+        <v>11000375377607</v>
+      </c>
+      <c r="Q580" t="n">
+        <v>1785233880087</v>
+      </c>
+      <c r="R580" t="n">
+        <v>155702464895</v>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V580" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W580" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y580" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z580" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA580" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB580" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC580" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD580" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE580" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF580" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG580" t="inlineStr"/>
+      <c r="AH580" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI580" t="n">
+        <v>20379</v>
+      </c>
+      <c r="AJ580" t="inlineStr">
+        <is>
+          <t>277201</t>
+        </is>
+      </c>
+      <c r="AK580" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL580" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>17237</v>
+      </c>
+      <c r="B581" t="inlineStr"/>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>77****6649</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E581" t="inlineStr"/>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>29-Jul-2026 12:36:07</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr"/>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>*9949</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N581" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P581" t="n">
+        <v>11000375497424</v>
+      </c>
+      <c r="Q581" t="n">
+        <v>1785308737161</v>
+      </c>
+      <c r="R581" t="n">
+        <v>657688039747</v>
+      </c>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V581" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W581" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X581" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y581" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z581" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA581" t="inlineStr"/>
+      <c r="AB581" t="inlineStr"/>
+      <c r="AC581" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD581" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE581" t="inlineStr"/>
+      <c r="AF581" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG581" t="inlineStr"/>
+      <c r="AH581" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI581" t="n">
+        <v>19949</v>
+      </c>
+      <c r="AJ581" t="inlineStr">
+        <is>
+          <t>271346</t>
+        </is>
+      </c>
+      <c r="AK581" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL581" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>17250</v>
+      </c>
+      <c r="B582" t="inlineStr"/>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>98****1059</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E582" t="inlineStr"/>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>29-Jul-2026 20:28:32</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr"/>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>*9962</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N582" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P582" t="n">
+        <v>11000375576230</v>
+      </c>
+      <c r="Q582" t="n">
+        <v>1785337100210</v>
+      </c>
+      <c r="R582" t="n">
+        <v>127058470634</v>
+      </c>
+      <c r="S582" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V582" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="W582" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X582" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y582" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z582" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA582" t="inlineStr"/>
+      <c r="AB582" t="inlineStr"/>
+      <c r="AC582" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD582" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE582" t="inlineStr"/>
+      <c r="AF582" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG582" t="inlineStr"/>
+      <c r="AH582" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI582" t="n">
+        <v>19962</v>
+      </c>
+      <c r="AJ582" t="inlineStr">
+        <is>
+          <t>273790</t>
+        </is>
+      </c>
+      <c r="AK582" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="AL582" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>

--- a/output_data/atom_report_cleaned.xlsx
+++ b/output_data/atom_report_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL582"/>
+  <dimension ref="A1:AL592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91417,13 +91417,19 @@
       <c r="D581" t="n">
         <v>8400</v>
       </c>
-      <c r="E581" t="inlineStr"/>
+      <c r="E581" t="n">
+        <v>8400</v>
+      </c>
       <c r="F581" t="inlineStr">
         <is>
           <t>29-Jul-2026 12:36:07</t>
         </is>
       </c>
-      <c r="G581" t="inlineStr"/>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>30-Jul-2026 18:21:14</t>
+        </is>
+      </c>
       <c r="H581" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -91488,7 +91494,7 @@
       </c>
       <c r="V581" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W581" t="inlineStr">
@@ -91511,15 +91517,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA581" t="inlineStr"/>
-      <c r="AB581" t="inlineStr"/>
+      <c r="AA581" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB581" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC581" t="n">
         <v>0</v>
       </c>
       <c r="AD581" t="n">
         <v>0</v>
       </c>
-      <c r="AE581" t="inlineStr"/>
+      <c r="AE581" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF581" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -91563,13 +91575,19 @@
       <c r="D582" t="n">
         <v>9000</v>
       </c>
-      <c r="E582" t="inlineStr"/>
+      <c r="E582" t="n">
+        <v>9000</v>
+      </c>
       <c r="F582" t="inlineStr">
         <is>
           <t>29-Jul-2026 20:28:32</t>
         </is>
       </c>
-      <c r="G582" t="inlineStr"/>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>30-Jul-2026 18:21:14</t>
+        </is>
+      </c>
       <c r="H582" t="inlineStr">
         <is>
           <t>TRANSACTION IS SUCCESSFUL</t>
@@ -91634,7 +91652,7 @@
       </c>
       <c r="V582" t="inlineStr">
         <is>
-          <t>NRNS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="W582" t="inlineStr">
@@ -91657,15 +91675,21 @@
           <t>m**********@gmail.com</t>
         </is>
       </c>
-      <c r="AA582" t="inlineStr"/>
-      <c r="AB582" t="inlineStr"/>
+      <c r="AA582" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB582" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AC582" t="n">
         <v>0</v>
       </c>
       <c r="AD582" t="n">
         <v>0</v>
       </c>
-      <c r="AE582" t="inlineStr"/>
+      <c r="AE582" t="n">
+        <v>5.9</v>
+      </c>
       <c r="AF582" t="inlineStr">
         <is>
           <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
@@ -91691,6 +91715,1574 @@
         </is>
       </c>
       <c r="AL582" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>14678</v>
+      </c>
+      <c r="B583" t="inlineStr"/>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>94****2034</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E583" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>30-Jul-2026 18:30:21</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr"/>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>*9417</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N583" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P583" t="n">
+        <v>11000375730748</v>
+      </c>
+      <c r="Q583" t="n">
+        <v>1785416059023</v>
+      </c>
+      <c r="R583" t="n">
+        <v>621142076460</v>
+      </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>HDFC Bank FSS PG</t>
+        </is>
+      </c>
+      <c r="V583" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W583" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X583" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y583" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="Z583" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA583" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="AB583" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="AC583" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD583" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE583" t="n">
+        <v>174.17</v>
+      </c>
+      <c r="AF583" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG583" t="inlineStr"/>
+      <c r="AH583" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI583" t="n">
+        <v>19417</v>
+      </c>
+      <c r="AJ583" t="inlineStr">
+        <is>
+          <t>276130</t>
+        </is>
+      </c>
+      <c r="AK583" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>16173</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>J******* G****** N****</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>91****3334</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E584" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>31-Jul-2026 17:58:16</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr"/>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>twelve thousand three hundred</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N584" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="P584" t="n">
+        <v>11000375916211</v>
+      </c>
+      <c r="Q584" t="n">
+        <v>1785500667</v>
+      </c>
+      <c r="R584" t="n">
+        <v>671330673177</v>
+      </c>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V584" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W584" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X584" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y584" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z584" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA584" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB584" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC584" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD584" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE584" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF584" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG584" t="inlineStr"/>
+      <c r="AH584" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI584" t="n">
+        <v>19450</v>
+      </c>
+      <c r="AJ584" t="inlineStr">
+        <is>
+          <t>276169</t>
+        </is>
+      </c>
+      <c r="AK584" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL584" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>17513</v>
+      </c>
+      <c r="B585" t="inlineStr"/>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>77****9575</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E585" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>01-Aug-2026 00:17:56</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>03-Aug-2026 19:12:07</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>*0232</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N585" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P585" t="n">
+        <v>11000375966814</v>
+      </c>
+      <c r="Q585" t="n">
+        <v>1785523595374</v>
+      </c>
+      <c r="R585" t="n">
+        <v>540732502001</v>
+      </c>
+      <c r="S585" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V585" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W585" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X585" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y585" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z585" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA585" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB585" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC585" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD585" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE585" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF585" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG585" t="inlineStr"/>
+      <c r="AH585" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI585" t="n">
+        <v>20232</v>
+      </c>
+      <c r="AJ585" t="inlineStr">
+        <is>
+          <t>271318</t>
+        </is>
+      </c>
+      <c r="AK585" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="AL585" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>17526</v>
+      </c>
+      <c r="B586" t="inlineStr"/>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>85****1552</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E586" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>02-Aug-2026 09:20:02</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>03-Aug-2026 19:12:07</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>*0245</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N586" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P586" t="n">
+        <v>11000376155889</v>
+      </c>
+      <c r="Q586" t="n">
+        <v>1785642585008</v>
+      </c>
+      <c r="R586" t="n">
+        <v>658021498803</v>
+      </c>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V586" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W586" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X586" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y586" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z586" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA586" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB586" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC586" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD586" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE586" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF586" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG586" t="inlineStr"/>
+      <c r="AH586" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI586" t="n">
+        <v>20245</v>
+      </c>
+      <c r="AJ586" t="inlineStr">
+        <is>
+          <t>269406</t>
+        </is>
+      </c>
+      <c r="AK586" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="AL586" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>17490</v>
+      </c>
+      <c r="B587" t="inlineStr"/>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>91****3633</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E587" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>02-Aug-2026 21:58:54</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>03-Aug-2026 19:12:07</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>*0209</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N587" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P587" t="n">
+        <v>11000376251107</v>
+      </c>
+      <c r="Q587" t="n">
+        <v>1785688120063</v>
+      </c>
+      <c r="R587" t="n">
+        <v>50125021561</v>
+      </c>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V587" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W587" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X587" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y587" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z587" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA587" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB587" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC587" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD587" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE587" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF587" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG587" t="inlineStr"/>
+      <c r="AH587" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI587" t="n">
+        <v>20209</v>
+      </c>
+      <c r="AJ587" t="inlineStr">
+        <is>
+          <t>269193</t>
+        </is>
+      </c>
+      <c r="AK587" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL587" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>17645</v>
+      </c>
+      <c r="B588" t="inlineStr"/>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>85****2836</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>9600</v>
+      </c>
+      <c r="E588" t="n">
+        <v>9600</v>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>03-Aug-2026 15:54:20</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>04-Aug-2026 18:49:35</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>*0410</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N588" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P588" t="n">
+        <v>11000376378749</v>
+      </c>
+      <c r="Q588" t="n">
+        <v>1785752647725</v>
+      </c>
+      <c r="R588" t="n">
+        <v>35002140938</v>
+      </c>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V588" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W588" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X588" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y588" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z588" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA588" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB588" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC588" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD588" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE588" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF588" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG588" t="inlineStr"/>
+      <c r="AH588" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI588" t="n">
+        <v>20410</v>
+      </c>
+      <c r="AJ588" t="inlineStr">
+        <is>
+          <t>277429,277386</t>
+        </is>
+      </c>
+      <c r="AK588" t="inlineStr">
+        <is>
+          <t>2067,2085</t>
+        </is>
+      </c>
+      <c r="AL588" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>16673</v>
+      </c>
+      <c r="B589" t="inlineStr"/>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>90****3576</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E589" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>03-Aug-2026 16:34:45</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>04-Aug-2026 18:49:35</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>lVl</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>*8166</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N589" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P589" t="n">
+        <v>11000376387349</v>
+      </c>
+      <c r="Q589" t="n">
+        <v>1785755067649</v>
+      </c>
+      <c r="R589" t="n">
+        <v>766691665144</v>
+      </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V589" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W589" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X589" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y589" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z589" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA589" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB589" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC589" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD589" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE589" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF589" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN PRIMARY SCHOOL</t>
+        </is>
+      </c>
+      <c r="AG589" t="inlineStr"/>
+      <c r="AH589" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI589" t="n">
+        <v>18166</v>
+      </c>
+      <c r="AJ589" t="inlineStr">
+        <is>
+          <t>270486,271674</t>
+        </is>
+      </c>
+      <c r="AK589" t="inlineStr">
+        <is>
+          <t>2067,2077</t>
+        </is>
+      </c>
+      <c r="AL589" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>17695</v>
+      </c>
+      <c r="B590" t="inlineStr"/>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>95****2375</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>7250</v>
+      </c>
+      <c r="E590" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>03-Aug-2026 16:39:43</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>04-Aug-2026 18:49:35</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>*0448</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N590" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P590" t="n">
+        <v>11000376388500</v>
+      </c>
+      <c r="Q590" t="n">
+        <v>1785755355314</v>
+      </c>
+      <c r="R590" t="n">
+        <v>400534302497</v>
+      </c>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V590" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W590" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y590" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z590" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA590" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB590" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC590" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD590" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE590" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF590" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG590" t="inlineStr"/>
+      <c r="AH590" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI590" t="n">
+        <v>20448</v>
+      </c>
+      <c r="AJ590" t="inlineStr">
+        <is>
+          <t>277535</t>
+        </is>
+      </c>
+      <c r="AK590" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="AL590" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>17426</v>
+      </c>
+      <c r="B591" t="inlineStr"/>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>81****8349</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E591" t="n">
+        <v>14500</v>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>03-Aug-2026 23:50:08</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>04-Aug-2026 18:49:35</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>*0124</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N591" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P591" t="n">
+        <v>11000376461485</v>
+      </c>
+      <c r="Q591" t="n">
+        <v>1785781200787</v>
+      </c>
+      <c r="R591" t="n">
+        <v>299949053116</v>
+      </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W591" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y591" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z591" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA591" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB591" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC591" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD591" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE591" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF591" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG591" t="inlineStr"/>
+      <c r="AH591" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI591" t="n">
+        <v>20124</v>
+      </c>
+      <c r="AJ591" t="inlineStr">
+        <is>
+          <t>269434,269508</t>
+        </is>
+      </c>
+      <c r="AK591" t="inlineStr">
+        <is>
+          <t>2071,2072</t>
+        </is>
+      </c>
+      <c r="AL591" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>15012</v>
+      </c>
+      <c r="B592" t="inlineStr"/>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>99****2276</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E592" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>04-Aug-2026 11:02:28</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>VlllX</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Rupees Only...</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>*9377</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="N592" t="n">
+        <v>753702</v>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="P592" t="n">
+        <v>11000376510070</v>
+      </c>
+      <c r="Q592" t="n">
+        <v>1785821536635</v>
+      </c>
+      <c r="R592" t="n">
+        <v>705240251922</v>
+      </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="V592" t="inlineStr">
+        <is>
+          <t>RNS</t>
+        </is>
+      </c>
+      <c r="W592" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="Y592" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="Z592" t="inlineStr">
+        <is>
+          <t>m**********@gmail.com</t>
+        </is>
+      </c>
+      <c r="AA592" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB592" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC592" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD592" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE592" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AF592" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SECONDARY SCHOOL ICSE</t>
+        </is>
+      </c>
+      <c r="AG592" t="inlineStr"/>
+      <c r="AH592" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AI592" t="n">
+        <v>19377</v>
+      </c>
+      <c r="AJ592" t="inlineStr">
+        <is>
+          <t>276099</t>
+        </is>
+      </c>
+      <c r="AK592" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="AL592" t="inlineStr">
         <is>
           <t>UPI INTENT</t>
         </is>
